--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -35,7 +35,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Супесь: остаточное разрыхление 3–5 % (табл. П2.1 методички), Kор = 1,03…1,05. Принято среднее 1,04 — уточнить у преподавателя.</t>
+          <t xml:space="preserve">Супесь: остаточное разрыхление 3–5 % (табл. П2.1 методички), Kор = 1,03…1,05. Принято 1,04 — по указанию преподавателя брать в этом диапазоне.</t>
         </r>
       </text>
     </comment>

--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Исходные данные" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="ЛНР" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Объёмы" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Котлован" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Сводный баланс" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -318,7 +320,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="243">
   <si>
     <t xml:space="preserve">Курсовая работа «Технологическая карта на производство земляных работ». Вариант 2</t>
   </si>
@@ -588,19 +590,482 @@
   </si>
   <si>
     <t xml:space="preserve">Разницу покрывают в сводном балансе грунта: грунт из котлована, завоз из резерва или поправка отметок Δh — следующий этап.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Котлован: контуры, размеры, геометрический объём (п. 2.2.2 методички)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Задание 4, вариант 2 — только габариты; грунт — супесь. Здание — вариант размещения 8: центр здания в центре квадрата 8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Параметр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обозн.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Значение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ед.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Формула / источник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исходные данные — Задание 4, вариант 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Глубина котлована по заданию (от планировочной отметки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нк</t>
+  </si>
+  <si>
+    <t xml:space="preserve">м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высота фундаментной плиты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нф.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Толщина бетонной подготовки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hб.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Толщина подсыпки (щебень)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hподс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Толщина стены подвала (по оси)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">схема размещения фундамента</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вылет плиты за наружную грань стены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">схема: 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выход бетонной подготовки за плиту</t>
+  </si>
+  <si>
+    <t xml:space="preserve">схема: 200; методичка — не менее 0,2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">От края подготовки до низа откоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Длина здания по осям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ширина здания по осям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вырез (правый нижний угол): длина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вырез: ширина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Левый нижний угол квадрата 8: x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Левый нижний угол квадрата 8: y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Левая ось здания (центр в центре квадрата 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нижняя ось здания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Привязки от осей здания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ось → наружная грань стены</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ось → край фундаментной плиты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ось → край бетонной подготовки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ось → низ откоса (подошва котлована)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рабочая зона от плиты до откоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">не менее 0,6 м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Положение котлована относительно ЛНР</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крутизна откоса при Нк (предварительно)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">прил. 3, супесь: до 1,5 — 0,25; до 3 — 0,67; до 5 — 0,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ось → бровка (предварительно)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднее рабочих отметок по углам котлована</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hср.углов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">таблица углов ниже; «+» — насыпь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Котлован в зоне</t>
+  </si>
+  <si>
+    <t xml:space="preserve">вариант 2: ЛНР пересекает котлован</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рабочая отметка в центре котлована (центр квадрата 8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hр</t>
+  </si>
+  <si>
+    <t xml:space="preserve">билинейно; в центре квадрата = среднее h9, h10, h15, h16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фактическая глубина от естественной поверхности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hк</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hк = Нк − hр (котлован в насыпи)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Откосы и контуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент откоса (супесь)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">прил. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заложение откоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l = hк · m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Низ котлована: длина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Низ котлована: ширина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь по низу</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fк.н</t>
+  </si>
+  <si>
+    <t xml:space="preserve">м²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Г-образный контур: L·B − вырез 42 × 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верх котлована: длина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Верх котлована: ширина</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь по верху</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fк.в</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь по наружному контуру стен</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fк.с.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь фундаментной плиты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fф.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь бетонной подготовки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fб.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пандус (принято: однополосный въезд автосамосвалов)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ширина пандуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bп</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 м — один проезд, 6 м — два</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уклон пандуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,10–0,15 при вывозе самосвалами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Коэффициент заложения пандуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n = 1 / i</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Длина пандуса в плане</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Объём пандуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vпан</t>
+  </si>
+  <si>
+    <t xml:space="preserve">м³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n·(bп·hк²/2 + m·hк³/3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Объёмы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Котлован без пандуса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hк/3·(Fк.н + Fк.в + √(Fк.н·Fк.в))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Объём котлована</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vк</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подсыпка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vподс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fк.н · hподс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бетонная подготовка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vб.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fб.п · hб.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гидроизоляция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vг.и</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 слоя рулонной, толщина в задании не дана</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Защитная стяжка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vст</t>
+  </si>
+  <si>
+    <t xml:space="preserve">в задании нет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фундаментная плита</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vф.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fф.п · Нф.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высота стен ниже естественной поверхности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hк − Нф.п − hб.п − hподс</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Стены подвала по наружному контуру</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vк.с.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подземная часть здания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vп.ч</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vф.п + Vк.с.п</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обратная засыпка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vо.з</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vк − Vп.ч − Vподс − Vб.п − Vг.и − Vст</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рабочие отметки по углам котлована (бровка при Нк), билинейная интерполяция в квадрате 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Угол</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x отн. осей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y отн. осей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X, м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y, м</t>
+  </si>
+  <si>
+    <t xml:space="preserve">u</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вершины квадрата 8: h15 — левый нижний, h16 — правый нижний, h9 — левый верхний, h10 — правый верхний. Отметки разного знака — котлован пересекает ЛНР.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сводная ведомость объёмов разрабатываемого грунта (табл. 2 методички)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">До корректировки средней отметки планировки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">№</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вид работы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выемка Vв, м³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Насыпь Vн, м³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vн / Kор, м³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В призмах (планировка)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В котловане (Vк; обратная засыпка Vо.з)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Суммарные объёмы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баланс Vв − Vн/Kор («−» — грунта не хватает)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расхождение, % (допускается не более 5 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вывод</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Площадь площадки Fпл без котлована по верху (котлован в насыпи), м²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поправка Δh = (Vв − Vн/Kор) / Fпл, м («−» — понижение)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δh — к следующему этапу: все рабочие отметки сдвигаются на Δh, заново строится ЛНР и пересчитываются объёмы и котлован.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0"/>
+    <numFmt numFmtId="170" formatCode="0.0000"/>
+    <numFmt numFmtId="171" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -683,6 +1148,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
+      <name val="GOST type B"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -745,7 +1217,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -820,6 +1292,50 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2562,4 +3078,1378 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H74"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="21"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="8"/>
+      <c r="C13" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="22" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" s="21"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E16" s="21"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="21"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="21"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="21"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C20" s="24" t="n">
+        <f aca="false">$C$18+'Исходные данные'!$B$3/2-$C$14/2</f>
+        <v>220</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="21"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="24" t="n">
+        <f aca="false">$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
+        <v>135</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="21"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B23" s="8"/>
+      <c r="C23" s="15" t="n">
+        <f aca="false">$C$10/2</f>
+        <v>0.2</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="15" t="n">
+        <f aca="false">$C$23+$C$11</f>
+        <v>0.7</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="8"/>
+      <c r="C25" s="15" t="n">
+        <f aca="false">$C$24+$C$12</f>
+        <v>0.9</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="21"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="15" t="n">
+        <f aca="false">$C$25+$C$13</f>
+        <v>1.4</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="21"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="15" t="n">
+        <f aca="false">$C$26-$C$24</f>
+        <v>0.7</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <f aca="false">IF($C$6&lt;=1.5,0.25,IF($C$6&lt;=3,0.67,0.85))</f>
+        <v>0.67</v>
+      </c>
+      <c r="D29" s="8"/>
+      <c r="E29" s="21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="8"/>
+      <c r="C30" s="15" t="n">
+        <f aca="false">$C$26+$C$6*$C$29</f>
+        <v>3.008</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="25" t="n">
+        <f aca="false">AVERAGE(H68:H73)</f>
+        <v>0.143860123050667</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="8"/>
+      <c r="C32" s="15" t="str">
+        <f aca="false">IF($C$31&gt;0,"насыпи","выемки")</f>
+        <v>насыпи</v>
+      </c>
+      <c r="D32" s="8"/>
+      <c r="E32" s="21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" s="25" t="n">
+        <f aca="false">('Исходные данные'!$B$17+'Исходные данные'!$B$18+'Исходные данные'!$B$23+'Исходные данные'!$B$24)/4</f>
+        <v>0.165</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" s="25" t="n">
+        <f aca="false">IF($C$32="насыпи",$C$6-$C$33,$C$6)</f>
+        <v>2.235</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <f aca="false">IF($C$34&lt;=1.5,0.25,IF($C$34&lt;=3,0.67,0.85))</f>
+        <v>0.67</v>
+      </c>
+      <c r="D36" s="8"/>
+      <c r="E36" s="21" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="25" t="n">
+        <f aca="false">$C$34*$C$36</f>
+        <v>1.49745</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="15" t="n">
+        <f aca="false">$C$14+2*$C$26</f>
+        <v>62.8</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E38" s="21"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B39" s="8"/>
+      <c r="C39" s="15" t="n">
+        <f aca="false">$C$15+2*$C$26</f>
+        <v>32.8</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E39" s="21"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <f aca="false">($C$14+2*$C$26)*($C$15+2*$C$26)-$C$16*$C$17</f>
+        <v>1555.84</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B41" s="8"/>
+      <c r="C41" s="15" t="n">
+        <f aca="false">$C$38+2*$C$37</f>
+        <v>65.7949</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E41" s="21"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B42" s="8"/>
+      <c r="C42" s="15" t="n">
+        <f aca="false">$C$39+2*$C$37</f>
+        <v>35.7949</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="21"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <f aca="false">$C$41*$C$42-$C$16*$C$17</f>
+        <v>1851.12186601</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E43" s="21"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <f aca="false">($C$14+2*$C$23)*($C$15+2*$C$23)-$C$16*$C$17</f>
+        <v>1332.16</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E44" s="21"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <f aca="false">($C$14+2*$C$24)*($C$15+2*$C$24)-$C$16*$C$17</f>
+        <v>1423.96</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" s="21"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <f aca="false">($C$14+2*$C$25)*($C$15+2*$C$25)-$C$16*$C$17</f>
+        <v>1461.24</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" s="21"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D49" s="8"/>
+      <c r="E49" s="21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <f aca="false">1/$C$49</f>
+        <v>10</v>
+      </c>
+      <c r="D50" s="8"/>
+      <c r="E50" s="21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="15" t="n">
+        <f aca="false">$C$34*$C$50</f>
+        <v>22.35</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E51" s="21"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <f aca="false">$C$50*($C$48*$C$34^2/2+$C$36*$C$34^3/3)</f>
+        <v>99.8620405875</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="11" t="n">
+        <f aca="false">$C$34/3*($C$40+$C$43+SQRT($C$40*$C$43))</f>
+        <v>3802.50436774103</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <f aca="false">$C$54+$C$52</f>
+        <v>3902.36640832853</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E55" s="21"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <f aca="false">$C$40*$C$9</f>
+        <v>155.584</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <f aca="false">$C$46*$C$8</f>
+        <v>219.186</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <f aca="false">$C$45*$C$7</f>
+        <v>569.584</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B61" s="8"/>
+      <c r="C61" s="15" t="n">
+        <f aca="false">$C$34-$C$7-$C$8-$C$9</f>
+        <v>1.585</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <f aca="false">$C$44*$C$61</f>
+        <v>2111.4736</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E62" s="21"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <f aca="false">$C$60+$C$62</f>
+        <v>2681.0576</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <f aca="false">$C$55-$C$63-$C$56-$C$57-$C$58-$C$59</f>
+        <v>846.538808328531</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B68" s="15" t="n">
+        <f aca="false">-$C$30</f>
+        <v>-3.008</v>
+      </c>
+      <c r="C68" s="15" t="n">
+        <f aca="false">-$C$30</f>
+        <v>-3.008</v>
+      </c>
+      <c r="D68" s="15" t="n">
+        <f aca="false">$C$20+B68</f>
+        <v>216.992</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <f aca="false">$C$21+C68</f>
+        <v>131.992</v>
+      </c>
+      <c r="F68" s="25" t="n">
+        <f aca="false">(D68-$C$18)/'Исходные данные'!$B$3</f>
+        <v>0.16992</v>
+      </c>
+      <c r="G68" s="25" t="n">
+        <f aca="false">(E68-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.31992</v>
+      </c>
+      <c r="H68" s="25" t="n">
+        <f aca="false">'Исходные данные'!$B$23*(1-F68)*(1-G68)+'Исходные данные'!$B$24*F68*(1-G68)+'Исходные данные'!$B$17*(1-F68)*G68+'Исходные данные'!$B$18*F68*G68</f>
+        <v>-0.0392633451520001</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B69" s="15" t="n">
+        <f aca="false">$C$14-$C$16+$C$30</f>
+        <v>21.008</v>
+      </c>
+      <c r="C69" s="15" t="n">
+        <f aca="false">-$C$30</f>
+        <v>-3.008</v>
+      </c>
+      <c r="D69" s="15" t="n">
+        <f aca="false">$C$20+B69</f>
+        <v>241.008</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <f aca="false">$C$21+C69</f>
+        <v>131.992</v>
+      </c>
+      <c r="F69" s="25" t="n">
+        <f aca="false">(D69-$C$18)/'Исходные данные'!$B$3</f>
+        <v>0.41008</v>
+      </c>
+      <c r="G69" s="25" t="n">
+        <f aca="false">(E69-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.31992</v>
+      </c>
+      <c r="H69" s="25" t="n">
+        <f aca="false">'Исходные данные'!$B$23*(1-F69)*(1-G69)+'Исходные данные'!$B$24*F69*(1-G69)+'Исходные данные'!$B$17*(1-F69)*G69+'Исходные данные'!$B$18*F69*G69</f>
+        <v>0.047774097152</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="15" t="n">
+        <f aca="false">$C$14-$C$16+$C$30</f>
+        <v>21.008</v>
+      </c>
+      <c r="C70" s="15" t="n">
+        <f aca="false">$C$17-$C$30</f>
+        <v>8.992</v>
+      </c>
+      <c r="D70" s="15" t="n">
+        <f aca="false">$C$20+B70</f>
+        <v>241.008</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <f aca="false">$C$21+C70</f>
+        <v>143.992</v>
+      </c>
+      <c r="F70" s="25" t="n">
+        <f aca="false">(D70-$C$18)/'Исходные данные'!$B$3</f>
+        <v>0.41008</v>
+      </c>
+      <c r="G70" s="25" t="n">
+        <f aca="false">(E70-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.43992</v>
+      </c>
+      <c r="H70" s="25" t="n">
+        <f aca="false">'Исходные данные'!$B$23*(1-F70)*(1-G70)+'Исходные данные'!$B$24*F70*(1-G70)+'Исходные данные'!$B$17*(1-F70)*G70+'Исходные данные'!$B$18*F70*G70</f>
+        <v>0.106116369152</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B71" s="15" t="n">
+        <f aca="false">$C$14+$C$30</f>
+        <v>63.008</v>
+      </c>
+      <c r="C71" s="15" t="n">
+        <f aca="false">$C$17-$C$30</f>
+        <v>8.992</v>
+      </c>
+      <c r="D71" s="15" t="n">
+        <f aca="false">$C$20+B71</f>
+        <v>283.008</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <f aca="false">$C$21+C71</f>
+        <v>143.992</v>
+      </c>
+      <c r="F71" s="25" t="n">
+        <f aca="false">(D71-$C$18)/'Исходные данные'!$B$3</f>
+        <v>0.83008</v>
+      </c>
+      <c r="G71" s="25" t="n">
+        <f aca="false">(E71-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.43992</v>
+      </c>
+      <c r="H71" s="25" t="n">
+        <f aca="false">'Исходные данные'!$B$23*(1-F71)*(1-G71)+'Исходные данные'!$B$24*F71*(1-G71)+'Исходные данные'!$B$17*(1-F71)*G71+'Исходные данные'!$B$18*F71*G71</f>
+        <v>0.249258417152</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" s="15" t="n">
+        <f aca="false">$C$14+$C$30</f>
+        <v>63.008</v>
+      </c>
+      <c r="C72" s="15" t="n">
+        <f aca="false">$C$15+$C$30</f>
+        <v>33.008</v>
+      </c>
+      <c r="D72" s="15" t="n">
+        <f aca="false">$C$20+B72</f>
+        <v>283.008</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <f aca="false">$C$21+C72</f>
+        <v>168.008</v>
+      </c>
+      <c r="F72" s="25" t="n">
+        <f aca="false">(D72-$C$18)/'Исходные данные'!$B$3</f>
+        <v>0.83008</v>
+      </c>
+      <c r="G72" s="25" t="n">
+        <f aca="false">(E72-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.68008</v>
+      </c>
+      <c r="H72" s="25" t="n">
+        <f aca="false">'Исходные данные'!$B$23*(1-F72)*(1-G72)+'Исходные данные'!$B$24*F72*(1-G72)+'Исходные данные'!$B$17*(1-F72)*G72+'Исходные данные'!$B$18*F72*G72</f>
+        <v>0.347864654848</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="15" t="n">
+        <f aca="false">-$C$30</f>
+        <v>-3.008</v>
+      </c>
+      <c r="C73" s="15" t="n">
+        <f aca="false">$C$15+$C$30</f>
+        <v>33.008</v>
+      </c>
+      <c r="D73" s="15" t="n">
+        <f aca="false">$C$20+B73</f>
+        <v>216.992</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <f aca="false">$C$21+C73</f>
+        <v>168.008</v>
+      </c>
+      <c r="F73" s="25" t="n">
+        <f aca="false">(D73-$C$18)/'Исходные данные'!$B$3</f>
+        <v>0.16992</v>
+      </c>
+      <c r="G73" s="25" t="n">
+        <f aca="false">(E73-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.68008</v>
+      </c>
+      <c r="H73" s="25" t="n">
+        <f aca="false">'Исходные данные'!$B$23*(1-F73)*(1-G73)+'Исходные данные'!$B$24*F73*(1-G73)+'Исходные данные'!$B$17*(1-F73)*G73+'Исходные данные'!$B$18*F73*G73</f>
+        <v>0.151410545152</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="26" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A53:E53"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <f aca="false">Объёмы!D21</f>
+        <v>20192.0818431221</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <f aca="false">Объёмы!H21</f>
+        <v>33522.0168584468</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <f aca="false">D5/'Исходные данные'!$B$4</f>
+        <v>32232.7085177373</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <f aca="false">Котлован!$C$55</f>
+        <v>3902.36640832853</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <f aca="false">Котлован!$C$64</f>
+        <v>846.538808328531</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <f aca="false">D6/'Исходные данные'!$B$4</f>
+        <v>813.979623392818</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8"/>
+      <c r="B7" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="16" t="n">
+        <f aca="false">SUM(C5:C6)</f>
+        <v>24094.4482514506</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <f aca="false">SUM(D5:D6)</f>
+        <v>34368.5556667753</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <f aca="false">SUM(E5:E6)</f>
+        <v>33046.6881411301</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8"/>
+      <c r="B8" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <f aca="false">C7-E7</f>
+        <v>-8952.23988967951</v>
+      </c>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="28" t="n">
+        <f aca="false">ABS(C8)/MAX(C7,E7)</f>
+        <v>0.270896734082636</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="72.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="14" t="str">
+        <f aca="false">IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
+        <v>не хватает грунта — нужен перерасчёт Нср (Δh)</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="16" t="n">
+        <f aca="false">'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF(Котлован!$C$32="насыпи",Котлован!$C$43,0)</f>
+        <v>148148.87813399</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="29" t="n">
+        <f aca="false">C8/D12</f>
+        <v>-0.0604273215054849</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kursovoy\.claude\worktrees\earthwork-drawings-autocad-d57f76\kursovaya-tsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F90E65E-9C18-43EE-90DD-7819E1612D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C767318A-8A9F-47B5-9493-5ED2D61FAD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,6 +23,10 @@
     <sheet name="Объёмы (оконч.)" sheetId="8" r:id="rId8"/>
     <sheet name="Котлован (оконч.)" sheetId="9" r:id="rId9"/>
     <sheet name="Баланс (оконч.)" sheetId="10" r:id="rId10"/>
+    <sheet name="Табл. 3 котлован" sheetId="11" r:id="rId11"/>
+    <sheet name="Табл. 4 распределение" sheetId="12" r:id="rId12"/>
+    <sheet name="Табл. 5 скрепер" sheetId="13" r:id="rId13"/>
+    <sheet name="Табл. 6 самосвал" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,6 +65,20 @@
             <scheme val="minor"/>
           </rPr>
           <t>Супесь: kо.р = 1,03…1,05 (прил. 2 методички). Принято 1,04 — по указанию преподавателя брать в этом диапазоне.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Супесь: kр = 1,12…1,17 (прил. 2 методички). Принято 1,15 — решение пользователя.</t>
         </r>
       </text>
     </comment>
@@ -817,7 +835,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="299">
   <si>
     <t>Курсовая работа «Технологическая карта на производство земляных работ». Вариант 2</t>
   </si>
@@ -846,6 +864,9 @@
     <t>Число квадратов</t>
   </si>
   <si>
+    <t>Коэффициент первоначального разрыхления kр</t>
+  </si>
+  <si>
     <t>№ вершины</t>
   </si>
   <si>
@@ -1594,6 +1615,123 @@
   </si>
   <si>
     <t>По окончательным отметкам — после поправки Δh</t>
+  </si>
+  <si>
+    <t>Ведомость объёмов грунта в котловане (табл. 3 методички), по окончательным отметкам</t>
+  </si>
+  <si>
+    <t>Баланс отрицательный - лишнего грунта нет (Vлиш.гр = 0), недостача восполняется из карьера.</t>
+  </si>
+  <si>
+    <t>Место разработки / назначение</t>
+  </si>
+  <si>
+    <t>V в плотном теле, м³</t>
+  </si>
+  <si>
+    <t>V с kр, м³</t>
+  </si>
+  <si>
+    <t>Место укладки</t>
+  </si>
+  <si>
+    <t>V с kо.р, м³</t>
+  </si>
+  <si>
+    <t>Котлован: разрабатываемый грунт</t>
+  </si>
+  <si>
+    <t>Насыпь</t>
+  </si>
+  <si>
+    <t>Вывоз</t>
+  </si>
+  <si>
+    <t>Отвал</t>
+  </si>
+  <si>
+    <t>Карьер: щебень для подсыпки</t>
+  </si>
+  <si>
+    <t>Котлован: подсыпка</t>
+  </si>
+  <si>
+    <t>Отвал: грунт обратной засыпки</t>
+  </si>
+  <si>
+    <t>Vлиш.гр - лишний грунт, м³ (баланс отрицательный)</t>
+  </si>
+  <si>
+    <t>Баланс распределения земляных масс (табл. 4 методички): из выемок и котлована в насыпь, м³</t>
+  </si>
+  <si>
+    <t>Минимум моментов V·l (l - между центрами тяжести фигур): сначала выемки (ЗТМ), затем котлован (самосвалы); остаток - недостача, подвоз из карьера. Выемка - плотное тело, насыпь - Vн / kо.р.</t>
+  </si>
+  <si>
+    <t>Выемка</t>
+  </si>
+  <si>
+    <t>Котлован</t>
+  </si>
+  <si>
+    <t>Недостача</t>
+  </si>
+  <si>
+    <t>Объём</t>
+  </si>
+  <si>
+    <t>Насыпь №</t>
+  </si>
+  <si>
+    <t>Проверка: Σ по строке − объём</t>
+  </si>
+  <si>
+    <t>Проверка: Σ по столбцу − объём</t>
+  </si>
+  <si>
+    <t>Средняя дальность перемещения грунта скрепером (бульдозером): выемка — насыпь (табл. 5)</t>
+  </si>
+  <si>
+    <t>№ фигур</t>
+  </si>
+  <si>
+    <t>x, м</t>
+  </si>
+  <si>
+    <t>y, м</t>
+  </si>
+  <si>
+    <t>Mx = x·V</t>
+  </si>
+  <si>
+    <t>My = y·V</t>
+  </si>
+  <si>
+    <t>Центр тяжести «Выемка»: Lx = ΣMx / ΣV, м</t>
+  </si>
+  <si>
+    <t>Центр тяжести «Выемка»: Ly = ΣMy / ΣV, м</t>
+  </si>
+  <si>
+    <t>Центр тяжести «Насыпь»: Lx, м</t>
+  </si>
+  <si>
+    <t>Центр тяжести «Насыпь»: Ly, м</t>
+  </si>
+  <si>
+    <t>Средняя дальность Lср = √((Lxв − Lxн)² + (Lyв − Lyн)²), м</t>
+  </si>
+  <si>
+    <t>Средняя дальность перемещения грунта автосамосвалом: котлован — насыпь (табл. 6)</t>
+  </si>
+  <si>
+    <t>котлован</t>
+  </si>
+  <si>
+    <t>Центр тяжести «Котлован»: Lx = ΣMx / ΣV, м</t>
+  </si>
+  <si>
+    <t>Центр тяжести «Котлован»: Ly = ΣMy / ΣV, м</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +1815,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1700,11 +1838,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1780,6 +1931,9 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1793,6 +1947,7 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2152,46 +2307,54 @@
         <v>15</v>
       </c>
     </row>
+    <row r="7" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="9">
         <v>-0.25</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="9">
         <v>0.15</v>
@@ -2223,33 +2386,33 @@
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="9">
         <v>0.34</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="9">
         <v>0.47</v>
@@ -2281,33 +2444,33 @@
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="9">
         <v>0.66</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="9">
         <v>0.85</v>
@@ -2339,33 +2502,33 @@
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="9">
         <v>-0.49</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="9">
         <v>-0.31</v>
@@ -2397,7 +2560,7 @@
     </row>
     <row r="17" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="9">
         <v>0.28000000000000003</v>
@@ -2405,7 +2568,7 @@
     </row>
     <row r="18" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="9">
         <v>0.52</v>
@@ -2413,7 +2576,7 @@
     </row>
     <row r="19" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="9">
         <v>0.84</v>
@@ -2421,7 +2584,7 @@
     </row>
     <row r="20" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="9">
         <v>0.47</v>
@@ -2429,7 +2592,7 @@
     </row>
     <row r="21" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="9">
         <v>-0.24</v>
@@ -2437,7 +2600,7 @@
     </row>
     <row r="22" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" s="9">
         <v>-0.43</v>
@@ -2445,7 +2608,7 @@
     </row>
     <row r="23" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="9">
         <v>-0.28000000000000003</v>
@@ -2453,7 +2616,7 @@
     </row>
     <row r="24" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="9">
         <v>0.14000000000000001</v>
@@ -2461,7 +2624,7 @@
     </row>
     <row r="25" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="9">
         <v>0.36</v>
@@ -2469,7 +2632,7 @@
     </row>
     <row r="26" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="9">
         <v>0.76</v>
@@ -2477,7 +2640,7 @@
     </row>
     <row r="27" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="9">
         <v>-0.4</v>
@@ -2485,7 +2648,7 @@
     </row>
     <row r="28" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="9">
         <v>-0.65</v>
@@ -2493,7 +2656,7 @@
     </row>
     <row r="29" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="9">
         <v>-0.52</v>
@@ -2501,7 +2664,7 @@
     </row>
     <row r="30" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="9">
         <v>-0.28000000000000003</v>
@@ -2509,7 +2672,7 @@
     </row>
     <row r="31" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="9">
         <v>-0.43</v>
@@ -2517,7 +2680,7 @@
     </row>
     <row r="32" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="9">
         <v>0.14000000000000001</v>
@@ -2545,29 +2708,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -2575,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C5" s="24">
         <f>'Объёмы (оконч.)'!$F$31</f>
@@ -2595,7 +2758,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C6" s="24">
         <f>'Котлован (оконч.)'!$C$56</f>
@@ -2613,7 +2776,7 @@
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C7" s="16">
         <f>SUM(C5:C6)</f>
@@ -2631,65 +2794,65 @@
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="33">
+        <v>245</v>
+      </c>
+      <c r="C8" s="34">
         <f>C7-E7</f>
         <v>-545.97887343050388</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="26">
         <f>ABS(C8)/MAX(C7,E7)</f>
         <v>1.9193628153547412E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="14" t="str">
         <f>IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
         <v>баланс соблюдён</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="A12" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF('Котлован (оконч.)'!$C$33="насыпи",'Котлован (оконч.)'!$C$44,0)</f>
         <v>148167.58923381407</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
+      <c r="A13" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="27">
         <f>C8/D12</f>
         <v>-3.6848738395070229E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="A14" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="28">
         <f>ROUND(D13,4)</f>
         <v>-3.7000000000000002E-3</v>
@@ -2703,6 +2866,1552 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="A12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B5" s="24">
+        <f>'Котлован (оконч.)'!$C$56</f>
+        <v>3635.720177060251</v>
+      </c>
+      <c r="C5" s="11">
+        <f>B5*'Исходные данные'!$B$7</f>
+        <v>4181.0782036192886</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E5" s="11">
+        <f>('Котлован (оконч.)'!$C$56-'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4-$B$12)*'Исходные данные'!$B$7</f>
+        <v>3337.0102609084333</v>
+      </c>
+      <c r="F5" s="11">
+        <f>('Котлован (оконч.)'!$C$56-'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4-$B$12)*'Исходные данные'!$B$4</f>
+        <v>3017.8179750824092</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="11">
+        <f>$B$12*'Исходные данные'!$B$7</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="11">
+        <f>$B$12*'Исходные данные'!$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E7" s="11">
+        <f>'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4*'Исходные данные'!$B$7</f>
+        <v>844.06794271085516</v>
+      </c>
+      <c r="F7" s="11">
+        <f>'Котлован (оконч.)'!$C$65</f>
+        <v>763.33100906025174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="11">
+        <f>'Котлован (оконч.)'!$C$57/'Исходные данные'!$B$4</f>
+        <v>149.59999999999997</v>
+      </c>
+      <c r="C8" s="11">
+        <f>B8*'Исходные данные'!$B$7</f>
+        <v>172.03999999999994</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E8" s="11">
+        <f>'Котлован (оконч.)'!$C$57/'Исходные данные'!$B$4*'Исходные данные'!$B$7</f>
+        <v>172.03999999999994</v>
+      </c>
+      <c r="F8" s="11">
+        <f>'Котлован (оконч.)'!$C$57</f>
+        <v>155.58399999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9" s="11">
+        <f>'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4</f>
+        <v>733.97212409639587</v>
+      </c>
+      <c r="C9" s="11">
+        <f>B9*'Исходные данные'!$B$7</f>
+        <v>844.06794271085516</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="11">
+        <f>'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4*'Исходные данные'!$B$7</f>
+        <v>844.06794271085516</v>
+      </c>
+      <c r="F9" s="11">
+        <f>'Котлован (оконч.)'!$C$65</f>
+        <v>763.33100906025174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="16">
+        <f>SUM(C5:C9)</f>
+        <v>5197.1861463301439</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="16">
+        <f>SUM(E5:E9)</f>
+        <v>5197.1861463301439</v>
+      </c>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="12" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:O20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="14" width="10" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="29"/>
+      <c r="B5" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2422.0969749945648</v>
+      </c>
+      <c r="D5" s="9">
+        <v>316.89691763080322</v>
+      </c>
+      <c r="E5" s="9">
+        <v>4298</v>
+      </c>
+      <c r="F5" s="9">
+        <v>2240.6796558686442</v>
+      </c>
+      <c r="G5" s="9">
+        <v>284.20527187499999</v>
+      </c>
+      <c r="H5" s="9">
+        <v>4923</v>
+      </c>
+      <c r="I5" s="9">
+        <v>5323</v>
+      </c>
+      <c r="J5" s="9">
+        <v>2490.4403474999999</v>
+      </c>
+      <c r="K5" s="9">
+        <v>1500.365174050633</v>
+      </c>
+      <c r="L5" s="9">
+        <v>441.60736718854099</v>
+      </c>
+      <c r="M5" s="9">
+        <v>2901.748052963856</v>
+      </c>
+      <c r="N5" s="9">
+        <v>554.40313033579719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="9">
+        <v>5.8748443857998884</v>
+      </c>
+      <c r="C7" s="9">
+        <v>5.8748443857998884</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="11">
+        <f t="shared" ref="O7:O18" si="0">SUM(C7:N7)-B7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="9">
+        <v>835.00357548112356</v>
+      </c>
+      <c r="C8" s="9">
+        <v>835.00357548112356</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="9">
+        <v>3271.1538461538462</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1581.218555127642</v>
+      </c>
+      <c r="D9" s="9">
+        <v>316.89691763080322</v>
+      </c>
+      <c r="E9" s="9">
+        <v>1373.0383733954011</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="9"/>
+      <c r="I9" s="9"/>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="9">
+        <v>5386.5384615384619</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9">
+        <v>2874.9177829292948</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2240.6796558686442</v>
+      </c>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9">
+        <v>270.94102274052278</v>
+      </c>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="9">
+        <v>6179.8076923076924</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9">
+        <v>2723.6565090080389</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9">
+        <v>2901.748052963856</v>
+      </c>
+      <c r="N11" s="9">
+        <v>554.40313033579719</v>
+      </c>
+      <c r="O11" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="9">
+        <v>50.043843675304217</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9">
+        <v>50.043843675304217</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="9">
+        <v>1087.527994591346</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9">
+        <v>1087.527994591346</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="9">
+        <v>3872.1153846153852</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9">
+        <v>284.20527187499999</v>
+      </c>
+      <c r="H14" s="9">
+        <v>840.87447366009201</v>
+      </c>
+      <c r="I14" s="9">
+        <v>2747.0356390802931</v>
+      </c>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="9">
+        <v>5242.3076923076924</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9">
+        <v>2571.70269024663</v>
+      </c>
+      <c r="J15" s="9">
+        <v>2236.9391151484911</v>
+      </c>
+      <c r="K15" s="9">
+        <v>433.66588691257112</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="9">
+        <v>4.2616706730769227</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9">
+        <v>4.2616706730769227</v>
+      </c>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="9">
+        <v>253.50123235150929</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9">
+        <v>253.50123235150929</v>
+      </c>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="9">
+        <v>1508.3066543266029</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9">
+        <v>1066.6992871380619</v>
+      </c>
+      <c r="L18" s="9">
+        <v>441.60736718854099</v>
+      </c>
+      <c r="M18" s="9"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="16">
+        <f t="shared" ref="B19:N19" si="1">SUM(B7:B18)</f>
+        <v>27696.442892407838</v>
+      </c>
+      <c r="C19" s="16">
+        <f t="shared" si="1"/>
+        <v>2422.0969749945652</v>
+      </c>
+      <c r="D19" s="16">
+        <f t="shared" si="1"/>
+        <v>316.89691763080322</v>
+      </c>
+      <c r="E19" s="16">
+        <f t="shared" si="1"/>
+        <v>4298</v>
+      </c>
+      <c r="F19" s="16">
+        <f t="shared" si="1"/>
+        <v>2240.6796558686442</v>
+      </c>
+      <c r="G19" s="16">
+        <f t="shared" si="1"/>
+        <v>284.20527187499999</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" si="1"/>
+        <v>4923</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="1"/>
+        <v>5323</v>
+      </c>
+      <c r="J19" s="16">
+        <f t="shared" si="1"/>
+        <v>2490.4403475000004</v>
+      </c>
+      <c r="K19" s="16">
+        <f t="shared" si="1"/>
+        <v>1500.365174050633</v>
+      </c>
+      <c r="L19" s="16">
+        <f t="shared" si="1"/>
+        <v>441.60736718854099</v>
+      </c>
+      <c r="M19" s="16">
+        <f t="shared" si="1"/>
+        <v>2901.748052963856</v>
+      </c>
+      <c r="N19" s="16">
+        <f t="shared" si="1"/>
+        <v>554.40313033579719</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="11">
+        <f t="shared" ref="C20:N20" si="2">C19-C5</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="11">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="23" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+      <c r="B2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="U2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="U3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="V3" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="9">
+        <v>2422.0969749945648</v>
+      </c>
+      <c r="C4" s="9">
+        <v>316.89691763080322</v>
+      </c>
+      <c r="D4" s="9">
+        <v>4298</v>
+      </c>
+      <c r="E4" s="9">
+        <v>2240.6796558686442</v>
+      </c>
+      <c r="F4" s="9">
+        <v>284.20527187499999</v>
+      </c>
+      <c r="G4" s="9">
+        <v>4923</v>
+      </c>
+      <c r="H4" s="9">
+        <v>5323</v>
+      </c>
+      <c r="I4" s="9">
+        <v>2490.4403474999999</v>
+      </c>
+      <c r="J4" s="9">
+        <v>1500.365174050633</v>
+      </c>
+      <c r="K4" s="9">
+        <v>441.60736718854099</v>
+      </c>
+      <c r="L4" s="9">
+        <v>5.8748443857998884</v>
+      </c>
+      <c r="M4" s="9">
+        <v>835.00357548112356</v>
+      </c>
+      <c r="N4" s="9">
+        <v>3271.1538461538462</v>
+      </c>
+      <c r="O4" s="9">
+        <v>5386.5384615384619</v>
+      </c>
+      <c r="P4" s="9">
+        <v>2723.6565090080389</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>50.043843675304217</v>
+      </c>
+      <c r="R4" s="9">
+        <v>1087.527994591346</v>
+      </c>
+      <c r="S4" s="9">
+        <v>3872.1153846153852</v>
+      </c>
+      <c r="T4" s="9">
+        <v>5242.3076923076924</v>
+      </c>
+      <c r="U4" s="9">
+        <v>4.2616706730769227</v>
+      </c>
+      <c r="V4" s="9">
+        <v>253.50123235150929</v>
+      </c>
+      <c r="W4" s="9">
+        <v>1508.3066543266029</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="9">
+        <v>49.088687062500753</v>
+      </c>
+      <c r="C5" s="9">
+        <v>121.0338983050847</v>
+      </c>
+      <c r="D5" s="9">
+        <v>50</v>
+      </c>
+      <c r="E5" s="9">
+        <v>147.08716292185639</v>
+      </c>
+      <c r="F5" s="9">
+        <v>227.16666666666671</v>
+      </c>
+      <c r="G5" s="9">
+        <v>50</v>
+      </c>
+      <c r="H5" s="9">
+        <v>150</v>
+      </c>
+      <c r="I5" s="9">
+        <v>249.23684255149581</v>
+      </c>
+      <c r="J5" s="9">
+        <v>347.77684871422503</v>
+      </c>
+      <c r="K5" s="9">
+        <v>428.78947368421052</v>
+      </c>
+      <c r="L5" s="9">
+        <v>92.691666666666663</v>
+      </c>
+      <c r="M5" s="9">
+        <v>159.93316494450531</v>
+      </c>
+      <c r="N5" s="9">
+        <v>250</v>
+      </c>
+      <c r="O5" s="9">
+        <v>350</v>
+      </c>
+      <c r="P5" s="9">
+        <v>450</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>187.70056497175139</v>
+      </c>
+      <c r="R5" s="9">
+        <v>257.57398883862618</v>
+      </c>
+      <c r="S5" s="9">
+        <v>350</v>
+      </c>
+      <c r="T5" s="9">
+        <v>450</v>
+      </c>
+      <c r="U5" s="9">
+        <v>293.83333333333331</v>
+      </c>
+      <c r="V5" s="9">
+        <v>355.69073635988133</v>
+      </c>
+      <c r="W5" s="9">
+        <v>457.80955662620897</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="9">
+        <v>249.06833838485301</v>
+      </c>
+      <c r="C6" s="9">
+        <v>226.97826086956519</v>
+      </c>
+      <c r="D6" s="9">
+        <v>150</v>
+      </c>
+      <c r="E6" s="9">
+        <v>147.13807100281531</v>
+      </c>
+      <c r="F6" s="9">
+        <v>120.375</v>
+      </c>
+      <c r="G6" s="9">
+        <v>50</v>
+      </c>
+      <c r="H6" s="9">
+        <v>50</v>
+      </c>
+      <c r="I6" s="9">
+        <v>49.236842551495798</v>
+      </c>
+      <c r="J6" s="9">
+        <v>36.167353529974193</v>
+      </c>
+      <c r="K6" s="9">
+        <v>20.77215189873418</v>
+      </c>
+      <c r="L6" s="9">
+        <v>293.64492753623188</v>
+      </c>
+      <c r="M6" s="9">
+        <v>257.89470169305258</v>
+      </c>
+      <c r="N6" s="9">
+        <v>250</v>
+      </c>
+      <c r="O6" s="9">
+        <v>250</v>
+      </c>
+      <c r="P6" s="9">
+        <v>250</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>187.04166666666671</v>
+      </c>
+      <c r="R6" s="9">
+        <v>159.82683588369201</v>
+      </c>
+      <c r="S6" s="9">
+        <v>150</v>
+      </c>
+      <c r="T6" s="9">
+        <v>150</v>
+      </c>
+      <c r="U6" s="9">
+        <v>93.833333333333329</v>
+      </c>
+      <c r="V6" s="9">
+        <v>85.408271458645558</v>
+      </c>
+      <c r="W6" s="9">
+        <v>60.761474345837151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="21">
+        <f t="shared" ref="B7:W7" si="0">B5*B4</f>
+        <v>118897.5604405379</v>
+      </c>
+      <c r="C7" s="21">
+        <f t="shared" si="0"/>
+        <v>38355.269301721441</v>
+      </c>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>214900</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="0"/>
+        <v>329575.2135984404</v>
+      </c>
+      <c r="F7" s="21">
+        <f t="shared" si="0"/>
+        <v>64561.964260937515</v>
+      </c>
+      <c r="G7" s="21">
+        <f t="shared" si="0"/>
+        <v>246150</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="0"/>
+        <v>798450</v>
+      </c>
+      <c r="I7" s="21">
+        <f t="shared" si="0"/>
+        <v>620709.48877375002</v>
+      </c>
+      <c r="J7" s="21">
+        <f t="shared" si="0"/>
+        <v>521792.27215189888</v>
+      </c>
+      <c r="K7" s="21">
+        <f t="shared" si="0"/>
+        <v>189356.59055184439</v>
+      </c>
+      <c r="L7" s="21">
+        <f t="shared" si="0"/>
+        <v>544.54911752710132</v>
+      </c>
+      <c r="M7" s="21">
+        <f t="shared" si="0"/>
+        <v>133544.76456667422</v>
+      </c>
+      <c r="N7" s="21">
+        <f t="shared" si="0"/>
+        <v>817788.4615384615</v>
+      </c>
+      <c r="O7" s="21">
+        <f t="shared" si="0"/>
+        <v>1885288.4615384617</v>
+      </c>
+      <c r="P7" s="21">
+        <f t="shared" si="0"/>
+        <v>1225645.4290536174</v>
+      </c>
+      <c r="Q7" s="21">
+        <f t="shared" si="0"/>
+        <v>9393.2577312126086</v>
+      </c>
+      <c r="R7" s="21">
+        <f t="shared" si="0"/>
+        <v>280118.92354056484</v>
+      </c>
+      <c r="S7" s="21">
+        <f t="shared" si="0"/>
+        <v>1355240.3846153847</v>
+      </c>
+      <c r="T7" s="21">
+        <f t="shared" si="0"/>
+        <v>2359038.4615384615</v>
+      </c>
+      <c r="U7" s="21">
+        <f t="shared" si="0"/>
+        <v>1252.2208994391024</v>
+      </c>
+      <c r="V7" s="21">
+        <f t="shared" si="0"/>
+        <v>90168.040003245711</v>
+      </c>
+      <c r="W7" s="21">
+        <f t="shared" si="0"/>
+        <v>690517.20067362278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B8" s="21">
+        <f t="shared" ref="B8:W8" si="1">B6*B4</f>
+        <v>603267.66896887508</v>
+      </c>
+      <c r="C8" s="21">
+        <f t="shared" si="1"/>
+        <v>71928.711238765565</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="1"/>
+        <v>644700</v>
+      </c>
+      <c r="E8" s="21">
+        <f t="shared" si="1"/>
+        <v>329689.28229976434</v>
+      </c>
+      <c r="F8" s="21">
+        <f t="shared" si="1"/>
+        <v>34211.209601953124</v>
+      </c>
+      <c r="G8" s="21">
+        <f t="shared" si="1"/>
+        <v>246150</v>
+      </c>
+      <c r="H8" s="21">
+        <f t="shared" si="1"/>
+        <v>266150</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="1"/>
+        <v>122621.41927374998</v>
+      </c>
+      <c r="J8" s="21">
+        <f t="shared" si="1"/>
+        <v>54264.237673950505</v>
+      </c>
+      <c r="K8" s="21">
+        <f t="shared" si="1"/>
+        <v>9173.1353108404546</v>
+      </c>
+      <c r="L8" s="21">
+        <f t="shared" si="1"/>
+        <v>1725.118253954847</v>
+      </c>
+      <c r="M8" s="21">
+        <f t="shared" si="1"/>
+        <v>215342.99801133666</v>
+      </c>
+      <c r="N8" s="21">
+        <f t="shared" si="1"/>
+        <v>817788.4615384615</v>
+      </c>
+      <c r="O8" s="21">
+        <f t="shared" si="1"/>
+        <v>1346634.6153846155</v>
+      </c>
+      <c r="P8" s="21">
+        <f t="shared" si="1"/>
+        <v>680914.1272520097</v>
+      </c>
+      <c r="Q8" s="21">
+        <f t="shared" si="1"/>
+        <v>9360.2839274350281</v>
+      </c>
+      <c r="R8" s="21">
+        <f t="shared" si="1"/>
+        <v>173816.15831047174</v>
+      </c>
+      <c r="S8" s="21">
+        <f t="shared" si="1"/>
+        <v>580817.30769230775</v>
+      </c>
+      <c r="T8" s="21">
+        <f t="shared" si="1"/>
+        <v>786346.15384615387</v>
+      </c>
+      <c r="U8" s="21">
+        <f t="shared" si="1"/>
+        <v>399.8867648237179</v>
+      </c>
+      <c r="V8" s="21">
+        <f t="shared" si="1"/>
+        <v>21651.102067778887</v>
+      </c>
+      <c r="W8" s="21">
+        <f t="shared" si="1"/>
+        <v>91646.936082521352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="16">
+        <f>SUM(B7:K7)/SUM(B4:K4)</f>
+        <v>129.64977471365398</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="16">
+        <f>SUM(B8:K8)/SUM(B4:K4)</f>
+        <v>98.272565897910127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="16">
+        <f>SUM(L7:W7)/SUM(L4:W4)</f>
+        <v>365.0343923663209</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="16">
+        <f>SUM(L8:W8)/SUM(L4:W4)</f>
+        <v>194.98293196512685</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="16">
+        <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
+        <v>254.47752971990917</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="3" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="29"/>
+      <c r="B2" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="9">
+        <v>2901.748052963856</v>
+      </c>
+      <c r="C4" s="9">
+        <v>2901.748052963856</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" s="9">
+        <v>250</v>
+      </c>
+      <c r="C5" s="9">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" s="9">
+        <v>150</v>
+      </c>
+      <c r="C6" s="9">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="21">
+        <f>B5*B4</f>
+        <v>725437.01324096404</v>
+      </c>
+      <c r="C7" s="21">
+        <f>C5*C4</f>
+        <v>1305786.6238337352</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="B8" s="21">
+        <f>B6*B4</f>
+        <v>435262.20794457837</v>
+      </c>
+      <c r="C8" s="21">
+        <f>C6*C4</f>
+        <v>725437.01324096404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="16">
+        <f>SUM(B7:B7)/SUM(B4:B4)</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="16">
+        <f>SUM(B8:B8)/SUM(B4:B4)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="16">
+        <f>SUM(C7:C7)/SUM(C4:C4)</f>
+        <v>450</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="30" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="16">
+        <f>SUM(C8:C8)/SUM(C4:C4)</f>
+        <v>250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="B15" s="31"/>
+      <c r="C15" s="16">
+        <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
+        <v>223.60679774997897</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -2728,38 +4437,38 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -2767,17 +4476,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="13">
         <f>'Исходные данные'!$B$9</f>
         <v>-0.25</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="13">
         <f>'Исходные данные'!$B$10</f>
@@ -2797,17 +4506,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="13">
         <f>'Исходные данные'!$B$10</f>
         <v>0.15</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="13">
         <f>'Исходные данные'!$B$16</f>
@@ -2827,17 +4536,17 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="13">
         <f>'Исходные данные'!$B$16</f>
         <v>-0.31</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="13">
         <f>'Исходные данные'!$B$17</f>
@@ -2857,17 +4566,17 @@
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="13">
         <f>'Исходные данные'!$B$17</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="13">
         <f>'Исходные данные'!$B$23</f>
@@ -2887,17 +4596,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="13">
         <f>'Исходные данные'!$B$23</f>
         <v>-0.28000000000000003</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="13">
         <f>'Исходные данные'!$B$24</f>
@@ -2917,17 +4626,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="13">
         <f>'Исходные данные'!$B$24</f>
         <v>0.14000000000000001</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="13">
         <f>'Исходные данные'!$B$30</f>
@@ -2947,17 +4656,17 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="13">
         <f>'Исходные данные'!$B$25</f>
         <v>0.36</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="13">
         <f>'Исходные данные'!$B$31</f>
@@ -2977,17 +4686,17 @@
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="13">
         <f>'Исходные данные'!$B$31</f>
         <v>-0.43</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="13">
         <f>'Исходные данные'!$B$32</f>
@@ -3029,61 +4738,61 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31" t="s">
+      <c r="A4" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="11">
         <f>'Исходные данные'!$B$3^2-$F$6</f>
@@ -3098,7 +4807,7 @@
         <v>1971.6032608695655</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" s="11">
         <f>ЛНР!$G$6*ЛНР!$H$5/2</f>
@@ -3119,7 +4828,7 @@
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="11">
         <f>ЛНР!$H$6*ЛНР!$G$7/2</f>
@@ -3134,7 +4843,7 @@
         <v>182.94645050356175</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="11">
         <f>'Исходные данные'!$B$3^2-$B$7</f>
@@ -3155,19 +4864,19 @@
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F8" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3188,19 +4897,19 @@
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3221,19 +4930,19 @@
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F10" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3254,7 +4963,7 @@
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3269,24 +4978,24 @@
         <v>3675</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" s="11">
         <f>'Исходные данные'!$B$3^2-$F$12</f>
@@ -3301,7 +5010,7 @@
         <v>1797.9661016949153</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" s="11">
         <f>ЛНР!$G$8*ЛНР!$H$7/2</f>
@@ -3322,7 +5031,7 @@
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="11">
         <f>ЛНР!$H$8*ЛНР!$G$9/2</f>
@@ -3337,7 +5046,7 @@
         <v>155.55555555555557</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11">
         <f>'Исходные данные'!$B$3^2-$B$13</f>
@@ -3358,19 +5067,19 @@
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3391,19 +5100,19 @@
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3424,7 +5133,7 @@
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3439,24 +5148,24 @@
         <v>4300</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -3471,24 +5180,24 @@
         <v>4700</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="11">
         <f>'Исходные данные'!$B$3^2-$F$18</f>
@@ -3503,7 +5212,7 @@
         <v>2040.0000000000005</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="11">
         <f>ЛНР!$G$10*ЛНР!$H$9/2</f>
@@ -3524,7 +5233,7 @@
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="11">
         <f>(ЛНР!$H$10+ЛНР!$H$11)/2*'Исходные данные'!$B$3</f>
@@ -3539,7 +5248,7 @@
         <v>1074.7362869198312</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="11">
         <f>(ЛНР!$G$11+ЛНР!$G$10)/2*'Исходные данные'!$B$3</f>
@@ -3560,7 +5269,7 @@
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="11">
         <f>ЛНР!$H$11*ЛНР!$G$12/2</f>
@@ -3575,7 +5284,7 @@
         <v>294.27418757865127</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="11">
         <f>'Исходные данные'!$B$3^2-$B$20</f>
@@ -3596,7 +5305,7 @@
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="16">
         <f>SUM(B6:B20)</f>
@@ -3608,7 +5317,7 @@
         <v>20192.08184312208</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="16">
         <f>SUM(F6:F20)</f>
@@ -3626,32 +5335,32 @@
     </row>
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="15">
         <f>ABS('Исходные данные'!$B$9)+ABS('Исходные данные'!$B$31)+ABS('Исходные данные'!$B$30)+ABS('Исходные данные'!$B$29)+ABS('Исходные данные'!$B$28)+ABS('Исходные данные'!$B$27)+ABS('Исходные данные'!$B$21)+ABS('Исходные данные'!$B$15)</f>
@@ -3674,7 +5383,7 @@
     </row>
     <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="15">
         <f>ABS('Исходные данные'!$B$10)+ABS('Исходные данные'!$B$11)+ABS('Исходные данные'!$B$12)+ABS('Исходные данные'!$B$13)+ABS('Исходные данные'!$B$14)+ABS('Исходные данные'!$B$20)+ABS('Исходные данные'!$B$26)+ABS('Исходные данные'!$B$32)</f>
@@ -3697,69 +5406,69 @@
     </row>
     <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
       <c r="F29" s="16">
         <f>B21+F21</f>
         <v>150000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
+      <c r="A30" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
       <c r="F30" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
+      <c r="A31" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
       <c r="F31" s="16">
         <f>D21+F25</f>
         <v>20209.474960755029</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
       <c r="F32" s="16">
         <f>H21+F26</f>
         <v>33543.964226867858</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
+      <c r="A33" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
       <c r="F33" s="16">
         <f>F32/'Исходные данные'!$B$4</f>
         <v>32253.811756603707</v>
@@ -3800,301 +5509,301 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="17">
         <v>2.4</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="17">
         <v>0.4</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="17">
         <v>0.15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="17">
         <v>0.1</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="17">
         <v>0.2</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="17">
         <v>0.4</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="17">
         <v>0.5</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="17">
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="17">
         <v>0.5</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="19">
         <v>60</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="19">
         <v>30</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="19">
         <v>42</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="19">
         <v>12</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="20">
         <v>200</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="20">
         <v>100</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C21" s="21">
         <f>$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
         <v>220</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" s="21">
         <f>$C$20+'Исходные данные'!$B$3/2-$C$16/2</f>
         <v>135</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
+      <c r="A23" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="22">
@@ -4102,29 +5811,29 @@
         <v>0.2</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C25" s="22">
         <f>$C$24+$C$12</f>
         <v>0.7</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="22">
@@ -4132,13 +5841,13 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="22">
@@ -4146,43 +5855,43 @@
         <v>1.4</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C28" s="22">
         <f>$C$27-$C$25</f>
         <v>0.7</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
+      <c r="A29" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C30" s="11">
         <f>IF($C$6&lt;=1.5,0.25,IF($C$6&lt;=3,0.67,0.85))</f>
@@ -4190,12 +5899,12 @@
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="22">
@@ -4203,31 +5912,31 @@
         <v>3.008</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" s="15">
         <f>AVERAGE(H69:H74)</f>
         <v>0.14386012305066664</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="22" t="str">
@@ -4236,60 +5945,60 @@
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" s="15">
         <f>('Исходные данные'!$B$17+'Исходные данные'!$B$18+'Исходные данные'!$B$23+'Исходные данные'!$B$24)/4</f>
         <v>0.16500000000000001</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C35" s="15">
         <f>IF($C$33="насыпи",$C$6-$C$10-$C$34,$C$6-$C$10)</f>
         <v>2.0349999999999997</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
+      <c r="A36" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="11">
         <f>IF($C$35&lt;=1.5,0.25,IF($C$35&lt;=3,0.67,0.85))</f>
@@ -4297,30 +6006,30 @@
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C38" s="15">
         <f>$C$35*$C$37</f>
         <v>1.3634499999999998</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22">
@@ -4328,13 +6037,13 @@
         <v>62.8</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="22">
@@ -4342,31 +6051,31 @@
         <v>32.799999999999997</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C41" s="11">
         <f>($C$15+2*$C$27)*($C$16+2*$C$27)-$C$17*$C$18</f>
         <v>1555.8399999999997</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="22">
@@ -4374,13 +6083,13 @@
         <v>65.526899999999998</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E42" s="18"/>
     </row>
     <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="22">
@@ -4388,121 +6097,121 @@
         <v>35.526899999999998</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C44" s="11">
         <f>$C$42*$C$43-$C$17*$C$18</f>
         <v>1823.9676236099999</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C45" s="11">
         <f>($C$15+2*$C$24)*($C$16+2*$C$24)-$C$17*$C$18</f>
         <v>1332.1599999999999</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E45" s="18"/>
     </row>
     <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C46" s="11">
         <f>($C$15+2*$C$25)*($C$16+2*$C$25)-$C$17*$C$18</f>
         <v>1423.9599999999998</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E46" s="18"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C47" s="11">
         <f>($C$15+2*$C$26)*($C$16+2*$C$26)-$C$17*$C$18</f>
         <v>1461.24</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E47" s="18"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
+      <c r="A48" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C49" s="19">
         <v>3</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C50" s="9">
         <v>0.1</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C51" s="11">
         <f>1/$C$50</f>
@@ -4510,12 +6219,12 @@
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="22">
@@ -4523,40 +6232,40 @@
         <v>20.349999999999998</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E52" s="18"/>
     </row>
     <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C53" s="11">
         <f>$C$51*($C$49*$C$35^2/2+$C$37*$C$35^3/3)</f>
         <v>80.939552420833309</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
+      <c r="A54" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="11">
@@ -4564,119 +6273,119 @@
         <v>3435.3413295643254</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C56" s="11">
         <f>$C$55+$C$53</f>
         <v>3516.2808819851589</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" s="18"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C57" s="11">
         <f>$C$41*$C$9</f>
         <v>155.58399999999997</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C58" s="11">
         <f>$C$47*$C$8</f>
         <v>219.18600000000001</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C59" s="9">
         <v>0</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C60" s="9">
         <v>0</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C61" s="11">
         <f>$C$46*$C$7</f>
         <v>569.58399999999995</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="22">
@@ -4684,98 +6393,98 @@
         <v>1.3849999999999998</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C63" s="11">
         <f>$C$45*$C$62</f>
         <v>1845.0415999999996</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E63" s="18"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C64" s="11">
         <f>$C$61+$C$63</f>
         <v>2414.6255999999994</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C65" s="11">
         <f>$C$56-$C$64-$C$57-$C$58-$C$59-$C$60</f>
         <v>726.88528198515951</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B69" s="22">
         <f>-$C$31</f>
@@ -4808,7 +6517,7 @@
     </row>
     <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B70" s="22">
         <f>$C$15-$C$17+$C$31</f>
@@ -4841,7 +6550,7 @@
     </row>
     <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B71" s="22">
         <f>$C$15-$C$17+$C$31</f>
@@ -4874,7 +6583,7 @@
     </row>
     <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B72" s="22">
         <f>$C$15+$C$31</f>
@@ -4907,7 +6616,7 @@
     </row>
     <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B73" s="22">
         <f>$C$15+$C$31</f>
@@ -4940,7 +6649,7 @@
     </row>
     <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B74" s="22">
         <f>-$C$31</f>
@@ -4973,7 +6682,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -5005,29 +6714,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -5035,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C5" s="24">
         <f>Объёмы!$F$31</f>
@@ -5055,7 +6764,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C6" s="24">
         <f>Котлован!$C$56</f>
@@ -5073,7 +6782,7 @@
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C7" s="16">
         <f>SUM(C5:C6)</f>
@@ -5091,65 +6800,65 @@
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="33">
+        <v>245</v>
+      </c>
+      <c r="C8" s="34">
         <f>C7-E7</f>
         <v>-9226.9840696184765</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="31"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="30" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="26">
         <f>ABS(C8)/MAX(C7,E7)</f>
         <v>0.28000658197644951</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="31"/>
       <c r="D11" s="14" t="str">
         <f>IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
         <v>не хватает грунта — нужен перерасчёт Нср (Δh)</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="A12" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="B12" s="31"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF(Котлован!$C$33="насыпи",Котлован!$C$44,0)</f>
         <v>148176.03237639001</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="30"/>
+      <c r="A13" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="27">
         <f>C8/D12</f>
         <v>-6.227042202196717E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
+      <c r="A14" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
       <c r="D14" s="28">
         <f>ROUND(D13,4)</f>
         <v>-6.2300000000000001E-2</v>
@@ -5184,12 +6893,12 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B3" s="13">
         <f>'Сводный баланс'!$D$14</f>
@@ -5198,24 +6907,24 @@
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="24">
         <f>'Исходные данные'!$B$9</f>
@@ -5230,27 +6939,27 @@
         <v>-0.31230000000000002</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="24">
         <f>'Исходные данные'!$B$10</f>
@@ -5291,7 +7000,7 @@
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="24">
         <f>'Исходные данные'!$B$11</f>
@@ -5306,27 +7015,27 @@
         <v>0.2777</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B12" s="24">
         <f>'Исходные данные'!$B$12</f>
@@ -5367,7 +7076,7 @@
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" s="24">
         <f>'Исходные данные'!$B$13</f>
@@ -5382,27 +7091,27 @@
         <v>0.59770000000000001</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B14" s="24">
         <f>'Исходные данные'!$B$14</f>
@@ -5443,7 +7152,7 @@
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="24">
         <f>'Исходные данные'!$B$15</f>
@@ -5458,27 +7167,27 @@
         <v>-0.55230000000000001</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B16" s="24">
         <f>'Исходные данные'!$B$16</f>
@@ -5519,7 +7228,7 @@
     </row>
     <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="24">
         <f>'Исходные данные'!$B$17</f>
@@ -5536,7 +7245,7 @@
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="24">
         <f>'Исходные данные'!$B$18</f>
@@ -5553,7 +7262,7 @@
     </row>
     <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="24">
         <f>'Исходные данные'!$B$19</f>
@@ -5570,7 +7279,7 @@
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="24">
         <f>'Исходные данные'!$B$20</f>
@@ -5587,7 +7296,7 @@
     </row>
     <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B21" s="24">
         <f>'Исходные данные'!$B$21</f>
@@ -5604,7 +7313,7 @@
     </row>
     <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B22" s="24">
         <f>'Исходные данные'!$B$22</f>
@@ -5621,7 +7330,7 @@
     </row>
     <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="24">
         <f>'Исходные данные'!$B$23</f>
@@ -5638,7 +7347,7 @@
     </row>
     <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="24">
         <f>'Исходные данные'!$B$24</f>
@@ -5655,7 +7364,7 @@
     </row>
     <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B25" s="24">
         <f>'Исходные данные'!$B$25</f>
@@ -5672,7 +7381,7 @@
     </row>
     <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B26" s="24">
         <f>'Исходные данные'!$B$26</f>
@@ -5689,7 +7398,7 @@
     </row>
     <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" s="24">
         <f>'Исходные данные'!$B$27</f>
@@ -5706,7 +7415,7 @@
     </row>
     <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="24">
         <f>'Исходные данные'!$B$28</f>
@@ -5723,7 +7432,7 @@
     </row>
     <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="24">
         <f>'Исходные данные'!$B$29</f>
@@ -5740,7 +7449,7 @@
     </row>
     <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="24">
         <f>'Исходные данные'!$B$30</f>
@@ -5757,7 +7466,7 @@
     </row>
     <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="24">
         <f>'Исходные данные'!$B$31</f>
@@ -5774,7 +7483,7 @@
     </row>
     <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B32" s="24">
         <f>'Исходные данные'!$B$32</f>
@@ -5814,38 +7523,38 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -5853,17 +7562,17 @@
         <v>1</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="13">
         <f>'Отметки (оконч.)'!$D$9</f>
         <v>-0.31230000000000002</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" s="13">
         <f>'Отметки (оконч.)'!$D$10</f>
@@ -5883,17 +7592,17 @@
         <v>2</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="13">
         <f>'Отметки (оконч.)'!$D$10</f>
         <v>8.77E-2</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="13">
         <f>'Отметки (оконч.)'!$D$16</f>
@@ -5913,17 +7622,17 @@
         <v>3</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="13">
         <f>'Отметки (оконч.)'!$D$16</f>
         <v>-0.37230000000000002</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="13">
         <f>'Отметки (оконч.)'!$D$17</f>
@@ -5943,17 +7652,17 @@
         <v>4</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="13">
         <f>'Отметки (оконч.)'!$D$17</f>
         <v>0.21770000000000003</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="13">
         <f>'Отметки (оконч.)'!$D$23</f>
@@ -5973,17 +7682,17 @@
         <v>5</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="13">
         <f>'Отметки (оконч.)'!$D$23</f>
         <v>-0.34230000000000005</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="13">
         <f>'Отметки (оконч.)'!$D$24</f>
@@ -6003,17 +7712,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" s="13">
         <f>'Отметки (оконч.)'!$D$24</f>
         <v>7.7700000000000019E-2</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="13">
         <f>'Отметки (оконч.)'!$D$30</f>
@@ -6033,17 +7742,17 @@
         <v>7</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" s="13">
         <f>'Отметки (оконч.)'!$D$25</f>
         <v>0.29769999999999996</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F11" s="13">
         <f>'Отметки (оконч.)'!$D$31</f>
@@ -6063,17 +7772,17 @@
         <v>8</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="13">
         <f>'Отметки (оконч.)'!$D$31</f>
         <v>-0.49230000000000002</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="13">
         <f>'Отметки (оконч.)'!$D$32</f>
@@ -6115,61 +7824,61 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31" t="s">
+      <c r="A4" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="H5" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B6" s="11">
         <f>'Исходные данные'!$B$3^2-$F$6</f>
@@ -6184,7 +7893,7 @@
         <v>2422.0969749945657</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" s="11">
         <f>'ЛНР (оконч.)'!$G$6*'ЛНР (оконч.)'!$H$5/2</f>
@@ -6205,7 +7914,7 @@
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="11">
         <f>'ЛНР (оконч.)'!$H$6*'ЛНР (оконч.)'!$G$7/2</f>
@@ -6220,7 +7929,7 @@
         <v>316.89691763080327</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" s="11">
         <f>'Исходные данные'!$B$3^2-$B$7</f>
@@ -6241,19 +7950,19 @@
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F8" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6274,19 +7983,19 @@
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F9" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6307,19 +8016,19 @@
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F10" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6340,7 +8049,7 @@
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B11" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6355,24 +8064,24 @@
         <v>4298</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B12" s="11">
         <f>'Исходные данные'!$B$3^2-$F$12</f>
@@ -6387,7 +8096,7 @@
         <v>2240.6796558686442</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F12" s="11">
         <f>'ЛНР (оконч.)'!$G$8*'ЛНР (оконч.)'!$H$7/2</f>
@@ -6408,7 +8117,7 @@
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="11">
         <f>'ЛНР (оконч.)'!$H$8*'ЛНР (оконч.)'!$G$9/2</f>
@@ -6423,7 +8132,7 @@
         <v>284.20527187500005</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="11">
         <f>'Исходные данные'!$B$3^2-$B$13</f>
@@ -6444,19 +8153,19 @@
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6477,19 +8186,19 @@
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6510,7 +8219,7 @@
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B16" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6525,24 +8234,24 @@
         <v>4923</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B17" s="11">
         <f>'Исходные данные'!$B$3^2</f>
@@ -6557,24 +8266,24 @@
         <v>5323</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B18" s="11">
         <f>'Исходные данные'!$B$3^2-$F$18</f>
@@ -6589,7 +8298,7 @@
         <v>2490.4403475000004</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F18" s="11">
         <f>'ЛНР (оконч.)'!$G$10*'ЛНР (оконч.)'!$H$9/2</f>
@@ -6610,7 +8319,7 @@
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B19" s="11">
         <f>('ЛНР (оконч.)'!$H$10+'ЛНР (оконч.)'!$H$11)/2*'Исходные данные'!$B$3</f>
@@ -6625,7 +8334,7 @@
         <v>1500.3651740506327</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F19" s="11">
         <f>('ЛНР (оконч.)'!$G$11+'ЛНР (оконч.)'!$G$10)/2*'Исходные данные'!$B$3</f>
@@ -6646,7 +8355,7 @@
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="11">
         <f>'ЛНР (оконч.)'!$H$11*'ЛНР (оконч.)'!$G$12/2</f>
@@ -6661,7 +8370,7 @@
         <v>441.60736718854099</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F20" s="11">
         <f>'Исходные данные'!$B$3^2-$B$20</f>
@@ -6682,7 +8391,7 @@
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="16">
         <f>SUM(B6:B20)</f>
@@ -6694,7 +8403,7 @@
         <v>24240.291709108187</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="16">
         <f>SUM(F6:F20)</f>
@@ -6712,32 +8421,32 @@
     </row>
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B25" s="15">
         <f>ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$31)+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$15)</f>
@@ -6760,7 +8469,7 @@
     </row>
     <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B26" s="15">
         <f>ABS('Отметки (оконч.)'!$D$10)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$32)</f>
@@ -6783,69 +8492,69 @@
     </row>
     <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
       <c r="F29" s="16">
         <f>B21+F21</f>
         <v>150000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
+      <c r="A30" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
       <c r="F30" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
+      <c r="A31" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
       <c r="F31" s="16">
         <f>D21+F25</f>
         <v>24264.140842973826</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
       <c r="F32" s="16">
         <f>H21+F26</f>
         <v>28820.342480142914</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
+      <c r="A33" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="31"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
       <c r="F33" s="16">
         <f>F32/'Исходные данные'!$B$4</f>
         <v>27711.867769368186</v>
@@ -6886,301 +8595,301 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
+      <c r="A5" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="17">
         <v>2.4</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E6" s="18"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="17">
         <v>0.4</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="18"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="17">
         <v>0.15</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="17">
         <v>0.1</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10" s="17">
         <v>0.2</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="17">
         <v>0.4</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="17">
         <v>0.5</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="17">
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="17">
         <v>0.5</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="19">
         <v>60</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="19">
         <v>30</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E16" s="18"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="19">
         <v>42</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E17" s="18"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="19">
         <v>12</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" s="18"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="20">
         <v>200</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" s="18"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="8"/>
       <c r="C20" s="20">
         <v>100</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" s="18"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C21" s="21">
         <f>$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
         <v>220</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E21" s="18"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C22" s="21">
         <f>$C$20+'Исходные данные'!$B$3/2-$C$16/2</f>
         <v>135</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" s="18"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
+      <c r="A23" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B24" s="8"/>
       <c r="C24" s="22">
@@ -7188,29 +8897,29 @@
         <v>0.2</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E24" s="18"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C25" s="22">
         <f>$C$24+$C$12</f>
         <v>0.7</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E25" s="18"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="22">
@@ -7218,13 +8927,13 @@
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="18"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="22">
@@ -7232,43 +8941,43 @@
         <v>1.4</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" s="18"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C28" s="22">
         <f>$C$27-$C$25</f>
         <v>0.7</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
+      <c r="A29" s="33" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
     </row>
     <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C30" s="11">
         <f>IF($C$6&lt;=1.5,0.25,IF($C$6&lt;=3,0.67,0.85))</f>
@@ -7276,12 +8985,12 @@
       </c>
       <c r="D30" s="8"/>
       <c r="E30" s="18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="22">
@@ -7289,31 +8998,31 @@
         <v>3.008</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E31" s="18"/>
     </row>
     <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C32" s="15">
         <f>AVERAGE(H69:H74)</f>
         <v>8.156012305066665E-2</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B33" s="8"/>
       <c r="C33" s="22" t="str">
@@ -7322,60 +9031,60 @@
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" s="15">
         <f>('Отметки (оконч.)'!$D$17+'Отметки (оконч.)'!$D$18+'Отметки (оконч.)'!$D$23+'Отметки (оконч.)'!$D$24)/4</f>
         <v>0.10269999999999999</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C35" s="15">
         <f>IF($C$33="насыпи",$C$6-$C$10-$C$34,$C$6-$C$10)</f>
         <v>2.0972999999999997</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
+      <c r="A36" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="31"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37" s="11">
         <f>IF($C$35&lt;=1.5,0.25,IF($C$35&lt;=3,0.67,0.85))</f>
@@ -7383,30 +9092,30 @@
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="18" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C38" s="15">
         <f>$C$35*$C$37</f>
         <v>1.4051909999999999</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B39" s="8"/>
       <c r="C39" s="22">
@@ -7414,13 +9123,13 @@
         <v>62.8</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E39" s="18"/>
     </row>
     <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B40" s="8"/>
       <c r="C40" s="22">
@@ -7428,31 +9137,31 @@
         <v>32.799999999999997</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E40" s="18"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C41" s="11">
         <f>($C$15+2*$C$27)*($C$16+2*$C$27)-$C$17*$C$18</f>
         <v>1555.8399999999997</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B42" s="8"/>
       <c r="C42" s="22">
@@ -7460,13 +9169,13 @@
         <v>65.610382000000001</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E42" s="18"/>
     </row>
     <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B43" s="8"/>
       <c r="C43" s="22">
@@ -7474,121 +9183,121 @@
         <v>35.610381999999994</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E43" s="18"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C44" s="11">
         <f>$C$42*$C$43-$C$17*$C$18</f>
         <v>1832.4107661859239</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E44" s="18"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C45" s="11">
         <f>($C$15+2*$C$24)*($C$16+2*$C$24)-$C$17*$C$18</f>
         <v>1332.1599999999999</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E45" s="18"/>
     </row>
     <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C46" s="11">
         <f>($C$15+2*$C$25)*($C$16+2*$C$25)-$C$17*$C$18</f>
         <v>1423.9599999999998</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E46" s="18"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C47" s="11">
         <f>($C$15+2*$C$26)*($C$16+2*$C$26)-$C$17*$C$18</f>
         <v>1461.24</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E47" s="18"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
+      <c r="A48" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C49" s="19">
         <v>3</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C50" s="9">
         <v>0.1</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="18" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C51" s="11">
         <f>1/$C$50</f>
@@ -7596,12 +9305,12 @@
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="18" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="22">
@@ -7609,40 +9318,40 @@
         <v>20.972999999999999</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E52" s="18"/>
     </row>
     <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C53" s="11">
         <f>$C$51*($C$49*$C$35^2/2+$C$37*$C$35^3/3)</f>
         <v>86.583234976341274</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
+      <c r="A54" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="11">
@@ -7650,119 +9359,119 @@
         <v>3549.1369420839096</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E55" s="18" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C56" s="11">
         <f>$C$55+$C$53</f>
         <v>3635.720177060251</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E56" s="18"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C57" s="11">
         <f>$C$41*$C$9</f>
         <v>155.58399999999997</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E57" s="18" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C58" s="11">
         <f>$C$47*$C$8</f>
         <v>219.18600000000001</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C59" s="9">
         <v>0</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E59" s="18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C60" s="9">
         <v>0</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C61" s="11">
         <f>$C$46*$C$7</f>
         <v>569.58399999999995</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="22">
@@ -7770,98 +9479,98 @@
         <v>1.4472999999999998</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C63" s="11">
         <f>$C$45*$C$62</f>
         <v>1928.0351679999994</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E63" s="18"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C64" s="11">
         <f>$C$61+$C$63</f>
         <v>2497.6191679999993</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C65" s="11">
         <f>$C$56-$C$64-$C$57-$C$58-$C$59-$C$60</f>
         <v>763.33100906025174</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B69" s="22">
         <f>-$C$31</f>
@@ -7894,7 +9603,7 @@
     </row>
     <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B70" s="22">
         <f>$C$15-$C$17+$C$31</f>
@@ -7927,7 +9636,7 @@
     </row>
     <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B71" s="22">
         <f>$C$15-$C$17+$C$31</f>
@@ -7960,7 +9669,7 @@
     </row>
     <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B72" s="22">
         <f>$C$15+$C$31</f>
@@ -7993,7 +9702,7 @@
     </row>
     <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B73" s="22">
         <f>$C$15+$C$31</f>
@@ -8026,7 +9735,7 @@
     </row>
     <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B74" s="22">
         <f>-$C$31</f>
@@ -8059,7 +9768,7 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kursovoy\.claude\worktrees\earthwork-drawings-autocad-d57f76\kursovaya-tsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C767318A-8A9F-47B5-9493-5ED2D61FAD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFAE6DB-BAC1-4A9F-BAD0-7E2BE1137311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,6 +27,9 @@
     <sheet name="Табл. 4 распределение" sheetId="12" r:id="rId12"/>
     <sheet name="Табл. 5 скрепер" sheetId="13" r:id="rId13"/>
     <sheet name="Табл. 6 самосвал" sheetId="14" r:id="rId14"/>
+    <sheet name="2.3 Грунт и нормы ЕНиР" sheetId="15" r:id="rId15"/>
+    <sheet name="Табл. 7 варианты" sheetId="16" r:id="rId16"/>
+    <sheet name="2.3.2 Экскаватор, самосвалы" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -835,7 +838,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="457">
   <si>
     <t>Курсовая работа «Технологическая карта на производство земляных работ». Вариант 2</t>
   </si>
@@ -1732,17 +1735,492 @@
   </si>
   <si>
     <t>Центр тяжести «Котлован»: Ly = ΣMy / ΣV, м</t>
+  </si>
+  <si>
+    <t>Назначение комплекта машин (п. 2.3 методички): грунт и нормы времени ЕНиР Е2-1</t>
+  </si>
+  <si>
+    <t>Наименование и краткая характеристика грунта</t>
+  </si>
+  <si>
+    <t>Супесь без примесей (ЕНиР Е2-1, техчасть, табл. 1, п. 22)</t>
+  </si>
+  <si>
+    <t>Группа грунта в зависимости от трудности разработки</t>
+  </si>
+  <si>
+    <t>одноковшовые экскаваторы — I; скреперы — II; бульдозеры — II</t>
+  </si>
+  <si>
+    <t>Средняя плотность в естественном залегании, кг/м³</t>
+  </si>
+  <si>
+    <t>Машина</t>
+  </si>
+  <si>
+    <t>Марка</t>
+  </si>
+  <si>
+    <t>Обоснование (ЕНиР Е2-1)</t>
+  </si>
+  <si>
+    <t>Нвр, маш.-ч на 100 м³</t>
+  </si>
+  <si>
+    <t>Добавлять на каждые следующие 10 м</t>
+  </si>
+  <si>
+    <t>Нвр дана до, м</t>
+  </si>
+  <si>
+    <t>Условия</t>
+  </si>
+  <si>
+    <t>Бульдозер (ведущая, вариант 1)</t>
+  </si>
+  <si>
+    <t>ДЗ-34С (Д-572С), трактор ДЭТ-250</t>
+  </si>
+  <si>
+    <t>Е2-1-22, табл. 2, № 9б, 9д</t>
+  </si>
+  <si>
+    <t>тяжёлый (прил. 4); грунт II группы</t>
+  </si>
+  <si>
+    <t>Скрепер прицепной (ведущая, вариант 2)</t>
+  </si>
+  <si>
+    <t>ДЗ-20 (Д-498), ковш 6,7 м3, трактор Т-100</t>
+  </si>
+  <si>
+    <t>Е2-1-21, табл. 2, № 2б, 2г</t>
+  </si>
+  <si>
+    <t>ковш 6 м3 - 100-350 м (прил. 5); грунт II группы</t>
+  </si>
+  <si>
+    <t>Трактор-рыхлитель</t>
+  </si>
+  <si>
+    <t>ДП-22С на бульдозере ДЗ-35С, трактор Т-180</t>
+  </si>
+  <si>
+    <t>Е2-1-1, табл. 2, № 3в</t>
+  </si>
+  <si>
+    <t>рыхление слоями 0,35 м, участок св. 200 м</t>
+  </si>
+  <si>
+    <t>Бульдозер (разравнивание)</t>
+  </si>
+  <si>
+    <t>ДЗ-35С (Д-575С), трактор Т-180</t>
+  </si>
+  <si>
+    <t>Е2-1-28, № 6д</t>
+  </si>
+  <si>
+    <t>разравнивание слоями до 0,6 м (отсыпка скрепером 0,35 м)</t>
+  </si>
+  <si>
+    <t>Каток</t>
+  </si>
+  <si>
+    <t>ДУ-16В (Д-551В), на пневматических шинах</t>
+  </si>
+  <si>
+    <t>Е2-1-29, табл. 4, № 2в</t>
+  </si>
+  <si>
+    <t>слой 0,2-0,35 м, 4 прохода по следу, гон св. 200 м</t>
+  </si>
+  <si>
+    <t>Трактор-толкач</t>
+  </si>
+  <si>
+    <t>Т-180</t>
+  </si>
+  <si>
+    <t>Е2-1-21, примеч. 2: Нвр скрепера / число скреперов</t>
+  </si>
+  <si>
+    <t>Нвр скрепера / k</t>
+  </si>
+  <si>
+    <t>3 скрепера на толкач (прил. 5)</t>
+  </si>
+  <si>
+    <t>Добавка на расстояние сверх указанного в норме - пропорционально: Нвр = Нвр.до + добавка · (Lср − L) / 10. Толкач: Нвр скрепера, делённая на число обслуживаемых скреперов (Е2-1-21, примеч. 2; прил. 5).</t>
+  </si>
+  <si>
+    <t>Варианты с различными ведущими машинами (табл. 7 методички), вертикальная планировка</t>
+  </si>
+  <si>
+    <t>Vдн = 100·N·8 / Нвр;  Mсм = Нвр·V / (100·8);  nвед = Mсм / (m·t);  n = nвед·Vдн.вед / Vдн.об (с. 25-27; Нвр - на 100 м³). Ведущая машина и толкач - V с kр, рыхлитель - V в плотном теле.</t>
+  </si>
+  <si>
+    <t>Средняя дальность перемещения грунта Lср (табл. 5), м</t>
+  </si>
+  <si>
+    <t>Грунт выемок в насыпь (табл. 4), в плотном теле V, м³</t>
+  </si>
+  <si>
+    <t>То же с коэффициентом первоначального разрыхления V·kр, м³</t>
+  </si>
+  <si>
+    <t>Объём насыпи - разравнивание и уплотнение Vн, м³</t>
+  </si>
+  <si>
+    <t>Число смен в сутках m (N), по 8 ч</t>
+  </si>
+  <si>
+    <t>Срок планировочных работ t, дн. (5-20, для обоих вариантов)</t>
+  </si>
+  <si>
+    <t>Скреперов на один трактор-толкач (прил. 5)</t>
+  </si>
+  <si>
+    <t>Вариант 1</t>
+  </si>
+  <si>
+    <t>Вариант 2</t>
+  </si>
+  <si>
+    <t>Ведущая машина — бульдозер</t>
+  </si>
+  <si>
+    <t>Ведущая машина — скрепер</t>
+  </si>
+  <si>
+    <t>объём с коэффициентом первоначального разрыхления</t>
+  </si>
+  <si>
+    <t>Нвр вед, маш.-ч</t>
+  </si>
+  <si>
+    <t>Mсм вед, маш.-см</t>
+  </si>
+  <si>
+    <t>Vдн вед, м³/дн</t>
+  </si>
+  <si>
+    <t>n, шт.</t>
+  </si>
+  <si>
+    <t>Обеспечивающие машины</t>
+  </si>
+  <si>
+    <t>объём в плотном теле</t>
+  </si>
+  <si>
+    <t>Нвр об, маш.-ч</t>
+  </si>
+  <si>
+    <t>Mсм об, маш.-см</t>
+  </si>
+  <si>
+    <t>Vдн об, м³/дн</t>
+  </si>
+  <si>
+    <t>Бульдозер</t>
+  </si>
+  <si>
+    <t>Mсм вед + ΣMсм об, маш.-см</t>
+  </si>
+  <si>
+    <t>V / (Mсм вед + ΣMсм об), м³/маш.-см</t>
+  </si>
+  <si>
+    <t>(Mсм вед + ΣMсм об) / V, маш.-см/м³</t>
+  </si>
+  <si>
+    <t>Продолжительность работ ведущими машинами, дн.</t>
+  </si>
+  <si>
+    <t>Машины для разработки грунта в котловане (п. 2.3.2): экскаватор и автосамосвалы</t>
+  </si>
+  <si>
+    <t>Объём котлована Vк, м³</t>
+  </si>
+  <si>
+    <t>Глубина котлована hк, м</t>
+  </si>
+  <si>
+    <t>Число смен в сутках m</t>
+  </si>
+  <si>
+    <t>Экскаватор (обратная лопата)</t>
+  </si>
+  <si>
+    <t>Привод</t>
+  </si>
+  <si>
+    <t>Ковш q, м³</t>
+  </si>
+  <si>
+    <t>Нвр, маш.-ч на 100 м³ (I гр., с погрузкой)</t>
+  </si>
+  <si>
+    <t>Псм = 100·8 / Нвр, м³/смену</t>
+  </si>
+  <si>
+    <t>Hк max для котлованов, м</t>
+  </si>
+  <si>
+    <t>Rmax, м</t>
+  </si>
+  <si>
+    <t>Высота выгрузки, м</t>
+  </si>
+  <si>
+    <t>Недобор (прил. 7), см</t>
+  </si>
+  <si>
+    <t>Э-505</t>
+  </si>
+  <si>
+    <t>механический</t>
+  </si>
+  <si>
+    <t>Е2-1-11, табл. 3, № 4а</t>
+  </si>
+  <si>
+    <t>Э-652</t>
+  </si>
+  <si>
+    <t>Е2-1-11, табл. 3, № 5а</t>
+  </si>
+  <si>
+    <t>ЭО-4121А</t>
+  </si>
+  <si>
+    <t>гидравлический</t>
+  </si>
+  <si>
+    <t>Е2-1-11, табл. 7, № 4а</t>
+  </si>
+  <si>
+    <t>Прил. 6: ёмкость ковша по объёму сооружения</t>
+  </si>
+  <si>
+    <t>Принят экскаватор - наибольшая производительность</t>
+  </si>
+  <si>
+    <t>Ковш, м³</t>
+  </si>
+  <si>
+    <t>Vк от, м³</t>
+  </si>
+  <si>
+    <t>Vк до, м³</t>
+  </si>
+  <si>
+    <t>Подходит</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>0,25 и 0,30</t>
+  </si>
+  <si>
+    <t>Недобор, м</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>Глубина копания экскаватором hк − недобор, м</t>
+  </si>
+  <si>
+    <t>0,65</t>
+  </si>
+  <si>
+    <t>Проверка: Hк max не меньше глубины копания</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>Mсм = Нвр·Vк / (100·8), маш.-см</t>
+  </si>
+  <si>
+    <t>Продолжительность одним экскаватором Mсм / m, дн.</t>
+  </si>
+  <si>
+    <t>1,25</t>
+  </si>
+  <si>
+    <t>1,50 и более</t>
+  </si>
+  <si>
+    <t>Автосамосвалы (с. 28-29, прил. 8)</t>
+  </si>
+  <si>
+    <t>Коэффициент наполнения ковша kнап (табл. 8: 0,8-1,0)</t>
+  </si>
+  <si>
+    <t>Плотность грунта γ, т/м³</t>
+  </si>
+  <si>
+    <t>Грунт в ковше в плотном теле Vгр.к = q·kнап / kр, м³</t>
+  </si>
+  <si>
+    <t>Масса грунта в ковше Mковша = Vгр.к·γ, т</t>
+  </si>
+  <si>
+    <t>Дальность транспортирования L, км (до карьера, отвала)</t>
+  </si>
+  <si>
+    <t>Установка под погрузку Ту.п, мин</t>
+  </si>
+  <si>
+    <t>Установка под разгрузку Ту.р, мин</t>
+  </si>
+  <si>
+    <t>Разгрузка Тр, мин</t>
+  </si>
+  <si>
+    <t>Маневрирование Тм, мин</t>
+  </si>
+  <si>
+    <t>Модель</t>
+  </si>
+  <si>
+    <t>Va, м³</t>
+  </si>
+  <si>
+    <t>Па, т</t>
+  </si>
+  <si>
+    <t>Погрузочная высота, м</t>
+  </si>
+  <si>
+    <t>Uгр, км/ч</t>
+  </si>
+  <si>
+    <t>Uпор, км/ч</t>
+  </si>
+  <si>
+    <t>Па / Mковша</t>
+  </si>
+  <si>
+    <t>Va / q</t>
+  </si>
+  <si>
+    <t>n (целое меньшее)</t>
+  </si>
+  <si>
+    <t>6 ≤ n ≤ 11</t>
+  </si>
+  <si>
+    <t>Va пл = n·Vгр.к, м³</t>
+  </si>
+  <si>
+    <t>Тп = Va пл·Нвр / 100 · 60, мин</t>
+  </si>
+  <si>
+    <t>Тпр гр = L / Uгр · 60, мин</t>
+  </si>
+  <si>
+    <t>Тпр пор = L / Uпор · 60, мин</t>
+  </si>
+  <si>
+    <t>Тцикла, мин</t>
+  </si>
+  <si>
+    <t>Тцикла / Тп</t>
+  </si>
+  <si>
+    <t>N, шт.</t>
+  </si>
+  <si>
+    <t>Va р = q·kнап·n, м³</t>
+  </si>
+  <si>
+    <t>Нвр а = Тцикла / (Va р·60), маш.-ч/м³</t>
+  </si>
+  <si>
+    <t>Нвр а подходящих</t>
+  </si>
+  <si>
+    <t>ГАЗ-САЗ-35072</t>
+  </si>
+  <si>
+    <t>ГАЗ-САЗ-35072-10</t>
+  </si>
+  <si>
+    <t>ЗИЛ-ММЗ-45085</t>
+  </si>
+  <si>
+    <t>МАЗ-555102-220</t>
+  </si>
+  <si>
+    <t>МАЗ-555130-2120</t>
+  </si>
+  <si>
+    <t>МАЗ-555402-220</t>
+  </si>
+  <si>
+    <t>МАЗ-551603-2121</t>
+  </si>
+  <si>
+    <t>МАЗ-551605-2125</t>
+  </si>
+  <si>
+    <t>КамАЗ-6520</t>
+  </si>
+  <si>
+    <t>КамАЗ-6540</t>
+  </si>
+  <si>
+    <t>КамАЗ-55111</t>
+  </si>
+  <si>
+    <t>КамАЗ-65115</t>
+  </si>
+  <si>
+    <t>КамАЗ-53605</t>
+  </si>
+  <si>
+    <t>КрАЗ-65032</t>
+  </si>
+  <si>
+    <t>КрАЗ-65055</t>
+  </si>
+  <si>
+    <t>КрАЗ-6510</t>
+  </si>
+  <si>
+    <t>КрАЗ-7133С4</t>
+  </si>
+  <si>
+    <t>КрАЗ-6130С4</t>
+  </si>
+  <si>
+    <t>Принят автосамосвал - наименьшая Нвр а из подходящих</t>
+  </si>
+  <si>
+    <t>Ковшей в кузове n</t>
+  </si>
+  <si>
+    <t>Количество автосамосвалов N ≥ Тцикла / Тп, шт.</t>
+  </si>
+  <si>
+    <t>Нвр а, маш.-ч/м³</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -1855,7 +2333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1897,6 +2375,9 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1934,6 +2415,30 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1948,6 +2453,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2740,11 +3257,11 @@
       <c r="B5" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>'Объёмы (оконч.)'!$F$31</f>
         <v>24264.140842973826</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>'Объёмы (оконч.)'!$F$32</f>
         <v>28820.342480142914</v>
       </c>
@@ -2760,11 +3277,11 @@
       <c r="B6" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>'Котлован (оконч.)'!$C$56</f>
         <v>3635.720177060251</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <f>'Котлован (оконч.)'!$C$65</f>
         <v>763.33100906025174</v>
       </c>
@@ -2775,7 +3292,7 @@
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>244</v>
       </c>
       <c r="C7" s="16">
@@ -2793,67 +3310,67 @@
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="43">
         <f>C7-E7</f>
         <v>-545.97887343050388</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="26">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="27">
         <f>ABS(C8)/MAX(C7,E7)</f>
         <v>1.9193628153547412E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="14" t="str">
         <f>IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
         <v>баланс соблюдён</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF('Котлован (оконч.)'!$C$33="насыпи",'Котлован (оконч.)'!$C$44,0)</f>
         <v>148167.58923381407</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="27">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="28">
         <f>C8/D12</f>
         <v>-3.6848738395070229E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="28">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="29">
         <f>ROUND(D13,4)</f>
         <v>-3.7000000000000002E-3</v>
       </c>
@@ -2921,7 +3438,7 @@
       <c r="A5" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="25">
         <f>'Котлован (оконч.)'!$C$56</f>
         <v>3635.720177060251</v>
       </c>
@@ -3122,7 +3639,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="29"/>
+      <c r="A5" s="30"/>
       <c r="B5" s="6" t="s">
         <v>280</v>
       </c>
@@ -3170,18 +3687,18 @@
       <c r="B6" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
       <c r="O6" s="6" t="s">
         <v>282</v>
       </c>
@@ -3578,10 +4095,10 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="B20" s="35"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="11">
         <f t="shared" ref="C20:N20" si="2">C19-C5</f>
         <v>0</v>
@@ -3658,7 +4175,7 @@
       </c>
     </row>
     <row r="2" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
+      <c r="A2" s="30"/>
       <c r="B2" s="6" t="s">
         <v>277</v>
       </c>
@@ -4014,91 +4531,91 @@
       <c r="A7" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="22">
         <f t="shared" ref="B7:W7" si="0">B5*B4</f>
         <v>118897.5604405379</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f t="shared" si="0"/>
         <v>38355.269301721441</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="22">
         <f t="shared" si="0"/>
         <v>214900</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f t="shared" si="0"/>
         <v>329575.2135984404</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f t="shared" si="0"/>
         <v>64561.964260937515</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f t="shared" si="0"/>
         <v>246150</v>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f t="shared" si="0"/>
         <v>798450</v>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f t="shared" si="0"/>
         <v>620709.48877375002</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="22">
         <f t="shared" si="0"/>
         <v>521792.27215189888</v>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="22">
         <f t="shared" si="0"/>
         <v>189356.59055184439</v>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="22">
         <f t="shared" si="0"/>
         <v>544.54911752710132</v>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="22">
         <f t="shared" si="0"/>
         <v>133544.76456667422</v>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f t="shared" si="0"/>
         <v>817788.4615384615</v>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="22">
         <f t="shared" si="0"/>
         <v>1885288.4615384617</v>
       </c>
-      <c r="P7" s="21">
+      <c r="P7" s="22">
         <f t="shared" si="0"/>
         <v>1225645.4290536174</v>
       </c>
-      <c r="Q7" s="21">
+      <c r="Q7" s="22">
         <f t="shared" si="0"/>
         <v>9393.2577312126086</v>
       </c>
-      <c r="R7" s="21">
+      <c r="R7" s="22">
         <f t="shared" si="0"/>
         <v>280118.92354056484</v>
       </c>
-      <c r="S7" s="21">
+      <c r="S7" s="22">
         <f t="shared" si="0"/>
         <v>1355240.3846153847</v>
       </c>
-      <c r="T7" s="21">
+      <c r="T7" s="22">
         <f t="shared" si="0"/>
         <v>2359038.4615384615</v>
       </c>
-      <c r="U7" s="21">
+      <c r="U7" s="22">
         <f t="shared" si="0"/>
         <v>1252.2208994391024</v>
       </c>
-      <c r="V7" s="21">
+      <c r="V7" s="22">
         <f t="shared" si="0"/>
         <v>90168.040003245711</v>
       </c>
-      <c r="W7" s="21">
+      <c r="W7" s="22">
         <f t="shared" si="0"/>
         <v>690517.20067362278</v>
       </c>
@@ -4107,140 +4624,140 @@
       <c r="A8" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="22">
         <f t="shared" ref="B8:W8" si="1">B6*B4</f>
         <v>603267.66896887508</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f t="shared" si="1"/>
         <v>71928.711238765565</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="22">
         <f t="shared" si="1"/>
         <v>644700</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="22">
         <f t="shared" si="1"/>
         <v>329689.28229976434</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>34211.209601953124</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <f t="shared" si="1"/>
         <v>246150</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="22">
         <f t="shared" si="1"/>
         <v>266150</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="22">
         <f t="shared" si="1"/>
         <v>122621.41927374998</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="22">
         <f t="shared" si="1"/>
         <v>54264.237673950505</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="22">
         <f t="shared" si="1"/>
         <v>9173.1353108404546</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="22">
         <f t="shared" si="1"/>
         <v>1725.118253954847</v>
       </c>
-      <c r="M8" s="21">
+      <c r="M8" s="22">
         <f t="shared" si="1"/>
         <v>215342.99801133666</v>
       </c>
-      <c r="N8" s="21">
+      <c r="N8" s="22">
         <f t="shared" si="1"/>
         <v>817788.4615384615</v>
       </c>
-      <c r="O8" s="21">
+      <c r="O8" s="22">
         <f t="shared" si="1"/>
         <v>1346634.6153846155</v>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="22">
         <f t="shared" si="1"/>
         <v>680914.1272520097</v>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="22">
         <f t="shared" si="1"/>
         <v>9360.2839274350281</v>
       </c>
-      <c r="R8" s="21">
+      <c r="R8" s="22">
         <f t="shared" si="1"/>
         <v>173816.15831047174</v>
       </c>
-      <c r="S8" s="21">
+      <c r="S8" s="22">
         <f t="shared" si="1"/>
         <v>580817.30769230775</v>
       </c>
-      <c r="T8" s="21">
+      <c r="T8" s="22">
         <f t="shared" si="1"/>
         <v>786346.15384615387</v>
       </c>
-      <c r="U8" s="21">
+      <c r="U8" s="22">
         <f t="shared" si="1"/>
         <v>399.8867648237179</v>
       </c>
-      <c r="V8" s="21">
+      <c r="V8" s="22">
         <f t="shared" si="1"/>
         <v>21651.102067778887</v>
       </c>
-      <c r="W8" s="21">
+      <c r="W8" s="22">
         <f t="shared" si="1"/>
         <v>91646.936082521352</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="39" t="s">
         <v>290</v>
       </c>
-      <c r="B11" s="31"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="16">
         <f>SUM(B7:K7)/SUM(B4:K4)</f>
         <v>129.64977471365398</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="B12" s="31"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="16">
         <f>SUM(B8:K8)/SUM(B4:K4)</f>
         <v>98.272565897910127</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="31"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="16">
         <f>SUM(L7:W7)/SUM(L4:W4)</f>
         <v>365.0343923663209</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="31"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="16">
         <f>SUM(L8:W8)/SUM(L4:W4)</f>
         <v>194.98293196512685</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="B15" s="31"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="16">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
         <v>254.47752971990917</v>
@@ -4277,7 +4794,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="29"/>
+      <c r="A2" s="30"/>
       <c r="B2" s="6" t="s">
         <v>278</v>
       </c>
@@ -4333,11 +4850,11 @@
       <c r="A7" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="21">
+      <c r="B7" s="22">
         <f>B5*B4</f>
         <v>725437.01324096404</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>C5*C4</f>
         <v>1305786.6238337352</v>
       </c>
@@ -4346,60 +4863,60 @@
       <c r="A8" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="22">
         <f>B6*B4</f>
         <v>435262.20794457837</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>C6*C4</f>
         <v>725437.01324096404</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="B11" s="31"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="16">
         <f>SUM(B7:B7)/SUM(B4:B4)</f>
         <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="B12" s="31"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="16">
         <f>SUM(B8:B8)/SUM(B4:B4)</f>
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="39" t="s">
         <v>292</v>
       </c>
-      <c r="B13" s="31"/>
+      <c r="B13" s="40"/>
       <c r="C13" s="16">
         <f>SUM(C7:C7)/SUM(C4:C4)</f>
         <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="39" t="s">
         <v>293</v>
       </c>
-      <c r="B14" s="31"/>
+      <c r="B14" s="40"/>
       <c r="C14" s="16">
         <f>SUM(C8:C8)/SUM(C4:C4)</f>
         <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="B15" s="31"/>
+      <c r="B15" s="40"/>
       <c r="C15" s="16">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
         <v>223.60679774997897</v>
@@ -4412,6 +4929,2932 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>301</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+    </row>
+    <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+    </row>
+    <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B5" s="46">
+        <v>1650</v>
+      </c>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+    </row>
+    <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.24</v>
+      </c>
+      <c r="E8" s="9">
+        <v>0.21</v>
+      </c>
+      <c r="F8" s="3">
+        <v>10</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>100</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0.06</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
+        <v>340</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="25">
+        <f>'Табл. 5 скрепер'!$C$15</f>
+        <v>254.47752971990917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="25">
+        <f>SUM('Табл. 4 распределение'!C5:L5)</f>
+        <v>24240.291709108187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="39" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="11">
+        <f>C5*'Исходные данные'!$B$7</f>
+        <v>27876.335465474414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="39" t="s">
+        <v>343</v>
+      </c>
+      <c r="B7" s="40"/>
+      <c r="C7" s="25">
+        <f>'Табл. 4 распределение'!B19*'Исходные данные'!$B$4</f>
+        <v>28804.300608104153</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="39" t="s">
+        <v>345</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="32">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="41" t="s">
+        <v>347</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="E12" s="41" t="s">
+        <v>348</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+    </row>
+    <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="E13" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="F13" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="G13" s="40"/>
+    </row>
+    <row r="14" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>351</v>
+      </c>
+      <c r="C14" s="11">
+        <f>$C$6</f>
+        <v>27876.335465474414</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="23"/>
+      <c r="G14" s="11">
+        <f>$C$6</f>
+        <v>27876.335465474414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$8+'2.3 Грунт и нормы ЕНиР'!$E$8*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$8)/10</f>
+        <v>5.3740281241180927</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$9+'2.3 Грунт и нормы ЕНиР'!$E$9*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$9)/10</f>
+        <v>3.2447752971990917</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="11">
+        <f>C15*C14/800</f>
+        <v>187.26026348601266</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F16" s="23"/>
+      <c r="G16" s="11">
+        <f>G15*G14/800</f>
+        <v>113.06555586850791</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="11">
+        <f>100*$C$8*8/C15</f>
+        <v>297.72825207582417</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F17" s="23"/>
+      <c r="G17" s="11">
+        <f>100*$C$8*8/G15</f>
+        <v>493.1004009372017</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B18" s="23">
+        <f>C16/($C$8*$C$9)</f>
+        <v>4.6815065871503165</v>
+      </c>
+      <c r="C18" s="34">
+        <f>ROUNDUP(ROUND(B18,6),0)</f>
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F18" s="23">
+        <f>G16/($C$8*$C$9)</f>
+        <v>2.8266388967126979</v>
+      </c>
+      <c r="G18" s="34">
+        <f>ROUNDUP(ROUND(F18,6),0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="47" t="s">
+        <v>356</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="E19" s="47" t="s">
+        <v>356</v>
+      </c>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+    </row>
+    <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="C20" s="40"/>
+      <c r="E20" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="F20" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="G20" s="40"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="C21" s="11">
+        <f>$C$5</f>
+        <v>24240.291709108187</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="23"/>
+      <c r="G21" s="11">
+        <f>$C$5</f>
+        <v>24240.291709108187</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B22" s="23"/>
+      <c r="C22" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$10</f>
+        <v>0.06</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$10</f>
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B23" s="23"/>
+      <c r="C23" s="11">
+        <f>C22*C21/800</f>
+        <v>1.8180218781831141</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F23" s="23"/>
+      <c r="G23" s="11">
+        <f>G22*G21/800</f>
+        <v>1.8180218781831141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="23"/>
+      <c r="C24" s="11">
+        <f>100*$C$8*8/C22</f>
+        <v>26666.666666666668</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F24" s="23"/>
+      <c r="G24" s="11">
+        <f>100*$C$8*8/G22</f>
+        <v>26666.666666666668</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B25" s="23">
+        <f>C18*C17/C24</f>
+        <v>5.5824047264217032E-2</v>
+      </c>
+      <c r="C25" s="34">
+        <f>ROUNDUP(ROUND(B25,6),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F25" s="23">
+        <f>G18*G17/G24</f>
+        <v>5.5473795105435188E-2</v>
+      </c>
+      <c r="G25" s="34">
+        <f>ROUNDUP(ROUND(F25,6),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="40"/>
+      <c r="E26" s="17" t="s">
+        <v>361</v>
+      </c>
+      <c r="F26" s="48" t="s">
+        <v>325</v>
+      </c>
+      <c r="G26" s="40"/>
+    </row>
+    <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="23"/>
+      <c r="C27" s="11">
+        <f>$C$7</f>
+        <v>28804.300608104153</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F27" s="23"/>
+      <c r="G27" s="11">
+        <f>$C$7</f>
+        <v>28804.300608104153</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B28" s="23"/>
+      <c r="C28" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$12</f>
+        <v>0.25</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F28" s="23"/>
+      <c r="G28" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$11</f>
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B29" s="23"/>
+      <c r="C29" s="11">
+        <f>C28*C27/800</f>
+        <v>9.0013439400325481</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F29" s="23"/>
+      <c r="G29" s="11">
+        <f>G28*G27/800</f>
+        <v>9.7214514552351527</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="11">
+        <f>100*$C$8*8/C28</f>
+        <v>6400</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F30" s="23"/>
+      <c r="G30" s="11">
+        <f>100*$C$8*8/G28</f>
+        <v>5925.9259259259252</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B31" s="23">
+        <f>C18*C17/C30</f>
+        <v>0.23260019693423764</v>
+      </c>
+      <c r="C31" s="34">
+        <f>ROUNDUP(ROUND(B31,6),0)</f>
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F31" s="23">
+        <f>G18*G17/G30</f>
+        <v>0.24963207797445838</v>
+      </c>
+      <c r="G31" s="34">
+        <f>ROUNDUP(ROUND(F31,6),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E32" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="F32" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="G32" s="40"/>
+    </row>
+    <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" s="11">
+        <f>$C$7</f>
+        <v>28804.300608104153</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E34" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" s="13">
+        <f>'2.3 Грунт и нормы ЕНиР'!$D$12</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E35" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" s="11">
+        <f>G34*G33/800</f>
+        <v>9.0013439400325481</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E36" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" s="11">
+        <f>100*$C$8*8/G34</f>
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E37" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F37" s="23">
+        <f>G18*G17/G36</f>
+        <v>0.23114081293931327</v>
+      </c>
+      <c r="G37" s="34">
+        <f>ROUNDUP(ROUND(F37,6),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E38" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="F38" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="G38" s="40"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F39" s="23"/>
+      <c r="G39" s="11">
+        <f>$C$6</f>
+        <v>27876.335465474414</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E40" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F40" s="23"/>
+      <c r="G40" s="15">
+        <f>G15/$C$10</f>
+        <v>1.0815917657330305</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E41" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F41" s="23"/>
+      <c r="G41" s="11">
+        <f>G40*G39/800</f>
+        <v>37.688518622835971</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E42" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" s="11">
+        <f>100*$C$8*8/G40</f>
+        <v>1479.3012028116052</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E43" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="F43" s="23">
+        <f>G18*G17/G42</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="G43" s="34">
+        <f>ROUNDUP(ROUND(F43,6),0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="B45" s="40"/>
+      <c r="C45" s="16">
+        <f>C16+C23+C29</f>
+        <v>198.07962930422832</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>362</v>
+      </c>
+      <c r="F45" s="40"/>
+      <c r="G45" s="16">
+        <f>G16+G23+G29+G35+G41</f>
+        <v>171.2948917647947</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="47" t="s">
+        <v>363</v>
+      </c>
+      <c r="B46" s="40"/>
+      <c r="C46" s="16">
+        <f>C14/C45</f>
+        <v>140.73297473037704</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>363</v>
+      </c>
+      <c r="F46" s="40"/>
+      <c r="G46" s="16">
+        <f>G14/G45</f>
+        <v>162.73886032603622</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="47" t="s">
+        <v>364</v>
+      </c>
+      <c r="B47" s="40"/>
+      <c r="C47" s="35">
+        <f>C45/C14</f>
+        <v>7.1056552447345605E-3</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>364</v>
+      </c>
+      <c r="F47" s="40"/>
+      <c r="G47" s="35">
+        <f>G45/G14</f>
+        <v>6.1448138323973028E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="B48" s="40"/>
+      <c r="C48" s="22">
+        <f>C16/(C18*$C$8)</f>
+        <v>18.726026348601266</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>365</v>
+      </c>
+      <c r="F48" s="40"/>
+      <c r="G48" s="22">
+        <f>G16/(G18*$C$8)</f>
+        <v>18.844259311417986</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="47" t="str">
+        <f>IF(C47&lt;G47,"Принимается вариант 1 - ведущая машина бульдозер: меньше маш.-см на 1 м³","Принимается вариант 2 - ведущая машина скрепер: меньше маш.-см на 1 м³")</f>
+        <v>Принимается вариант 2 - ведущая машина скрепер: меньше маш.-см на 1 м³</v>
+      </c>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A47:B47"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:T56"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="20" width="11" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="25">
+        <f>'Котлован (оконч.)'!$C$56</f>
+        <v>3635.720177060251</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="39" t="s">
+        <v>368</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="13">
+        <f>'Котлован (оконч.)'!$C$35</f>
+        <v>2.0972999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="39" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="36">
+        <f>'Табл. 7 варианты'!$C$8</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="E8" s="20">
+        <v>2.9</v>
+      </c>
+      <c r="F8" s="11">
+        <f>100*8/E8</f>
+        <v>275.86206896551727</v>
+      </c>
+      <c r="G8" s="20">
+        <v>4</v>
+      </c>
+      <c r="H8" s="20">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I8" s="20">
+        <v>1.7</v>
+      </c>
+      <c r="J8" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>382</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>380</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="E9" s="20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="F9" s="11">
+        <f>100*8/E9</f>
+        <v>347.82608695652175</v>
+      </c>
+      <c r="G9" s="20">
+        <v>4</v>
+      </c>
+      <c r="H9" s="20">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="I9" s="20">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="J9" s="21">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.65</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="20">
+        <v>2.1</v>
+      </c>
+      <c r="F10" s="11">
+        <f>100*8/E10</f>
+        <v>380.95238095238096</v>
+      </c>
+      <c r="G10" s="20">
+        <v>5.8</v>
+      </c>
+      <c r="H10" s="20">
+        <v>9</v>
+      </c>
+      <c r="I10" s="20">
+        <v>5</v>
+      </c>
+      <c r="J10" s="21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="93.6" x14ac:dyDescent="0.3">
+      <c r="E11" s="37" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="47" t="s">
+        <v>388</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="14" t="str">
+        <f>INDEX($A$8:$A$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))</f>
+        <v>ЭО-4121А</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="39" t="s">
+        <v>372</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="11">
+        <f>INDEX($C$8:$C$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))</f>
+        <v>0.65</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>393</v>
+      </c>
+      <c r="F13" s="21">
+        <v>0</v>
+      </c>
+      <c r="G13" s="21">
+        <v>500</v>
+      </c>
+      <c r="H13" s="8" t="str">
+        <f t="shared" ref="H13:H20" si="0">IF(AND($C$3&gt;=F13,$C$3&lt;=IF(ISNUMBER(G13),G13,1E+99)),"да","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="39" t="s">
+        <v>308</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="22">
+        <f>INDEX($E$8:$E$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))</f>
+        <v>2.1</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F14" s="21">
+        <v>500</v>
+      </c>
+      <c r="G14" s="21">
+        <v>1500</v>
+      </c>
+      <c r="H14" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="39" t="s">
+        <v>395</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="11">
+        <f>INDEX($J$8:$J$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))/100</f>
+        <v>0.1</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="F15" s="21">
+        <v>1500</v>
+      </c>
+      <c r="G15" s="21">
+        <v>5000</v>
+      </c>
+      <c r="H15" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="39" t="s">
+        <v>397</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="15">
+        <f>C4-C15</f>
+        <v>1.9972999999999996</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="F16" s="21">
+        <v>2000</v>
+      </c>
+      <c r="G16" s="21">
+        <v>8000</v>
+      </c>
+      <c r="H16" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v>да</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="39" t="s">
+        <v>399</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="8" t="str">
+        <f>IF(INDEX($G$8:$G$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))&gt;=C16,"выполняется","НЕТ")</f>
+        <v>выполняется</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="F17" s="21">
+        <v>6000</v>
+      </c>
+      <c r="G17" s="21">
+        <v>11000</v>
+      </c>
+      <c r="H17" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="39" t="s">
+        <v>401</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="11">
+        <f>C14*C3/800</f>
+        <v>9.54376546478316</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="21">
+        <v>11000</v>
+      </c>
+      <c r="G18" s="21">
+        <v>15000</v>
+      </c>
+      <c r="H18" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="39" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="22">
+        <f>C18/C5</f>
+        <v>4.77188273239158</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="F19" s="21">
+        <v>13000</v>
+      </c>
+      <c r="G19" s="21">
+        <v>18000</v>
+      </c>
+      <c r="H19" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E20" s="8" t="s">
+        <v>404</v>
+      </c>
+      <c r="F20" s="21">
+        <v>17000</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="8" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="37" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="39" t="s">
+        <v>406</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="25">
+        <f>'Исходные данные'!$B$7</f>
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="38">
+        <f>'2.3 Грунт и нормы ЕНиР'!$B$5/1000</f>
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="39" t="s">
+        <v>408</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="15">
+        <f>C13*C22/C23</f>
+        <v>0.5086956521739131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="39" t="s">
+        <v>409</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="15">
+        <f>C25*C24</f>
+        <v>0.83934782608695657</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="39" t="s">
+        <v>411</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="20">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="39" t="s">
+        <v>412</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="20">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="39" t="s">
+        <v>413</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="39" t="s">
+        <v>414</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="S33" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="T33" s="6" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="31" t="s">
+        <v>435</v>
+      </c>
+      <c r="B34" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="C34" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D34" s="9">
+        <v>2.48</v>
+      </c>
+      <c r="E34" s="21">
+        <v>45</v>
+      </c>
+      <c r="F34" s="21">
+        <v>60</v>
+      </c>
+      <c r="G34" s="11">
+        <f t="shared" ref="G34:G51" si="1">C34/$C$26</f>
+        <v>4.884744884744884</v>
+      </c>
+      <c r="H34" s="11">
+        <f t="shared" ref="H34:H51" si="2">B34/$C$13</f>
+        <v>6.9230769230769225</v>
+      </c>
+      <c r="I34" s="34">
+        <f t="shared" ref="I34:I51" si="3">INT(ROUND(MIN(G34,H34),6))</f>
+        <v>4</v>
+      </c>
+      <c r="J34" s="8" t="str">
+        <f t="shared" ref="J34:J51" si="4">IF(AND(I34&gt;=6,I34&lt;=11),"да","нет")</f>
+        <v>нет</v>
+      </c>
+      <c r="K34" s="23">
+        <f t="shared" ref="K34:K51" si="5">I34*$C$25</f>
+        <v>2.0347826086956524</v>
+      </c>
+      <c r="L34" s="11">
+        <f t="shared" ref="L34:L51" si="6">K34*$C$14/100*60</f>
+        <v>2.5638260869565221</v>
+      </c>
+      <c r="M34" s="11">
+        <f t="shared" ref="M34:M51" si="7">$C$27/E34*60</f>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="N34" s="11">
+        <f t="shared" ref="N34:N51" si="8">$C$27/F34*60</f>
+        <v>10</v>
+      </c>
+      <c r="O34" s="11">
+        <f t="shared" ref="O34:O51" si="9">$C$28+L34+M34+N34+$C$29+$C$30+$C$31</f>
+        <v>29.797159420289855</v>
+      </c>
+      <c r="P34" s="11">
+        <f t="shared" ref="P34:P51" si="10">O34/L34</f>
+        <v>11.622145344367565</v>
+      </c>
+      <c r="Q34" s="34">
+        <f t="shared" ref="Q34:Q51" si="11">ROUNDUP(ROUND(P34,6),0)</f>
+        <v>12</v>
+      </c>
+      <c r="R34" s="11">
+        <f t="shared" ref="R34:R51" si="12">$C$13*$C$22*I34</f>
+        <v>2.3400000000000003</v>
+      </c>
+      <c r="S34" s="15">
+        <f t="shared" ref="S34:S51" si="13">O34/(R34*60)</f>
+        <v>0.21223048020149468</v>
+      </c>
+      <c r="T34" s="15" t="str">
+        <f t="shared" ref="T34:T51" si="14">IF(J34="да",S34,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="B35" s="20">
+        <v>4.5</v>
+      </c>
+      <c r="C35" s="9">
+        <v>3.95</v>
+      </c>
+      <c r="D35" s="9">
+        <v>2.48</v>
+      </c>
+      <c r="E35" s="21">
+        <v>47</v>
+      </c>
+      <c r="F35" s="21">
+        <v>60</v>
+      </c>
+      <c r="G35" s="11">
+        <f t="shared" si="1"/>
+        <v>4.7060347060347061</v>
+      </c>
+      <c r="H35" s="11">
+        <f t="shared" si="2"/>
+        <v>6.9230769230769225</v>
+      </c>
+      <c r="I35" s="34">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="J35" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K35" s="23">
+        <f t="shared" si="5"/>
+        <v>2.0347826086956524</v>
+      </c>
+      <c r="L35" s="11">
+        <f t="shared" si="6"/>
+        <v>2.5638260869565221</v>
+      </c>
+      <c r="M35" s="11">
+        <f t="shared" si="7"/>
+        <v>12.76595744680851</v>
+      </c>
+      <c r="N35" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O35" s="11">
+        <f t="shared" si="9"/>
+        <v>29.229783533765033</v>
+      </c>
+      <c r="P35" s="11">
+        <f t="shared" si="10"/>
+        <v>11.400844886660488</v>
+      </c>
+      <c r="Q35" s="34">
+        <f t="shared" si="11"/>
+        <v>12</v>
+      </c>
+      <c r="R35" s="11">
+        <f t="shared" si="12"/>
+        <v>2.3400000000000003</v>
+      </c>
+      <c r="S35" s="15">
+        <f t="shared" si="13"/>
+        <v>0.20818934140858286</v>
+      </c>
+      <c r="T35" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B36" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="C36" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="D36" s="9">
+        <v>2.81</v>
+      </c>
+      <c r="E36" s="21">
+        <v>42</v>
+      </c>
+      <c r="F36" s="21">
+        <v>60</v>
+      </c>
+      <c r="G36" s="11">
+        <f t="shared" si="1"/>
+        <v>6.5527065527065522</v>
+      </c>
+      <c r="H36" s="11">
+        <f t="shared" si="2"/>
+        <v>5.8461538461538458</v>
+      </c>
+      <c r="I36" s="34">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="J36" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K36" s="23">
+        <f t="shared" si="5"/>
+        <v>2.5434782608695654</v>
+      </c>
+      <c r="L36" s="11">
+        <f t="shared" si="6"/>
+        <v>3.2047826086956528</v>
+      </c>
+      <c r="M36" s="11">
+        <f t="shared" si="7"/>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="N36" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O36" s="11">
+        <f t="shared" si="9"/>
+        <v>31.390496894409939</v>
+      </c>
+      <c r="P36" s="11">
+        <f t="shared" si="10"/>
+        <v>9.7948911758435546</v>
+      </c>
+      <c r="Q36" s="34">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="R36" s="11">
+        <f t="shared" si="12"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="S36" s="15">
+        <f t="shared" si="13"/>
+        <v>0.17886323016757796</v>
+      </c>
+      <c r="T36" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="31" t="s">
+        <v>438</v>
+      </c>
+      <c r="B37" s="20">
+        <v>5.4</v>
+      </c>
+      <c r="C37" s="9">
+        <v>10</v>
+      </c>
+      <c r="D37" s="9">
+        <v>2.15</v>
+      </c>
+      <c r="E37" s="21">
+        <v>48</v>
+      </c>
+      <c r="F37" s="21">
+        <v>60</v>
+      </c>
+      <c r="G37" s="11">
+        <f t="shared" si="1"/>
+        <v>11.914011914011914</v>
+      </c>
+      <c r="H37" s="11">
+        <f t="shared" si="2"/>
+        <v>8.3076923076923084</v>
+      </c>
+      <c r="I37" s="34">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J37" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>да</v>
+      </c>
+      <c r="K37" s="23">
+        <f t="shared" si="5"/>
+        <v>4.0695652173913048</v>
+      </c>
+      <c r="L37" s="11">
+        <f t="shared" si="6"/>
+        <v>5.1276521739130443</v>
+      </c>
+      <c r="M37" s="11">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="N37" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O37" s="11">
+        <f t="shared" si="9"/>
+        <v>31.527652173913047</v>
+      </c>
+      <c r="P37" s="11">
+        <f t="shared" si="10"/>
+        <v>6.1485551485551486</v>
+      </c>
+      <c r="Q37" s="34">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="R37" s="11">
+        <f t="shared" si="12"/>
+        <v>4.6800000000000006</v>
+      </c>
+      <c r="S37" s="15">
+        <f t="shared" si="13"/>
+        <v>0.11227796358231142</v>
+      </c>
+      <c r="T37" s="15">
+        <f t="shared" si="14"/>
+        <v>0.11227796358231142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="31" t="s">
+        <v>439</v>
+      </c>
+      <c r="B38" s="20">
+        <v>5.5</v>
+      </c>
+      <c r="C38" s="9">
+        <v>9</v>
+      </c>
+      <c r="D38" s="9">
+        <v>2.15</v>
+      </c>
+      <c r="E38" s="21">
+        <v>40</v>
+      </c>
+      <c r="F38" s="21">
+        <v>60</v>
+      </c>
+      <c r="G38" s="11">
+        <f t="shared" si="1"/>
+        <v>10.722610722610723</v>
+      </c>
+      <c r="H38" s="11">
+        <f t="shared" si="2"/>
+        <v>8.4615384615384617</v>
+      </c>
+      <c r="I38" s="34">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J38" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>да</v>
+      </c>
+      <c r="K38" s="23">
+        <f t="shared" si="5"/>
+        <v>4.0695652173913048</v>
+      </c>
+      <c r="L38" s="11">
+        <f t="shared" si="6"/>
+        <v>5.1276521739130443</v>
+      </c>
+      <c r="M38" s="11">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="N38" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O38" s="11">
+        <f t="shared" si="9"/>
+        <v>34.027652173913047</v>
+      </c>
+      <c r="P38" s="11">
+        <f t="shared" si="10"/>
+        <v>6.6361077194410525</v>
+      </c>
+      <c r="Q38" s="34">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="R38" s="11">
+        <f t="shared" si="12"/>
+        <v>4.6800000000000006</v>
+      </c>
+      <c r="S38" s="15">
+        <f t="shared" si="13"/>
+        <v>0.12118109748544532</v>
+      </c>
+      <c r="T38" s="15">
+        <f t="shared" si="14"/>
+        <v>0.12118109748544532</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="B39" s="20">
+        <v>5.5</v>
+      </c>
+      <c r="C39" s="9">
+        <v>7</v>
+      </c>
+      <c r="D39" s="9">
+        <v>2.15</v>
+      </c>
+      <c r="E39" s="21">
+        <v>42</v>
+      </c>
+      <c r="F39" s="21">
+        <v>60</v>
+      </c>
+      <c r="G39" s="11">
+        <f t="shared" si="1"/>
+        <v>8.3398083398083394</v>
+      </c>
+      <c r="H39" s="11">
+        <f t="shared" si="2"/>
+        <v>8.4615384615384617</v>
+      </c>
+      <c r="I39" s="34">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J39" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>да</v>
+      </c>
+      <c r="K39" s="23">
+        <f t="shared" si="5"/>
+        <v>4.0695652173913048</v>
+      </c>
+      <c r="L39" s="11">
+        <f t="shared" si="6"/>
+        <v>5.1276521739130443</v>
+      </c>
+      <c r="M39" s="11">
+        <f t="shared" si="7"/>
+        <v>14.285714285714285</v>
+      </c>
+      <c r="N39" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O39" s="11">
+        <f t="shared" si="9"/>
+        <v>33.313366459627332</v>
+      </c>
+      <c r="P39" s="11">
+        <f t="shared" si="10"/>
+        <v>6.4968069849022223</v>
+      </c>
+      <c r="Q39" s="34">
+        <f t="shared" si="11"/>
+        <v>7</v>
+      </c>
+      <c r="R39" s="11">
+        <f t="shared" si="12"/>
+        <v>4.6800000000000006</v>
+      </c>
+      <c r="S39" s="15">
+        <f t="shared" si="13"/>
+        <v>0.11863734494169277</v>
+      </c>
+      <c r="T39" s="15">
+        <f t="shared" si="14"/>
+        <v>0.11863734494169277</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="31" t="s">
+        <v>441</v>
+      </c>
+      <c r="B40" s="20">
+        <v>10.5</v>
+      </c>
+      <c r="C40" s="9">
+        <v>20</v>
+      </c>
+      <c r="D40" s="9">
+        <v>2.6</v>
+      </c>
+      <c r="E40" s="21">
+        <v>50</v>
+      </c>
+      <c r="F40" s="21">
+        <v>60</v>
+      </c>
+      <c r="G40" s="11">
+        <f t="shared" si="1"/>
+        <v>23.828023828023827</v>
+      </c>
+      <c r="H40" s="11">
+        <f t="shared" si="2"/>
+        <v>16.153846153846153</v>
+      </c>
+      <c r="I40" s="34">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="J40" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K40" s="23">
+        <f t="shared" si="5"/>
+        <v>8.1391304347826097</v>
+      </c>
+      <c r="L40" s="11">
+        <f t="shared" si="6"/>
+        <v>10.255304347826089</v>
+      </c>
+      <c r="M40" s="11">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="N40" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O40" s="11">
+        <f t="shared" si="9"/>
+        <v>36.155304347826089</v>
+      </c>
+      <c r="P40" s="11">
+        <f t="shared" si="10"/>
+        <v>3.5255223171889836</v>
+      </c>
+      <c r="Q40" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R40" s="11">
+        <f t="shared" si="12"/>
+        <v>9.3600000000000012</v>
+      </c>
+      <c r="S40" s="15">
+        <f t="shared" si="13"/>
+        <v>6.4379103183451011E-2</v>
+      </c>
+      <c r="T40" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="B41" s="20">
+        <v>11</v>
+      </c>
+      <c r="C41" s="9">
+        <v>20</v>
+      </c>
+      <c r="D41" s="9">
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="E41" s="21">
+        <v>48</v>
+      </c>
+      <c r="F41" s="21">
+        <v>60</v>
+      </c>
+      <c r="G41" s="11">
+        <f t="shared" si="1"/>
+        <v>23.828023828023827</v>
+      </c>
+      <c r="H41" s="11">
+        <f t="shared" si="2"/>
+        <v>16.923076923076923</v>
+      </c>
+      <c r="I41" s="34">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="J41" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K41" s="23">
+        <f t="shared" si="5"/>
+        <v>8.1391304347826097</v>
+      </c>
+      <c r="L41" s="11">
+        <f t="shared" si="6"/>
+        <v>10.255304347826089</v>
+      </c>
+      <c r="M41" s="11">
+        <f t="shared" si="7"/>
+        <v>12.5</v>
+      </c>
+      <c r="N41" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O41" s="11">
+        <f t="shared" si="9"/>
+        <v>36.655304347826089</v>
+      </c>
+      <c r="P41" s="11">
+        <f t="shared" si="10"/>
+        <v>3.5742775742775739</v>
+      </c>
+      <c r="Q41" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R41" s="11">
+        <f t="shared" si="12"/>
+        <v>9.3600000000000012</v>
+      </c>
+      <c r="S41" s="15">
+        <f t="shared" si="13"/>
+        <v>6.5269416573764394E-2</v>
+      </c>
+      <c r="T41" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="B42" s="20">
+        <v>12</v>
+      </c>
+      <c r="C42" s="9">
+        <v>14.4</v>
+      </c>
+      <c r="D42" s="9">
+        <v>3.2</v>
+      </c>
+      <c r="E42" s="21">
+        <v>55</v>
+      </c>
+      <c r="F42" s="21">
+        <v>60</v>
+      </c>
+      <c r="G42" s="11">
+        <f t="shared" si="1"/>
+        <v>17.156177156177154</v>
+      </c>
+      <c r="H42" s="11">
+        <f t="shared" si="2"/>
+        <v>18.46153846153846</v>
+      </c>
+      <c r="I42" s="34">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="J42" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K42" s="23">
+        <f t="shared" si="5"/>
+        <v>8.6478260869565222</v>
+      </c>
+      <c r="L42" s="11">
+        <f t="shared" si="6"/>
+        <v>10.896260869565218</v>
+      </c>
+      <c r="M42" s="11">
+        <f t="shared" si="7"/>
+        <v>10.90909090909091</v>
+      </c>
+      <c r="N42" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O42" s="11">
+        <f t="shared" si="9"/>
+        <v>35.70535177865613</v>
+      </c>
+      <c r="P42" s="11">
+        <f t="shared" si="10"/>
+        <v>3.2768444337071791</v>
+      </c>
+      <c r="Q42" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R42" s="11">
+        <f t="shared" si="12"/>
+        <v>9.9450000000000021</v>
+      </c>
+      <c r="S42" s="15">
+        <f t="shared" si="13"/>
+        <v>5.9838028789435428E-2</v>
+      </c>
+      <c r="T42" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="B43" s="20">
+        <v>11</v>
+      </c>
+      <c r="C43" s="9">
+        <v>18.5</v>
+      </c>
+      <c r="D43" s="9">
+        <v>3.02</v>
+      </c>
+      <c r="E43" s="21">
+        <v>55</v>
+      </c>
+      <c r="F43" s="21">
+        <v>60</v>
+      </c>
+      <c r="G43" s="11">
+        <f t="shared" si="1"/>
+        <v>22.040922040922041</v>
+      </c>
+      <c r="H43" s="11">
+        <f t="shared" si="2"/>
+        <v>16.923076923076923</v>
+      </c>
+      <c r="I43" s="34">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="J43" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K43" s="23">
+        <f t="shared" si="5"/>
+        <v>8.1391304347826097</v>
+      </c>
+      <c r="L43" s="11">
+        <f t="shared" si="6"/>
+        <v>10.255304347826089</v>
+      </c>
+      <c r="M43" s="11">
+        <f t="shared" si="7"/>
+        <v>10.90909090909091</v>
+      </c>
+      <c r="N43" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O43" s="11">
+        <f t="shared" si="9"/>
+        <v>35.064395256917003</v>
+      </c>
+      <c r="P43" s="11">
+        <f t="shared" si="10"/>
+        <v>3.4191472108138776</v>
+      </c>
+      <c r="Q43" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R43" s="11">
+        <f t="shared" si="12"/>
+        <v>9.3600000000000012</v>
+      </c>
+      <c r="S43" s="15">
+        <f t="shared" si="13"/>
+        <v>6.2436601240949074E-2</v>
+      </c>
+      <c r="T43" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="B44" s="20">
+        <v>6.6</v>
+      </c>
+      <c r="C44" s="9">
+        <v>13</v>
+      </c>
+      <c r="D44" s="9">
+        <v>2.85</v>
+      </c>
+      <c r="E44" s="21">
+        <v>55</v>
+      </c>
+      <c r="F44" s="21">
+        <v>60</v>
+      </c>
+      <c r="G44" s="11">
+        <f t="shared" si="1"/>
+        <v>15.488215488215488</v>
+      </c>
+      <c r="H44" s="11">
+        <f t="shared" si="2"/>
+        <v>10.153846153846153</v>
+      </c>
+      <c r="I44" s="34">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="J44" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>да</v>
+      </c>
+      <c r="K44" s="23">
+        <f t="shared" si="5"/>
+        <v>5.0869565217391308</v>
+      </c>
+      <c r="L44" s="11">
+        <f t="shared" si="6"/>
+        <v>6.4095652173913056</v>
+      </c>
+      <c r="M44" s="11">
+        <f t="shared" si="7"/>
+        <v>10.90909090909091</v>
+      </c>
+      <c r="N44" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O44" s="11">
+        <f t="shared" si="9"/>
+        <v>31.218656126482216</v>
+      </c>
+      <c r="P44" s="11">
+        <f t="shared" si="10"/>
+        <v>4.8706355373022037</v>
+      </c>
+      <c r="Q44" s="34">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="R44" s="11">
+        <f t="shared" si="12"/>
+        <v>5.8500000000000005</v>
+      </c>
+      <c r="S44" s="15">
+        <f t="shared" si="13"/>
+        <v>8.8942040246388063E-2</v>
+      </c>
+      <c r="T44" s="15">
+        <f t="shared" si="14"/>
+        <v>8.8942040246388063E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B45" s="20">
+        <v>8.5</v>
+      </c>
+      <c r="C45" s="9">
+        <v>15</v>
+      </c>
+      <c r="D45" s="9">
+        <v>2.96</v>
+      </c>
+      <c r="E45" s="21">
+        <v>55</v>
+      </c>
+      <c r="F45" s="21">
+        <v>60</v>
+      </c>
+      <c r="G45" s="11">
+        <f t="shared" si="1"/>
+        <v>17.87101787101787</v>
+      </c>
+      <c r="H45" s="11">
+        <f t="shared" si="2"/>
+        <v>13.076923076923077</v>
+      </c>
+      <c r="I45" s="34">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="J45" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K45" s="23">
+        <f t="shared" si="5"/>
+        <v>6.6130434782608702</v>
+      </c>
+      <c r="L45" s="11">
+        <f t="shared" si="6"/>
+        <v>8.3324347826086971</v>
+      </c>
+      <c r="M45" s="11">
+        <f t="shared" si="7"/>
+        <v>10.90909090909091</v>
+      </c>
+      <c r="N45" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O45" s="11">
+        <f t="shared" si="9"/>
+        <v>33.141525691699613</v>
+      </c>
+      <c r="P45" s="11">
+        <f t="shared" si="10"/>
+        <v>3.9774119517709265</v>
+      </c>
+      <c r="Q45" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R45" s="11">
+        <f t="shared" si="12"/>
+        <v>7.6050000000000013</v>
+      </c>
+      <c r="S45" s="15">
+        <f t="shared" si="13"/>
+        <v>7.2631000858425609E-2</v>
+      </c>
+      <c r="T45" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="31" t="s">
+        <v>447</v>
+      </c>
+      <c r="B46" s="20">
+        <v>6.5</v>
+      </c>
+      <c r="C46" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="D46" s="9">
+        <v>2.87</v>
+      </c>
+      <c r="E46" s="21">
+        <v>52</v>
+      </c>
+      <c r="F46" s="21">
+        <v>60</v>
+      </c>
+      <c r="G46" s="11">
+        <f t="shared" si="1"/>
+        <v>8.9355089355089348</v>
+      </c>
+      <c r="H46" s="11">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="I46" s="34">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="J46" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>да</v>
+      </c>
+      <c r="K46" s="23">
+        <f t="shared" si="5"/>
+        <v>4.0695652173913048</v>
+      </c>
+      <c r="L46" s="11">
+        <f t="shared" si="6"/>
+        <v>5.1276521739130443</v>
+      </c>
+      <c r="M46" s="11">
+        <f t="shared" si="7"/>
+        <v>11.538461538461538</v>
+      </c>
+      <c r="N46" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O46" s="11">
+        <f t="shared" si="9"/>
+        <v>30.566113712374584</v>
+      </c>
+      <c r="P46" s="11">
+        <f t="shared" si="10"/>
+        <v>5.9610349289836462</v>
+      </c>
+      <c r="Q46" s="34">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="R46" s="11">
+        <f t="shared" si="12"/>
+        <v>4.6800000000000006</v>
+      </c>
+      <c r="S46" s="15">
+        <f t="shared" si="13"/>
+        <v>0.1088536813118753</v>
+      </c>
+      <c r="T46" s="15">
+        <f t="shared" si="14"/>
+        <v>0.1088536813118753</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="B47" s="20">
+        <v>12</v>
+      </c>
+      <c r="C47" s="9">
+        <v>18</v>
+      </c>
+      <c r="D47" s="9">
+        <v>2.7</v>
+      </c>
+      <c r="E47" s="21">
+        <v>45</v>
+      </c>
+      <c r="F47" s="21">
+        <v>60</v>
+      </c>
+      <c r="G47" s="11">
+        <f t="shared" si="1"/>
+        <v>21.445221445221446</v>
+      </c>
+      <c r="H47" s="11">
+        <f t="shared" si="2"/>
+        <v>18.46153846153846</v>
+      </c>
+      <c r="I47" s="34">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="J47" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K47" s="23">
+        <f t="shared" si="5"/>
+        <v>9.1565217391304365</v>
+      </c>
+      <c r="L47" s="11">
+        <f t="shared" si="6"/>
+        <v>11.537217391304351</v>
+      </c>
+      <c r="M47" s="11">
+        <f t="shared" si="7"/>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="N47" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O47" s="11">
+        <f t="shared" si="9"/>
+        <v>38.770550724637687</v>
+      </c>
+      <c r="P47" s="11">
+        <f t="shared" si="10"/>
+        <v>3.360476743192792</v>
+      </c>
+      <c r="Q47" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R47" s="11">
+        <f t="shared" si="12"/>
+        <v>10.530000000000001</v>
+      </c>
+      <c r="S47" s="15">
+        <f t="shared" si="13"/>
+        <v>6.1365227484390127E-2</v>
+      </c>
+      <c r="T47" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="31" t="s">
+        <v>449</v>
+      </c>
+      <c r="B48" s="20">
+        <v>10.5</v>
+      </c>
+      <c r="C48" s="9">
+        <v>16</v>
+      </c>
+      <c r="D48" s="9">
+        <v>2.42</v>
+      </c>
+      <c r="E48" s="21">
+        <v>45</v>
+      </c>
+      <c r="F48" s="21">
+        <v>60</v>
+      </c>
+      <c r="G48" s="11">
+        <f t="shared" si="1"/>
+        <v>19.06241906241906</v>
+      </c>
+      <c r="H48" s="11">
+        <f t="shared" si="2"/>
+        <v>16.153846153846153</v>
+      </c>
+      <c r="I48" s="34">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="J48" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K48" s="23">
+        <f t="shared" si="5"/>
+        <v>8.1391304347826097</v>
+      </c>
+      <c r="L48" s="11">
+        <f t="shared" si="6"/>
+        <v>10.255304347826089</v>
+      </c>
+      <c r="M48" s="11">
+        <f t="shared" si="7"/>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="N48" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O48" s="11">
+        <f t="shared" si="9"/>
+        <v>37.488637681159425</v>
+      </c>
+      <c r="P48" s="11">
+        <f t="shared" si="10"/>
+        <v>3.6555363360918913</v>
+      </c>
+      <c r="Q48" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R48" s="11">
+        <f t="shared" si="12"/>
+        <v>9.3600000000000012</v>
+      </c>
+      <c r="S48" s="15">
+        <f t="shared" si="13"/>
+        <v>6.6753272224286717E-2</v>
+      </c>
+      <c r="T48" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="B49" s="20">
+        <v>10.5</v>
+      </c>
+      <c r="C49" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="D49" s="9">
+        <v>2.46</v>
+      </c>
+      <c r="E49" s="21">
+        <v>45</v>
+      </c>
+      <c r="F49" s="21">
+        <v>60</v>
+      </c>
+      <c r="G49" s="11">
+        <f t="shared" si="1"/>
+        <v>16.083916083916083</v>
+      </c>
+      <c r="H49" s="11">
+        <f t="shared" si="2"/>
+        <v>16.153846153846153</v>
+      </c>
+      <c r="I49" s="34">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="J49" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K49" s="23">
+        <f t="shared" si="5"/>
+        <v>8.1391304347826097</v>
+      </c>
+      <c r="L49" s="11">
+        <f t="shared" si="6"/>
+        <v>10.255304347826089</v>
+      </c>
+      <c r="M49" s="11">
+        <f t="shared" si="7"/>
+        <v>13.333333333333332</v>
+      </c>
+      <c r="N49" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O49" s="11">
+        <f t="shared" si="9"/>
+        <v>37.488637681159425</v>
+      </c>
+      <c r="P49" s="11">
+        <f t="shared" si="10"/>
+        <v>3.6555363360918913</v>
+      </c>
+      <c r="Q49" s="34">
+        <f t="shared" si="11"/>
+        <v>4</v>
+      </c>
+      <c r="R49" s="11">
+        <f t="shared" si="12"/>
+        <v>9.3600000000000012</v>
+      </c>
+      <c r="S49" s="15">
+        <f t="shared" si="13"/>
+        <v>6.6753272224286717E-2</v>
+      </c>
+      <c r="T49" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="31" t="s">
+        <v>451</v>
+      </c>
+      <c r="B50" s="20">
+        <v>20</v>
+      </c>
+      <c r="C50" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="D50" s="9">
+        <v>2.96</v>
+      </c>
+      <c r="E50" s="21">
+        <v>40</v>
+      </c>
+      <c r="F50" s="21">
+        <v>60</v>
+      </c>
+      <c r="G50" s="11">
+        <f t="shared" si="1"/>
+        <v>26.806526806526804</v>
+      </c>
+      <c r="H50" s="11">
+        <f t="shared" si="2"/>
+        <v>30.769230769230766</v>
+      </c>
+      <c r="I50" s="34">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="J50" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K50" s="23">
+        <f t="shared" si="5"/>
+        <v>13.22608695652174</v>
+      </c>
+      <c r="L50" s="11">
+        <f t="shared" si="6"/>
+        <v>16.664869565217394</v>
+      </c>
+      <c r="M50" s="11">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="N50" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O50" s="11">
+        <f t="shared" si="9"/>
+        <v>45.5648695652174</v>
+      </c>
+      <c r="P50" s="11">
+        <f t="shared" si="10"/>
+        <v>2.7341869905972471</v>
+      </c>
+      <c r="Q50" s="34">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="R50" s="11">
+        <f t="shared" si="12"/>
+        <v>15.210000000000003</v>
+      </c>
+      <c r="S50" s="15">
+        <f t="shared" si="13"/>
+        <v>4.99286320022106E-2</v>
+      </c>
+      <c r="T50" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="31" t="s">
+        <v>452</v>
+      </c>
+      <c r="B51" s="20">
+        <v>18</v>
+      </c>
+      <c r="C51" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="D51" s="9">
+        <v>2.96</v>
+      </c>
+      <c r="E51" s="21">
+        <v>40</v>
+      </c>
+      <c r="F51" s="21">
+        <v>60</v>
+      </c>
+      <c r="G51" s="11">
+        <f t="shared" si="1"/>
+        <v>24.423724423724423</v>
+      </c>
+      <c r="H51" s="11">
+        <f t="shared" si="2"/>
+        <v>27.69230769230769</v>
+      </c>
+      <c r="I51" s="34">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="J51" s="8" t="str">
+        <f t="shared" si="4"/>
+        <v>нет</v>
+      </c>
+      <c r="K51" s="23">
+        <f t="shared" si="5"/>
+        <v>12.208695652173915</v>
+      </c>
+      <c r="L51" s="11">
+        <f t="shared" si="6"/>
+        <v>15.382956521739132</v>
+      </c>
+      <c r="M51" s="11">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="N51" s="11">
+        <f t="shared" si="8"/>
+        <v>10</v>
+      </c>
+      <c r="O51" s="11">
+        <f t="shared" si="9"/>
+        <v>44.282956521739131</v>
+      </c>
+      <c r="P51" s="11">
+        <f t="shared" si="10"/>
+        <v>2.8787025731470175</v>
+      </c>
+      <c r="Q51" s="34">
+        <f t="shared" si="11"/>
+        <v>3</v>
+      </c>
+      <c r="R51" s="11">
+        <f t="shared" si="12"/>
+        <v>14.040000000000003</v>
+      </c>
+      <c r="S51" s="15">
+        <f t="shared" si="13"/>
+        <v>5.2567612205293351E-2</v>
+      </c>
+      <c r="T51" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A53" s="47" t="s">
+        <v>453</v>
+      </c>
+      <c r="B53" s="40"/>
+      <c r="C53" s="14" t="str">
+        <f>INDEX($A$34:$A$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
+        <v>КамАЗ-55111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="39" t="s">
+        <v>454</v>
+      </c>
+      <c r="B54" s="40"/>
+      <c r="C54" s="34">
+        <f>INDEX($I$34:$I$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="39" t="s">
+        <v>455</v>
+      </c>
+      <c r="B55" s="40"/>
+      <c r="C55" s="34">
+        <f>INDEX($Q$34:$Q$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A56" s="39" t="s">
+        <v>456</v>
+      </c>
+      <c r="B56" s="40"/>
+      <c r="C56" s="15">
+        <f>INDEX($S$34:$S$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
+        <v>8.8942040246388063E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -4747,19 +8190,19 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -5410,65 +8853,65 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="16">
         <f>B21+F21</f>
         <v>150000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
       <c r="F31" s="16">
         <f>D21+F25</f>
         <v>20209.474960755029</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="16">
         <f>H21+F26</f>
         <v>33543.964226867858</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
       <c r="F33" s="16">
         <f>F32/'Исходные данные'!$B$4</f>
         <v>32253.811756603707</v>
@@ -5535,13 +8978,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -5550,13 +8993,13 @@
       <c r="B6" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <v>2.4</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -5565,13 +9008,13 @@
       <c r="B7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <v>0.4</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -5580,13 +9023,13 @@
       <c r="B8" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <v>0.15</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -5595,13 +9038,13 @@
       <c r="B9" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <v>0.1</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -5610,13 +9053,13 @@
       <c r="B10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <v>0.2</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>116</v>
       </c>
     </row>
@@ -5627,13 +9070,13 @@
       <c r="B11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <v>0.4</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -5642,13 +9085,13 @@
         <v>120</v>
       </c>
       <c r="B12" s="8"/>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <v>0.5</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>121</v>
       </c>
     </row>
@@ -5657,13 +9100,13 @@
         <v>122</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>123</v>
       </c>
     </row>
@@ -5672,13 +9115,13 @@
         <v>124</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="17">
+      <c r="C14" s="18">
         <v>0.5</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>121</v>
       </c>
     </row>
@@ -5687,78 +9130,78 @@
         <v>125</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>60</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>30</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>42</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>12</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="18"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B19" s="8"/>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>200</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <v>100</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="18"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -5767,14 +9210,14 @@
       <c r="B21" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <f>$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
         <v>220</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="18"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -5783,37 +9226,37 @@
       <c r="B22" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>$C$20+'Исходные данные'!$B$3/2-$C$16/2</f>
         <v>135</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="18"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>$C$11/2</f>
         <v>0.2</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -5822,42 +9265,42 @@
       <c r="B25" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>$C$24+$C$12</f>
         <v>0.7</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="18"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B26" s="8"/>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>$C$25+$C$13</f>
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="18"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <f>$C$26+$C$14</f>
         <v>1.4</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="18"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -5866,25 +9309,25 @@
       <c r="B28" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <f>$C$27-$C$25</f>
         <v>0.7</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="19" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
     </row>
     <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -5898,7 +9341,7 @@
         <v>0.67</v>
       </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="19" t="s">
         <v>147</v>
       </c>
     </row>
@@ -5907,14 +9350,14 @@
         <v>148</v>
       </c>
       <c r="B31" s="8"/>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>$C$27+$C$6*$C$30</f>
         <v>3.008</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="18"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -5930,7 +9373,7 @@
       <c r="D32" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5939,12 +9382,12 @@
         <v>152</v>
       </c>
       <c r="B33" s="8"/>
-      <c r="C33" s="22" t="str">
+      <c r="C33" s="23" t="str">
         <f>IF($C$32&gt;0,"насыпи","выемки")</f>
         <v>насыпи</v>
       </c>
       <c r="D33" s="8"/>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="19" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5962,7 +9405,7 @@
       <c r="D34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="19" t="s">
         <v>156</v>
       </c>
     </row>
@@ -5980,18 +9423,18 @@
       <c r="D35" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="19" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
@@ -6005,7 +9448,7 @@
         <v>0.67</v>
       </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="19" t="s">
         <v>162</v>
       </c>
     </row>
@@ -6023,7 +9466,7 @@
       <c r="D38" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="19" t="s">
         <v>165</v>
       </c>
     </row>
@@ -6032,28 +9475,28 @@
         <v>166</v>
       </c>
       <c r="B39" s="8"/>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <f>$C$15+2*$C$27</f>
         <v>62.8</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="18"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B40" s="8"/>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <f>$C$16+2*$C$27</f>
         <v>32.799999999999997</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E40" s="18"/>
+      <c r="E40" s="19"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
@@ -6069,7 +9512,7 @@
       <c r="D41" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="19" t="s">
         <v>171</v>
       </c>
     </row>
@@ -6078,28 +9521,28 @@
         <v>172</v>
       </c>
       <c r="B42" s="8"/>
-      <c r="C42" s="22">
+      <c r="C42" s="23">
         <f>$C$39+2*$C$38</f>
         <v>65.526899999999998</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="18"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B43" s="8"/>
-      <c r="C43" s="22">
+      <c r="C43" s="23">
         <f>$C$40+2*$C$38</f>
         <v>35.526899999999998</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E43" s="18"/>
+      <c r="E43" s="19"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
@@ -6115,7 +9558,7 @@
       <c r="D44" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E44" s="18"/>
+      <c r="E44" s="19"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
@@ -6131,7 +9574,7 @@
       <c r="D45" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E45" s="18"/>
+      <c r="E45" s="19"/>
     </row>
     <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
@@ -6147,7 +9590,7 @@
       <c r="D46" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E46" s="18"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
@@ -6163,16 +9606,16 @@
       <c r="D47" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="18"/>
+      <c r="E47" s="19"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="33" t="s">
+      <c r="A48" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
@@ -6181,13 +9624,13 @@
       <c r="B49" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C49" s="20">
         <v>3</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>185</v>
       </c>
     </row>
@@ -6202,7 +9645,7 @@
         <v>0.1</v>
       </c>
       <c r="D50" s="8"/>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>188</v>
       </c>
     </row>
@@ -6218,7 +9661,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="8"/>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>190</v>
       </c>
     </row>
@@ -6227,14 +9670,14 @@
         <v>191</v>
       </c>
       <c r="B52" s="8"/>
-      <c r="C52" s="22">
+      <c r="C52" s="23">
         <f>$C$35*$C$51</f>
         <v>20.349999999999998</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="18"/>
+      <c r="E52" s="19"/>
     </row>
     <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
@@ -6250,18 +9693,18 @@
       <c r="D53" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="19" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
@@ -6275,7 +9718,7 @@
       <c r="D55" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="19" t="s">
         <v>198</v>
       </c>
     </row>
@@ -6293,7 +9736,7 @@
       <c r="D56" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E56" s="18"/>
+      <c r="E56" s="19"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -6309,7 +9752,7 @@
       <c r="D57" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="19" t="s">
         <v>203</v>
       </c>
     </row>
@@ -6327,7 +9770,7 @@
       <c r="D58" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="19" t="s">
         <v>206</v>
       </c>
     </row>
@@ -6344,7 +9787,7 @@
       <c r="D59" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="19" t="s">
         <v>209</v>
       </c>
     </row>
@@ -6361,7 +9804,7 @@
       <c r="D60" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="19" t="s">
         <v>212</v>
       </c>
     </row>
@@ -6379,7 +9822,7 @@
       <c r="D61" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="19" t="s">
         <v>215</v>
       </c>
     </row>
@@ -6388,14 +9831,14 @@
         <v>216</v>
       </c>
       <c r="B62" s="8"/>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <f>$C$35-$C$7-$C$8-$C$9</f>
         <v>1.3849999999999998</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="19" t="s">
         <v>217</v>
       </c>
     </row>
@@ -6413,7 +9856,7 @@
       <c r="D63" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E63" s="18"/>
+      <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
@@ -6429,7 +9872,7 @@
       <c r="D64" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E64" s="19" t="s">
         <v>222</v>
       </c>
     </row>
@@ -6447,7 +9890,7 @@
       <c r="D65" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="19" t="s">
         <v>225</v>
       </c>
     </row>
@@ -6486,19 +9929,19 @@
       <c r="A69" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="22">
+      <c r="B69" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="23">
         <f t="shared" ref="D69:D74" si="0">$C$21+B69</f>
         <v>216.99199999999999</v>
       </c>
-      <c r="E69" s="22">
+      <c r="E69" s="23">
         <f t="shared" ref="E69:E74" si="1">$C$22+C69</f>
         <v>131.99199999999999</v>
       </c>
@@ -6519,19 +9962,19 @@
       <c r="A70" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="23">
         <f>$C$15-$C$17+$C$31</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E70" s="22">
+      <c r="E70" s="23">
         <f t="shared" si="1"/>
         <v>131.99199999999999</v>
       </c>
@@ -6552,19 +9995,19 @@
       <c r="A71" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="23">
         <f>$C$15-$C$17+$C$31</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="23">
         <f>$C$18-$C$31</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E71" s="22">
+      <c r="E71" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
@@ -6585,19 +10028,19 @@
       <c r="A72" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="23">
         <f>$C$15+$C$31</f>
         <v>63.008000000000003</v>
       </c>
-      <c r="C72" s="22">
+      <c r="C72" s="23">
         <f>$C$18-$C$31</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D72" s="22">
+      <c r="D72" s="23">
         <f t="shared" si="0"/>
         <v>283.00799999999998</v>
       </c>
-      <c r="E72" s="22">
+      <c r="E72" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
@@ -6618,19 +10061,19 @@
       <c r="A73" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="23">
         <f>$C$15+$C$31</f>
         <v>63.008000000000003</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="23">
         <f>$C$16+$C$31</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="23">
         <f t="shared" si="0"/>
         <v>283.00799999999998</v>
       </c>
-      <c r="E73" s="22">
+      <c r="E73" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
@@ -6651,19 +10094,19 @@
       <c r="A74" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="23">
         <f>$C$16+$C$31</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D74" s="23">
         <f t="shared" si="0"/>
         <v>216.99199999999999</v>
       </c>
-      <c r="E74" s="22">
+      <c r="E74" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
@@ -6681,7 +10124,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="24" t="s">
         <v>234</v>
       </c>
     </row>
@@ -6746,11 +10189,11 @@
       <c r="B5" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="25">
         <f>Объёмы!$F$31</f>
         <v>20209.474960755029</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <f>Объёмы!$F$32</f>
         <v>33543.964226867858</v>
       </c>
@@ -6766,11 +10209,11 @@
       <c r="B6" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="25">
         <f>Котлован!$C$56</f>
         <v>3516.2808819851589</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="25">
         <f>Котлован!$C$65</f>
         <v>726.88528198515951</v>
       </c>
@@ -6781,7 +10224,7 @@
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="26" t="s">
         <v>244</v>
       </c>
       <c r="C7" s="16">
@@ -6799,67 +10242,67 @@
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="34">
+      <c r="C8" s="43">
         <f>C7-E7</f>
         <v>-9226.9840696184765</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="26">
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="27">
         <f>ABS(C8)/MAX(C7,E7)</f>
         <v>0.28000658197644951</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="39" t="s">
         <v>247</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
       <c r="D11" s="14" t="str">
         <f>IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
         <v>не хватает грунта — нужен перерасчёт Нср (Δh)</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="B12" s="31"/>
-      <c r="C12" s="31"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
       <c r="D12" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF(Котлован!$C$33="насыпи",Котлован!$C$44,0)</f>
         <v>148176.03237639001</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="27">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="28">
         <f>C8/D12</f>
         <v>-6.227042202196717E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="39" t="s">
         <v>250</v>
       </c>
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="28">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="29">
         <f>ROUND(D13,4)</f>
         <v>-6.2300000000000001E-2</v>
       </c>
@@ -6926,7 +10369,7 @@
       <c r="A9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="25">
         <f>'Исходные данные'!$B$9</f>
         <v>-0.25</v>
       </c>
@@ -6961,7 +10404,7 @@
       <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="25">
         <f>'Исходные данные'!$B$10</f>
         <v>0.15</v>
       </c>
@@ -7002,7 +10445,7 @@
       <c r="A11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="25">
         <f>'Исходные данные'!$B$11</f>
         <v>0.34</v>
       </c>
@@ -7037,7 +10480,7 @@
       <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B12" s="25">
         <f>'Исходные данные'!$B$12</f>
         <v>0.47</v>
       </c>
@@ -7078,7 +10521,7 @@
       <c r="A13" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="25">
         <f>'Исходные данные'!$B$13</f>
         <v>0.66</v>
       </c>
@@ -7113,7 +10556,7 @@
       <c r="A14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="25">
         <f>'Исходные данные'!$B$14</f>
         <v>0.85</v>
       </c>
@@ -7154,7 +10597,7 @@
       <c r="A15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="25">
         <f>'Исходные данные'!$B$15</f>
         <v>-0.49</v>
       </c>
@@ -7189,7 +10632,7 @@
       <c r="A16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="25">
         <f>'Исходные данные'!$B$16</f>
         <v>-0.31</v>
       </c>
@@ -7230,7 +10673,7 @@
       <c r="A17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="25">
         <f>'Исходные данные'!$B$17</f>
         <v>0.28000000000000003</v>
       </c>
@@ -7247,7 +10690,7 @@
       <c r="A18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="25">
         <f>'Исходные данные'!$B$18</f>
         <v>0.52</v>
       </c>
@@ -7264,7 +10707,7 @@
       <c r="A19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B19" s="25">
         <f>'Исходные данные'!$B$19</f>
         <v>0.84</v>
       </c>
@@ -7281,7 +10724,7 @@
       <c r="A20" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="25">
         <f>'Исходные данные'!$B$20</f>
         <v>0.47</v>
       </c>
@@ -7298,7 +10741,7 @@
       <c r="A21" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B21" s="25">
         <f>'Исходные данные'!$B$21</f>
         <v>-0.24</v>
       </c>
@@ -7315,7 +10758,7 @@
       <c r="A22" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="25">
         <f>'Исходные данные'!$B$22</f>
         <v>-0.43</v>
       </c>
@@ -7332,7 +10775,7 @@
       <c r="A23" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B23" s="25">
         <f>'Исходные данные'!$B$23</f>
         <v>-0.28000000000000003</v>
       </c>
@@ -7349,7 +10792,7 @@
       <c r="A24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="25">
         <f>'Исходные данные'!$B$24</f>
         <v>0.14000000000000001</v>
       </c>
@@ -7366,7 +10809,7 @@
       <c r="A25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="25">
         <f>'Исходные данные'!$B$25</f>
         <v>0.36</v>
       </c>
@@ -7383,7 +10826,7 @@
       <c r="A26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B26" s="25">
         <f>'Исходные данные'!$B$26</f>
         <v>0.76</v>
       </c>
@@ -7400,7 +10843,7 @@
       <c r="A27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B27" s="25">
         <f>'Исходные данные'!$B$27</f>
         <v>-0.4</v>
       </c>
@@ -7417,7 +10860,7 @@
       <c r="A28" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="25">
         <f>'Исходные данные'!$B$28</f>
         <v>-0.65</v>
       </c>
@@ -7434,7 +10877,7 @@
       <c r="A29" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B29" s="25">
         <f>'Исходные данные'!$B$29</f>
         <v>-0.52</v>
       </c>
@@ -7451,7 +10894,7 @@
       <c r="A30" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B30" s="25">
         <f>'Исходные данные'!$B$30</f>
         <v>-0.28000000000000003</v>
       </c>
@@ -7468,7 +10911,7 @@
       <c r="A31" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="25">
         <f>'Исходные данные'!$B$31</f>
         <v>-0.43</v>
       </c>
@@ -7485,7 +10928,7 @@
       <c r="A32" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B32" s="25">
         <f>'Исходные данные'!$B$32</f>
         <v>0.14000000000000001</v>
       </c>
@@ -7833,19 +11276,19 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="32" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -8496,65 +11939,65 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
       <c r="F29" s="16">
         <f>B21+F21</f>
         <v>150000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
       <c r="F30" s="16">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
       <c r="F31" s="16">
         <f>D21+F25</f>
         <v>24264.140842973826</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="16">
         <f>H21+F26</f>
         <v>28820.342480142914</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="40"/>
       <c r="F33" s="16">
         <f>F32/'Исходные данные'!$B$4</f>
         <v>27711.867769368186</v>
@@ -8621,13 +12064,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
+      <c r="B5" s="40"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
     </row>
     <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -8636,13 +12079,13 @@
       <c r="B6" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="18">
         <v>2.4</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E6" s="18"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -8651,13 +12094,13 @@
       <c r="B7" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <v>0.4</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="18"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
@@ -8666,13 +12109,13 @@
       <c r="B8" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <v>0.15</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="18"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
@@ -8681,13 +12124,13 @@
       <c r="B9" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <v>0.1</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E9" s="18"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
@@ -8696,13 +12139,13 @@
       <c r="B10" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="18">
         <v>0.2</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>116</v>
       </c>
     </row>
@@ -8713,13 +12156,13 @@
       <c r="B11" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="18">
         <v>0.4</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>119</v>
       </c>
     </row>
@@ -8728,13 +12171,13 @@
         <v>120</v>
       </c>
       <c r="B12" s="8"/>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <v>0.5</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8743,13 +12186,13 @@
         <v>122</v>
       </c>
       <c r="B13" s="8"/>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <v>0.2</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>123</v>
       </c>
     </row>
@@ -8758,13 +12201,13 @@
         <v>124</v>
       </c>
       <c r="B14" s="8"/>
-      <c r="C14" s="17">
+      <c r="C14" s="18">
         <v>0.5</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8773,78 +12216,78 @@
         <v>125</v>
       </c>
       <c r="B15" s="8"/>
-      <c r="C15" s="19">
+      <c r="C15" s="20">
         <v>60</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>126</v>
       </c>
       <c r="B16" s="8"/>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <v>30</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E16" s="18"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>127</v>
       </c>
       <c r="B17" s="8"/>
-      <c r="C17" s="19">
+      <c r="C17" s="20">
         <v>42</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="18"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>128</v>
       </c>
       <c r="B18" s="8"/>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <v>12</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E18" s="18"/>
+      <c r="E18" s="19"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B19" s="8"/>
-      <c r="C19" s="20">
+      <c r="C19" s="21">
         <v>200</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E19" s="18"/>
+      <c r="E19" s="19"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>130</v>
       </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="20">
+      <c r="C20" s="21">
         <v>100</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E20" s="18"/>
+      <c r="E20" s="19"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -8853,14 +12296,14 @@
       <c r="B21" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="22">
         <f>$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
         <v>220</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="18"/>
+      <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -8869,37 +12312,37 @@
       <c r="B22" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="22">
         <f>$C$20+'Исходные данные'!$B$3/2-$C$16/2</f>
         <v>135</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E22" s="18"/>
+      <c r="E22" s="19"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="31"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>136</v>
       </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>$C$11/2</f>
         <v>0.2</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="19"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -8908,42 +12351,42 @@
       <c r="B25" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="22">
+      <c r="C25" s="23">
         <f>$C$24+$C$12</f>
         <v>0.7</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E25" s="18"/>
+      <c r="E25" s="19"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>139</v>
       </c>
       <c r="B26" s="8"/>
-      <c r="C26" s="22">
+      <c r="C26" s="23">
         <f>$C$25+$C$13</f>
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="18"/>
+      <c r="E26" s="19"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>140</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="22">
+      <c r="C27" s="23">
         <f>$C$26+$C$14</f>
         <v>1.4</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="18"/>
+      <c r="E27" s="19"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -8952,25 +12395,25 @@
       <c r="B28" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <f>$C$27-$C$25</f>
         <v>0.7</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="19" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="42" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
     </row>
     <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -8984,7 +12427,7 @@
         <v>0.67</v>
       </c>
       <c r="D30" s="8"/>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="19" t="s">
         <v>147</v>
       </c>
     </row>
@@ -8993,14 +12436,14 @@
         <v>148</v>
       </c>
       <c r="B31" s="8"/>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <f>$C$27+$C$6*$C$30</f>
         <v>3.008</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="18"/>
+      <c r="E31" s="19"/>
     </row>
     <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -9016,7 +12459,7 @@
       <c r="D32" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>151</v>
       </c>
     </row>
@@ -9025,12 +12468,12 @@
         <v>152</v>
       </c>
       <c r="B33" s="8"/>
-      <c r="C33" s="22" t="str">
+      <c r="C33" s="23" t="str">
         <f>IF($C$32&gt;0,"насыпи","выемки")</f>
         <v>насыпи</v>
       </c>
       <c r="D33" s="8"/>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="19" t="s">
         <v>153</v>
       </c>
     </row>
@@ -9048,7 +12491,7 @@
       <c r="D34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="19" t="s">
         <v>156</v>
       </c>
     </row>
@@ -9066,18 +12509,18 @@
       <c r="D35" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="18" t="s">
+      <c r="E35" s="19" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="42" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="31"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
+      <c r="B36" s="40"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
@@ -9091,7 +12534,7 @@
         <v>0.67</v>
       </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="19" t="s">
         <v>162</v>
       </c>
     </row>
@@ -9109,7 +12552,7 @@
       <c r="D38" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="19" t="s">
         <v>165</v>
       </c>
     </row>
@@ -9118,28 +12561,28 @@
         <v>166</v>
       </c>
       <c r="B39" s="8"/>
-      <c r="C39" s="22">
+      <c r="C39" s="23">
         <f>$C$15+2*$C$27</f>
         <v>62.8</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="18"/>
+      <c r="E39" s="19"/>
     </row>
     <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>167</v>
       </c>
       <c r="B40" s="8"/>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <f>$C$16+2*$C$27</f>
         <v>32.799999999999997</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E40" s="18"/>
+      <c r="E40" s="19"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
@@ -9155,7 +12598,7 @@
       <c r="D41" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="19" t="s">
         <v>171</v>
       </c>
     </row>
@@ -9164,28 +12607,28 @@
         <v>172</v>
       </c>
       <c r="B42" s="8"/>
-      <c r="C42" s="22">
+      <c r="C42" s="23">
         <f>$C$39+2*$C$38</f>
         <v>65.610382000000001</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E42" s="18"/>
+      <c r="E42" s="19"/>
     </row>
     <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B43" s="8"/>
-      <c r="C43" s="22">
+      <c r="C43" s="23">
         <f>$C$40+2*$C$38</f>
         <v>35.610381999999994</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E43" s="18"/>
+      <c r="E43" s="19"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
@@ -9201,7 +12644,7 @@
       <c r="D44" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E44" s="18"/>
+      <c r="E44" s="19"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
@@ -9217,7 +12660,7 @@
       <c r="D45" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E45" s="18"/>
+      <c r="E45" s="19"/>
     </row>
     <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
@@ -9233,7 +12676,7 @@
       <c r="D46" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E46" s="18"/>
+      <c r="E46" s="19"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
@@ -9249,16 +12692,16 @@
       <c r="D47" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E47" s="18"/>
+      <c r="E47" s="19"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="33" t="s">
+      <c r="A48" s="42" t="s">
         <v>182</v>
       </c>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
-      <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
+      <c r="B48" s="40"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="40"/>
+      <c r="E48" s="40"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
@@ -9267,13 +12710,13 @@
       <c r="B49" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C49" s="19">
+      <c r="C49" s="20">
         <v>3</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="19" t="s">
         <v>185</v>
       </c>
     </row>
@@ -9288,7 +12731,7 @@
         <v>0.1</v>
       </c>
       <c r="D50" s="8"/>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="19" t="s">
         <v>188</v>
       </c>
     </row>
@@ -9304,7 +12747,7 @@
         <v>10</v>
       </c>
       <c r="D51" s="8"/>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="19" t="s">
         <v>190</v>
       </c>
     </row>
@@ -9313,14 +12756,14 @@
         <v>191</v>
       </c>
       <c r="B52" s="8"/>
-      <c r="C52" s="22">
+      <c r="C52" s="23">
         <f>$C$35*$C$51</f>
         <v>20.972999999999999</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="18"/>
+      <c r="E52" s="19"/>
     </row>
     <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
@@ -9336,18 +12779,18 @@
       <c r="D53" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E53" s="18" t="s">
+      <c r="E53" s="19" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="33" t="s">
+      <c r="A54" s="42" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="31"/>
-      <c r="C54" s="31"/>
-      <c r="D54" s="31"/>
-      <c r="E54" s="31"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
@@ -9361,7 +12804,7 @@
       <c r="D55" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E55" s="18" t="s">
+      <c r="E55" s="19" t="s">
         <v>198</v>
       </c>
     </row>
@@ -9379,7 +12822,7 @@
       <c r="D56" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E56" s="18"/>
+      <c r="E56" s="19"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
@@ -9395,7 +12838,7 @@
       <c r="D57" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E57" s="18" t="s">
+      <c r="E57" s="19" t="s">
         <v>203</v>
       </c>
     </row>
@@ -9413,7 +12856,7 @@
       <c r="D58" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E58" s="18" t="s">
+      <c r="E58" s="19" t="s">
         <v>206</v>
       </c>
     </row>
@@ -9430,7 +12873,7 @@
       <c r="D59" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="19" t="s">
         <v>209</v>
       </c>
     </row>
@@ -9447,7 +12890,7 @@
       <c r="D60" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E60" s="18" t="s">
+      <c r="E60" s="19" t="s">
         <v>212</v>
       </c>
     </row>
@@ -9465,7 +12908,7 @@
       <c r="D61" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E61" s="19" t="s">
         <v>215</v>
       </c>
     </row>
@@ -9474,14 +12917,14 @@
         <v>216</v>
       </c>
       <c r="B62" s="8"/>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <f>$C$35-$C$7-$C$8-$C$9</f>
         <v>1.4472999999999998</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E62" s="18" t="s">
+      <c r="E62" s="19" t="s">
         <v>217</v>
       </c>
     </row>
@@ -9499,7 +12942,7 @@
       <c r="D63" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E63" s="18"/>
+      <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
@@ -9515,7 +12958,7 @@
       <c r="D64" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E64" s="18" t="s">
+      <c r="E64" s="19" t="s">
         <v>222</v>
       </c>
     </row>
@@ -9533,7 +12976,7 @@
       <c r="D65" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="19" t="s">
         <v>225</v>
       </c>
     </row>
@@ -9572,19 +13015,19 @@
       <c r="A69" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="22">
+      <c r="B69" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="C69" s="22">
+      <c r="C69" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="D69" s="22">
+      <c r="D69" s="23">
         <f t="shared" ref="D69:D74" si="0">$C$21+B69</f>
         <v>216.99199999999999</v>
       </c>
-      <c r="E69" s="22">
+      <c r="E69" s="23">
         <f t="shared" ref="E69:E74" si="1">$C$22+C69</f>
         <v>131.99199999999999</v>
       </c>
@@ -9605,19 +13048,19 @@
       <c r="A70" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="22">
+      <c r="B70" s="23">
         <f>$C$15-$C$17+$C$31</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C70" s="22">
+      <c r="C70" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E70" s="22">
+      <c r="E70" s="23">
         <f t="shared" si="1"/>
         <v>131.99199999999999</v>
       </c>
@@ -9638,19 +13081,19 @@
       <c r="A71" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="22">
+      <c r="B71" s="23">
         <f>$C$15-$C$17+$C$31</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C71" s="22">
+      <c r="C71" s="23">
         <f>$C$18-$C$31</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E71" s="22">
+      <c r="E71" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
@@ -9671,19 +13114,19 @@
       <c r="A72" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="22">
+      <c r="B72" s="23">
         <f>$C$15+$C$31</f>
         <v>63.008000000000003</v>
       </c>
-      <c r="C72" s="22">
+      <c r="C72" s="23">
         <f>$C$18-$C$31</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D72" s="22">
+      <c r="D72" s="23">
         <f t="shared" si="0"/>
         <v>283.00799999999998</v>
       </c>
-      <c r="E72" s="22">
+      <c r="E72" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
@@ -9704,19 +13147,19 @@
       <c r="A73" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="22">
+      <c r="B73" s="23">
         <f>$C$15+$C$31</f>
         <v>63.008000000000003</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="23">
         <f>$C$16+$C$31</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D73" s="22">
+      <c r="D73" s="23">
         <f t="shared" si="0"/>
         <v>283.00799999999998</v>
       </c>
-      <c r="E73" s="22">
+      <c r="E73" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
@@ -9737,19 +13180,19 @@
       <c r="A74" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="22">
+      <c r="B74" s="23">
         <f>-$C$31</f>
         <v>-3.008</v>
       </c>
-      <c r="C74" s="22">
+      <c r="C74" s="23">
         <f>$C$16+$C$31</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D74" s="22">
+      <c r="D74" s="23">
         <f t="shared" si="0"/>
         <v>216.99199999999999</v>
       </c>
-      <c r="E74" s="22">
+      <c r="E74" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
@@ -9767,7 +13210,7 @@
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="23" t="s">
+      <c r="A75" s="24" t="s">
         <v>234</v>
       </c>
     </row>

--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kursovoy\.claude\worktrees\earthwork-drawings-autocad-d57f76\kursovaya-tsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CFAE6DB-BAC1-4A9F-BAD0-7E2BE1137311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33142FCA-CB7F-4962-A572-348C06BECD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -838,7 +838,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1129" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="480">
   <si>
     <t>Курсовая работа «Технологическая карта на производство земляных работ». Вариант 2</t>
   </si>
@@ -1272,6 +1272,27 @@
     <t>не менее 0,6 м</t>
   </si>
   <si>
+    <t>Радиус поворотной платформы крана</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>лекция</t>
+  </si>
+  <si>
+    <t>Со стороны съезда: от плиты до низа откоса</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>лекция: c = 1 + 2r + 1 - место для крана на дне</t>
+  </si>
+  <si>
+    <t>Ось → низ откоса со стороны съезда (правая)</t>
+  </si>
+  <si>
     <t>Положение котлована относительно ЛНР</t>
   </si>
   <si>
@@ -1287,6 +1308,9 @@
     <t>Ось → бровка (предварительно)</t>
   </si>
   <si>
+    <t>Ось → бровка со стороны съезда (предварительно)</t>
+  </si>
+  <si>
     <t>Среднее рабочих отметок по углам котлована</t>
   </si>
   <si>
@@ -1353,7 +1377,7 @@
     <t>м²</t>
   </si>
   <si>
-    <t>Г-образный контур: L·B − вырез 42 × 12</t>
+    <t>L·B − вырез (42 − d + dс) × 12</t>
   </si>
   <si>
     <t>Верх котлована: длина</t>
@@ -1386,46 +1410,49 @@
     <t>Fб.п</t>
   </si>
   <si>
-    <t>Пандус (принято: однополосный въезд автосамосвалов)</t>
-  </si>
-  <si>
-    <t>Ширина пандуса</t>
+    <t>Съезд (пандус): один, двусторонний проезд</t>
+  </si>
+  <si>
+    <t>Ширина съезда</t>
   </si>
   <si>
     <t>bп</t>
   </si>
   <si>
-    <t>3 м — один проезд, 6 м — два</t>
-  </si>
-  <si>
-    <t>Уклон пандуса</t>
+    <t>методичка: 6 м — двусторонний; лекция: один съезд — 6 м</t>
+  </si>
+  <si>
+    <t>Уклон съезда</t>
   </si>
   <si>
     <t>i</t>
   </si>
   <si>
-    <t>0,10–0,15 при вывозе самосвалами</t>
-  </si>
-  <si>
-    <t>Коэффициент заложения пандуса</t>
-  </si>
-  <si>
-    <t>n = 1 / i</t>
-  </si>
-  <si>
-    <t>Длина пандуса в плане</t>
-  </si>
-  <si>
-    <t>Объём пандуса</t>
-  </si>
-  <si>
-    <t>Vпан</t>
+    <t>методичка 0,10–0,15; лекция m' = 8…15</t>
+  </si>
+  <si>
+    <t>Коэффициент заложения съезда</t>
+  </si>
+  <si>
+    <t>m'</t>
+  </si>
+  <si>
+    <t>m' = 1 / i</t>
+  </si>
+  <si>
+    <t>Длина съезда в плане (от низа откоса)</t>
+  </si>
+  <si>
+    <t>Объём съезда сверх откоса котлована</t>
+  </si>
+  <si>
+    <t>Vс</t>
   </si>
   <si>
     <t>м³</t>
   </si>
   <si>
-    <t>n·(bп·hк²/2 + m·hк³/3)</t>
+    <t>лекция: hк²/6·(3bп + 2m·hк·(m' − m)/m')·(m' − m)</t>
   </si>
   <si>
     <t>Объёмы</t>
@@ -1437,7 +1464,7 @@
     <t>hк/3·(Fк.н + Fк.в + √(Fк.н·Fк.в))</t>
   </si>
   <si>
-    <t>Объём котлована</t>
+    <t>Объём котлована со съездом</t>
   </si>
   <si>
     <t>Vк</t>
@@ -1509,13 +1536,25 @@
     <t>Vф.п + Vк.с.п</t>
   </si>
   <si>
-    <t>Обратная засыпка</t>
+    <t>Засыпка пазух — привозной песок</t>
+  </si>
+  <si>
+    <t>Vп.с</t>
+  </si>
+  <si>
+    <t>котлован без съезда − Vп.ч − Vподс − Vб.п − Vг.и − Vст</t>
+  </si>
+  <si>
+    <t>Засыпка съезда — местный грунт</t>
+  </si>
+  <si>
+    <t>Обратная засыпка всего</t>
   </si>
   <si>
     <t>Vо.з</t>
   </si>
   <si>
-    <t>Vк − Vп.ч − Vподс − Vб.п − Vг.и − Vст</t>
+    <t>Vк − Vп.ч − Vподс − Vб.п − Vг.и − Vст (с. 14)</t>
   </si>
   <si>
     <t>Рабочие отметки по углам котлована (бровка при Нк), билинейная интерполяция в квадрате 8</t>
@@ -1569,7 +1608,7 @@
     <t>В призмах (планировка с откосами)</t>
   </si>
   <si>
-    <t>В котловане (Vк; обратная засыпка Vо.з)</t>
+    <t>В котловане (Vк; засыпка съезда Vс — пазухи засыпаются привозным песком)</t>
   </si>
   <si>
     <t>Суммарные объёмы</t>
@@ -1620,61 +1659,91 @@
     <t>По окончательным отметкам — после поправки Δh</t>
   </si>
   <si>
-    <t>Ведомость объёмов грунта в котловане (табл. 3 методички), по окончательным отметкам</t>
-  </si>
-  <si>
-    <t>Баланс отрицательный - лишнего грунта нет (Vлиш.гр = 0), недостача восполняется из карьера.</t>
-  </si>
-  <si>
-    <t>Место разработки / назначение</t>
-  </si>
-  <si>
-    <t>V в плотном теле, м³</t>
-  </si>
-  <si>
-    <t>V с kр, м³</t>
-  </si>
-  <si>
-    <t>Место укладки</t>
-  </si>
-  <si>
-    <t>V с kо.р, м³</t>
-  </si>
-  <si>
-    <t>Котлован: разрабатываемый грунт</t>
+    <t>Баланс земляных работ по котловану (табл. 3; форма - с доски), по окончательным отметкам</t>
+  </si>
+  <si>
+    <t>Пазухи засыпаются привозным песком (грунт площадки - супесь, не песок). В отвал у котлована - только грунт для засыпки съезда; остальной грунт котлована - в транспортные средства: в насыпь планировки, излишек - на вывоз (с. 16).</t>
+  </si>
+  <si>
+    <t>Выемка</t>
   </si>
   <si>
     <t>Насыпь</t>
   </si>
   <si>
-    <t>Вывоз</t>
-  </si>
-  <si>
-    <t>Отвал</t>
-  </si>
-  <si>
-    <t>Карьер: щебень для подсыпки</t>
-  </si>
-  <si>
-    <t>Котлован: подсыпка</t>
-  </si>
-  <si>
-    <t>Отвал: грунт обратной засыпки</t>
-  </si>
-  <si>
-    <t>Vлиш.гр - лишний грунт, м³ (баланс отрицательный)</t>
+    <t>№ п/п</t>
+  </si>
+  <si>
+    <t>Место разработки грунта</t>
+  </si>
+  <si>
+    <t>Объём разработки грунта, м³ (плотное тело)</t>
+  </si>
+  <si>
+    <t>Место укладки грунта и его объём, м³ (с kр)</t>
+  </si>
+  <si>
+    <t>Место устройства насыпи</t>
+  </si>
+  <si>
+    <t>Геометрический объём насыпи, м³</t>
+  </si>
+  <si>
+    <t>Потребный объём грунта V / kо.р, м³</t>
+  </si>
+  <si>
+    <t>Котлован</t>
+  </si>
+  <si>
+    <t>Отвал (засыпка съезда)</t>
+  </si>
+  <si>
+    <t>Пазухи сооружения - песок из карьера</t>
+  </si>
+  <si>
+    <t>Съезд</t>
+  </si>
+  <si>
+    <t>Транспортные средства</t>
+  </si>
+  <si>
+    <t>Съезд - грунт котлована из отвала</t>
+  </si>
+  <si>
+    <t>ΣVв</t>
+  </si>
+  <si>
+    <t>Σ (с kр)</t>
+  </si>
+  <si>
+    <t>ΣVн местного грунта (песок - привозной)</t>
+  </si>
+  <si>
+    <t>Объём грунта в отвал (засыпка съезда): ΣVн · kр, м³</t>
+  </si>
+  <si>
+    <t>В транспортные средства: (ΣVв − ΣVн) · kр, м³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   из них в насыпь планировки (табл. 4), с kр, м³</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   вывоз (лишний грунт), с kр, м³</t>
+  </si>
+  <si>
+    <t>Привозится из карьера: песок для засыпки пазух, плотное тело / с kр, м³</t>
+  </si>
+  <si>
+    <t>Привозится из карьера: щебень для подсыпки Vподс / kо.р, м³</t>
+  </si>
+  <si>
+    <t>Проверка: отвал + транспорт − ΣVв · kр (должно быть 0)</t>
   </si>
   <si>
     <t>Баланс распределения земляных масс (табл. 4 методички): из выемок и котлована в насыпь, м³</t>
   </si>
   <si>
     <t>Минимум моментов V·l (l - между центрами тяжести фигур): сначала выемки (ЗТМ), затем котлован (самосвалы); остаток - недостача, подвоз из карьера. Выемка - плотное тело, насыпь - Vн / kо.р.</t>
-  </si>
-  <si>
-    <t>Выемка</t>
-  </si>
-  <si>
-    <t>Котлован</t>
   </si>
   <si>
     <t>Недостача</t>
@@ -3225,29 +3294,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -3255,85 +3324,85 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C5" s="25">
         <f>'Объёмы (оконч.)'!$F$31</f>
-        <v>24264.140842973826</v>
+        <v>23859.416812386338</v>
       </c>
       <c r="D5" s="25">
         <f>'Объёмы (оконч.)'!$F$32</f>
-        <v>28820.342480142914</v>
+        <v>29271.722611115256</v>
       </c>
       <c r="E5" s="11">
         <f>D5/'Исходные данные'!$B$4</f>
-        <v>27711.867769368186</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+        <v>28145.887126072361</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C6" s="25">
-        <f>'Котлован (оконч.)'!$C$56</f>
-        <v>3635.720177060251</v>
+        <f>'Котлован (оконч.)'!$C$60</f>
+        <v>3970.4648798091712</v>
       </c>
       <c r="D6" s="25">
-        <f>'Котлован (оконч.)'!$C$65</f>
-        <v>763.33100906025174</v>
+        <f>'Котлован (оконч.)'!$C$70</f>
+        <v>140.18240224830623</v>
       </c>
       <c r="E6" s="11">
         <f>D6/'Исходные данные'!$B$4</f>
-        <v>733.97212409639587</v>
+        <v>134.79077139260215</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="26" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C7" s="16">
         <f>SUM(C5:C6)</f>
-        <v>27899.861020034077</v>
+        <v>27829.881692195508</v>
       </c>
       <c r="D7" s="16">
         <f>SUM(D5:D6)</f>
-        <v>29583.673489203167</v>
+        <v>29411.905013363561</v>
       </c>
       <c r="E7" s="16">
         <f>SUM(E5:E6)</f>
-        <v>28445.839893464581</v>
+        <v>28280.677897464964</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="26" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C8" s="43">
         <f>C7-E7</f>
-        <v>-545.97887343050388</v>
+        <v>-450.79620526945655</v>
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
       <c r="D10" s="27">
         <f>ABS(C8)/MAX(C7,E7)</f>
-        <v>1.9193628153547412E-2</v>
+        <v>1.5940077776914436E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
@@ -3344,35 +3413,35 @@
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
       <c r="D12" s="16">
-        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF('Котлован (оконч.)'!$C$33="насыпи",'Котлован (оконч.)'!$C$44,0)</f>
-        <v>148167.58923381407</v>
+        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF('Котлован (оконч.)'!$C$37="насыпи",'Котлован (оконч.)'!$C$48,0)</f>
+        <v>148019.72263512472</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B13" s="40"/>
       <c r="C13" s="40"/>
       <c r="D13" s="28">
         <f>C8/D12</f>
-        <v>-3.6848738395070229E-3</v>
+        <v>-3.0455144574259843E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
       <c r="D14" s="29">
         <f>ROUND(D13,4)</f>
-        <v>-3.7000000000000002E-3</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -3394,177 +3463,270 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5" s="25">
-        <f>'Котлован (оконч.)'!$C$56</f>
-        <v>3635.720177060251</v>
-      </c>
-      <c r="C5" s="11">
-        <f>B5*'Исходные данные'!$B$7</f>
-        <v>4181.0782036192886</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E5" s="11">
-        <f>('Котлован (оконч.)'!$C$56-'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4-$B$12)*'Исходные данные'!$B$7</f>
-        <v>3337.0102609084333</v>
-      </c>
-      <c r="F5" s="11">
-        <f>('Котлован (оконч.)'!$C$56-'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4-$B$12)*'Исходные данные'!$B$4</f>
-        <v>3017.8179750824092</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
+        <v>274</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="41" t="s">
+        <v>275</v>
+      </c>
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="G4" s="41" t="s">
+        <v>276</v>
+      </c>
+      <c r="H4" s="40"/>
+      <c r="I4" s="40"/>
+      <c r="J4" s="40"/>
+    </row>
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>280</v>
+      </c>
+      <c r="E5" s="40"/>
+      <c r="G5" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="25">
+        <f>'Котлован (оконч.)'!$C$59</f>
+        <v>3830.2824775608651</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="E6" s="11">
-        <f>$B$12*'Исходные данные'!$B$7</f>
+        <f>J8*'Исходные данные'!$B$7</f>
+        <v>155.00938710149245</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I6" s="25">
+        <f>'Котлован (оконч.)'!$C$69</f>
+        <v>952.91548556086548</v>
+      </c>
+      <c r="J6" s="11">
+        <f>I6/'Исходные данные'!$B$4</f>
+        <v>916.2648899623706</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>2</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C7" s="25">
+        <f>'Котлован (оконч.)'!$C$70</f>
+        <v>140.18240224830623</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="11">
+        <f>(C8-J8)*'Исходные данные'!$B$7</f>
+        <v>4411.0252246790542</v>
+      </c>
+      <c r="G7" s="8">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="I7" s="25">
+        <f>'Котлован (оконч.)'!$C$70</f>
+        <v>140.18240224830623</v>
+      </c>
+      <c r="J7" s="11">
+        <f>I7/'Исходные данные'!$B$4</f>
+        <v>134.79077139260215</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="C8" s="16">
+        <f>C6+C7</f>
+        <v>3970.4648798091712</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="16">
+        <f>E6+E7</f>
+        <v>4566.0346117805466</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="26" t="s">
+        <v>292</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="16">
+        <f>J7</f>
+        <v>134.79077139260215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="11">
+        <f>E6</f>
+        <v>155.00938710149245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="39" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="11">
+        <f>E7</f>
+        <v>4411.0252246790542</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="39" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="11">
+        <f>MIN(C8-J8,'Табл. 4 распределение'!B19-SUM('Табл. 4 распределение'!C5:L5))*'Исходные данные'!$B$7</f>
+        <v>4411.0252246790542</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="11">
+        <f>E11-E12</f>
         <v>0</v>
       </c>
-      <c r="F6" s="11">
-        <f>$B$12*'Исходные данные'!$B$4</f>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="39" t="s">
+        <v>297</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="11">
+        <f>J6</f>
+        <v>916.2648899623706</v>
+      </c>
+      <c r="F14" s="11">
+        <f>E14*'Исходные данные'!$B$7</f>
+        <v>1053.704623456726</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="11">
+        <f>'Котлован (оконч.)'!$C$61/'Исходные данные'!$B$4</f>
+        <v>162.19999999999999</v>
+      </c>
+      <c r="F15" s="11">
+        <f>E15*'Исходные данные'!$B$7</f>
+        <v>186.52999999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="39" t="s">
+        <v>299</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="11">
+        <f>E6+E7-C8*'Исходные данные'!$B$7</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E7" s="11">
-        <f>'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4*'Исходные данные'!$B$7</f>
-        <v>844.06794271085516</v>
-      </c>
-      <c r="F7" s="11">
-        <f>'Котлован (оконч.)'!$C$65</f>
-        <v>763.33100906025174</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="11">
-        <f>'Котлован (оконч.)'!$C$57/'Исходные данные'!$B$4</f>
-        <v>149.59999999999997</v>
-      </c>
-      <c r="C8" s="11">
-        <f>B8*'Исходные данные'!$B$7</f>
-        <v>172.03999999999994</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E8" s="11">
-        <f>'Котлован (оконч.)'!$C$57/'Исходные данные'!$B$4*'Исходные данные'!$B$7</f>
-        <v>172.03999999999994</v>
-      </c>
-      <c r="F8" s="11">
-        <f>'Котлован (оконч.)'!$C$57</f>
-        <v>155.58399999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B9" s="11">
-        <f>'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4</f>
-        <v>733.97212409639587</v>
-      </c>
-      <c r="C9" s="11">
-        <f>B9*'Исходные данные'!$B$7</f>
-        <v>844.06794271085516</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E9" s="11">
-        <f>'Котлован (оконч.)'!$C$65/'Исходные данные'!$B$4*'Исходные данные'!$B$7</f>
-        <v>844.06794271085516</v>
-      </c>
-      <c r="F9" s="11">
-        <f>'Котлован (оконч.)'!$C$65</f>
-        <v>763.33100906025174</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="16">
-        <f>SUM(C5:C9)</f>
-        <v>5197.1861463301439</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="16">
-        <f>SUM(E5:E9)</f>
-        <v>5197.1861463301439</v>
-      </c>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="12" spans="1:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B12" s="9">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A15:D15"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
 </worksheet>
@@ -3586,20 +3748,20 @@
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>58</v>
@@ -3632,60 +3794,60 @@
         <v>79</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="30"/>
       <c r="B5" s="6" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C5" s="9">
-        <v>2422.0969749945648</v>
+        <v>2378.929462043478</v>
       </c>
       <c r="D5" s="9">
-        <v>316.89691763080322</v>
+        <v>301.57402068287888</v>
       </c>
       <c r="E5" s="9">
-        <v>4298</v>
+        <v>4237</v>
       </c>
       <c r="F5" s="9">
-        <v>2240.6796558686442</v>
+        <v>2197.0161544067801</v>
       </c>
       <c r="G5" s="9">
-        <v>284.20527187499999</v>
+        <v>269.28028577097513</v>
       </c>
       <c r="H5" s="9">
-        <v>4923</v>
+        <v>4862</v>
       </c>
       <c r="I5" s="9">
-        <v>5323</v>
+        <v>5262</v>
       </c>
       <c r="J5" s="9">
-        <v>2490.4403474999999</v>
+        <v>2447.493545442177</v>
       </c>
       <c r="K5" s="9">
-        <v>1500.365174050633</v>
+        <v>1455.564966847498</v>
       </c>
       <c r="L5" s="9">
-        <v>441.60736718854099</v>
+        <v>425.39429982974309</v>
       </c>
       <c r="M5" s="9">
-        <v>2901.748052963856</v>
+        <v>3835.6741084165701</v>
       </c>
       <c r="N5" s="9">
-        <v>554.40313033579719</v>
+        <v>458.02557003790901</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -3700,7 +3862,7 @@
       <c r="M6" s="30"/>
       <c r="N6" s="30"/>
       <c r="O6" s="6" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -3708,10 +3870,10 @@
         <v>59</v>
       </c>
       <c r="B7" s="9">
-        <v>5.8748443857998884</v>
+        <v>7.1879674609810484</v>
       </c>
       <c r="C7" s="9">
-        <v>5.8748443857998884</v>
+        <v>7.1879674609810484</v>
       </c>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
@@ -3734,10 +3896,10 @@
         <v>61</v>
       </c>
       <c r="B8" s="9">
-        <v>835.00357548112356</v>
+        <v>870.8077510628649</v>
       </c>
       <c r="C8" s="9">
-        <v>835.00357548112356</v>
+        <v>870.8077510628649</v>
       </c>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
@@ -3760,16 +3922,16 @@
         <v>63</v>
       </c>
       <c r="B9" s="9">
-        <v>3271.1538461538462</v>
+        <v>3329.8076923076919</v>
       </c>
       <c r="C9" s="9">
-        <v>1581.218555127642</v>
+        <v>1500.9337435196319</v>
       </c>
       <c r="D9" s="9">
-        <v>316.89691763080322</v>
+        <v>301.57402068287888</v>
       </c>
       <c r="E9" s="9">
-        <v>1373.0383733954011</v>
+        <v>1527.2999281051809</v>
       </c>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
@@ -3790,19 +3952,19 @@
         <v>64</v>
       </c>
       <c r="B10" s="9">
-        <v>5386.5384615384619</v>
+        <v>5445.1923076923076</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9">
-        <v>2874.9177829292948</v>
+        <v>2655.330536948833</v>
       </c>
       <c r="F10" s="9">
-        <v>2240.6796558686442</v>
+        <v>2197.0161544067801</v>
       </c>
       <c r="G10" s="9"/>
       <c r="H10" s="9">
-        <v>270.94102274052278</v>
+        <v>592.84561633669534</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -3820,7 +3982,7 @@
         <v>65</v>
       </c>
       <c r="B11" s="9">
-        <v>6179.8076923076924</v>
+        <v>6238.4615384615381</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -3828,17 +3990,17 @@
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9">
-        <v>2723.6565090080389</v>
+        <v>1944.76186000706</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9">
-        <v>2901.748052963856</v>
+        <v>3835.6741084165701</v>
       </c>
       <c r="N11" s="9">
-        <v>554.40313033579719</v>
+        <v>458.02557003790901</v>
       </c>
       <c r="O11" s="11">
         <f t="shared" si="0"/>
@@ -3850,12 +4012,12 @@
         <v>68</v>
       </c>
       <c r="B12" s="9">
-        <v>50.043843675304217</v>
+        <v>54.369534945986217</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9">
-        <v>50.043843675304217</v>
+        <v>54.369534945986217</v>
       </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
@@ -3876,7 +4038,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="9">
-        <v>1087.527994591346</v>
+        <v>1127.006796932234</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -3884,7 +4046,7 @@
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9">
-        <v>1087.527994591346</v>
+        <v>1127.006796932234</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -3902,20 +4064,20 @@
         <v>71</v>
       </c>
       <c r="B14" s="9">
-        <v>3872.1153846153852</v>
+        <v>3930.7692307692309</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9">
-        <v>284.20527187499999</v>
+        <v>269.28028577097513</v>
       </c>
       <c r="H14" s="9">
-        <v>840.87447366009201</v>
+        <v>1197.385726724011</v>
       </c>
       <c r="I14" s="9">
-        <v>2747.0356390802931</v>
+        <v>2464.1032182742451</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
@@ -3932,7 +4094,7 @@
         <v>72</v>
       </c>
       <c r="B15" s="9">
-        <v>5242.3076923076924</v>
+        <v>5300.9615384615381</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -3941,13 +4103,13 @@
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9">
-        <v>2571.70269024663</v>
+        <v>2792.5505363771881</v>
       </c>
       <c r="J15" s="9">
-        <v>2236.9391151484911</v>
+        <v>2175.3905321579932</v>
       </c>
       <c r="K15" s="9">
-        <v>433.66588691257112</v>
+        <v>333.02046992635758</v>
       </c>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -3962,7 +4124,7 @@
         <v>76</v>
       </c>
       <c r="B16" s="9">
-        <v>4.2616706730769227</v>
+        <v>5.3462453485667769</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -3971,7 +4133,7 @@
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
       <c r="I16" s="9">
-        <v>4.2616706730769227</v>
+        <v>5.3462453485667769</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
@@ -3988,7 +4150,7 @@
         <v>78</v>
       </c>
       <c r="B17" s="9">
-        <v>253.50123235150929</v>
+        <v>272.10301328418421</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
@@ -3998,7 +4160,7 @@
       <c r="H17" s="9"/>
       <c r="I17" s="9"/>
       <c r="J17" s="9">
-        <v>253.50123235150929</v>
+        <v>272.10301328418421</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
@@ -4014,7 +4176,7 @@
         <v>80</v>
       </c>
       <c r="B18" s="9">
-        <v>1508.3066543266029</v>
+        <v>1547.938796750884</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -4025,10 +4187,10 @@
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
       <c r="K18" s="9">
-        <v>1066.6992871380619</v>
+        <v>1122.544496921141</v>
       </c>
       <c r="L18" s="9">
-        <v>441.60736718854099</v>
+        <v>425.39429982974309</v>
       </c>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
@@ -4043,60 +4205,60 @@
       </c>
       <c r="B19" s="16">
         <f t="shared" ref="B19:N19" si="1">SUM(B7:B18)</f>
-        <v>27696.442892407838</v>
+        <v>28129.952413478011</v>
       </c>
       <c r="C19" s="16">
         <f t="shared" si="1"/>
-        <v>2422.0969749945652</v>
+        <v>2378.929462043478</v>
       </c>
       <c r="D19" s="16">
         <f t="shared" si="1"/>
-        <v>316.89691763080322</v>
+        <v>301.57402068287888</v>
       </c>
       <c r="E19" s="16">
         <f t="shared" si="1"/>
-        <v>4298</v>
+        <v>4237</v>
       </c>
       <c r="F19" s="16">
         <f t="shared" si="1"/>
-        <v>2240.6796558686442</v>
+        <v>2197.0161544067801</v>
       </c>
       <c r="G19" s="16">
         <f t="shared" si="1"/>
-        <v>284.20527187499999</v>
+        <v>269.28028577097513</v>
       </c>
       <c r="H19" s="16">
         <f t="shared" si="1"/>
-        <v>4923</v>
+        <v>4862</v>
       </c>
       <c r="I19" s="16">
         <f t="shared" si="1"/>
-        <v>5323</v>
+        <v>5262.0000000000009</v>
       </c>
       <c r="J19" s="16">
         <f t="shared" si="1"/>
-        <v>2490.4403475000004</v>
+        <v>2447.4935454421775</v>
       </c>
       <c r="K19" s="16">
         <f t="shared" si="1"/>
-        <v>1500.365174050633</v>
+        <v>1455.5649668474985</v>
       </c>
       <c r="L19" s="16">
         <f t="shared" si="1"/>
-        <v>441.60736718854099</v>
+        <v>425.39429982974309</v>
       </c>
       <c r="M19" s="16">
         <f t="shared" si="1"/>
-        <v>2901.748052963856</v>
+        <v>3835.6741084165701</v>
       </c>
       <c r="N19" s="16">
         <f t="shared" si="1"/>
-        <v>554.40313033579719</v>
+        <v>458.02557003790901</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="39" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="B20" s="44"/>
       <c r="C20" s="11">
@@ -4171,81 +4333,81 @@
   <sheetData>
     <row r="1" spans="1:23" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="30"/>
       <c r="B2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="T2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="U2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>58</v>
@@ -4319,90 +4481,90 @@
         <v>88</v>
       </c>
       <c r="B4" s="9">
-        <v>2422.0969749945648</v>
+        <v>2378.929462043478</v>
       </c>
       <c r="C4" s="9">
-        <v>316.89691763080322</v>
+        <v>301.57402068287888</v>
       </c>
       <c r="D4" s="9">
-        <v>4298</v>
+        <v>4237</v>
       </c>
       <c r="E4" s="9">
-        <v>2240.6796558686442</v>
+        <v>2197.0161544067801</v>
       </c>
       <c r="F4" s="9">
-        <v>284.20527187499999</v>
+        <v>269.28028577097513</v>
       </c>
       <c r="G4" s="9">
-        <v>4923</v>
+        <v>4862</v>
       </c>
       <c r="H4" s="9">
-        <v>5323</v>
+        <v>5262</v>
       </c>
       <c r="I4" s="9">
-        <v>2490.4403474999999</v>
+        <v>2447.493545442177</v>
       </c>
       <c r="J4" s="9">
-        <v>1500.365174050633</v>
+        <v>1455.564966847498</v>
       </c>
       <c r="K4" s="9">
-        <v>441.60736718854099</v>
+        <v>425.39429982974309</v>
       </c>
       <c r="L4" s="9">
-        <v>5.8748443857998884</v>
+        <v>7.1879674609810484</v>
       </c>
       <c r="M4" s="9">
-        <v>835.00357548112356</v>
+        <v>870.8077510628649</v>
       </c>
       <c r="N4" s="9">
-        <v>3271.1538461538462</v>
+        <v>3329.8076923076919</v>
       </c>
       <c r="O4" s="9">
-        <v>5386.5384615384619</v>
+        <v>5445.1923076923076</v>
       </c>
       <c r="P4" s="9">
-        <v>2723.6565090080389</v>
+        <v>1944.76186000706</v>
       </c>
       <c r="Q4" s="9">
-        <v>50.043843675304217</v>
+        <v>54.369534945986217</v>
       </c>
       <c r="R4" s="9">
-        <v>1087.527994591346</v>
+        <v>1127.006796932234</v>
       </c>
       <c r="S4" s="9">
-        <v>3872.1153846153852</v>
+        <v>3930.7692307692309</v>
       </c>
       <c r="T4" s="9">
-        <v>5242.3076923076924</v>
+        <v>5300.9615384615381</v>
       </c>
       <c r="U4" s="9">
-        <v>4.2616706730769227</v>
+        <v>5.3462453485667769</v>
       </c>
       <c r="V4" s="9">
-        <v>253.50123235150929</v>
+        <v>272.10301328418421</v>
       </c>
       <c r="W4" s="9">
-        <v>1508.3066543266029</v>
+        <v>1547.938796750884</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="B5" s="9">
-        <v>49.088687062500753</v>
+        <v>48.966742997070128</v>
       </c>
       <c r="C5" s="9">
-        <v>121.0338983050847</v>
+        <v>120.6892655367232</v>
       </c>
       <c r="D5" s="9">
         <v>50</v>
       </c>
       <c r="E5" s="9">
-        <v>147.08716292185639</v>
+        <v>146.9363286170539</v>
       </c>
       <c r="F5" s="9">
-        <v>227.16666666666671</v>
+        <v>226.6825396825397</v>
       </c>
       <c r="G5" s="9">
         <v>50</v>
@@ -4411,19 +4573,19 @@
         <v>150</v>
       </c>
       <c r="I5" s="9">
-        <v>249.23684255149581</v>
+        <v>249.119615510518</v>
       </c>
       <c r="J5" s="9">
-        <v>347.77684871422503</v>
+        <v>347.82199025688828</v>
       </c>
       <c r="K5" s="9">
-        <v>428.78947368421052</v>
+        <v>428.43274853801171</v>
       </c>
       <c r="L5" s="9">
-        <v>92.691666666666663</v>
+        <v>92.183333333333337</v>
       </c>
       <c r="M5" s="9">
-        <v>159.93316494450531</v>
+        <v>159.61748097962101</v>
       </c>
       <c r="N5" s="9">
         <v>250</v>
@@ -4435,10 +4597,10 @@
         <v>450</v>
       </c>
       <c r="Q5" s="9">
-        <v>187.70056497175139</v>
+        <v>187.35593220338981</v>
       </c>
       <c r="R5" s="9">
-        <v>257.57398883862618</v>
+        <v>257.37495045567141</v>
       </c>
       <c r="S5" s="9">
         <v>350</v>
@@ -4447,33 +4609,33 @@
         <v>450</v>
       </c>
       <c r="U5" s="9">
-        <v>293.83333333333331</v>
+        <v>293.34920634920633</v>
       </c>
       <c r="V5" s="9">
-        <v>355.69073635988133</v>
+        <v>355.2798962493593</v>
       </c>
       <c r="W5" s="9">
-        <v>457.80955662620897</v>
+        <v>457.67572821850092</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="B6" s="9">
-        <v>249.06833838485301</v>
+        <v>248.94176932103349</v>
       </c>
       <c r="C6" s="9">
-        <v>226.97826086956519</v>
+        <v>226.536231884058</v>
       </c>
       <c r="D6" s="9">
         <v>150</v>
       </c>
       <c r="E6" s="9">
-        <v>147.13807100281531</v>
+        <v>146.99188099386089</v>
       </c>
       <c r="F6" s="9">
-        <v>120.375</v>
+        <v>120.0119047619048</v>
       </c>
       <c r="G6" s="9">
         <v>50</v>
@@ -4482,19 +4644,19 @@
         <v>50</v>
       </c>
       <c r="I6" s="9">
-        <v>49.236842551495798</v>
+        <v>49.119615510518031</v>
       </c>
       <c r="J6" s="9">
-        <v>36.167353529974193</v>
+        <v>35.599482715745317</v>
       </c>
       <c r="K6" s="9">
-        <v>20.77215189873418</v>
+        <v>20.514767932489448</v>
       </c>
       <c r="L6" s="9">
-        <v>293.64492753623188</v>
+        <v>293.20289855072463</v>
       </c>
       <c r="M6" s="9">
-        <v>257.89470169305258</v>
+        <v>257.69896584638781</v>
       </c>
       <c r="N6" s="9">
         <v>250</v>
@@ -4506,10 +4668,10 @@
         <v>250</v>
       </c>
       <c r="Q6" s="9">
-        <v>187.04166666666671</v>
+        <v>186.67857142857139</v>
       </c>
       <c r="R6" s="9">
-        <v>159.82683588369201</v>
+        <v>159.48476865103959</v>
       </c>
       <c r="S6" s="9">
         <v>150</v>
@@ -4518,249 +4680,249 @@
         <v>150</v>
       </c>
       <c r="U6" s="9">
-        <v>93.833333333333329</v>
+        <v>93.349206349206355</v>
       </c>
       <c r="V6" s="9">
-        <v>85.408271458645558</v>
+        <v>84.909502787321941</v>
       </c>
       <c r="W6" s="9">
-        <v>60.761474345837151</v>
+        <v>60.49371674496966</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B7" s="22">
         <f t="shared" ref="B7:W7" si="0">B5*B4</f>
-        <v>118897.5604405379</v>
+        <v>116488.42757604129</v>
       </c>
       <c r="C7" s="22">
         <f t="shared" si="0"/>
-        <v>38355.269301721441</v>
+        <v>36396.747061173221</v>
       </c>
       <c r="D7" s="22">
         <f t="shared" si="0"/>
-        <v>214900</v>
+        <v>211850</v>
       </c>
       <c r="E7" s="22">
         <f t="shared" si="0"/>
-        <v>329575.2135984404</v>
+        <v>322821.4876408907</v>
       </c>
       <c r="F7" s="22">
         <f t="shared" si="0"/>
-        <v>64561.964260937515</v>
+        <v>61041.139065004696</v>
       </c>
       <c r="G7" s="22">
         <f t="shared" si="0"/>
-        <v>246150</v>
+        <v>243100</v>
       </c>
       <c r="H7" s="22">
         <f t="shared" si="0"/>
-        <v>798450</v>
+        <v>789300</v>
       </c>
       <c r="I7" s="22">
         <f t="shared" si="0"/>
-        <v>620709.48877375002</v>
+        <v>609718.65100502968</v>
       </c>
       <c r="J7" s="22">
         <f t="shared" si="0"/>
-        <v>521792.27215189888</v>
+        <v>506277.50371709839</v>
       </c>
       <c r="K7" s="22">
         <f t="shared" si="0"/>
-        <v>189356.59055184439</v>
+        <v>182252.84908845989</v>
       </c>
       <c r="L7" s="22">
         <f t="shared" si="0"/>
-        <v>544.54911752710132</v>
+        <v>662.61080044476967</v>
       </c>
       <c r="M7" s="22">
         <f t="shared" si="0"/>
-        <v>133544.76456667422</v>
+        <v>138996.13964218338</v>
       </c>
       <c r="N7" s="22">
         <f t="shared" si="0"/>
-        <v>817788.4615384615</v>
+        <v>832451.92307692301</v>
       </c>
       <c r="O7" s="22">
         <f t="shared" si="0"/>
-        <v>1885288.4615384617</v>
+        <v>1905817.3076923077</v>
       </c>
       <c r="P7" s="22">
         <f t="shared" si="0"/>
-        <v>1225645.4290536174</v>
+        <v>875142.83700317703</v>
       </c>
       <c r="Q7" s="22">
         <f t="shared" si="0"/>
-        <v>9393.2577312126086</v>
+        <v>10186.454903270027</v>
       </c>
       <c r="R7" s="22">
         <f t="shared" si="0"/>
-        <v>280118.92354056484</v>
+        <v>290063.31852363865</v>
       </c>
       <c r="S7" s="22">
         <f t="shared" si="0"/>
-        <v>1355240.3846153847</v>
+        <v>1375769.2307692308</v>
       </c>
       <c r="T7" s="22">
         <f t="shared" si="0"/>
-        <v>2359038.4615384615</v>
+        <v>2385432.692307692</v>
       </c>
       <c r="U7" s="22">
         <f t="shared" si="0"/>
-        <v>1252.2208994391024</v>
+        <v>1568.3168299501999</v>
       </c>
       <c r="V7" s="22">
         <f t="shared" si="0"/>
-        <v>90168.040003245711</v>
+        <v>96672.730328742997</v>
       </c>
       <c r="W7" s="22">
         <f t="shared" si="0"/>
-        <v>690517.20067362278</v>
+        <v>708454.01604063087</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="B8" s="22">
         <f t="shared" ref="B8:W8" si="1">B6*B4</f>
-        <v>603267.66896887508</v>
+        <v>592214.90937103785</v>
       </c>
       <c r="C8" s="22">
         <f t="shared" si="1"/>
-        <v>71928.711238765565</v>
+        <v>68317.44227962436</v>
       </c>
       <c r="D8" s="22">
         <f t="shared" si="1"/>
-        <v>644700</v>
+        <v>635550</v>
       </c>
       <c r="E8" s="22">
         <f t="shared" si="1"/>
-        <v>329689.28229976434</v>
+        <v>322943.53711015132</v>
       </c>
       <c r="F8" s="22">
         <f t="shared" si="1"/>
-        <v>34211.209601953124</v>
+        <v>32316.840010204774</v>
       </c>
       <c r="G8" s="22">
         <f t="shared" si="1"/>
-        <v>246150</v>
+        <v>243100</v>
       </c>
       <c r="H8" s="22">
         <f t="shared" si="1"/>
-        <v>266150</v>
+        <v>263100</v>
       </c>
       <c r="I8" s="22">
         <f t="shared" si="1"/>
-        <v>122621.41927374998</v>
+        <v>120219.94191659433</v>
       </c>
       <c r="J8" s="22">
         <f t="shared" si="1"/>
-        <v>54264.237673950505</v>
+        <v>51817.359878931908</v>
       </c>
       <c r="K8" s="22">
         <f t="shared" si="1"/>
-        <v>9173.1353108404546</v>
+        <v>8726.8653408110149</v>
       </c>
       <c r="L8" s="22">
         <f t="shared" si="1"/>
-        <v>1725.118253954847</v>
+        <v>2107.5328942479359</v>
       </c>
       <c r="M8" s="22">
         <f t="shared" si="1"/>
-        <v>215342.99801133666</v>
+        <v>224406.25689991898</v>
       </c>
       <c r="N8" s="22">
         <f t="shared" si="1"/>
-        <v>817788.4615384615</v>
+        <v>832451.92307692301</v>
       </c>
       <c r="O8" s="22">
         <f t="shared" si="1"/>
-        <v>1346634.6153846155</v>
+        <v>1361298.076923077</v>
       </c>
       <c r="P8" s="22">
         <f t="shared" si="1"/>
-        <v>680914.1272520097</v>
+        <v>486190.465001765</v>
       </c>
       <c r="Q8" s="22">
         <f t="shared" si="1"/>
-        <v>9360.2839274350281</v>
+        <v>10149.627112952496</v>
       </c>
       <c r="R8" s="22">
         <f t="shared" si="1"/>
-        <v>173816.15831047174</v>
+        <v>179740.41827688648</v>
       </c>
       <c r="S8" s="22">
         <f t="shared" si="1"/>
-        <v>580817.30769230775</v>
+        <v>589615.38461538462</v>
       </c>
       <c r="T8" s="22">
         <f t="shared" si="1"/>
-        <v>786346.15384615387</v>
+        <v>795144.23076923075</v>
       </c>
       <c r="U8" s="22">
         <f t="shared" si="1"/>
-        <v>399.8867648237179</v>
+        <v>499.06776023684472</v>
       </c>
       <c r="V8" s="22">
         <f t="shared" si="1"/>
-        <v>21651.102067778887</v>
+        <v>23104.131564892137</v>
       </c>
       <c r="W8" s="22">
         <f t="shared" si="1"/>
-        <v>91646.936082521352</v>
+        <v>93640.571109197132</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="B11" s="40"/>
       <c r="C11" s="16">
         <f>SUM(B7:K7)/SUM(B4:K4)</f>
-        <v>129.64977471365398</v>
+        <v>129.18334267488453</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="16">
         <f>SUM(B8:K8)/SUM(B4:K4)</f>
-        <v>98.272565897910127</v>
+        <v>98.098762498502595</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="B13" s="40"/>
       <c r="C13" s="16">
         <f>SUM(L7:W7)/SUM(L4:W4)</f>
-        <v>365.0343923663209</v>
+        <v>361.68510519485733</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="16">
         <f>SUM(L8:W8)/SUM(L4:W4)</f>
-        <v>194.98293196512685</v>
+        <v>192.91403464807962</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="16">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
-        <v>254.47752971990917</v>
+        <v>251.09162751412518</v>
       </c>
     </row>
   </sheetData>
@@ -4790,24 +4952,24 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="30"/>
       <c r="B2" s="6" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>65</v>
@@ -4818,15 +4980,15 @@
         <v>88</v>
       </c>
       <c r="B4" s="9">
-        <v>2901.748052963856</v>
+        <v>3835.6741084165701</v>
       </c>
       <c r="C4" s="9">
-        <v>2901.748052963856</v>
+        <v>3835.6741084165701</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="B5" s="9">
         <v>250</v>
@@ -4837,7 +4999,7 @@
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="B6" s="9">
         <v>150</v>
@@ -4848,43 +5010,43 @@
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B7" s="22">
         <f>B5*B4</f>
-        <v>725437.01324096404</v>
+        <v>958918.52710414247</v>
       </c>
       <c r="C7" s="22">
         <f>C5*C4</f>
-        <v>1305786.6238337352</v>
+        <v>1726053.3487874565</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="B8" s="22">
         <f>B6*B4</f>
-        <v>435262.20794457837</v>
+        <v>575351.11626248551</v>
       </c>
       <c r="C8" s="22">
         <f>C6*C4</f>
-        <v>725437.01324096404</v>
+        <v>958918.52710414247</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="B11" s="40"/>
       <c r="C11" s="16">
         <f>SUM(B7:B7)/SUM(B4:B4)</f>
-        <v>250</v>
+        <v>249.99999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="16">
@@ -4894,7 +5056,7 @@
     </row>
     <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="B13" s="40"/>
       <c r="C13" s="16">
@@ -4904,22 +5066,22 @@
     </row>
     <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="16">
         <f>SUM(C8:C8)/SUM(C4:C4)</f>
-        <v>250</v>
+        <v>249.99999999999997</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="16">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
-        <v>223.60679774997897</v>
+        <v>223.60679774997899</v>
       </c>
     </row>
   </sheetData>
@@ -4953,15 +5115,15 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="C3" s="40"/>
       <c r="D3" s="40"/>
@@ -4971,10 +5133,10 @@
     </row>
     <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>303</v>
+        <v>326</v>
       </c>
       <c r="C4" s="40"/>
       <c r="D4" s="40"/>
@@ -4984,7 +5146,7 @@
     </row>
     <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="B5" s="46">
         <v>1650</v>
@@ -4997,36 +5159,36 @@
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>306</v>
+        <v>329</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="D8" s="9">
         <v>0.24</v>
@@ -5038,18 +5200,18 @@
         <v>10</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="D9" s="9">
         <v>1.7</v>
@@ -5061,18 +5223,18 @@
         <v>100</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="D10" s="9">
         <v>0.06</v>
@@ -5084,18 +5246,18 @@
         <v>62</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="D11" s="9">
         <v>0.27</v>
@@ -5107,18 +5269,18 @@
         <v>62</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>327</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="D12" s="9">
         <v>0.25</v>
@@ -5130,21 +5292,21 @@
         <v>62</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>62</v>
@@ -5153,12 +5315,12 @@
         <v>62</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>336</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -5191,57 +5353,57 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="39" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="B4" s="40"/>
       <c r="C4" s="25">
         <f>'Табл. 5 скрепер'!$C$15</f>
-        <v>254.47752971990917</v>
+        <v>251.09162751412518</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="25">
         <f>SUM('Табл. 4 распределение'!C5:L5)</f>
-        <v>24240.291709108187</v>
+        <v>23836.252735023529</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="39" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="B6" s="40"/>
       <c r="C6" s="11">
         <f>C5*'Исходные данные'!$B$7</f>
-        <v>27876.335465474414</v>
+        <v>27411.690645277056</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="39" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="25">
         <f>'Табл. 4 распределение'!B19*'Исходные данные'!$B$4</f>
-        <v>28804.300608104153</v>
+        <v>29255.150510017134</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="39" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="B8" s="40"/>
       <c r="C8" s="32">
@@ -5250,7 +5412,7 @@
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="39" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="B9" s="40"/>
       <c r="C9" s="32">
@@ -5259,7 +5421,7 @@
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="32">
@@ -5268,29 +5430,29 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="41" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
       <c r="E12" s="41" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="F12" s="40"/>
       <c r="G12" s="40"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>349</v>
+        <v>372</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C13" s="40"/>
       <c r="E13" s="17" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="F13" s="48" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="G13" s="40"/>
     </row>
@@ -5299,11 +5461,11 @@
         <v>88</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C14" s="11">
         <f>$C$6</f>
-        <v>27876.335465474414</v>
+        <v>27411.690645277056</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>88</v>
@@ -5311,81 +5473,81 @@
       <c r="F14" s="23"/>
       <c r="G14" s="11">
         <f>$C$6</f>
-        <v>27876.335465474414</v>
+        <v>27411.690645277056</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="B15" s="23"/>
       <c r="C15" s="13">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$8+'2.3 Грунт и нормы ЕНиР'!$E$8*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$8)/10</f>
-        <v>5.3740281241180927</v>
+        <v>5.3029241777966289</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="13">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$9+'2.3 Грунт и нормы ЕНиР'!$E$9*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$9)/10</f>
-        <v>3.2447752971990917</v>
+        <v>3.2109162751412521</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="B16" s="23"/>
       <c r="C16" s="11">
         <f>C15*C14/800</f>
-        <v>187.26026348601266</v>
+        <v>181.70264634640171</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="F16" s="23"/>
       <c r="G16" s="11">
         <f>G15*G14/800</f>
-        <v>113.06555586850791</v>
+        <v>110.02080452757164</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="11">
         <f>100*$C$8*8/C15</f>
-        <v>297.72825207582417</v>
+        <v>301.72032379780353</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="F17" s="23"/>
       <c r="G17" s="11">
         <f>100*$C$8*8/G15</f>
-        <v>493.1004009372017</v>
+        <v>498.30013083402929</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B18" s="23">
         <f>C16/($C$8*$C$9)</f>
-        <v>4.6815065871503165</v>
+        <v>4.5425661586600423</v>
       </c>
       <c r="C18" s="34">
         <f>ROUNDUP(ROUND(B18,6),0)</f>
         <v>5</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="F18" s="23">
         <f>G16/($C$8*$C$9)</f>
-        <v>2.8266388967126979</v>
+        <v>2.7505201131892911</v>
       </c>
       <c r="G18" s="34">
         <f>ROUNDUP(ROUND(F18,6),0)</f>
@@ -5394,29 +5556,29 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="B19" s="40"/>
       <c r="C19" s="40"/>
       <c r="E19" s="47" t="s">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="F19" s="40"/>
       <c r="G19" s="40"/>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="B20" s="48" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="C20" s="40"/>
       <c r="E20" s="17" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="F20" s="48" t="s">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="G20" s="40"/>
     </row>
@@ -5425,11 +5587,11 @@
         <v>88</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>357</v>
+        <v>380</v>
       </c>
       <c r="C21" s="11">
         <f>$C$5</f>
-        <v>24240.291709108187</v>
+        <v>23836.252735023529</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>88</v>
@@ -5437,12 +5599,12 @@
       <c r="F21" s="23"/>
       <c r="G21" s="11">
         <f>$C$5</f>
-        <v>24240.291709108187</v>
+        <v>23836.252735023529</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="B22" s="23"/>
       <c r="C22" s="13">
@@ -5450,7 +5612,7 @@
         <v>0.06</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="13">
@@ -5460,25 +5622,25 @@
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="B23" s="23"/>
       <c r="C23" s="11">
         <f>C22*C21/800</f>
-        <v>1.8180218781831141</v>
+        <v>1.7877189551267645</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="11">
         <f>G22*G21/800</f>
-        <v>1.8180218781831141</v>
+        <v>1.7877189551267645</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="B24" s="23"/>
       <c r="C24" s="11">
@@ -5486,7 +5648,7 @@
         <v>26666.666666666668</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="11">
@@ -5496,22 +5658,22 @@
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B25" s="23">
         <f>C18*C17/C24</f>
-        <v>5.5824047264217032E-2</v>
+        <v>5.657256071208816E-2</v>
       </c>
       <c r="C25" s="34">
         <f>ROUNDUP(ROUND(B25,6),0)</f>
         <v>1</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="F25" s="23">
         <f>G18*G17/G24</f>
-        <v>5.5473795105435188E-2</v>
+        <v>5.6058764718828293E-2</v>
       </c>
       <c r="G25" s="34">
         <f>ROUNDUP(ROUND(F25,6),0)</f>
@@ -5520,17 +5682,17 @@
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="C26" s="40"/>
       <c r="E26" s="17" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="G26" s="40"/>
     </row>
@@ -5541,7 +5703,7 @@
       <c r="B27" s="23"/>
       <c r="C27" s="11">
         <f>$C$7</f>
-        <v>28804.300608104153</v>
+        <v>29255.150510017134</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>88</v>
@@ -5549,12 +5711,12 @@
       <c r="F27" s="23"/>
       <c r="G27" s="11">
         <f>$C$7</f>
-        <v>28804.300608104153</v>
+        <v>29255.150510017134</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="B28" s="23"/>
       <c r="C28" s="13">
@@ -5562,7 +5724,7 @@
         <v>0.25</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="13">
@@ -5572,25 +5734,25 @@
     </row>
     <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="B29" s="23"/>
       <c r="C29" s="11">
         <f>C28*C27/800</f>
-        <v>9.0013439400325481</v>
+        <v>9.1422345343803553</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="11">
         <f>G28*G27/800</f>
-        <v>9.7214514552351527</v>
+        <v>9.8736132971307828</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="B30" s="23"/>
       <c r="C30" s="11">
@@ -5598,7 +5760,7 @@
         <v>6400</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="F30" s="23"/>
       <c r="G30" s="11">
@@ -5608,22 +5770,22 @@
     </row>
     <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="B31" s="23">
         <f>C18*C17/C30</f>
-        <v>0.23260019693423764</v>
+        <v>0.23571900296703402</v>
       </c>
       <c r="C31" s="34">
         <f>ROUNDUP(ROUND(B31,6),0)</f>
         <v>1</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="F31" s="23">
         <f>G18*G17/G30</f>
-        <v>0.24963207797445838</v>
+        <v>0.25226444123472735</v>
       </c>
       <c r="G31" s="34">
         <f>ROUNDUP(ROUND(F31,6),0)</f>
@@ -5632,10 +5794,10 @@
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E32" s="17" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="G32" s="40"/>
     </row>
@@ -5646,12 +5808,12 @@
       <c r="F33" s="23"/>
       <c r="G33" s="11">
         <f>$C$7</f>
-        <v>28804.300608104153</v>
+        <v>29255.150510017134</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E34" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="F34" s="23"/>
       <c r="G34" s="13">
@@ -5661,17 +5823,17 @@
     </row>
     <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E35" s="2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="F35" s="23"/>
       <c r="G35" s="11">
         <f>G34*G33/800</f>
-        <v>9.0013439400325481</v>
+        <v>9.1422345343803553</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E36" s="2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="F36" s="23"/>
       <c r="G36" s="11">
@@ -5681,11 +5843,11 @@
     </row>
     <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E37" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="F37" s="23">
         <f>G18*G17/G36</f>
-        <v>0.23114081293931327</v>
+        <v>0.23357818632845123</v>
       </c>
       <c r="G37" s="34">
         <f>ROUNDUP(ROUND(F37,6),0)</f>
@@ -5694,10 +5856,10 @@
     </row>
     <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E38" s="17" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="F38" s="48" t="s">
-        <v>333</v>
+        <v>356</v>
       </c>
       <c r="G38" s="40"/>
     </row>
@@ -5708,46 +5870,46 @@
       <c r="F39" s="23"/>
       <c r="G39" s="11">
         <f>$C$6</f>
-        <v>27876.335465474414</v>
+        <v>27411.690645277056</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E40" s="2" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="F40" s="23"/>
       <c r="G40" s="15">
         <f>G15/$C$10</f>
-        <v>1.0815917657330305</v>
+        <v>1.070305425047084</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E41" s="2" t="s">
-        <v>359</v>
+        <v>382</v>
       </c>
       <c r="F41" s="23"/>
       <c r="G41" s="11">
         <f>G40*G39/800</f>
-        <v>37.688518622835971</v>
+        <v>36.673601509190547</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E42" s="2" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="F42" s="23"/>
       <c r="G42" s="11">
         <f>100*$C$8*8/G40</f>
-        <v>1479.3012028116052</v>
+        <v>1494.9003925020879</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E43" s="2" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="F43" s="23">
         <f>G18*G17/G42</f>
-        <v>0.99999999999999989</v>
+        <v>1</v>
       </c>
       <c r="G43" s="34">
         <f>ROUNDUP(ROUND(F43,6),0)</f>
@@ -5756,74 +5918,74 @@
     </row>
     <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="B45" s="40"/>
       <c r="C45" s="16">
         <f>C16+C23+C29</f>
-        <v>198.07962930422832</v>
+        <v>192.63259983590882</v>
       </c>
       <c r="E45" s="47" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="F45" s="40"/>
       <c r="G45" s="16">
         <f>G16+G23+G29+G35+G41</f>
-        <v>171.2948917647947</v>
+        <v>167.49797282340009</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="B46" s="40"/>
       <c r="C46" s="16">
         <f>C14/C45</f>
-        <v>140.73297473037704</v>
+        <v>142.30037215210351</v>
       </c>
       <c r="E46" s="47" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="F46" s="40"/>
       <c r="G46" s="16">
         <f>G14/G45</f>
-        <v>162.73886032603622</v>
+        <v>163.65386507798704</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="B47" s="40"/>
       <c r="C47" s="35">
         <f>C45/C14</f>
-        <v>7.1056552447345605E-3</v>
+        <v>7.0273885083807766E-3</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="F47" s="40"/>
       <c r="G47" s="35">
         <f>G45/G14</f>
-        <v>6.1448138323973028E-3</v>
+        <v>6.1104575777875068E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="39" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="B48" s="40"/>
       <c r="C48" s="22">
         <f>C16/(C18*$C$8)</f>
-        <v>18.726026348601266</v>
+        <v>18.170264634640169</v>
       </c>
       <c r="E48" s="39" t="s">
-        <v>365</v>
+        <v>388</v>
       </c>
       <c r="F48" s="40"/>
       <c r="G48" s="22">
         <f>G16/(G18*$C$8)</f>
-        <v>18.844259311417986</v>
+        <v>18.336800754595274</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -5892,32 +6054,32 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>366</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="39" t="s">
-        <v>367</v>
+        <v>390</v>
       </c>
       <c r="B3" s="40"/>
       <c r="C3" s="25">
-        <f>'Котлован (оконч.)'!$C$56</f>
-        <v>3635.720177060251</v>
+        <f>'Котлован (оконч.)'!$C$60</f>
+        <v>3970.4648798091712</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="39" t="s">
-        <v>368</v>
+        <v>391</v>
       </c>
       <c r="B4" s="40"/>
       <c r="C4" s="13">
-        <f>'Котлован (оконч.)'!$C$35</f>
-        <v>2.0972999999999997</v>
+        <f>'Котлован (оконч.)'!$C$39</f>
+        <v>2.0911999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="39" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="B5" s="40"/>
       <c r="C5" s="36">
@@ -5927,48 +6089,48 @@
     </row>
     <row r="7" spans="1:10" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>370</v>
+        <v>393</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>373</v>
+        <v>396</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>374</v>
+        <v>397</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>375</v>
+        <v>398</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>376</v>
+        <v>399</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>377</v>
+        <v>400</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>378</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="31" t="s">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C8" s="9">
         <v>0.5</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="E8" s="20">
         <v>2.9</v>
@@ -5992,16 +6154,16 @@
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
-        <v>382</v>
+        <v>405</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>380</v>
+        <v>403</v>
       </c>
       <c r="C9" s="9">
         <v>0.65</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>383</v>
+        <v>406</v>
       </c>
       <c r="E9" s="20">
         <v>2.2999999999999998</v>
@@ -6025,16 +6187,16 @@
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="C10" s="9">
         <v>0.65</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="E10" s="20">
         <v>2.1</v>
@@ -6058,12 +6220,12 @@
     </row>
     <row r="11" spans="1:10" ht="93.6" x14ac:dyDescent="0.3">
       <c r="E11" s="37" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="47" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="14" t="str">
@@ -6071,21 +6233,21 @@
         <v>ЭО-4121А</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>390</v>
+        <v>413</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>392</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>372</v>
+        <v>395</v>
       </c>
       <c r="B13" s="40"/>
       <c r="C13" s="11">
@@ -6093,7 +6255,7 @@
         <v>0.65</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>393</v>
+        <v>416</v>
       </c>
       <c r="F13" s="21">
         <v>0</v>
@@ -6108,7 +6270,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="22">
@@ -6116,7 +6278,7 @@
         <v>2.1</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="F14" s="21">
         <v>500</v>
@@ -6131,7 +6293,7 @@
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="39" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="B15" s="40"/>
       <c r="C15" s="11">
@@ -6139,7 +6301,7 @@
         <v>0.1</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="F15" s="21">
         <v>1500</v>
@@ -6154,15 +6316,15 @@
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="39" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="B16" s="40"/>
       <c r="C16" s="15">
         <f>C4-C15</f>
-        <v>1.9972999999999996</v>
+        <v>1.9911999999999996</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="F16" s="21">
         <v>2000</v>
@@ -6177,7 +6339,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="39" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="B17" s="40"/>
       <c r="C17" s="8" t="str">
@@ -6185,7 +6347,7 @@
         <v>выполняется</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
       <c r="F17" s="21">
         <v>6000</v>
@@ -6200,12 +6362,12 @@
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="39" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="B18" s="40"/>
       <c r="C18" s="11">
         <f>C14*C3/800</f>
-        <v>9.54376546478316</v>
+        <v>10.422470309499074</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>58</v>
@@ -6223,15 +6385,15 @@
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="39" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="B19" s="40"/>
       <c r="C19" s="22">
         <f>C18/C5</f>
-        <v>4.77188273239158</v>
+        <v>5.211235154749537</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="F19" s="21">
         <v>13000</v>
@@ -6246,7 +6408,7 @@
     </row>
     <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E20" s="8" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="F20" s="21">
         <v>17000</v>
@@ -6261,12 +6423,12 @@
     </row>
     <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="37" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="39" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="B22" s="40"/>
       <c r="C22" s="5">
@@ -6285,7 +6447,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="39" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="B24" s="40"/>
       <c r="C24" s="38">
@@ -6295,7 +6457,7 @@
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="39" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="15">
@@ -6305,7 +6467,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="39" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="B26" s="40"/>
       <c r="C26" s="15">
@@ -6315,7 +6477,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="39" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="20">
@@ -6324,7 +6486,7 @@
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="39" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="B28" s="40"/>
       <c r="C28" s="20">
@@ -6333,7 +6495,7 @@
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="39" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="20">
@@ -6342,7 +6504,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="39" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="B30" s="40"/>
       <c r="C30" s="20">
@@ -6351,7 +6513,7 @@
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="39" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="20">
@@ -6360,69 +6522,69 @@
     </row>
     <row r="33" spans="1:20" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
       <c r="S33" s="6" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="T33" s="6" t="s">
-        <v>434</v>
+        <v>457</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="31" t="s">
-        <v>435</v>
+        <v>458</v>
       </c>
       <c r="B34" s="20">
         <v>4.5</v>
@@ -6498,7 +6660,7 @@
     </row>
     <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="31" t="s">
-        <v>436</v>
+        <v>459</v>
       </c>
       <c r="B35" s="20">
         <v>4.5</v>
@@ -6574,7 +6736,7 @@
     </row>
     <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="31" t="s">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="B36" s="20">
         <v>3.8</v>
@@ -6650,7 +6812,7 @@
     </row>
     <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="31" t="s">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="B37" s="20">
         <v>5.4</v>
@@ -6726,7 +6888,7 @@
     </row>
     <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="31" t="s">
-        <v>439</v>
+        <v>462</v>
       </c>
       <c r="B38" s="20">
         <v>5.5</v>
@@ -6802,7 +6964,7 @@
     </row>
     <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="31" t="s">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="B39" s="20">
         <v>5.5</v>
@@ -6878,7 +7040,7 @@
     </row>
     <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="31" t="s">
-        <v>441</v>
+        <v>464</v>
       </c>
       <c r="B40" s="20">
         <v>10.5</v>
@@ -6954,7 +7116,7 @@
     </row>
     <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="31" t="s">
-        <v>442</v>
+        <v>465</v>
       </c>
       <c r="B41" s="20">
         <v>11</v>
@@ -7030,7 +7192,7 @@
     </row>
     <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="31" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="B42" s="20">
         <v>12</v>
@@ -7106,7 +7268,7 @@
     </row>
     <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="31" t="s">
-        <v>444</v>
+        <v>467</v>
       </c>
       <c r="B43" s="20">
         <v>11</v>
@@ -7182,7 +7344,7 @@
     </row>
     <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="31" t="s">
-        <v>445</v>
+        <v>468</v>
       </c>
       <c r="B44" s="20">
         <v>6.6</v>
@@ -7258,7 +7420,7 @@
     </row>
     <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="31" t="s">
-        <v>446</v>
+        <v>469</v>
       </c>
       <c r="B45" s="20">
         <v>8.5</v>
@@ -7334,7 +7496,7 @@
     </row>
     <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="31" t="s">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="B46" s="20">
         <v>6.5</v>
@@ -7410,7 +7572,7 @@
     </row>
     <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="31" t="s">
-        <v>448</v>
+        <v>471</v>
       </c>
       <c r="B47" s="20">
         <v>12</v>
@@ -7486,7 +7648,7 @@
     </row>
     <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="31" t="s">
-        <v>449</v>
+        <v>472</v>
       </c>
       <c r="B48" s="20">
         <v>10.5</v>
@@ -7562,7 +7724,7 @@
     </row>
     <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="31" t="s">
-        <v>450</v>
+        <v>473</v>
       </c>
       <c r="B49" s="20">
         <v>10.5</v>
@@ -7638,7 +7800,7 @@
     </row>
     <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="31" t="s">
-        <v>451</v>
+        <v>474</v>
       </c>
       <c r="B50" s="20">
         <v>20</v>
@@ -7714,7 +7876,7 @@
     </row>
     <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="31" t="s">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="B51" s="20">
         <v>18</v>
@@ -7790,7 +7952,7 @@
     </row>
     <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="47" t="s">
-        <v>453</v>
+        <v>476</v>
       </c>
       <c r="B53" s="40"/>
       <c r="C53" s="14" t="str">
@@ -7800,7 +7962,7 @@
     </row>
     <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="39" t="s">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="B54" s="40"/>
       <c r="C54" s="34">
@@ -7810,7 +7972,7 @@
     </row>
     <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="39" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
       <c r="B55" s="40"/>
       <c r="C55" s="34">
@@ -7820,7 +7982,7 @@
     </row>
     <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="39" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
       <c r="B56" s="40"/>
       <c r="C56" s="15">
@@ -8938,7 +9100,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -9320,243 +9482,244 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
+    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-    </row>
-    <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="11">
+        <v>148</v>
+      </c>
+      <c r="C30" s="22">
+        <f>1+2*$C$29+1</f>
+        <v>7</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="23">
+        <f>$C$25+$C$30</f>
+        <v>7.7</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+    </row>
+    <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="11">
         <f>IF($C$6&lt;=1.5,0.25,IF($C$6&lt;=3,0.67,0.85))</f>
         <v>0.67</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="23">
-        <f>$C$27+$C$6*$C$30</f>
-        <v>3.008</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" s="19"/>
-    </row>
-    <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="15">
-        <f>AVERAGE(H69:H74)</f>
-        <v>0.14386012305066664</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="23" t="str">
-        <f>IF($C$32&gt;0,"насыпи","выемки")</f>
-        <v>насыпи</v>
-      </c>
       <c r="D33" s="8"/>
       <c r="E33" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B34" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C34" s="15">
+      <c r="B34" s="8"/>
+      <c r="C34" s="23">
+        <f>$C$27+$C$6*$C$33</f>
+        <v>3.008</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="23">
+        <f>$C$31+$C$6*$C$33</f>
+        <v>9.3079999999999998</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="15">
+        <f>AVERAGE(H75:H80)</f>
+        <v>0.15056332305066666</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="23" t="str">
+        <f>IF($C$36&gt;0,"насыпи","выемки")</f>
+        <v>насыпи</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="15">
         <f>('Исходные данные'!$B$17+'Исходные данные'!$B$18+'Исходные данные'!$B$23+'Исходные данные'!$B$24)/4</f>
         <v>0.16500000000000001</v>
       </c>
-      <c r="D34" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C35" s="15">
-        <f>IF($C$33="насыпи",$C$6-$C$10-$C$34,$C$6-$C$10)</f>
-        <v>2.0349999999999997</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E35" s="19" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
-    </row>
-    <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="11">
-        <f>IF($C$35&lt;=1.5,0.25,IF($C$35&lt;=3,0.67,0.85))</f>
-        <v>0.67</v>
-      </c>
-      <c r="D37" s="8"/>
-      <c r="E37" s="19" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="C38" s="15">
-        <f>$C$35*$C$37</f>
-        <v>1.3634499999999998</v>
-      </c>
       <c r="D38" s="8" t="s">
         <v>107</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="23">
-        <f>$C$15+2*$C$27</f>
-        <v>62.8</v>
+      <c r="C39" s="15">
+        <f>IF($C$37="насыпи",$C$6-$C$10-$C$38,$C$6-$C$10)</f>
+        <v>2.0349999999999997</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="19"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="E39" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="23">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+    </row>
+    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="11">
+        <f>IF($C$39&lt;=1.5,0.25,IF($C$39&lt;=3,0.67,0.85))</f>
+        <v>0.67</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="15">
+        <f>$C$39*$C$41</f>
+        <v>1.3634499999999998</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="23">
+        <f>$C$15+$C$27+$C$31</f>
+        <v>69.099999999999994</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="23">
         <f>$C$16+2*$C$27</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D44" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="E40" s="19"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="11">
-        <f>($C$15+2*$C$27)*($C$16+2*$C$27)-$C$17*$C$18</f>
-        <v>1555.8399999999997</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="23">
-        <f>$C$39+2*$C$38</f>
-        <v>65.526899999999998</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E42" s="19"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="23">
-        <f>$C$40+2*$C$38</f>
-        <v>35.526899999999998</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" s="19"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C44" s="11">
-        <f>$C$42*$C$43-$C$17*$C$18</f>
-        <v>1823.9676236099999</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>170</v>
       </c>
       <c r="E44" s="19"/>
     </row>
@@ -9568,71 +9731,75 @@
         <v>177</v>
       </c>
       <c r="C45" s="11">
+        <f>$C$43*$C$44-($C$17-$C$27+$C$31)*$C$18</f>
+        <v>1686.8799999999997</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="23">
+        <f>$C$43+2*$C$42</f>
+        <v>71.826899999999995</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="23">
+        <f>$C$44+2*$C$42</f>
+        <v>35.526899999999998</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="11">
+        <f>$C$46*$C$47-($C$17-$C$27+$C$31)*$C$18</f>
+        <v>1972.1870936099999</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="11">
         <f>($C$15+2*$C$24)*($C$16+2*$C$24)-$C$17*$C$18</f>
         <v>1332.1599999999999</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="19"/>
-    </row>
-    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="D49" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C46" s="11">
-        <f>($C$15+2*$C$25)*($C$16+2*$C$25)-$C$17*$C$18</f>
-        <v>1423.9599999999998</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E46" s="19"/>
-    </row>
-    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C47" s="11">
-        <f>($C$15+2*$C$26)*($C$16+2*$C$26)-$C$17*$C$18</f>
-        <v>1461.24</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E47" s="19"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" s="20">
-        <v>3</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>185</v>
-      </c>
+      <c r="E49" s="19"/>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
@@ -9641,100 +9808,99 @@
       <c r="B50" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C50" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="19" t="s">
-        <v>188</v>
-      </c>
+      <c r="C50" s="11">
+        <f>($C$15+2*$C$25)*($C$16+2*$C$25)-$C$17*$C$18</f>
+        <v>1423.9599999999998</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>85</v>
-      </c>
       <c r="C51" s="11">
-        <f>1/$C$50</f>
-        <v>10</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="19" t="s">
+        <f>($C$15+2*$C$26)*($C$16+2*$C$26)-$C$17*$C$18</f>
+        <v>1461.24</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="42" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+    </row>
+    <row r="53" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="23">
-        <f>$C$35*$C$51</f>
-        <v>20.349999999999998</v>
-      </c>
-      <c r="D52" s="8" t="s">
+      <c r="B53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="20">
+        <v>6</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="19"/>
-    </row>
-    <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B53" s="8" t="s">
+      <c r="E53" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="11">
-        <f>$C$51*($C$49*$C$35^2/2+$C$37*$C$35^3/3)</f>
-        <v>80.939552420833309</v>
-      </c>
-      <c r="D53" s="8" t="s">
+    </row>
+    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="B54" s="8" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="42" t="s">
+      <c r="C54" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="8"/>
+      <c r="B55" s="8" t="s">
+        <v>198</v>
+      </c>
       <c r="C55" s="11">
-        <f>$C$35/3*($C$41+$C$44+SQRT($C$41*$C$44))</f>
-        <v>3435.3413295643254</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>194</v>
-      </c>
+        <f>1/$C$54</f>
+        <v>10</v>
+      </c>
+      <c r="D55" s="8"/>
       <c r="E55" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B56" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C56" s="11">
-        <f>$C$55+$C$53</f>
-        <v>3516.2808819851589</v>
+      <c r="B56" s="8"/>
+      <c r="C56" s="23">
+        <f>$C$39*$C$55</f>
+        <v>20.349999999999998</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="E56" s="19"/>
     </row>
@@ -9746,396 +9912,489 @@
         <v>202</v>
       </c>
       <c r="C57" s="11">
-        <f>$C$41*$C$9</f>
-        <v>155.58399999999997</v>
+        <f>$C$39^2/6*(3*$C$53+2*$C$41*$C$39*($C$55-$C$41)/$C$55)*($C$55-$C$41)</f>
+        <v>132.29651566188372</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B58" s="8" t="s">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="C58" s="11">
-        <f>$C$47*$C$8</f>
-        <v>219.18600000000001</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>206</v>
-      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B59" s="8"/>
+      <c r="C59" s="11">
+        <f>$C$39/3*($C$45+$C$48+SQRT($C$45*$C$48))</f>
+        <v>3719.3224407418052</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C59" s="9">
-        <v>0</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C60" s="9">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="C60" s="11">
+        <f>$C$59+$C$57</f>
+        <v>3851.618956403689</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>212</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="E60" s="19"/>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C61" s="11">
-        <f>$C$46*$C$7</f>
-        <v>569.58399999999995</v>
+        <f>$C$45*$C$9</f>
+        <v>168.68799999999999</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="23">
-        <f>$C$35-$C$7-$C$8-$C$9</f>
-        <v>1.3849999999999998</v>
+        <v>213</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="11">
+        <f>$C$51*$C$8</f>
+        <v>219.18600000000001</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C63" s="9">
+        <v>0</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E63" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C63" s="11">
-        <f>$C$45*$C$62</f>
-        <v>1845.0415999999996</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="9">
+        <v>0</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>221</v>
-      </c>
-      <c r="C64" s="11">
-        <f>$C$61+$C$63</f>
-        <v>2414.6255999999994</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="C65" s="11">
+        <f>$C$50*$C$7</f>
+        <v>569.58399999999995</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="C65" s="11">
-        <f>$C$56-$C$64-$C$57-$C$58-$C$59-$C$60</f>
-        <v>726.88528198515951</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E65" s="19" t="s">
+    </row>
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>225</v>
       </c>
+      <c r="B66" s="8"/>
+      <c r="C66" s="23">
+        <f>$C$39-$C$7-$C$8-$C$9</f>
+        <v>1.3849999999999998</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="A67" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B67" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C67" s="11">
+        <f>$C$49*$C$66</f>
+        <v>1845.0415999999996</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="B68" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="C68" s="11">
+        <f>$C$65+$C$67</f>
+        <v>2414.6255999999994</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E68" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F68" s="6" t="s">
+    </row>
+    <row r="69" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="B69" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="H68" s="6" t="s">
+      <c r="C69" s="11">
+        <f>$C$59-$C$68-$C$61-$C$62-$C$63-$C$64</f>
+        <v>916.82284074180563</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="11">
+        <f>$C$57</f>
+        <v>132.29651566188372</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" s="11">
+        <f>$C$69+$C$70</f>
+        <v>1049.1193564036894</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="8" t="s">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="23">
-        <f>-$C$31</f>
+      <c r="B75" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C69" s="23">
-        <f>-$C$31</f>
+      <c r="C75" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D69" s="23">
-        <f t="shared" ref="D69:D74" si="0">$C$21+B69</f>
+      <c r="D75" s="23">
+        <f t="shared" ref="D75:D80" si="0">$C$21+B75</f>
         <v>216.99199999999999</v>
       </c>
-      <c r="E69" s="23">
-        <f t="shared" ref="E69:E74" si="1">$C$22+C69</f>
+      <c r="E75" s="23">
+        <f t="shared" ref="E75:E80" si="1">$C$22+C75</f>
         <v>131.99199999999999</v>
       </c>
-      <c r="F69" s="15">
-        <f>(D69-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F75" s="15">
+        <f>(D75-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G69" s="15">
-        <f>(E69-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G75" s="15">
+        <f>(E75-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H69" s="15">
-        <f>'Исходные данные'!$B$23*(1-F69)*(1-G69)+'Исходные данные'!$B$24*F69*(1-G69)+'Исходные данные'!$B$17*(1-F69)*G69+'Исходные данные'!$B$18*F69*G69</f>
+      <c r="H75" s="15">
+        <f>'Исходные данные'!$B$23*(1-F75)*(1-G75)+'Исходные данные'!$B$24*F75*(1-G75)+'Исходные данные'!$B$17*(1-F75)*G75+'Исходные данные'!$B$18*F75*G75</f>
         <v>-3.926334515200007E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="23">
-        <f>$C$15-$C$17+$C$31</f>
+      <c r="B76" s="23">
+        <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C70" s="23">
-        <f>-$C$31</f>
+      <c r="C76" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D76" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E76" s="23">
         <f t="shared" si="1"/>
         <v>131.99199999999999</v>
       </c>
-      <c r="F70" s="15">
-        <f>(D70-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F76" s="15">
+        <f>(D76-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G70" s="15">
-        <f>(E70-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G76" s="15">
+        <f>(E76-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H70" s="15">
-        <f>'Исходные данные'!$B$23*(1-F70)*(1-G70)+'Исходные данные'!$B$24*F70*(1-G70)+'Исходные данные'!$B$17*(1-F70)*G70+'Исходные данные'!$B$18*F70*G70</f>
+      <c r="H76" s="15">
+        <f>'Исходные данные'!$B$23*(1-F76)*(1-G76)+'Исходные данные'!$B$24*F76*(1-G76)+'Исходные данные'!$B$17*(1-F76)*G76+'Исходные данные'!$B$18*F76*G76</f>
         <v>4.7774097152000004E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="s">
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="23">
-        <f>$C$15-$C$17+$C$31</f>
+      <c r="B77" s="23">
+        <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C71" s="23">
-        <f>$C$18-$C$31</f>
+      <c r="C77" s="23">
+        <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D77" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E77" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F71" s="15">
-        <f>(D71-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F77" s="15">
+        <f>(D77-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G71" s="15">
-        <f>(E71-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G77" s="15">
+        <f>(E77-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H71" s="15">
-        <f>'Исходные данные'!$B$23*(1-F71)*(1-G71)+'Исходные данные'!$B$24*F71*(1-G71)+'Исходные данные'!$B$17*(1-F71)*G71+'Исходные данные'!$B$18*F71*G71</f>
+      <c r="H77" s="15">
+        <f>'Исходные данные'!$B$23*(1-F77)*(1-G77)+'Исходные данные'!$B$24*F77*(1-G77)+'Исходные данные'!$B$17*(1-F77)*G77+'Исходные данные'!$B$18*F77*G77</f>
         <v>0.10611636915200001</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
+    <row r="78" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="23">
-        <f>$C$15+$C$31</f>
-        <v>63.008000000000003</v>
-      </c>
-      <c r="C72" s="23">
-        <f>$C$18-$C$31</f>
+      <c r="B78" s="23">
+        <f>$C$15+$C$35</f>
+        <v>69.307999999999993</v>
+      </c>
+      <c r="C78" s="23">
+        <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D72" s="23">
+      <c r="D78" s="23">
         <f t="shared" si="0"/>
-        <v>283.00799999999998</v>
-      </c>
-      <c r="E72" s="23">
+        <v>289.30799999999999</v>
+      </c>
+      <c r="E78" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F72" s="15">
-        <f>(D72-$C$19)/'Исходные данные'!$B$3</f>
-        <v>0.83007999999999982</v>
-      </c>
-      <c r="G72" s="15">
-        <f>(E72-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="F78" s="15">
+        <f>(D78-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.89307999999999987</v>
+      </c>
+      <c r="G78" s="15">
+        <f>(E78-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H72" s="15">
-        <f>'Исходные данные'!$B$23*(1-F72)*(1-G72)+'Исходные данные'!$B$24*F72*(1-G72)+'Исходные данные'!$B$17*(1-F72)*G72+'Исходные данные'!$B$18*F72*G72</f>
-        <v>0.24925841715199989</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="8" t="s">
+      <c r="H78" s="15">
+        <f>'Исходные данные'!$B$23*(1-F78)*(1-G78)+'Исходные данные'!$B$24*F78*(1-G78)+'Исходные данные'!$B$17*(1-F78)*G78+'Исходные данные'!$B$18*F78*G78</f>
+        <v>0.27072972435199993</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="23">
-        <f>$C$15+$C$31</f>
-        <v>63.008000000000003</v>
-      </c>
-      <c r="C73" s="23">
-        <f>$C$16+$C$31</f>
+      <c r="B79" s="23">
+        <f>$C$15+$C$35</f>
+        <v>69.307999999999993</v>
+      </c>
+      <c r="C79" s="23">
+        <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D79" s="23">
         <f t="shared" si="0"/>
-        <v>283.00799999999998</v>
-      </c>
-      <c r="E73" s="23">
+        <v>289.30799999999999</v>
+      </c>
+      <c r="E79" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F73" s="15">
-        <f>(D73-$C$19)/'Исходные данные'!$B$3</f>
-        <v>0.83007999999999982</v>
-      </c>
-      <c r="G73" s="15">
-        <f>(E73-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="F79" s="15">
+        <f>(D79-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.89307999999999987</v>
+      </c>
+      <c r="G79" s="15">
+        <f>(E79-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H73" s="15">
-        <f>'Исходные данные'!$B$23*(1-F73)*(1-G73)+'Исходные данные'!$B$24*F73*(1-G73)+'Исходные данные'!$B$17*(1-F73)*G73+'Исходные данные'!$B$18*F73*G73</f>
-        <v>0.347864654848</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="s">
+      <c r="H79" s="15">
+        <f>'Исходные данные'!$B$23*(1-F79)*(1-G79)+'Исходные данные'!$B$24*F79*(1-G79)+'Исходные данные'!$B$17*(1-F79)*G79+'Исходные данные'!$B$18*F79*G79</f>
+        <v>0.36661254764800005</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="23">
-        <f>-$C$31</f>
+      <c r="B80" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C74" s="23">
-        <f>$C$16+$C$31</f>
+      <c r="C80" s="23">
+        <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D74" s="23">
+      <c r="D80" s="23">
         <f t="shared" si="0"/>
         <v>216.99199999999999</v>
       </c>
-      <c r="E74" s="23">
+      <c r="E80" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F74" s="15">
-        <f>(D74-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F80" s="15">
+        <f>(D80-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G74" s="15">
-        <f>(E74-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G80" s="15">
+        <f>(E80-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H74" s="15">
-        <f>'Исходные данные'!$B$23*(1-F74)*(1-G74)+'Исходные данные'!$B$24*F74*(1-G74)+'Исходные данные'!$B$17*(1-F74)*G74+'Исходные данные'!$B$18*F74*G74</f>
+      <c r="H80" s="15">
+        <f>'Исходные данные'!$B$23*(1-F80)*(1-G80)+'Исходные данные'!$B$24*F80*(1-G80)+'Исходные данные'!$B$17*(1-F80)*G80+'Исходные данные'!$B$18*F80*G80</f>
         <v>0.15141054515200006</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="24" t="s">
-        <v>234</v>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="24" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -10157,29 +10416,29 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -10187,7 +10446,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C5" s="25">
         <f>Объёмы!$F$31</f>
@@ -10202,70 +10461,70 @@
         <v>32253.811756603707</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="C6" s="25">
-        <f>Котлован!$C$56</f>
-        <v>3516.2808819851589</v>
+        <f>Котлован!$C$60</f>
+        <v>3851.618956403689</v>
       </c>
       <c r="D6" s="25">
-        <f>Котлован!$C$65</f>
-        <v>726.88528198515951</v>
+        <f>Котлован!$C$70</f>
+        <v>132.29651566188372</v>
       </c>
       <c r="E6" s="11">
         <f>D6/'Исходные данные'!$B$4</f>
-        <v>698.92815575496104</v>
+        <v>127.20818813642664</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="26" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="C7" s="16">
         <f>SUM(C5:C6)</f>
-        <v>23725.755842740189</v>
+        <v>24061.09391715872</v>
       </c>
       <c r="D7" s="16">
         <f>SUM(D5:D6)</f>
-        <v>34270.849508853018</v>
+        <v>33676.260742529739</v>
       </c>
       <c r="E7" s="16">
         <f>SUM(E5:E6)</f>
-        <v>32952.739912358666</v>
+        <v>32381.019944740136</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="26" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="C8" s="43">
         <f>C7-E7</f>
-        <v>-9226.9840696184765</v>
+        <v>-8319.9260275814158</v>
       </c>
       <c r="D8" s="40"/>
       <c r="E8" s="40"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B10" s="40"/>
       <c r="C10" s="40"/>
       <c r="D10" s="27">
         <f>ABS(C8)/MAX(C7,E7)</f>
-        <v>0.28000658197644951</v>
+        <v>0.25693835591898573</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="39" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B11" s="40"/>
       <c r="C11" s="40"/>
@@ -10276,35 +10535,35 @@
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="39" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="B12" s="40"/>
       <c r="C12" s="40"/>
       <c r="D12" s="16">
-        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF(Котлован!$C$33="насыпи",Котлован!$C$44,0)</f>
-        <v>148176.03237639001</v>
+        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF(Котлован!$C$37="насыпи",Котлован!$C$48,0)</f>
+        <v>148027.81290639</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="39" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B13" s="40"/>
       <c r="C13" s="40"/>
       <c r="D13" s="28">
         <f>C8/D12</f>
-        <v>-6.227042202196717E-2</v>
+        <v>-5.6205154046576236E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="39" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="B14" s="40"/>
       <c r="C14" s="40"/>
       <c r="D14" s="29">
         <f>ROUND(D13,4)</f>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10336,16 +10595,16 @@
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="B3" s="13">
         <f>'Сводный баланс'!$D$14</f>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
@@ -10356,13 +10615,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -10375,11 +10634,11 @@
       </c>
       <c r="C9" s="15">
         <f t="shared" ref="C9:C32" si="0">$B$3</f>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D9" s="15">
         <f t="shared" ref="D9:D32" si="1">B9+C9</f>
-        <v>-0.31230000000000002</v>
+        <v>-0.30620000000000003</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>13</v>
@@ -10410,35 +10669,35 @@
       </c>
       <c r="C10" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D10" s="15">
         <f t="shared" si="1"/>
-        <v>8.77E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="F10" s="15">
         <f>D9</f>
-        <v>-0.31230000000000002</v>
+        <v>-0.30620000000000003</v>
       </c>
       <c r="G10" s="15">
         <f>D10</f>
-        <v>8.77E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="H10" s="15">
         <f>D11</f>
-        <v>0.2777</v>
+        <v>0.28380000000000005</v>
       </c>
       <c r="I10" s="15">
         <f>D12</f>
-        <v>0.40769999999999995</v>
+        <v>0.41379999999999995</v>
       </c>
       <c r="J10" s="15">
         <f>D13</f>
-        <v>0.59770000000000001</v>
+        <v>0.6038</v>
       </c>
       <c r="K10" s="15">
         <f>D14</f>
-        <v>0.78769999999999996</v>
+        <v>0.79379999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -10451,11 +10710,11 @@
       </c>
       <c r="C11" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D11" s="15">
         <f t="shared" si="1"/>
-        <v>0.2777</v>
+        <v>0.28380000000000005</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>19</v>
@@ -10486,35 +10745,35 @@
       </c>
       <c r="C12" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D12" s="15">
         <f t="shared" si="1"/>
-        <v>0.40769999999999995</v>
+        <v>0.41379999999999995</v>
       </c>
       <c r="F12" s="15">
         <f>D15</f>
-        <v>-0.55230000000000001</v>
+        <v>-0.54620000000000002</v>
       </c>
       <c r="G12" s="15">
         <f>D16</f>
-        <v>-0.37230000000000002</v>
+        <v>-0.36619999999999997</v>
       </c>
       <c r="H12" s="15">
         <f>D17</f>
-        <v>0.21770000000000003</v>
+        <v>0.22380000000000003</v>
       </c>
       <c r="I12" s="15">
         <f>D18</f>
-        <v>0.4577</v>
+        <v>0.46379999999999999</v>
       </c>
       <c r="J12" s="15">
         <f>D19</f>
-        <v>0.77769999999999995</v>
+        <v>0.78379999999999994</v>
       </c>
       <c r="K12" s="15">
         <f>D20</f>
-        <v>0.40769999999999995</v>
+        <v>0.41379999999999995</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -10527,11 +10786,11 @@
       </c>
       <c r="C13" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D13" s="15">
         <f t="shared" si="1"/>
-        <v>0.59770000000000001</v>
+        <v>0.6038</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>25</v>
@@ -10562,35 +10821,35 @@
       </c>
       <c r="C14" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D14" s="15">
         <f t="shared" si="1"/>
-        <v>0.78769999999999996</v>
+        <v>0.79379999999999995</v>
       </c>
       <c r="F14" s="15">
         <f>D21</f>
-        <v>-0.30230000000000001</v>
+        <v>-0.29620000000000002</v>
       </c>
       <c r="G14" s="15">
         <f>D22</f>
-        <v>-0.49230000000000002</v>
+        <v>-0.48619999999999997</v>
       </c>
       <c r="H14" s="15">
         <f>D23</f>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
       <c r="I14" s="15">
         <f>D24</f>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
       <c r="J14" s="15">
         <f>D25</f>
-        <v>0.29769999999999996</v>
+        <v>0.30379999999999996</v>
       </c>
       <c r="K14" s="15">
         <f>D26</f>
-        <v>0.69769999999999999</v>
+        <v>0.70379999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -10603,11 +10862,11 @@
       </c>
       <c r="C15" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D15" s="15">
         <f t="shared" si="1"/>
-        <v>-0.55230000000000001</v>
+        <v>-0.54620000000000002</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>31</v>
@@ -10638,35 +10897,35 @@
       </c>
       <c r="C16" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D16" s="15">
         <f t="shared" si="1"/>
-        <v>-0.37230000000000002</v>
+        <v>-0.36619999999999997</v>
       </c>
       <c r="F16" s="15">
         <f>D27</f>
-        <v>-0.46230000000000004</v>
+        <v>-0.45620000000000005</v>
       </c>
       <c r="G16" s="15">
         <f>D28</f>
-        <v>-0.71230000000000004</v>
+        <v>-0.70620000000000005</v>
       </c>
       <c r="H16" s="15">
         <f>D29</f>
-        <v>-0.58230000000000004</v>
+        <v>-0.57620000000000005</v>
       </c>
       <c r="I16" s="15">
         <f>D30</f>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
       <c r="J16" s="15">
         <f>D31</f>
-        <v>-0.49230000000000002</v>
+        <v>-0.48619999999999997</v>
       </c>
       <c r="K16" s="15">
         <f>D32</f>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10679,11 +10938,11 @@
       </c>
       <c r="C17" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D17" s="15">
         <f t="shared" si="1"/>
-        <v>0.21770000000000003</v>
+        <v>0.22380000000000003</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10696,11 +10955,11 @@
       </c>
       <c r="C18" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D18" s="15">
         <f t="shared" si="1"/>
-        <v>0.4577</v>
+        <v>0.46379999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10713,11 +10972,11 @@
       </c>
       <c r="C19" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D19" s="15">
         <f t="shared" si="1"/>
-        <v>0.77769999999999995</v>
+        <v>0.78379999999999994</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10730,11 +10989,11 @@
       </c>
       <c r="C20" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D20" s="15">
         <f t="shared" si="1"/>
-        <v>0.40769999999999995</v>
+        <v>0.41379999999999995</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10747,11 +11006,11 @@
       </c>
       <c r="C21" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D21" s="15">
         <f t="shared" si="1"/>
-        <v>-0.30230000000000001</v>
+        <v>-0.29620000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10764,11 +11023,11 @@
       </c>
       <c r="C22" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D22" s="15">
         <f t="shared" si="1"/>
-        <v>-0.49230000000000002</v>
+        <v>-0.48619999999999997</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10781,11 +11040,11 @@
       </c>
       <c r="C23" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D23" s="15">
         <f t="shared" si="1"/>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10798,11 +11057,11 @@
       </c>
       <c r="C24" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D24" s="15">
         <f t="shared" si="1"/>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10815,11 +11074,11 @@
       </c>
       <c r="C25" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D25" s="15">
         <f t="shared" si="1"/>
-        <v>0.29769999999999996</v>
+        <v>0.30379999999999996</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10832,11 +11091,11 @@
       </c>
       <c r="C26" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D26" s="15">
         <f t="shared" si="1"/>
-        <v>0.69769999999999999</v>
+        <v>0.70379999999999998</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10849,11 +11108,11 @@
       </c>
       <c r="C27" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D27" s="15">
         <f t="shared" si="1"/>
-        <v>-0.46230000000000004</v>
+        <v>-0.45620000000000005</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10866,11 +11125,11 @@
       </c>
       <c r="C28" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D28" s="15">
         <f t="shared" si="1"/>
-        <v>-0.71230000000000004</v>
+        <v>-0.70620000000000005</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10883,11 +11142,11 @@
       </c>
       <c r="C29" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D29" s="15">
         <f t="shared" si="1"/>
-        <v>-0.58230000000000004</v>
+        <v>-0.57620000000000005</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10900,11 +11159,11 @@
       </c>
       <c r="C30" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D30" s="15">
         <f t="shared" si="1"/>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10917,11 +11176,11 @@
       </c>
       <c r="C31" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D31" s="15">
         <f t="shared" si="1"/>
-        <v>-0.49230000000000002</v>
+        <v>-0.48619999999999997</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -10934,11 +11193,11 @@
       </c>
       <c r="C32" s="15">
         <f t="shared" si="0"/>
-        <v>-6.2300000000000001E-2</v>
+        <v>-5.62E-2</v>
       </c>
       <c r="D32" s="15">
         <f t="shared" si="1"/>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10966,7 +11225,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -11012,22 +11271,22 @@
       </c>
       <c r="D5" s="13">
         <f>'Отметки (оконч.)'!$D$9</f>
-        <v>-0.31230000000000002</v>
+        <v>-0.30620000000000003</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="13">
         <f>'Отметки (оконч.)'!$D$10</f>
-        <v>8.77E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="G5" s="11">
         <f>'Исходные данные'!$B$3*ABS(D5)/(ABS(D5)+ABS(F5))</f>
-        <v>78.075000000000003</v>
+        <v>76.550000000000011</v>
       </c>
       <c r="H5" s="11">
         <f>'Исходные данные'!$B$3-G5</f>
-        <v>21.924999999999997</v>
+        <v>23.449999999999989</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -11042,22 +11301,22 @@
       </c>
       <c r="D6" s="13">
         <f>'Отметки (оконч.)'!$D$10</f>
-        <v>8.77E-2</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="13">
         <f>'Отметки (оконч.)'!$D$16</f>
-        <v>-0.37230000000000002</v>
+        <v>-0.36619999999999997</v>
       </c>
       <c r="G6" s="11">
         <f>'Исходные данные'!$B$3*ABS(D6)/(ABS(D6)+ABS(F6))</f>
-        <v>19.065217391304348</v>
+        <v>20.391304347826086</v>
       </c>
       <c r="H6" s="11">
         <f>'Исходные данные'!$B$3-G6</f>
-        <v>80.934782608695656</v>
+        <v>79.608695652173907</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -11072,22 +11331,22 @@
       </c>
       <c r="D7" s="13">
         <f>'Отметки (оконч.)'!$D$16</f>
-        <v>-0.37230000000000002</v>
+        <v>-0.36619999999999997</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F7" s="13">
         <f>'Отметки (оконч.)'!$D$17</f>
-        <v>0.21770000000000003</v>
+        <v>0.22380000000000003</v>
       </c>
       <c r="G7" s="11">
         <f>'Исходные данные'!$B$3*ABS(D7)/(ABS(D7)+ABS(F7))</f>
-        <v>63.101694915254235</v>
+        <v>62.067796610169488</v>
       </c>
       <c r="H7" s="11">
         <f>'Исходные данные'!$B$3-G7</f>
-        <v>36.898305084745765</v>
+        <v>37.932203389830512</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -11102,22 +11361,22 @@
       </c>
       <c r="D8" s="13">
         <f>'Отметки (оконч.)'!$D$17</f>
-        <v>0.21770000000000003</v>
+        <v>0.22380000000000003</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F8" s="13">
         <f>'Отметки (оконч.)'!$D$23</f>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
       <c r="G8" s="11">
         <f>'Исходные данные'!$B$3*ABS(D8)/(ABS(D8)+ABS(F8))</f>
-        <v>38.875</v>
+        <v>39.964285714285715</v>
       </c>
       <c r="H8" s="11">
         <f>'Исходные данные'!$B$3-G8</f>
-        <v>61.125</v>
+        <v>60.035714285714285</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -11132,22 +11391,22 @@
       </c>
       <c r="D9" s="13">
         <f>'Отметки (оконч.)'!$D$23</f>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="13">
         <f>'Отметки (оконч.)'!$D$24</f>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
       <c r="G9" s="11">
         <f>'Исходные данные'!$B$3*ABS(D9)/(ABS(D9)+ABS(F9))</f>
-        <v>81.5</v>
+        <v>80.047619047619051</v>
       </c>
       <c r="H9" s="11">
         <f>'Исходные данные'!$B$3-G9</f>
-        <v>18.5</v>
+        <v>19.952380952380949</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -11162,22 +11421,22 @@
       </c>
       <c r="D10" s="13">
         <f>'Отметки (оконч.)'!$D$24</f>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="13">
         <f>'Отметки (оконч.)'!$D$30</f>
-        <v>-0.34230000000000005</v>
+        <v>-0.33620000000000005</v>
       </c>
       <c r="G10" s="11">
         <f>'Исходные данные'!$B$3*ABS(D10)/(ABS(D10)+ABS(F10))</f>
-        <v>18.500000000000004</v>
+        <v>19.952380952380953</v>
       </c>
       <c r="H10" s="11">
         <f>'Исходные данные'!$B$3-G10</f>
-        <v>81.5</v>
+        <v>80.047619047619051</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -11192,22 +11451,22 @@
       </c>
       <c r="D11" s="13">
         <f>'Отметки (оконч.)'!$D$25</f>
-        <v>0.29769999999999996</v>
+        <v>0.30379999999999996</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>35</v>
       </c>
       <c r="F11" s="13">
         <f>'Отметки (оконч.)'!$D$31</f>
-        <v>-0.49230000000000002</v>
+        <v>-0.48619999999999997</v>
       </c>
       <c r="G11" s="11">
         <f>'Исходные данные'!$B$3*ABS(D11)/(ABS(D11)+ABS(F11))</f>
-        <v>37.683544303797461</v>
+        <v>38.455696202531641</v>
       </c>
       <c r="H11" s="11">
         <f>'Исходные данные'!$B$3-G11</f>
-        <v>62.316455696202539</v>
+        <v>61.544303797468359</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -11222,22 +11481,22 @@
       </c>
       <c r="D12" s="13">
         <f>'Отметки (оконч.)'!$D$31</f>
-        <v>-0.49230000000000002</v>
+        <v>-0.48619999999999997</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>36</v>
       </c>
       <c r="F12" s="13">
         <f>'Отметки (оконч.)'!$D$32</f>
-        <v>7.7700000000000019E-2</v>
+        <v>8.3800000000000013E-2</v>
       </c>
       <c r="G12" s="11">
         <f>'Исходные данные'!$B$3*ABS(D12)/(ABS(D12)+ABS(F12))</f>
-        <v>86.368421052631575</v>
+        <v>85.298245614035096</v>
       </c>
       <c r="H12" s="11">
         <f>'Исходные данные'!$B$3-G12</f>
-        <v>13.631578947368425</v>
+        <v>14.701754385964904</v>
       </c>
     </row>
   </sheetData>
@@ -11267,7 +11526,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11325,34 +11584,34 @@
       </c>
       <c r="B6" s="11">
         <f>'Исходные данные'!$B$3^2-$F$6</f>
-        <v>9790.9975543478267</v>
+        <v>9760.9119565217388</v>
       </c>
       <c r="C6" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$15)+ABS('Отметки (оконч.)'!$D$16)+0)/5</f>
-        <v>0.24738000000000002</v>
+        <v>0.24371999999999999</v>
       </c>
       <c r="D6" s="11">
         <f>B6*C6</f>
-        <v>2422.0969749945657</v>
+        <v>2378.929462043478</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>59</v>
       </c>
       <c r="F6" s="11">
         <f>'ЛНР (оконч.)'!$G$6*'ЛНР (оконч.)'!$H$5/2</f>
-        <v>209.00244565217389</v>
+        <v>239.08804347826074</v>
       </c>
       <c r="G6" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$10)+0)/3</f>
-        <v>2.9233333333333333E-2</v>
+        <v>3.1266666666666665E-2</v>
       </c>
       <c r="H6" s="11">
         <f>F6*G6</f>
-        <v>6.1098381612318837</v>
+        <v>7.475486159420285</v>
       </c>
       <c r="I6" s="11">
         <f>H6/'Исходные данные'!$B$4</f>
-        <v>5.8748443857998884</v>
+        <v>7.1879674609810431</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11361,34 +11620,34 @@
       </c>
       <c r="B7" s="11">
         <f>'ЛНР (оконч.)'!$H$6*'ЛНР (оконч.)'!$G$7/2</f>
-        <v>2553.5609801031687</v>
+        <v>2470.5681650700071</v>
       </c>
       <c r="C7" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$16)+0)/3</f>
-        <v>0.1241</v>
+        <v>0.12206666666666666</v>
       </c>
       <c r="D7" s="11">
         <f>B7*C7</f>
-        <v>316.89691763080327</v>
+        <v>301.57402068287882</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>61</v>
       </c>
       <c r="F7" s="11">
         <f>'Исходные данные'!$B$3^2-$B$7</f>
-        <v>7446.4390198968313</v>
+        <v>7529.4318349299929</v>
       </c>
       <c r="G7" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$17)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$10)+0)/5</f>
-        <v>0.11662000000000002</v>
+        <v>0.12028000000000001</v>
       </c>
       <c r="H7" s="11">
         <f>F7*G7</f>
-        <v>868.40371850036854</v>
+        <v>905.64006110537969</v>
       </c>
       <c r="I7" s="11">
         <f>H7/'Исходные данные'!$B$4</f>
-        <v>835.00357548112356</v>
+        <v>870.80775106286501</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11413,15 +11672,15 @@
       </c>
       <c r="G8" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$17)+ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$11))/4</f>
-        <v>0.3402</v>
+        <v>0.3463</v>
       </c>
       <c r="H8" s="11">
         <f>F8*G8</f>
-        <v>3402</v>
+        <v>3463</v>
       </c>
       <c r="I8" s="11">
         <f>H8/'Исходные данные'!$B$4</f>
-        <v>3271.1538461538462</v>
+        <v>3329.8076923076924</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11446,15 +11705,15 @@
       </c>
       <c r="G9" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$12))/4</f>
-        <v>0.56020000000000003</v>
+        <v>0.56630000000000003</v>
       </c>
       <c r="H9" s="11">
         <f>F9*G9</f>
-        <v>5602</v>
+        <v>5663</v>
       </c>
       <c r="I9" s="11">
         <f>H9/'Исходные данные'!$B$4</f>
-        <v>5386.538461538461</v>
+        <v>5445.1923076923076</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11479,15 +11738,15 @@
       </c>
       <c r="G10" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$13))/4</f>
-        <v>0.64270000000000005</v>
+        <v>0.64880000000000004</v>
       </c>
       <c r="H10" s="11">
         <f>F10*G10</f>
-        <v>6427.0000000000009</v>
+        <v>6488</v>
       </c>
       <c r="I10" s="11">
         <f>H10/'Исходные данные'!$B$4</f>
-        <v>6179.8076923076933</v>
+        <v>6238.4615384615381</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11500,11 +11759,11 @@
       </c>
       <c r="C11" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$16)+ABS('Отметки (оконч.)'!$D$15))/4</f>
-        <v>0.42980000000000002</v>
+        <v>0.42370000000000002</v>
       </c>
       <c r="D11" s="11">
         <f>B11*C11</f>
-        <v>4298</v>
+        <v>4237</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>62</v>
@@ -11528,34 +11787,34 @@
       </c>
       <c r="B12" s="11">
         <f>'Исходные данные'!$B$3^2-$F$12</f>
-        <v>9282.7891949152545</v>
+        <v>9242.0332929782089</v>
       </c>
       <c r="C12" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$16)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$23)+0)/5</f>
-        <v>0.24138000000000001</v>
+        <v>0.23772000000000001</v>
       </c>
       <c r="D12" s="11">
         <f>B12*C12</f>
-        <v>2240.6796558686442</v>
+        <v>2197.0161544067801</v>
       </c>
       <c r="E12" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F12" s="11">
         <f>'ЛНР (оконч.)'!$G$8*'ЛНР (оконч.)'!$H$7/2</f>
-        <v>717.21080508474586</v>
+        <v>757.96670702179188</v>
       </c>
       <c r="G12" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$17)+0)/3</f>
-        <v>7.2566666666666682E-2</v>
+        <v>7.4600000000000014E-2</v>
       </c>
       <c r="H12" s="11">
         <f>F12*G12</f>
-        <v>52.045597422316405</v>
+        <v>56.544316343825685</v>
       </c>
       <c r="I12" s="11">
         <f>H12/'Исходные данные'!$B$4</f>
-        <v>50.043843675304231</v>
+        <v>54.369534945986231</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11564,34 +11823,34 @@
       </c>
       <c r="B13" s="11">
         <f>'ЛНР (оконч.)'!$H$8*'ЛНР (оконч.)'!$G$9/2</f>
-        <v>2490.84375</v>
+        <v>2402.857993197279</v>
       </c>
       <c r="C13" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$23)+0)/3</f>
-        <v>0.11410000000000002</v>
+        <v>0.11206666666666669</v>
       </c>
       <c r="D13" s="11">
         <f>B13*C13</f>
-        <v>284.20527187500005</v>
+        <v>269.28028577097513</v>
       </c>
       <c r="E13" s="14" t="s">
         <v>70</v>
       </c>
       <c r="F13" s="11">
         <f>'Исходные данные'!$B$3^2-$B$13</f>
-        <v>7509.15625</v>
+        <v>7597.142006802721</v>
       </c>
       <c r="G13" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$24)+ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$17)+0)/5</f>
-        <v>0.15062</v>
+        <v>0.15428</v>
       </c>
       <c r="H13" s="11">
         <f>F13*G13</f>
-        <v>1131.0291143750001</v>
+        <v>1172.0870688095238</v>
       </c>
       <c r="I13" s="11">
         <f>H13/'Исходные данные'!$B$4</f>
-        <v>1087.5279945913462</v>
+        <v>1127.0067969322345</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11616,15 +11875,15 @@
       </c>
       <c r="G14" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$24)+ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$18))/4</f>
-        <v>0.40269999999999995</v>
+        <v>0.40879999999999994</v>
       </c>
       <c r="H14" s="11">
         <f>F14*G14</f>
-        <v>4026.9999999999995</v>
+        <v>4087.9999999999995</v>
       </c>
       <c r="I14" s="11">
         <f>H14/'Исходные данные'!$B$4</f>
-        <v>3872.1153846153838</v>
+        <v>3930.76923076923</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11649,15 +11908,15 @@
       </c>
       <c r="G15" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$19))/4</f>
-        <v>0.54519999999999991</v>
+        <v>0.55130000000000001</v>
       </c>
       <c r="H15" s="11">
         <f>F15*G15</f>
-        <v>5451.9999999999991</v>
+        <v>5513</v>
       </c>
       <c r="I15" s="11">
         <f>H15/'Исходные данные'!$B$4</f>
-        <v>5242.3076923076915</v>
+        <v>5300.9615384615381</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11670,11 +11929,11 @@
       </c>
       <c r="C16" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$21))/4</f>
-        <v>0.49230000000000002</v>
+        <v>0.48620000000000002</v>
       </c>
       <c r="D16" s="11">
         <f>B16*C16</f>
-        <v>4923</v>
+        <v>4862</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>62</v>
@@ -11702,11 +11961,11 @@
       </c>
       <c r="C17" s="15">
         <f>(ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$23)+ABS('Отметки (оконч.)'!$D$22))/4</f>
-        <v>0.5323</v>
+        <v>0.5262</v>
       </c>
       <c r="D17" s="11">
         <f>B17*C17</f>
-        <v>5323</v>
+        <v>5262</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>62</v>
@@ -11730,34 +11989,34 @@
       </c>
       <c r="B18" s="11">
         <f>'Исходные данные'!$B$3^2-$F$18</f>
-        <v>9828.875</v>
+        <v>9800.9512471655325</v>
       </c>
       <c r="C18" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$23)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$30)+0)/5</f>
-        <v>0.25338000000000005</v>
+        <v>0.24972000000000003</v>
       </c>
       <c r="D18" s="11">
         <f>B18*C18</f>
-        <v>2490.4403475000004</v>
+        <v>2447.493545442177</v>
       </c>
       <c r="E18" s="14" t="s">
         <v>76</v>
       </c>
       <c r="F18" s="11">
         <f>'ЛНР (оконч.)'!$G$10*'ЛНР (оконч.)'!$H$9/2</f>
-        <v>171.12500000000003</v>
+        <v>199.04875283446708</v>
       </c>
       <c r="G18" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$24)+0)/3</f>
-        <v>2.5900000000000006E-2</v>
+        <v>2.7933333333333338E-2</v>
       </c>
       <c r="H18" s="11">
         <f>F18*G18</f>
-        <v>4.4321375000000014</v>
+        <v>5.5600951625094481</v>
       </c>
       <c r="I18" s="11">
         <f>H18/'Исходные данные'!$B$4</f>
-        <v>4.2616706730769245</v>
+        <v>5.3462453485667769</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11766,34 +12025,34 @@
       </c>
       <c r="B19" s="11">
         <f>('ЛНР (оконч.)'!$H$10+'ЛНР (оконч.)'!$H$11)/2*'Исходные данные'!$B$3</f>
-        <v>7190.822784810126</v>
+        <v>7079.5961422543714</v>
       </c>
       <c r="C19" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$31)+0)/4</f>
-        <v>0.20865</v>
+        <v>0.2056</v>
       </c>
       <c r="D19" s="11">
         <f>B19*C19</f>
-        <v>1500.3651740506327</v>
+        <v>1455.5649668474989</v>
       </c>
       <c r="E19" s="14" t="s">
         <v>78</v>
       </c>
       <c r="F19" s="11">
         <f>('ЛНР (оконч.)'!$G$11+'ЛНР (оконч.)'!$G$10)/2*'Исходные данные'!$B$3</f>
-        <v>2809.1772151898731</v>
+        <v>2920.4038577456295</v>
       </c>
       <c r="G19" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$24)+0)/4</f>
-        <v>9.3849999999999989E-2</v>
+        <v>9.6899999999999986E-2</v>
       </c>
       <c r="H19" s="11">
         <f>F19*G19</f>
-        <v>263.64128164556956</v>
+        <v>282.98713381555143</v>
       </c>
       <c r="I19" s="11">
         <f>H19/'Исходные данные'!$B$4</f>
-        <v>253.50123235150917</v>
+        <v>272.10301328418404</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11802,34 +12061,34 @@
       </c>
       <c r="B20" s="11">
         <f>'ЛНР (оконч.)'!$H$11*'ЛНР (оконч.)'!$G$12/2</f>
-        <v>2691.0869420386412</v>
+        <v>2624.8105707306245</v>
       </c>
       <c r="C20" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$31)+0)/3</f>
-        <v>0.1641</v>
+        <v>0.16206666666666666</v>
       </c>
       <c r="D20" s="11">
         <f>B20*C20</f>
-        <v>441.60736718854099</v>
+        <v>425.3942998297432</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>80</v>
       </c>
       <c r="F20" s="11">
         <f>'Исходные данные'!$B$3^2-$B$20</f>
-        <v>7308.9130579613593</v>
+        <v>7375.189429269376</v>
       </c>
       <c r="G20" s="15">
         <f>(0+ABS('Отметки (оконч.)'!$D$32)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$25)+0)/5</f>
-        <v>0.21461999999999998</v>
+        <v>0.21827999999999997</v>
       </c>
       <c r="H20" s="11">
         <f>F20*G20</f>
-        <v>1568.6389204996667</v>
+        <v>1609.8563486209191</v>
       </c>
       <c r="I20" s="11">
         <f>H20/'Исходные данные'!$B$4</f>
-        <v>1508.3066543266025</v>
+        <v>1547.9387967508837</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11838,28 +12097,28 @@
       </c>
       <c r="B21" s="16">
         <f>SUM(B6:B20)</f>
-        <v>73828.976206215026</v>
+        <v>73381.729367917767</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="16">
         <f>SUM(D6:D20)</f>
-        <v>24240.291709108187</v>
+        <v>23836.252735023529</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>81</v>
       </c>
       <c r="F21" s="16">
         <f>SUM(F6:F20)</f>
-        <v>76171.023793784989</v>
+        <v>76618.270632082233</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="16">
         <f>SUM(H6:H20)</f>
-        <v>28804.300608104153</v>
+        <v>29255.150510017127</v>
       </c>
       <c r="I21" s="16">
         <f>SUM(I6:I20)</f>
-        <v>27696.442892407838</v>
+        <v>28129.952413478011</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11893,21 +12152,21 @@
       </c>
       <c r="B25" s="15">
         <f>ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$31)+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$15)</f>
-        <v>3.7584</v>
+        <v>3.7096</v>
       </c>
       <c r="C25" s="8">
         <v>8</v>
       </c>
       <c r="D25" s="11">
         <f>'ЛНР (оконч.)'!$G$5+'ЛНР (оконч.)'!$G$12+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3</f>
-        <v>864.44342105263161</v>
+        <v>861.84824561403514</v>
       </c>
       <c r="E25" s="9">
         <v>0.25</v>
       </c>
       <c r="F25" s="11">
         <f>(B25/C25)^2*D25*E25/2</f>
-        <v>23.849133865638159</v>
+        <v>23.16407736281031</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11916,21 +12175,21 @@
       </c>
       <c r="B26" s="15">
         <f>ABS('Отметки (оконч.)'!$D$10)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$32)</f>
-        <v>3.3416000000000006</v>
+        <v>3.3904000000000005</v>
       </c>
       <c r="C26" s="8">
         <v>8</v>
       </c>
       <c r="D26" s="11">
         <f>'ЛНР (оконч.)'!$H$5+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'ЛНР (оконч.)'!$H$12</f>
-        <v>735.55657894736839</v>
+        <v>738.15175438596498</v>
       </c>
       <c r="E26" s="9">
         <v>0.25</v>
       </c>
       <c r="F26" s="11">
         <f>(B26/C26)^2*D26*E26/2</f>
-        <v>16.041872038761518</v>
+        <v>16.572101098127199</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11974,7 +12233,7 @@
       <c r="E31" s="40"/>
       <c r="F31" s="16">
         <f>D21+F25</f>
-        <v>24264.140842973826</v>
+        <v>23859.416812386338</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -11987,7 +12246,7 @@
       <c r="E32" s="40"/>
       <c r="F32" s="16">
         <f>H21+F26</f>
-        <v>28820.342480142914</v>
+        <v>29271.722611115256</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -12000,7 +12259,7 @@
       <c r="E33" s="40"/>
       <c r="F33" s="16">
         <f>F32/'Исходные данные'!$B$4</f>
-        <v>27711.867769368186</v>
+        <v>28145.887126072361</v>
       </c>
     </row>
   </sheetData>
@@ -12024,7 +12283,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52" customWidth="1"/>
@@ -12038,7 +12297,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -12406,243 +12665,244 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
+    <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-    </row>
-    <row r="30" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B29" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C30" s="11">
+        <v>148</v>
+      </c>
+      <c r="C30" s="22">
+        <f>1+2*$C$29+1</f>
+        <v>7</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="23">
+        <f>$C$25+$C$30</f>
+        <v>7.7</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
+    </row>
+    <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="11">
         <f>IF($C$6&lt;=1.5,0.25,IF($C$6&lt;=3,0.67,0.85))</f>
         <v>0.67</v>
       </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="19" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="23">
-        <f>$C$27+$C$6*$C$30</f>
-        <v>3.008</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" s="19"/>
-    </row>
-    <row r="32" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="15">
-        <f>AVERAGE(H69:H74)</f>
-        <v>8.156012305066665E-2</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" s="19" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="23" t="str">
-        <f>IF($C$32&gt;0,"насыпи","выемки")</f>
-        <v>насыпи</v>
-      </c>
       <c r="D33" s="8"/>
       <c r="E33" s="19" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B34" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C34" s="15">
-        <f>('Отметки (оконч.)'!$D$17+'Отметки (оконч.)'!$D$18+'Отметки (оконч.)'!$D$23+'Отметки (оконч.)'!$D$24)/4</f>
-        <v>0.10269999999999999</v>
+      <c r="B34" s="8"/>
+      <c r="C34" s="23">
+        <f>$C$27+$C$6*$C$33</f>
+        <v>3.008</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C35" s="15">
-        <f>IF($C$33="насыпи",$C$6-$C$10-$C$34,$C$6-$C$10)</f>
-        <v>2.0972999999999997</v>
+      <c r="B35" s="8"/>
+      <c r="C35" s="23">
+        <f>$C$31+$C$6*$C$33</f>
+        <v>9.3079999999999998</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="15">
+        <f>AVERAGE(H75:H80)</f>
+        <v>9.4363323050666637E-2</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="19" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="42" t="s">
-        <v>160</v>
-      </c>
-      <c r="B36" s="40"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="40"/>
-      <c r="E36" s="40"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C37" s="11">
-        <f>IF($C$35&lt;=1.5,0.25,IF($C$35&lt;=3,0.67,0.85))</f>
-        <v>0.67</v>
+        <v>160</v>
+      </c>
+      <c r="B37" s="8"/>
+      <c r="C37" s="23" t="str">
+        <f>IF($C$36&gt;0,"насыпи","выемки")</f>
+        <v>насыпи</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="19" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="B38" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="C38" s="15">
-        <f>$C$35*$C$37</f>
-        <v>1.4051909999999999</v>
+        <f>('Отметки (оконч.)'!$D$17+'Отметки (оконч.)'!$D$18+'Отметки (оконч.)'!$D$23+'Отметки (оконч.)'!$D$24)/4</f>
+        <v>0.10879999999999998</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>107</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="23">
-        <f>$C$15+2*$C$27</f>
-        <v>62.8</v>
+      <c r="C39" s="15">
+        <f>IF($C$37="насыпи",$C$6-$C$10-$C$38,$C$6-$C$10)</f>
+        <v>2.0911999999999997</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E39" s="19"/>
-    </row>
-    <row r="40" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="E39" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="23">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="42" t="s">
+        <v>168</v>
+      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+    </row>
+    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="C41" s="11">
+        <f>IF($C$39&lt;=1.5,0.25,IF($C$39&lt;=3,0.67,0.85))</f>
+        <v>0.67</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="19" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="15">
+        <f>$C$39*$C$41</f>
+        <v>1.4011039999999999</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B43" s="8"/>
+      <c r="C43" s="23">
+        <f>$C$15+$C$27+$C$31</f>
+        <v>69.099999999999994</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E43" s="19"/>
+    </row>
+    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B44" s="8"/>
+      <c r="C44" s="23">
         <f>$C$16+2*$C$27</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D44" s="8" t="s">
         <v>107</v>
-      </c>
-      <c r="E40" s="19"/>
-    </row>
-    <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="11">
-        <f>($C$15+2*$C$27)*($C$16+2*$C$27)-$C$17*$C$18</f>
-        <v>1555.8399999999997</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" s="8"/>
-      <c r="C42" s="23">
-        <f>$C$39+2*$C$38</f>
-        <v>65.610382000000001</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E42" s="19"/>
-    </row>
-    <row r="43" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B43" s="8"/>
-      <c r="C43" s="23">
-        <f>$C$40+2*$C$38</f>
-        <v>35.610381999999994</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E43" s="19"/>
-    </row>
-    <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C44" s="11">
-        <f>$C$42*$C$43-$C$17*$C$18</f>
-        <v>1832.4107661859239</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>170</v>
       </c>
       <c r="E44" s="19"/>
     </row>
@@ -12654,71 +12914,75 @@
         <v>177</v>
       </c>
       <c r="C45" s="11">
+        <f>$C$43*$C$44-($C$17-$C$27+$C$31)*$C$18</f>
+        <v>1686.8799999999997</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E45" s="19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="23">
+        <f>$C$43+2*$C$42</f>
+        <v>71.902207999999987</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="19"/>
+    </row>
+    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="23">
+        <f>$C$44+2*$C$42</f>
+        <v>35.602207999999997</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" s="19"/>
+    </row>
+    <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C48" s="11">
+        <f>$C$46*$C$47-($C$17-$C$27+$C$31)*$C$18</f>
+        <v>1980.2773648752636</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" s="19"/>
+    </row>
+    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C49" s="11">
         <f>($C$15+2*$C$24)*($C$16+2*$C$24)-$C$17*$C$18</f>
         <v>1332.1599999999999</v>
       </c>
-      <c r="D45" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E45" s="19"/>
-    </row>
-    <row r="46" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="D49" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B46" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="C46" s="11">
-        <f>($C$15+2*$C$25)*($C$16+2*$C$25)-$C$17*$C$18</f>
-        <v>1423.9599999999998</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E46" s="19"/>
-    </row>
-    <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B47" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C47" s="11">
-        <f>($C$15+2*$C$26)*($C$16+2*$C$26)-$C$17*$C$18</f>
-        <v>1461.24</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E47" s="19"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="42" t="s">
-        <v>182</v>
-      </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="40"/>
-      <c r="D48" s="40"/>
-      <c r="E48" s="40"/>
-    </row>
-    <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="C49" s="20">
-        <v>3</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E49" s="19" t="s">
-        <v>185</v>
-      </c>
+      <c r="E49" s="19"/>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
@@ -12727,100 +12991,99 @@
       <c r="B50" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C50" s="9">
-        <v>0.1</v>
-      </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="19" t="s">
-        <v>188</v>
-      </c>
+      <c r="C50" s="11">
+        <f>($C$15+2*$C$25)*($C$16+2*$C$25)-$C$17*$C$18</f>
+        <v>1423.9599999999998</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E50" s="19"/>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B51" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B51" s="8" t="s">
-        <v>85</v>
-      </c>
       <c r="C51" s="11">
-        <f>1/$C$50</f>
-        <v>10</v>
-      </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="19" t="s">
+        <f>($C$15+2*$C$26)*($C$16+2*$C$26)-$C$17*$C$18</f>
+        <v>1461.24</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="42" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="40"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="40"/>
+      <c r="E52" s="40"/>
+    </row>
+    <row r="53" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B52" s="8"/>
-      <c r="C52" s="23">
-        <f>$C$35*$C$51</f>
-        <v>20.972999999999999</v>
-      </c>
-      <c r="D52" s="8" t="s">
+      <c r="B53" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="20">
+        <v>6</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E52" s="19"/>
-    </row>
-    <row r="53" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="B53" s="8" t="s">
+      <c r="E53" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="11">
-        <f>$C$51*($C$49*$C$35^2/2+$C$37*$C$35^3/3)</f>
-        <v>86.583234976341274</v>
-      </c>
-      <c r="D53" s="8" t="s">
+    </row>
+    <row r="54" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E53" s="19" t="s">
+      <c r="B54" s="8" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="42" t="s">
+      <c r="C54" s="9">
+        <v>0.1</v>
+      </c>
+      <c r="D54" s="8"/>
+      <c r="E54" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
     </row>
     <row r="55" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B55" s="8"/>
+      <c r="B55" s="8" t="s">
+        <v>198</v>
+      </c>
       <c r="C55" s="11">
-        <f>$C$35/3*($C$41+$C$44+SQRT($C$41*$C$44))</f>
-        <v>3549.1369420839096</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>194</v>
-      </c>
+        <f>1/$C$54</f>
+        <v>10</v>
+      </c>
+      <c r="D55" s="8"/>
       <c r="E55" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B56" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="C56" s="11">
-        <f>$C$55+$C$53</f>
-        <v>3635.720177060251</v>
+      <c r="B56" s="8"/>
+      <c r="C56" s="23">
+        <f>$C$39*$C$55</f>
+        <v>20.911999999999999</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>194</v>
+        <v>107</v>
       </c>
       <c r="E56" s="19"/>
     </row>
@@ -12832,396 +13095,489 @@
         <v>202</v>
       </c>
       <c r="C57" s="11">
-        <f>$C$41*$C$9</f>
-        <v>155.58399999999997</v>
+        <f>$C$39^2/6*(3*$C$53+2*$C$41*$C$39*($C$55-$C$41)/$C$55)*($C$55-$C$41)</f>
+        <v>140.18240224830623</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B58" s="8" t="s">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="C58" s="11">
-        <f>$C$47*$C$8</f>
-        <v>219.18600000000001</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>206</v>
-      </c>
+      <c r="B58" s="40"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="40"/>
+      <c r="E58" s="40"/>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B59" s="8"/>
+      <c r="C59" s="11">
+        <f>$C$39/3*($C$45+$C$48+SQRT($C$45*$C$48))</f>
+        <v>3830.2824775608651</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E59" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C59" s="9">
-        <v>0</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="C60" s="9">
-        <v>0</v>
+        <v>209</v>
+      </c>
+      <c r="C60" s="11">
+        <f>$C$59+$C$57</f>
+        <v>3970.4648798091712</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>212</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="E60" s="19"/>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C61" s="11">
-        <f>$C$46*$C$7</f>
-        <v>569.58399999999995</v>
+        <f>$C$45*$C$9</f>
+        <v>168.68799999999999</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B62" s="8"/>
-      <c r="C62" s="23">
-        <f>$C$35-$C$7-$C$8-$C$9</f>
-        <v>1.4472999999999998</v>
+        <v>213</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C62" s="11">
+        <f>$C$51*$C$8</f>
+        <v>219.18600000000001</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>107</v>
+        <v>203</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C63" s="9">
+        <v>0</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E63" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="B63" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="C63" s="11">
-        <f>$C$45*$C$62</f>
-        <v>1928.0351679999994</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E63" s="19"/>
     </row>
     <row r="64" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B64" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="C64" s="9">
+        <v>0</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>221</v>
-      </c>
-      <c r="C64" s="11">
-        <f>$C$61+$C$63</f>
-        <v>2497.6191679999993</v>
-      </c>
-      <c r="D64" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B65" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="C65" s="11">
+        <f>$C$50*$C$7</f>
+        <v>569.58399999999995</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E65" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="C65" s="11">
-        <f>$C$56-$C$64-$C$57-$C$58-$C$59-$C$60</f>
-        <v>763.33100906025174</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E65" s="19" t="s">
+    </row>
+    <row r="66" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
         <v>225</v>
       </c>
+      <c r="B66" s="8"/>
+      <c r="C66" s="23">
+        <f>$C$39-$C$7-$C$8-$C$9</f>
+        <v>1.4411999999999998</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E66" s="19" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="67" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A68" s="6" t="s">
+      <c r="A67" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B67" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C67" s="11">
+        <f>$C$49*$C$66</f>
+        <v>1919.9089919999994</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" s="19"/>
+    </row>
+    <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="B68" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="E68" s="6" t="s">
+      <c r="C68" s="11">
+        <f>$C$65+$C$67</f>
+        <v>2489.4929919999995</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E68" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="F68" s="6" t="s">
+    </row>
+    <row r="69" spans="1:8" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G68" s="6" t="s">
+      <c r="B69" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="H68" s="6" t="s">
+      <c r="C69" s="11">
+        <f>$C$59-$C$68-$C$61-$C$62-$C$63-$C$64</f>
+        <v>952.91548556086548</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E69" s="19" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="11">
+        <f>$C$57</f>
+        <v>140.18240224830623</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E70" s="19"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" s="11">
+        <f>$C$69+$C$70</f>
+        <v>1093.0978878091717</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A69" s="8" t="s">
+    <row r="75" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="23">
-        <f>-$C$31</f>
+      <c r="B75" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C69" s="23">
-        <f>-$C$31</f>
+      <c r="C75" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D69" s="23">
-        <f t="shared" ref="D69:D74" si="0">$C$21+B69</f>
+      <c r="D75" s="23">
+        <f t="shared" ref="D75:D80" si="0">$C$21+B75</f>
         <v>216.99199999999999</v>
       </c>
-      <c r="E69" s="23">
-        <f t="shared" ref="E69:E74" si="1">$C$22+C69</f>
+      <c r="E75" s="23">
+        <f t="shared" ref="E75:E80" si="1">$C$22+C75</f>
         <v>131.99199999999999</v>
       </c>
-      <c r="F69" s="15">
-        <f>(D69-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F75" s="15">
+        <f>(D75-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G69" s="15">
-        <f>(E69-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G75" s="15">
+        <f>(E75-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H69" s="15">
-        <f>'Отметки (оконч.)'!$D$23*(1-F69)*(1-G69)+'Отметки (оконч.)'!$D$24*F69*(1-G69)+'Отметки (оконч.)'!$D$17*(1-F69)*G69+'Отметки (оконч.)'!$D$18*F69*G69</f>
-        <v>-0.10156334515200006</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
+      <c r="H75" s="15">
+        <f>'Отметки (оконч.)'!$D$23*(1-F75)*(1-G75)+'Отметки (оконч.)'!$D$24*F75*(1-G75)+'Отметки (оконч.)'!$D$17*(1-F75)*G75+'Отметки (оконч.)'!$D$18*F75*G75</f>
+        <v>-9.546334515200007E-2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="23">
-        <f>$C$15-$C$17+$C$31</f>
+      <c r="B76" s="23">
+        <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C70" s="23">
-        <f>-$C$31</f>
+      <c r="C76" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D70" s="23">
+      <c r="D76" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E76" s="23">
         <f t="shared" si="1"/>
         <v>131.99199999999999</v>
       </c>
-      <c r="F70" s="15">
-        <f>(D70-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F76" s="15">
+        <f>(D76-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G70" s="15">
-        <f>(E70-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G76" s="15">
+        <f>(E76-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H70" s="15">
-        <f>'Отметки (оконч.)'!$D$23*(1-F70)*(1-G70)+'Отметки (оконч.)'!$D$24*F70*(1-G70)+'Отметки (оконч.)'!$D$17*(1-F70)*G70+'Отметки (оконч.)'!$D$18*F70*G70</f>
-        <v>-1.4525902847999983E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="8" t="s">
+      <c r="H76" s="15">
+        <f>'Отметки (оконч.)'!$D$23*(1-F76)*(1-G76)+'Отметки (оконч.)'!$D$24*F76*(1-G76)+'Отметки (оконч.)'!$D$17*(1-F76)*G76+'Отметки (оконч.)'!$D$18*F76*G76</f>
+        <v>-8.4259028480000095E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B71" s="23">
-        <f>$C$15-$C$17+$C$31</f>
+      <c r="B77" s="23">
+        <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C71" s="23">
-        <f>$C$18-$C$31</f>
+      <c r="C77" s="23">
+        <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D71" s="23">
+      <c r="D77" s="23">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E77" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F71" s="15">
-        <f>(D71-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F77" s="15">
+        <f>(D77-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G71" s="15">
-        <f>(E71-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G77" s="15">
+        <f>(E77-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H71" s="15">
-        <f>'Отметки (оконч.)'!$D$23*(1-F71)*(1-G71)+'Отметки (оконч.)'!$D$24*F71*(1-G71)+'Отметки (оконч.)'!$D$17*(1-F71)*G71+'Отметки (оконч.)'!$D$18*F71*G71</f>
-        <v>4.3816369151999976E-2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
+      <c r="H77" s="15">
+        <f>'Отметки (оконч.)'!$D$23*(1-F77)*(1-G77)+'Отметки (оконч.)'!$D$24*F77*(1-G77)+'Отметки (оконч.)'!$D$17*(1-F77)*G77+'Отметки (оконч.)'!$D$18*F77*G77</f>
+        <v>4.9916369151999977E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A78" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B72" s="23">
-        <f>$C$15+$C$31</f>
-        <v>63.008000000000003</v>
-      </c>
-      <c r="C72" s="23">
-        <f>$C$18-$C$31</f>
+      <c r="B78" s="23">
+        <f>$C$15+$C$35</f>
+        <v>69.307999999999993</v>
+      </c>
+      <c r="C78" s="23">
+        <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D72" s="23">
+      <c r="D78" s="23">
         <f t="shared" si="0"/>
-        <v>283.00799999999998</v>
-      </c>
-      <c r="E72" s="23">
+        <v>289.30799999999999</v>
+      </c>
+      <c r="E78" s="23">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F72" s="15">
-        <f>(D72-$C$19)/'Исходные данные'!$B$3</f>
-        <v>0.83007999999999982</v>
-      </c>
-      <c r="G72" s="15">
-        <f>(E72-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="F78" s="15">
+        <f>(D78-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.89307999999999987</v>
+      </c>
+      <c r="G78" s="15">
+        <f>(E78-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H72" s="15">
-        <f>'Отметки (оконч.)'!$D$23*(1-F72)*(1-G72)+'Отметки (оконч.)'!$D$24*F72*(1-G72)+'Отметки (оконч.)'!$D$17*(1-F72)*G72+'Отметки (оконч.)'!$D$18*F72*G72</f>
-        <v>0.1869584171519999</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="8" t="s">
+      <c r="H78" s="15">
+        <f>'Отметки (оконч.)'!$D$23*(1-F78)*(1-G78)+'Отметки (оконч.)'!$D$24*F78*(1-G78)+'Отметки (оконч.)'!$D$17*(1-F78)*G78+'Отметки (оконч.)'!$D$18*F78*G78</f>
+        <v>0.21452972435199991</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A79" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B73" s="23">
-        <f>$C$15+$C$31</f>
-        <v>63.008000000000003</v>
-      </c>
-      <c r="C73" s="23">
-        <f>$C$16+$C$31</f>
+      <c r="B79" s="23">
+        <f>$C$15+$C$35</f>
+        <v>69.307999999999993</v>
+      </c>
+      <c r="C79" s="23">
+        <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D73" s="23">
+      <c r="D79" s="23">
         <f t="shared" si="0"/>
-        <v>283.00799999999998</v>
-      </c>
-      <c r="E73" s="23">
+        <v>289.30799999999999</v>
+      </c>
+      <c r="E79" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F73" s="15">
-        <f>(D73-$C$19)/'Исходные данные'!$B$3</f>
-        <v>0.83007999999999982</v>
-      </c>
-      <c r="G73" s="15">
-        <f>(E73-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="F79" s="15">
+        <f>(D79-$C$19)/'Исходные данные'!$B$3</f>
+        <v>0.89307999999999987</v>
+      </c>
+      <c r="G79" s="15">
+        <f>(E79-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H73" s="15">
-        <f>'Отметки (оконч.)'!$D$23*(1-F73)*(1-G73)+'Отметки (оконч.)'!$D$24*F73*(1-G73)+'Отметки (оконч.)'!$D$17*(1-F73)*G73+'Отметки (оконч.)'!$D$18*F73*G73</f>
-        <v>0.28556465484799998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="8" t="s">
+      <c r="H79" s="15">
+        <f>'Отметки (оконч.)'!$D$23*(1-F79)*(1-G79)+'Отметки (оконч.)'!$D$24*F79*(1-G79)+'Отметки (оконч.)'!$D$17*(1-F79)*G79+'Отметки (оконч.)'!$D$18*F79*G79</f>
+        <v>0.31041254764800003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A80" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="B74" s="23">
-        <f>-$C$31</f>
+      <c r="B80" s="23">
+        <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C74" s="23">
-        <f>$C$16+$C$31</f>
+      <c r="C80" s="23">
+        <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D74" s="23">
+      <c r="D80" s="23">
         <f t="shared" si="0"/>
         <v>216.99199999999999</v>
       </c>
-      <c r="E74" s="23">
+      <c r="E80" s="23">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F74" s="15">
-        <f>(D74-$C$19)/'Исходные данные'!$B$3</f>
+      <c r="F80" s="15">
+        <f>(D80-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G74" s="15">
-        <f>(E74-$C$20)/'Исходные данные'!$B$3</f>
+      <c r="G80" s="15">
+        <f>(E80-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H74" s="15">
-        <f>'Отметки (оконч.)'!$D$23*(1-F74)*(1-G74)+'Отметки (оконч.)'!$D$24*F74*(1-G74)+'Отметки (оконч.)'!$D$17*(1-F74)*G74+'Отметки (оконч.)'!$D$18*F74*G74</f>
-        <v>8.9110545152000051E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="24" t="s">
-        <v>234</v>
+      <c r="H80" s="15">
+        <f>'Отметки (оконч.)'!$D$23*(1-F80)*(1-G80)+'Отметки (оконч.)'!$D$24*F80*(1-G80)+'Отметки (оконч.)'!$D$17*(1-F80)*G80+'Отметки (оконч.)'!$D$18*F80*G80</f>
+        <v>9.5210545152000031E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A81" s="24" t="s">
+        <v>247</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A52:E52"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kursovoy\.claude\worktrees\earthwork-drawings-autocad-d57f76\kursovaya-tsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8DBFC33-9BAE-47B8-913D-93C0DB03FAE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5302476-43E1-4CF8-87D6-1BD258E6B498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -839,7 +839,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="517">
   <si>
     <t>Курсовая работа по ТСП «Технологическая карта на производство земляных работ», вариант 2: таблицы расчёта</t>
   </si>
@@ -1660,7 +1660,7 @@
     <t>котлован без съезда − Vп.ч − Vподс − Vб.п − Vг.и − Vст</t>
   </si>
   <si>
-    <t>Засыпка съезда — местный грунт</t>
+    <t>Засыпка съезда — привозной песок</t>
   </si>
   <si>
     <t>Обратная засыпка всего</t>
@@ -1720,7 +1720,7 @@
     <t>В призмах (планировка с откосами)</t>
   </si>
   <si>
-    <t>В котловане (Vк; засыпка съезда Vс — пазухи засыпаются привозным песком)</t>
+    <t>В котловане (Vк; засыпка грунтом площадки ΣVн котл = 0 — супесь не песок, пазухи и съезд — привозной песок)</t>
   </si>
   <si>
     <t>Суммарные объёмы</t>
@@ -1729,16 +1729,16 @@
     <t>Баланс Vв − Vн/Kор («−» — грунта не хватает)</t>
   </si>
   <si>
-    <t>Расхождение, % (допускается не более 5 %)</t>
+    <t>Расхождение, % (методичка - не более 5 %, лекция 23.10 - до 10 %)</t>
   </si>
   <si>
     <t>Вывод</t>
   </si>
   <si>
-    <t>Площадь площадки Fпл без котлована по верху (котлован в насыпи), м²</t>
-  </si>
-  <si>
-    <t>Поправка Δh = (Vв − Vн/Kор) / Fпл, м («−» — понижение)</t>
+    <t>Площадь строительной площадки F = 300 × 500, м²</t>
+  </si>
+  <si>
+    <t>Поправка Δh = (Vв − Vн/Kор) · Kор / F, м (лекция 23.10; «−» — понижение)</t>
   </si>
   <si>
     <t>Δh, принятое (до 0,0001 м)</t>
@@ -1771,7 +1771,7 @@
     <t>Баланс земляных работ по котловану (табл. 3; форма - с доски), по окончательным отметкам</t>
   </si>
   <si>
-    <t>Пазухи засыпаются привозным песком (грунт площадки - супесь, не песок). В отвал у котлована - только грунт для засыпки съезда; остальной грунт котлована - в транспортные средства: в насыпь планировки, излишек - на вывоз (с. 16).</t>
+    <t>Грунт площадки - супесь, не песок: пазухи и съезд засыпаются привозным песком, ΣVн местного грунта = 0 (лекция 23.10), отвала у котлована нет; весь грунт котлована - в транспортные средства: в насыпь планировки, излишек - на вывоз (с. 16).</t>
   </si>
   <si>
     <t>Выемка</t>
@@ -1804,7 +1804,7 @@
     <t>Котлован</t>
   </si>
   <si>
-    <t>Отвал (засыпка съезда)</t>
+    <t>Отвал (не требуется)</t>
   </si>
   <si>
     <t>Пазухи сооружения - песок из карьера</t>
@@ -1816,7 +1816,7 @@
     <t>Транспортные средства</t>
   </si>
   <si>
-    <t>Съезд - грунт котлована из отвала</t>
+    <t>Съезд - песок из карьера</t>
   </si>
   <si>
     <t>ΣVв</t>
@@ -1825,10 +1825,10 @@
     <t>Σ (с kр)</t>
   </si>
   <si>
-    <t>ΣVн местного грунта (песок - привозной)</t>
-  </si>
-  <si>
-    <t>Объём грунта в отвал (засыпка съезда): ΣVн · kр, м³</t>
+    <t>ΣVн местного грунта (засыпка - привозной песок)</t>
+  </si>
+  <si>
+    <t>Объём грунта в отвал: ΣVн · kр, м³</t>
   </si>
   <si>
     <t>В транспортные средства: (ΣVв − ΣVн) · kр, м³</t>
@@ -1841,6 +1841,9 @@
   </si>
   <si>
     <t>Привозится из карьера: песок для засыпки пазух, плотное тело / с kр, м³</t>
+  </si>
+  <si>
+    <t>Привозится из карьера: песок для засыпки съезда, плотное тело / с kр, м³</t>
   </si>
   <si>
     <t>Привозится из карьера: щебень для подсыпки Vподс / kо.р, м³</t>
@@ -3691,7 +3694,7 @@
       </c>
       <c r="C36" s="16">
         <f>AVERAGE(H75:H80)</f>
-        <v>9.4363323050666637E-2</v>
+        <v>9.3763323050666647E-2</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>145</v>
@@ -3723,7 +3726,7 @@
       </c>
       <c r="C38" s="16">
         <f>('Отметки (оконч.)'!$D$17+'Отметки (оконч.)'!$D$18+'Отметки (оконч.)'!$D$23+'Отметки (оконч.)'!$D$24)/4</f>
-        <v>0.10879999999999998</v>
+        <v>0.10819999999999999</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>145</v>
@@ -3741,7 +3744,7 @@
       </c>
       <c r="C39" s="16">
         <f>IF($C$37="насыпи",$C$6-$C$10-$C$38,$C$6-$C$10)</f>
-        <v>2.0911999999999997</v>
+        <v>2.0917999999999997</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>145</v>
@@ -3784,7 +3787,7 @@
       </c>
       <c r="C42" s="16">
         <f>$C$39*$C$41</f>
-        <v>1.4011039999999999</v>
+        <v>1.4015059999999999</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>145</v>
@@ -3846,7 +3849,7 @@
       <c r="B46" s="3"/>
       <c r="C46" s="24">
         <f>$C$43+2*$C$42</f>
-        <v>71.902207999999987</v>
+        <v>71.90301199999999</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>145</v>
@@ -3860,7 +3863,7 @@
       <c r="B47" s="3"/>
       <c r="C47" s="24">
         <f>$C$44+2*$C$42</f>
-        <v>35.602207999999997</v>
+        <v>35.603012</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>145</v>
@@ -3876,7 +3879,7 @@
       </c>
       <c r="C48" s="12">
         <f>$C$46*$C$47-($C$17-$C$27+$C$31)*$C$18</f>
-        <v>1980.2773648752636</v>
+        <v>1980.3637990721436</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>216</v>
@@ -3995,7 +3998,7 @@
       <c r="B56" s="3"/>
       <c r="C56" s="24">
         <f>$C$39*$C$55</f>
-        <v>20.911999999999999</v>
+        <v>20.917999999999996</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>145</v>
@@ -4011,7 +4014,7 @@
       </c>
       <c r="C57" s="12">
         <f>$C$39^2/6*(3*$C$53+2*$C$41*$C$39*($C$55-$C$41)/$C$55)*($C$55-$C$41)</f>
-        <v>140.18240224830623</v>
+        <v>140.26795907897184</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>241</v>
@@ -4036,7 +4039,7 @@
       <c r="B59" s="3"/>
       <c r="C59" s="12">
         <f>$C$39/3*($C$45+$C$48+SQRT($C$45*$C$48))</f>
-        <v>3830.2824775608651</v>
+        <v>3831.4695286661999</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>241</v>
@@ -4054,7 +4057,7 @@
       </c>
       <c r="C60" s="12">
         <f>$C$59+$C$57</f>
-        <v>3970.4648798091712</v>
+        <v>3971.7374877451716</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>241</v>
@@ -4156,7 +4159,7 @@
       <c r="B66" s="3"/>
       <c r="C66" s="24">
         <f>$C$39-$C$7-$C$8-$C$9</f>
-        <v>1.4411999999999998</v>
+        <v>1.4417999999999997</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>145</v>
@@ -4174,7 +4177,7 @@
       </c>
       <c r="C67" s="12">
         <f>$C$49*$C$66</f>
-        <v>1919.9089919999994</v>
+        <v>1920.7082879999994</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>241</v>
@@ -4190,7 +4193,7 @@
       </c>
       <c r="C68" s="12">
         <f>$C$65+$C$67</f>
-        <v>2489.4929919999995</v>
+        <v>2490.2922879999992</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>241</v>
@@ -4208,7 +4211,7 @@
       </c>
       <c r="C69" s="12">
         <f>$C$59-$C$68-$C$61-$C$62-$C$63-$C$64</f>
-        <v>952.91548556086548</v>
+        <v>953.30324066620062</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>241</v>
@@ -4226,7 +4229,7 @@
       </c>
       <c r="C70" s="12">
         <f>$C$57</f>
-        <v>140.18240224830623</v>
+        <v>140.26795907897184</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>241</v>
@@ -4242,7 +4245,7 @@
       </c>
       <c r="C71" s="12">
         <f>$C$69+$C$70</f>
-        <v>1093.0978878091717</v>
+        <v>1093.5711997451724</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>241</v>
@@ -4312,7 +4315,7 @@
       </c>
       <c r="H75" s="16">
         <f>'Отметки (оконч.)'!$D$23*(1-F75)*(1-G75)+'Отметки (оконч.)'!$D$24*F75*(1-G75)+'Отметки (оконч.)'!$D$17*(1-F75)*G75+'Отметки (оконч.)'!$D$18*F75*G75</f>
-        <v>-9.546334515200007E-2</v>
+        <v>-9.6063345152000115E-2</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -4345,7 +4348,7 @@
       </c>
       <c r="H76" s="16">
         <f>'Отметки (оконч.)'!$D$23*(1-F76)*(1-G76)+'Отметки (оконч.)'!$D$24*F76*(1-G76)+'Отметки (оконч.)'!$D$17*(1-F76)*G76+'Отметки (оконч.)'!$D$18*F76*G76</f>
-        <v>-8.4259028480000095E-3</v>
+        <v>-9.0259028480000059E-3</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -4378,7 +4381,7 @@
       </c>
       <c r="H77" s="16">
         <f>'Отметки (оконч.)'!$D$23*(1-F77)*(1-G77)+'Отметки (оконч.)'!$D$24*F77*(1-G77)+'Отметки (оконч.)'!$D$17*(1-F77)*G77+'Отметки (оконч.)'!$D$18*F77*G77</f>
-        <v>4.9916369151999977E-2</v>
+        <v>4.9316369151999967E-2</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -4411,7 +4414,7 @@
       </c>
       <c r="H78" s="16">
         <f>'Отметки (оконч.)'!$D$23*(1-F78)*(1-G78)+'Отметки (оконч.)'!$D$24*F78*(1-G78)+'Отметки (оконч.)'!$D$17*(1-F78)*G78+'Отметки (оконч.)'!$D$18*F78*G78</f>
-        <v>0.21452972435199991</v>
+        <v>0.21392972435199992</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -4444,7 +4447,7 @@
       </c>
       <c r="H79" s="16">
         <f>'Отметки (оконч.)'!$D$23*(1-F79)*(1-G79)+'Отметки (оконч.)'!$D$24*F79*(1-G79)+'Отметки (оконч.)'!$D$17*(1-F79)*G79+'Отметки (оконч.)'!$D$18*F79*G79</f>
-        <v>0.31041254764800003</v>
+        <v>0.30981254764800004</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -4477,7 +4480,7 @@
       </c>
       <c r="H80" s="16">
         <f>'Отметки (оконч.)'!$D$23*(1-F80)*(1-G80)+'Отметки (оконч.)'!$D$24*F80*(1-G80)+'Отметки (оконч.)'!$D$17*(1-F80)*G80+'Отметки (оконч.)'!$D$18*F80*G80</f>
-        <v>9.5210545152000031E-2</v>
+        <v>9.4610545152000028E-2</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
@@ -4548,18 +4551,18 @@
       </c>
       <c r="C5" s="26">
         <f>'Табл. 1 объёмы (оконч.)'!$F$31</f>
-        <v>23859.416812386338</v>
+        <v>23899.156200244801</v>
       </c>
       <c r="D5" s="26">
         <f>'Табл. 1 объёмы (оконч.)'!$F$32</f>
-        <v>29271.722611115256</v>
+        <v>29227.216184948978</v>
       </c>
       <c r="E5" s="12">
         <f>D5/'Исходные данные'!$B$4</f>
-        <v>28145.887126072361</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+        <v>28103.092485527864</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -4568,15 +4571,14 @@
       </c>
       <c r="C6" s="26">
         <f>'Котлован (оконч.)'!$C$60</f>
-        <v>3970.4648798091712</v>
-      </c>
-      <c r="D6" s="26">
-        <f>'Котлован (оконч.)'!$C$70</f>
-        <v>140.18240224830623</v>
+        <v>3971.7374877451716</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
       </c>
       <c r="E6" s="12">
         <f>D6/'Исходные данные'!$B$4</f>
-        <v>134.79077139260215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -4586,15 +4588,15 @@
       </c>
       <c r="C7" s="17">
         <f>SUM(C5:C6)</f>
-        <v>27829.881692195508</v>
+        <v>27870.893687989974</v>
       </c>
       <c r="D7" s="17">
         <f>SUM(D5:D6)</f>
-        <v>29411.905013363561</v>
+        <v>29227.216184948978</v>
       </c>
       <c r="E7" s="17">
         <f>SUM(E5:E6)</f>
-        <v>28280.677897464964</v>
+        <v>28103.092485527864</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -4604,7 +4606,7 @@
       </c>
       <c r="C8" s="44">
         <f>C7-E7</f>
-        <v>-450.79620526945655</v>
+        <v>-232.19879753789064</v>
       </c>
       <c r="D8" s="41"/>
       <c r="E8" s="41"/>
@@ -4617,7 +4619,7 @@
       <c r="C10" s="41"/>
       <c r="D10" s="28">
         <f>ABS(C8)/MAX(C7,E7)</f>
-        <v>1.5940077776914436E-2</v>
+        <v>8.2623931034445808E-3</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -4638,8 +4640,8 @@
       <c r="B12" s="41"/>
       <c r="C12" s="41"/>
       <c r="D12" s="17">
-        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF('Котлован (оконч.)'!$C$37="насыпи",'Котлован (оконч.)'!$C$48,0)</f>
-        <v>148019.72263512472</v>
+        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
+        <v>150000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -4649,8 +4651,8 @@
       <c r="B13" s="41"/>
       <c r="C13" s="41"/>
       <c r="D13" s="29">
-        <f>C8/D12</f>
-        <v>-3.0455144574259843E-3</v>
+        <f>C8*'Исходные данные'!$B$4/D12</f>
+        <v>-1.6099116629293751E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -4661,7 +4663,7 @@
       <c r="C14" s="41"/>
       <c r="D14" s="30">
         <f>ROUND(D13,4)</f>
-        <v>-3.0000000000000001E-3</v>
+        <v>-1.6000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -4683,7 +4685,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -4759,14 +4761,14 @@
       </c>
       <c r="C6" s="26">
         <f>'Котлован (оконч.)'!$C$59</f>
-        <v>3830.2824775608651</v>
+        <v>3831.4695286661999</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>321</v>
       </c>
       <c r="E6" s="12">
         <f>J8*'Исходные данные'!$B$7</f>
-        <v>155.00938710149245</v>
+        <v>0</v>
       </c>
       <c r="G6" s="3">
         <v>1</v>
@@ -4776,11 +4778,11 @@
       </c>
       <c r="I6" s="26">
         <f>'Котлован (оконч.)'!$C$69</f>
-        <v>952.91548556086548</v>
+        <v>953.30324066620062</v>
       </c>
       <c r="J6" s="12">
         <f>I6/'Исходные данные'!$B$4</f>
-        <v>916.2648899623706</v>
+        <v>916.63773140980823</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
@@ -4792,14 +4794,14 @@
       </c>
       <c r="C7" s="26">
         <f>'Котлован (оконч.)'!$C$70</f>
-        <v>140.18240224830623</v>
+        <v>140.26795907897184</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>324</v>
       </c>
       <c r="E7" s="12">
         <f>(C8-J8)*'Исходные данные'!$B$7</f>
-        <v>4411.0252246790542</v>
+        <v>4567.4981109069467</v>
       </c>
       <c r="G7" s="3">
         <v>2</v>
@@ -4809,11 +4811,11 @@
       </c>
       <c r="I7" s="26">
         <f>'Котлован (оконч.)'!$C$70</f>
-        <v>140.18240224830623</v>
+        <v>140.26795907897184</v>
       </c>
       <c r="J7" s="12">
         <f>I7/'Исходные данные'!$B$4</f>
-        <v>134.79077139260215</v>
+        <v>134.87303757593446</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
@@ -4823,14 +4825,14 @@
       </c>
       <c r="C8" s="17">
         <f>C6+C7</f>
-        <v>3970.4648798091712</v>
+        <v>3971.7374877451716</v>
       </c>
       <c r="D8" s="27" t="s">
         <v>327</v>
       </c>
       <c r="E8" s="17">
         <f>E6+E7</f>
-        <v>4566.0346117805466</v>
+        <v>4567.4981109069467</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="27" t="s">
@@ -4838,8 +4840,7 @@
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="17">
-        <f>J7</f>
-        <v>134.79077139260215</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -4851,7 +4852,7 @@
       <c r="D10" s="41"/>
       <c r="E10" s="12">
         <f>E6</f>
-        <v>155.00938710149245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -4863,7 +4864,7 @@
       <c r="D11" s="41"/>
       <c r="E11" s="12">
         <f>E7</f>
-        <v>4411.0252246790542</v>
+        <v>4567.4981109069467</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -4875,7 +4876,7 @@
       <c r="D12" s="41"/>
       <c r="E12" s="12">
         <f>MIN(C8-J8,'Табл. 4 распределение'!B19-SUM('Табл. 4 распределение'!C5:L5))*'Исходные данные'!$B$7</f>
-        <v>4411.0252246790542</v>
+        <v>4567.4981109069467</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -4899,11 +4900,11 @@
       <c r="D14" s="41"/>
       <c r="E14" s="12">
         <f>J6</f>
-        <v>916.2648899623706</v>
+        <v>916.63773140980823</v>
       </c>
       <c r="F14" s="12">
         <f>E14*'Исходные данные'!$B$7</f>
-        <v>1053.704623456726</v>
+        <v>1054.1333911212794</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -4914,12 +4915,12 @@
       <c r="C15" s="41"/>
       <c r="D15" s="41"/>
       <c r="E15" s="12">
-        <f>'Котлован (оконч.)'!$C$61/'Исходные данные'!$B$4</f>
-        <v>162.19999999999999</v>
+        <f>J7</f>
+        <v>134.87303757593446</v>
       </c>
       <c r="F15" s="12">
         <f>E15*'Исходные данные'!$B$7</f>
-        <v>186.52999999999997</v>
+        <v>155.10399321232461</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
@@ -4930,22 +4931,39 @@
       <c r="C16" s="41"/>
       <c r="D16" s="41"/>
       <c r="E16" s="12">
+        <f>'Котлован (оконч.)'!$C$61/'Исходные данные'!$B$4</f>
+        <v>162.19999999999999</v>
+      </c>
+      <c r="F16" s="12">
+        <f>E16*'Исходные данные'!$B$7</f>
+        <v>186.52999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="B17" s="41"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="12">
         <f>E6+E7-C8*'Исходные данные'!$B$7</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape"/>
@@ -4968,12 +4986,12 @@
   <sheetData>
     <row r="1" spans="1:15" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="31.2" x14ac:dyDescent="0.3">
@@ -5017,57 +5035,57 @@
         <v>320</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="31"/>
       <c r="B5" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C5" s="10">
-        <v>2378.929462043478</v>
+        <v>2383.1875690434781</v>
       </c>
       <c r="D5" s="10">
-        <v>301.57402068287888</v>
+        <v>303.0587916482437</v>
       </c>
       <c r="E5" s="10">
-        <v>4237</v>
+        <v>4243</v>
       </c>
       <c r="F5" s="10">
-        <v>2197.0161544067801</v>
+        <v>2201.3095856658601</v>
       </c>
       <c r="G5" s="10">
-        <v>269.28028577097513</v>
+        <v>270.72457505668928</v>
       </c>
       <c r="H5" s="10">
-        <v>4862</v>
+        <v>4868</v>
       </c>
       <c r="I5" s="10">
-        <v>5262</v>
+        <v>5268</v>
       </c>
       <c r="J5" s="10">
-        <v>2447.493545442177</v>
+        <v>2451.7321491156458</v>
       </c>
       <c r="K5" s="10">
-        <v>1455.564966847498</v>
+        <v>1459.9414587100659</v>
       </c>
       <c r="L5" s="10">
-        <v>425.39429982974309</v>
+        <v>426.97113047597901</v>
       </c>
       <c r="M5" s="10">
-        <v>3835.6741084165701</v>
+        <v>3971.737487745173</v>
       </c>
       <c r="N5" s="10">
-        <v>458.02557003790901</v>
+        <v>239.54560791275179</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
@@ -5082,7 +5100,7 @@
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
       <c r="O6" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -5090,10 +5108,10 @@
         <v>97</v>
       </c>
       <c r="B7" s="10">
-        <v>7.1879674609810484</v>
+        <v>7.0509124860646599</v>
       </c>
       <c r="C7" s="10">
-        <v>7.1879674609810484</v>
+        <v>7.0509124860646599</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
@@ -5116,10 +5134,10 @@
         <v>99</v>
       </c>
       <c r="B8" s="10">
-        <v>870.8077510628649</v>
+        <v>867.26713655688457</v>
       </c>
       <c r="C8" s="10">
-        <v>870.8077510628649</v>
+        <v>867.26713655688457</v>
       </c>
       <c r="D8" s="10"/>
       <c r="E8" s="10"/>
@@ -5142,16 +5160,16 @@
         <v>101</v>
       </c>
       <c r="B9" s="10">
-        <v>3329.8076923076919</v>
+        <v>3324.038461538461</v>
       </c>
       <c r="C9" s="10">
-        <v>1500.9337435196319</v>
+        <v>1508.8695200005291</v>
       </c>
       <c r="D9" s="10">
-        <v>301.57402068287888</v>
+        <v>303.0587916482437</v>
       </c>
       <c r="E9" s="10">
-        <v>1527.2999281051809</v>
+        <v>1512.110149889689</v>
       </c>
       <c r="F9" s="10"/>
       <c r="G9" s="10"/>
@@ -5172,19 +5190,19 @@
         <v>102</v>
       </c>
       <c r="B10" s="10">
-        <v>5445.1923076923076</v>
+        <v>5439.4230769230771</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="E10" s="10">
-        <v>2655.330536948833</v>
+        <v>2676.9564323416389</v>
       </c>
       <c r="F10" s="10">
-        <v>2197.0161544067801</v>
+        <v>2201.3095856658601</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10">
-        <v>592.84561633669534</v>
+        <v>561.1570589155782</v>
       </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
@@ -5202,7 +5220,7 @@
         <v>103</v>
       </c>
       <c r="B11" s="10">
-        <v>6238.4615384615381</v>
+        <v>6232.6923076923076</v>
       </c>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
@@ -5210,17 +5228,17 @@
       <c r="F11" s="10"/>
       <c r="G11" s="10"/>
       <c r="H11" s="10">
-        <v>1944.76186000706</v>
+        <v>2021.409212034383</v>
       </c>
       <c r="I11" s="10"/>
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
       <c r="M11" s="10">
-        <v>3835.6741084165701</v>
+        <v>3971.737487745173</v>
       </c>
       <c r="N11" s="10">
-        <v>458.02557003790901</v>
+        <v>239.54560791275179</v>
       </c>
       <c r="O11" s="12">
         <f t="shared" si="0"/>
@@ -5232,12 +5250,12 @@
         <v>106</v>
       </c>
       <c r="B12" s="10">
-        <v>54.369534945986217</v>
+        <v>53.933417768672008</v>
       </c>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
       <c r="E12" s="10">
-        <v>54.369534945986217</v>
+        <v>53.933417768672008</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -5258,7 +5276,7 @@
         <v>108</v>
       </c>
       <c r="B13" s="10">
-        <v>1127.006796932234</v>
+        <v>1123.1065578231289</v>
       </c>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
@@ -5266,7 +5284,7 @@
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10">
-        <v>1127.006796932234</v>
+        <v>1123.1065578231289</v>
       </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
@@ -5284,20 +5302,20 @@
         <v>109</v>
       </c>
       <c r="B14" s="10">
-        <v>3930.7692307692309</v>
+        <v>3925</v>
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10">
-        <v>269.28028577097513</v>
+        <v>270.72457505668928</v>
       </c>
       <c r="H14" s="10">
-        <v>1197.385726724011</v>
+        <v>1162.32717122691</v>
       </c>
       <c r="I14" s="10">
-        <v>2464.1032182742451</v>
+        <v>2491.9482537164008</v>
       </c>
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
@@ -5314,7 +5332,7 @@
         <v>110</v>
       </c>
       <c r="B15" s="10">
-        <v>5300.9615384615381</v>
+        <v>5295.1923076923076</v>
       </c>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
@@ -5323,13 +5341,13 @@
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10">
-        <v>2792.5505363771881</v>
+        <v>2770.8195165027978</v>
       </c>
       <c r="J15" s="10">
-        <v>2175.3905321579932</v>
+        <v>2181.4877479471938</v>
       </c>
       <c r="K15" s="10">
-        <v>333.02046992635758</v>
+        <v>342.88504324231548</v>
       </c>
       <c r="L15" s="10"/>
       <c r="M15" s="10"/>
@@ -5344,7 +5362,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="10">
-        <v>5.3462453485667769</v>
+        <v>5.2322297808012097</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
@@ -5353,7 +5371,7 @@
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10">
-        <v>5.3462453485667769</v>
+        <v>5.2322297808012097</v>
       </c>
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
@@ -5370,7 +5388,7 @@
         <v>116</v>
       </c>
       <c r="B17" s="10">
-        <v>272.10301328418421</v>
+        <v>270.24440116845182</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="10"/>
@@ -5380,7 +5398,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
       <c r="J17" s="10">
-        <v>272.10301328418421</v>
+        <v>270.24440116845182</v>
       </c>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
@@ -5396,7 +5414,7 @@
         <v>118</v>
       </c>
       <c r="B18" s="10">
-        <v>1547.938796750884</v>
+        <v>1544.02754594373</v>
       </c>
       <c r="C18" s="10"/>
       <c r="D18" s="10"/>
@@ -5407,10 +5425,10 @@
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10">
-        <v>1122.544496921141</v>
+        <v>1117.0564154677511</v>
       </c>
       <c r="L18" s="10">
-        <v>425.39429982974309</v>
+        <v>426.97113047597901</v>
       </c>
       <c r="M18" s="10"/>
       <c r="N18" s="10"/>
@@ -5425,60 +5443,60 @@
       </c>
       <c r="B19" s="17">
         <f t="shared" ref="B19:N19" si="1">SUM(B7:B18)</f>
-        <v>28129.952413478011</v>
+        <v>28087.208355373888</v>
       </c>
       <c r="C19" s="17">
         <f t="shared" si="1"/>
-        <v>2378.929462043478</v>
+        <v>2383.1875690434781</v>
       </c>
       <c r="D19" s="17">
         <f t="shared" si="1"/>
-        <v>301.57402068287888</v>
+        <v>303.0587916482437</v>
       </c>
       <c r="E19" s="17">
         <f t="shared" si="1"/>
-        <v>4237</v>
+        <v>4243</v>
       </c>
       <c r="F19" s="17">
         <f t="shared" si="1"/>
-        <v>2197.0161544067801</v>
+        <v>2201.3095856658601</v>
       </c>
       <c r="G19" s="17">
         <f t="shared" si="1"/>
-        <v>269.28028577097513</v>
+        <v>270.72457505668928</v>
       </c>
       <c r="H19" s="17">
         <f t="shared" si="1"/>
-        <v>4862</v>
+        <v>4868</v>
       </c>
       <c r="I19" s="17">
         <f t="shared" si="1"/>
-        <v>5262.0000000000009</v>
+        <v>5268</v>
       </c>
       <c r="J19" s="17">
         <f t="shared" si="1"/>
-        <v>2447.4935454421775</v>
+        <v>2451.7321491156458</v>
       </c>
       <c r="K19" s="17">
         <f t="shared" si="1"/>
-        <v>1455.5649668474985</v>
+        <v>1459.9414587100666</v>
       </c>
       <c r="L19" s="17">
         <f t="shared" si="1"/>
-        <v>425.39429982974309</v>
+        <v>426.97113047597901</v>
       </c>
       <c r="M19" s="17">
         <f t="shared" si="1"/>
-        <v>3835.6741084165701</v>
+        <v>3971.737487745173</v>
       </c>
       <c r="N19" s="17">
         <f t="shared" si="1"/>
-        <v>458.02557003790901</v>
+        <v>239.54560791275179</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="40" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B20" s="45"/>
       <c r="C20" s="12">
@@ -5553,7 +5571,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
@@ -5627,7 +5645,7 @@
     </row>
     <row r="3" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>96</v>
@@ -5701,90 +5719,90 @@
         <v>126</v>
       </c>
       <c r="B4" s="10">
-        <v>2378.929462043478</v>
+        <v>2383.1875690434781</v>
       </c>
       <c r="C4" s="10">
-        <v>301.57402068287888</v>
+        <v>303.0587916482437</v>
       </c>
       <c r="D4" s="10">
-        <v>4237</v>
+        <v>4243</v>
       </c>
       <c r="E4" s="10">
-        <v>2197.0161544067801</v>
+        <v>2201.3095856658601</v>
       </c>
       <c r="F4" s="10">
-        <v>269.28028577097513</v>
+        <v>270.72457505668928</v>
       </c>
       <c r="G4" s="10">
-        <v>4862</v>
+        <v>4868</v>
       </c>
       <c r="H4" s="10">
-        <v>5262</v>
+        <v>5268</v>
       </c>
       <c r="I4" s="10">
-        <v>2447.493545442177</v>
+        <v>2451.7321491156458</v>
       </c>
       <c r="J4" s="10">
-        <v>1455.564966847498</v>
+        <v>1459.9414587100659</v>
       </c>
       <c r="K4" s="10">
-        <v>425.39429982974309</v>
+        <v>426.97113047597901</v>
       </c>
       <c r="L4" s="10">
-        <v>7.1879674609810484</v>
+        <v>7.0509124860646599</v>
       </c>
       <c r="M4" s="10">
-        <v>870.8077510628649</v>
+        <v>867.26713655688457</v>
       </c>
       <c r="N4" s="10">
-        <v>3329.8076923076919</v>
+        <v>3324.038461538461</v>
       </c>
       <c r="O4" s="10">
-        <v>5445.1923076923076</v>
+        <v>5439.4230769230771</v>
       </c>
       <c r="P4" s="10">
-        <v>1944.76186000706</v>
+        <v>2021.409212034383</v>
       </c>
       <c r="Q4" s="10">
-        <v>54.369534945986217</v>
+        <v>53.933417768672008</v>
       </c>
       <c r="R4" s="10">
-        <v>1127.006796932234</v>
+        <v>1123.1065578231289</v>
       </c>
       <c r="S4" s="10">
-        <v>3930.7692307692309</v>
+        <v>3925</v>
       </c>
       <c r="T4" s="10">
-        <v>5300.9615384615381</v>
+        <v>5295.1923076923076</v>
       </c>
       <c r="U4" s="10">
-        <v>5.3462453485667769</v>
+        <v>5.2322297808012097</v>
       </c>
       <c r="V4" s="10">
-        <v>272.10301328418421</v>
+        <v>270.24440116845182</v>
       </c>
       <c r="W4" s="10">
-        <v>1547.938796750884</v>
+        <v>1544.02754594373</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B5" s="10">
-        <v>48.966742997070128</v>
+        <v>48.979029165670333</v>
       </c>
       <c r="C5" s="10">
-        <v>120.6892655367232</v>
+        <v>120.7231638418079</v>
       </c>
       <c r="D5" s="10">
         <v>50</v>
       </c>
       <c r="E5" s="10">
-        <v>146.9363286170539</v>
+        <v>146.95130743374321</v>
       </c>
       <c r="F5" s="10">
-        <v>226.6825396825397</v>
+        <v>226.73015873015871</v>
       </c>
       <c r="G5" s="10">
         <v>50</v>
@@ -5793,19 +5811,19 @@
         <v>150</v>
       </c>
       <c r="I5" s="10">
-        <v>249.119615510518</v>
+        <v>249.13147569639941</v>
       </c>
       <c r="J5" s="10">
-        <v>347.82199025688828</v>
+        <v>347.81748730504171</v>
       </c>
       <c r="K5" s="10">
-        <v>428.43274853801171</v>
+        <v>428.46783625731001</v>
       </c>
       <c r="L5" s="10">
-        <v>92.183333333333337</v>
+        <v>92.233333333333334</v>
       </c>
       <c r="M5" s="10">
-        <v>159.61748097962101</v>
+        <v>159.6482455516244</v>
       </c>
       <c r="N5" s="10">
         <v>250</v>
@@ -5817,10 +5835,10 @@
         <v>450</v>
       </c>
       <c r="Q5" s="10">
-        <v>187.35593220338981</v>
+        <v>187.3898305084746</v>
       </c>
       <c r="R5" s="10">
-        <v>257.37495045567141</v>
+        <v>257.3945376704059</v>
       </c>
       <c r="S5" s="10">
         <v>350</v>
@@ -5829,33 +5847,33 @@
         <v>450</v>
       </c>
       <c r="U5" s="10">
-        <v>293.34920634920633</v>
+        <v>293.39682539682542</v>
       </c>
       <c r="V5" s="10">
-        <v>355.2798962493593</v>
+        <v>355.31891384215908</v>
       </c>
       <c r="W5" s="10">
-        <v>457.67572821850092</v>
+        <v>457.68892415882038</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" s="10">
-        <v>248.94176932103349</v>
+        <v>248.95453931929589</v>
       </c>
       <c r="C6" s="10">
-        <v>226.536231884058</v>
+        <v>226.5797101449275</v>
       </c>
       <c r="D6" s="10">
         <v>150</v>
       </c>
       <c r="E6" s="10">
-        <v>146.99188099386089</v>
+        <v>147.00639001540259</v>
       </c>
       <c r="F6" s="10">
-        <v>120.0119047619048</v>
+        <v>120.04761904761909</v>
       </c>
       <c r="G6" s="10">
         <v>50</v>
@@ -5864,19 +5882,19 @@
         <v>50</v>
       </c>
       <c r="I6" s="10">
-        <v>49.119615510518031</v>
+        <v>49.131475696399441</v>
       </c>
       <c r="J6" s="10">
-        <v>35.599482715745317</v>
+        <v>35.655331076269668</v>
       </c>
       <c r="K6" s="10">
-        <v>20.514767932489448</v>
+        <v>20.540084388185651</v>
       </c>
       <c r="L6" s="10">
-        <v>293.20289855072463</v>
+        <v>293.24637681159419</v>
       </c>
       <c r="M6" s="10">
-        <v>257.69896584638781</v>
+        <v>257.71820787570749</v>
       </c>
       <c r="N6" s="10">
         <v>250</v>
@@ -5888,10 +5906,10 @@
         <v>250</v>
       </c>
       <c r="Q6" s="10">
-        <v>186.67857142857139</v>
+        <v>186.71428571428569</v>
       </c>
       <c r="R6" s="10">
-        <v>159.48476865103959</v>
+        <v>159.51807133973799</v>
       </c>
       <c r="S6" s="10">
         <v>150</v>
@@ -5900,249 +5918,249 @@
         <v>150</v>
       </c>
       <c r="U6" s="10">
-        <v>93.349206349206355</v>
+        <v>93.396825396825392</v>
       </c>
       <c r="V6" s="10">
-        <v>84.909502787321941</v>
+        <v>84.958815257235571</v>
       </c>
       <c r="W6" s="10">
-        <v>60.49371674496966</v>
+        <v>60.519846475781527</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B7" s="23">
         <f t="shared" ref="B7:W7" si="0">B5*B4</f>
-        <v>116488.42757604129</v>
+        <v>116726.2134514435</v>
       </c>
       <c r="C7" s="23">
         <f t="shared" si="0"/>
-        <v>36396.747061173221</v>
+        <v>36586.216157851246</v>
       </c>
       <c r="D7" s="23">
         <f t="shared" si="0"/>
-        <v>211850</v>
+        <v>212150</v>
       </c>
       <c r="E7" s="23">
         <f t="shared" si="0"/>
-        <v>322821.4876408907</v>
+        <v>323485.32168002968</v>
       </c>
       <c r="F7" s="23">
         <f t="shared" si="0"/>
-        <v>61041.139065004696</v>
+        <v>61381.425874757922</v>
       </c>
       <c r="G7" s="23">
         <f t="shared" si="0"/>
-        <v>243100</v>
+        <v>243400</v>
       </c>
       <c r="H7" s="23">
         <f t="shared" si="0"/>
-        <v>789300</v>
+        <v>790200</v>
       </c>
       <c r="I7" s="23">
         <f t="shared" si="0"/>
-        <v>609718.65100502968</v>
+        <v>610803.64832148561</v>
       </c>
       <c r="J7" s="23">
         <f t="shared" si="0"/>
-        <v>506277.50371709839</v>
+        <v>507793.16978099244</v>
       </c>
       <c r="K7" s="23">
         <f t="shared" si="0"/>
-        <v>182252.84908845989</v>
+        <v>182943.39641938033</v>
       </c>
       <c r="L7" s="23">
         <f t="shared" si="0"/>
-        <v>662.61080044476967</v>
+        <v>650.32916163136383</v>
       </c>
       <c r="M7" s="23">
         <f t="shared" si="0"/>
-        <v>138996.13964218338</v>
+        <v>138457.67677588767</v>
       </c>
       <c r="N7" s="23">
         <f t="shared" si="0"/>
-        <v>832451.92307692301</v>
+        <v>831009.61538461526</v>
       </c>
       <c r="O7" s="23">
         <f t="shared" si="0"/>
-        <v>1905817.3076923077</v>
+        <v>1903798.076923077</v>
       </c>
       <c r="P7" s="23">
         <f t="shared" si="0"/>
-        <v>875142.83700317703</v>
+        <v>909634.14541547233</v>
       </c>
       <c r="Q7" s="23">
         <f t="shared" si="0"/>
-        <v>10186.454903270027</v>
+        <v>10106.5740144142</v>
       </c>
       <c r="R7" s="23">
         <f t="shared" si="0"/>
-        <v>290063.31852363865</v>
+        <v>289081.49320548528</v>
       </c>
       <c r="S7" s="23">
         <f t="shared" si="0"/>
-        <v>1375769.2307692308</v>
+        <v>1373750</v>
       </c>
       <c r="T7" s="23">
         <f t="shared" si="0"/>
-        <v>2385432.692307692</v>
+        <v>2382836.5384615385</v>
       </c>
       <c r="U7" s="23">
         <f t="shared" si="0"/>
-        <v>1568.3168299501999</v>
+        <v>1535.1196074338027</v>
       </c>
       <c r="V7" s="23">
         <f t="shared" si="0"/>
-        <v>96672.730328742997</v>
+        <v>96022.947095099007</v>
       </c>
       <c r="W7" s="23">
         <f t="shared" si="0"/>
-        <v>708454.01604063087</v>
+        <v>706684.30637456942</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B8" s="23">
         <f t="shared" ref="B8:W8" si="1">B6*B4</f>
-        <v>592214.90937103785</v>
+        <v>593305.36336269171</v>
       </c>
       <c r="C8" s="23">
         <f t="shared" si="1"/>
-        <v>68317.44227962436</v>
+        <v>68666.97316853104</v>
       </c>
       <c r="D8" s="23">
         <f t="shared" si="1"/>
-        <v>635550</v>
+        <v>636450</v>
       </c>
       <c r="E8" s="23">
         <f t="shared" si="1"/>
-        <v>322943.53711015132</v>
+        <v>323606.57549503969</v>
       </c>
       <c r="F8" s="23">
         <f t="shared" si="1"/>
-        <v>32316.840010204774</v>
+        <v>32499.840653233998</v>
       </c>
       <c r="G8" s="23">
         <f t="shared" si="1"/>
-        <v>243100</v>
+        <v>243400</v>
       </c>
       <c r="H8" s="23">
         <f t="shared" si="1"/>
-        <v>263100</v>
+        <v>263400</v>
       </c>
       <c r="I8" s="23">
         <f t="shared" si="1"/>
-        <v>120219.94191659433</v>
+        <v>120457.21849835652</v>
       </c>
       <c r="J8" s="23">
         <f t="shared" si="1"/>
-        <v>51817.359878931908</v>
+        <v>52054.696062279487</v>
       </c>
       <c r="K8" s="23">
         <f t="shared" si="1"/>
-        <v>8726.8653408110149</v>
+        <v>8770.023051295635</v>
       </c>
       <c r="L8" s="23">
         <f t="shared" si="1"/>
-        <v>2107.5328942479359</v>
+        <v>2067.6545397540917</v>
       </c>
       <c r="M8" s="23">
         <f t="shared" si="1"/>
-        <v>224406.25689991898</v>
+        <v>223510.53218293676</v>
       </c>
       <c r="N8" s="23">
         <f t="shared" si="1"/>
-        <v>832451.92307692301</v>
+        <v>831009.61538461526</v>
       </c>
       <c r="O8" s="23">
         <f t="shared" si="1"/>
-        <v>1361298.076923077</v>
+        <v>1359855.7692307692</v>
       </c>
       <c r="P8" s="23">
         <f t="shared" si="1"/>
-        <v>486190.465001765</v>
+        <v>505352.30300859577</v>
       </c>
       <c r="Q8" s="23">
         <f t="shared" si="1"/>
-        <v>10149.627112952496</v>
+        <v>10070.139574807758</v>
       </c>
       <c r="R8" s="23">
         <f t="shared" si="1"/>
-        <v>179740.41827688648</v>
+        <v>179155.79201295745</v>
       </c>
       <c r="S8" s="23">
         <f t="shared" si="1"/>
-        <v>589615.38461538462</v>
+        <v>588750</v>
       </c>
       <c r="T8" s="23">
         <f t="shared" si="1"/>
-        <v>795144.23076923075</v>
+        <v>794278.84615384613</v>
       </c>
       <c r="U8" s="23">
         <f t="shared" si="1"/>
-        <v>499.06776023684472</v>
+        <v>488.67365127356055</v>
       </c>
       <c r="V8" s="23">
         <f t="shared" si="1"/>
-        <v>23104.131564892137</v>
+        <v>22959.644153172754</v>
       </c>
       <c r="W8" s="23">
         <f t="shared" si="1"/>
-        <v>93640.571109197132</v>
+        <v>93444.310034892245</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B11" s="41"/>
       <c r="C11" s="17">
         <f>SUM(B7:K7)/SUM(B4:K4)</f>
-        <v>129.18334267488453</v>
+        <v>129.22931187474518</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" s="17">
         <f>SUM(B8:K8)/SUM(B4:K4)</f>
-        <v>98.098762498502595</v>
+        <v>98.116017067784028</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" s="17">
         <f>SUM(L7:W7)/SUM(L4:W4)</f>
-        <v>361.68510519485733</v>
+        <v>362.02018260640386</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="40" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B14" s="41"/>
       <c r="C14" s="17">
         <f>SUM(L8:W8)/SUM(L4:W4)</f>
-        <v>192.91403464807962</v>
+        <v>193.12103006568361</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="17">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
-        <v>251.09162751412518</v>
+        <v>251.43098852515158</v>
       </c>
     </row>
   </sheetData>
@@ -6172,7 +6190,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
@@ -6186,10 +6204,10 @@
     </row>
     <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>103</v>
@@ -6200,15 +6218,15 @@
         <v>126</v>
       </c>
       <c r="B4" s="10">
-        <v>3835.6741084165701</v>
+        <v>3971.737487745173</v>
       </c>
       <c r="C4" s="10">
-        <v>3835.6741084165701</v>
+        <v>3971.737487745173</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B5" s="10">
         <v>250</v>
@@ -6219,7 +6237,7 @@
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" s="10">
         <v>150</v>
@@ -6230,43 +6248,43 @@
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B7" s="23">
         <f>B5*B4</f>
-        <v>958918.52710414247</v>
+        <v>992934.3719362932</v>
       </c>
       <c r="C7" s="23">
         <f>C5*C4</f>
-        <v>1726053.3487874565</v>
+        <v>1787281.8694853277</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B8" s="23">
         <f>B6*B4</f>
-        <v>575351.11626248551</v>
+        <v>595760.62316177599</v>
       </c>
       <c r="C8" s="23">
         <f>C6*C4</f>
-        <v>958918.52710414247</v>
+        <v>992934.3719362932</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="40" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B11" s="41"/>
       <c r="C11" s="17">
         <f>SUM(B7:B7)/SUM(B4:B4)</f>
-        <v>249.99999999999997</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="40" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" s="17">
@@ -6276,7 +6294,7 @@
     </row>
     <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" s="17">
@@ -6286,22 +6304,22 @@
     </row>
     <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="40" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B14" s="41"/>
       <c r="C14" s="17">
         <f>SUM(C8:C8)/SUM(C4:C4)</f>
-        <v>249.99999999999997</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="17">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
-        <v>223.60679774997899</v>
+        <v>223.60679774997897</v>
       </c>
     </row>
   </sheetData>
@@ -6335,15 +6353,15 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
@@ -6353,10 +6371,10 @@
     </row>
     <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C4" s="41"/>
       <c r="D4" s="41"/>
@@ -6366,7 +6384,7 @@
     </row>
     <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B5" s="47">
         <v>1650</v>
@@ -6379,36 +6397,36 @@
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D8" s="10">
         <v>0.24</v>
@@ -6420,18 +6438,18 @@
         <v>10</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D9" s="10">
         <v>1.7</v>
@@ -6443,18 +6461,18 @@
         <v>100</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D10" s="10">
         <v>0.06</v>
@@ -6466,18 +6484,18 @@
         <v>100</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D11" s="10">
         <v>0.27</v>
@@ -6489,18 +6507,18 @@
         <v>100</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D12" s="10">
         <v>0.25</v>
@@ -6512,21 +6530,21 @@
         <v>100</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>100</v>
@@ -6535,12 +6553,12 @@
         <v>100</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -6573,57 +6591,57 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="40" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B4" s="41"/>
       <c r="C4" s="26">
         <f>'Табл. 5 скрепер'!$C$15</f>
-        <v>251.09162751412518</v>
+        <v>251.43098852515158</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B5" s="41"/>
       <c r="C5" s="26">
         <f>SUM('Табл. 4 распределение'!C5:L5)</f>
-        <v>23836.252735023529</v>
+        <v>23875.925259715965</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="40" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B6" s="41"/>
       <c r="C6" s="12">
         <f>C5*'Исходные данные'!$B$7</f>
-        <v>27411.690645277056</v>
+        <v>27457.314048673357</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="40" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B7" s="41"/>
       <c r="C7" s="26">
         <f>'Табл. 4 распределение'!B19*'Исходные данные'!$B$4</f>
-        <v>29255.150510017134</v>
+        <v>29210.696689588844</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="40" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B8" s="41"/>
       <c r="C8" s="33">
@@ -6632,7 +6650,7 @@
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="40" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B9" s="41"/>
       <c r="C9" s="33">
@@ -6641,7 +6659,7 @@
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="40" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B10" s="41"/>
       <c r="C10" s="33">
@@ -6650,29 +6668,29 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="42" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" s="41"/>
       <c r="E12" s="42" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F12" s="41"/>
       <c r="G12" s="41"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="18" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C13" s="41"/>
       <c r="E13" s="18" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G13" s="41"/>
     </row>
@@ -6681,11 +6699,11 @@
         <v>126</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C14" s="12">
         <f>$C$6</f>
-        <v>27411.690645277056</v>
+        <v>27457.314048673357</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>126</v>
@@ -6693,81 +6711,81 @@
       <c r="F14" s="24"/>
       <c r="G14" s="12">
         <f>$C$6</f>
-        <v>27411.690645277056</v>
+        <v>27457.314048673357</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B15" s="24"/>
       <c r="C15" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$8+'2.3 Грунт и нормы ЕНиР'!$E$8*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$8)/10</f>
-        <v>5.3029241777966289</v>
+        <v>5.3100507590281829</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F15" s="24"/>
       <c r="G15" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$9+'2.3 Грунт и нормы ЕНиР'!$E$9*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$9)/10</f>
-        <v>3.2109162751412521</v>
+        <v>3.2143098852515157</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="12">
         <f>C15*C14/800</f>
-        <v>181.70264634640171</v>
+        <v>182.24966413129144</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F16" s="24"/>
       <c r="G16" s="12">
         <f>G15*G14/800</f>
-        <v>110.02080452757164</v>
+        <v>110.3203949613826</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B17" s="24"/>
       <c r="C17" s="12">
         <f>100*$C$8*8/C15</f>
-        <v>301.72032379780353</v>
+        <v>301.3153871042889</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F17" s="24"/>
       <c r="G17" s="12">
         <f>100*$C$8*8/G15</f>
-        <v>498.30013083402929</v>
+        <v>497.77403458870361</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B18" s="24">
         <f>C16/($C$8*$C$9)</f>
-        <v>4.5425661586600423</v>
+        <v>4.5562416032822863</v>
       </c>
       <c r="C18" s="35">
         <f>ROUNDUP(ROUND(B18,6),0)</f>
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F18" s="24">
         <f>G16/($C$8*$C$9)</f>
-        <v>2.7505201131892911</v>
+        <v>2.7580098740345651</v>
       </c>
       <c r="G18" s="35">
         <f>ROUNDUP(ROUND(F18,6),0)</f>
@@ -6776,29 +6794,29 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="48" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="41"/>
       <c r="E19" s="48" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B20" s="49" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C20" s="41"/>
       <c r="E20" s="18" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F20" s="49" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G20" s="41"/>
     </row>
@@ -6807,11 +6825,11 @@
         <v>126</v>
       </c>
       <c r="B21" s="34" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C21" s="12">
         <f>$C$5</f>
-        <v>23836.252735023529</v>
+        <v>23875.925259715965</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>126</v>
@@ -6819,12 +6837,12 @@
       <c r="F21" s="24"/>
       <c r="G21" s="12">
         <f>$C$5</f>
-        <v>23836.252735023529</v>
+        <v>23875.925259715965</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B22" s="24"/>
       <c r="C22" s="14">
@@ -6832,7 +6850,7 @@
         <v>0.06</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F22" s="24"/>
       <c r="G22" s="14">
@@ -6842,25 +6860,25 @@
     </row>
     <row r="23" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B23" s="24"/>
       <c r="C23" s="12">
         <f>C22*C21/800</f>
-        <v>1.7877189551267645</v>
+        <v>1.7906943944786975</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F23" s="24"/>
       <c r="G23" s="12">
         <f>G22*G21/800</f>
-        <v>1.7877189551267645</v>
+        <v>1.7906943944786975</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B24" s="24"/>
       <c r="C24" s="12">
@@ -6868,7 +6886,7 @@
         <v>26666.666666666668</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F24" s="24"/>
       <c r="G24" s="12">
@@ -6878,22 +6896,22 @@
     </row>
     <row r="25" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B25" s="24">
         <f>C18*C17/C24</f>
-        <v>5.657256071208816E-2</v>
+        <v>5.6496635082054165E-2</v>
       </c>
       <c r="C25" s="35">
         <f>ROUNDUP(ROUND(B25,6),0)</f>
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F25" s="24">
         <f>G18*G17/G24</f>
-        <v>5.6058764718828293E-2</v>
+        <v>5.5999578891229154E-2</v>
       </c>
       <c r="G25" s="35">
         <f>ROUNDUP(ROUND(F25,6),0)</f>
@@ -6902,17 +6920,17 @@
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B26" s="49" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C26" s="41"/>
       <c r="E26" s="18" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G26" s="41"/>
     </row>
@@ -6923,7 +6941,7 @@
       <c r="B27" s="24"/>
       <c r="C27" s="12">
         <f>$C$7</f>
-        <v>29255.150510017134</v>
+        <v>29210.696689588844</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>126</v>
@@ -6931,12 +6949,12 @@
       <c r="F27" s="24"/>
       <c r="G27" s="12">
         <f>$C$7</f>
-        <v>29255.150510017134</v>
+        <v>29210.696689588844</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B28" s="24"/>
       <c r="C28" s="14">
@@ -6944,7 +6962,7 @@
         <v>0.25</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F28" s="24"/>
       <c r="G28" s="14">
@@ -6954,25 +6972,25 @@
     </row>
     <row r="29" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B29" s="24"/>
       <c r="C29" s="12">
         <f>C28*C27/800</f>
-        <v>9.1422345343803553</v>
+        <v>9.1283427154965135</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F29" s="24"/>
       <c r="G29" s="12">
         <f>G28*G27/800</f>
-        <v>9.8736132971307828</v>
+        <v>9.858610132736235</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B30" s="24"/>
       <c r="C30" s="12">
@@ -6980,7 +6998,7 @@
         <v>6400</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F30" s="24"/>
       <c r="G30" s="12">
@@ -6990,22 +7008,22 @@
     </row>
     <row r="31" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B31" s="24">
         <f>C18*C17/C30</f>
-        <v>0.23571900296703402</v>
+        <v>0.23540264617522572</v>
       </c>
       <c r="C31" s="35">
         <f>ROUNDUP(ROUND(B31,6),0)</f>
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F31" s="24">
         <f>G18*G17/G30</f>
-        <v>0.25226444123472735</v>
+        <v>0.25199810501053121</v>
       </c>
       <c r="G31" s="35">
         <f>ROUNDUP(ROUND(F31,6),0)</f>
@@ -7014,10 +7032,10 @@
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E32" s="18" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F32" s="49" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G32" s="41"/>
     </row>
@@ -7028,12 +7046,12 @@
       <c r="F33" s="24"/>
       <c r="G33" s="12">
         <f>$C$7</f>
-        <v>29255.150510017134</v>
+        <v>29210.696689588844</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E34" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F34" s="24"/>
       <c r="G34" s="14">
@@ -7043,17 +7061,17 @@
     </row>
     <row r="35" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E35" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F35" s="24"/>
       <c r="G35" s="12">
         <f>G34*G33/800</f>
-        <v>9.1422345343803553</v>
+        <v>9.1283427154965135</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E36" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F36" s="24"/>
       <c r="G36" s="12">
@@ -7063,11 +7081,11 @@
     </row>
     <row r="37" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E37" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F37" s="24">
         <f>G18*G17/G36</f>
-        <v>0.23357818632845123</v>
+        <v>0.23333157871345481</v>
       </c>
       <c r="G37" s="35">
         <f>ROUNDUP(ROUND(F37,6),0)</f>
@@ -7076,10 +7094,10 @@
     </row>
     <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E38" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F38" s="49" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G38" s="41"/>
     </row>
@@ -7090,46 +7108,46 @@
       <c r="F39" s="24"/>
       <c r="G39" s="12">
         <f>$C$6</f>
-        <v>27411.690645277056</v>
+        <v>27457.314048673357</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E40" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F40" s="24"/>
       <c r="G40" s="16">
         <f>G15/$C$10</f>
-        <v>1.070305425047084</v>
+        <v>1.0714366284171719</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E41" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F41" s="24"/>
       <c r="G41" s="12">
         <f>G40*G39/800</f>
-        <v>36.673601509190547</v>
+        <v>36.773464987127539</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E42" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F42" s="24"/>
       <c r="G42" s="12">
         <f>100*$C$8*8/G40</f>
-        <v>1494.9003925020879</v>
+        <v>1493.322103766111</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E43" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F43" s="24">
         <f>G18*G17/G42</f>
-        <v>1</v>
+        <v>0.99999999999999989</v>
       </c>
       <c r="G43" s="35">
         <f>ROUNDUP(ROUND(F43,6),0)</f>
@@ -7138,74 +7156,74 @@
     </row>
     <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="48" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B45" s="41"/>
       <c r="C45" s="17">
         <f>C16+C23+C29</f>
-        <v>192.63259983590882</v>
+        <v>193.16870124126663</v>
       </c>
       <c r="E45" s="48" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F45" s="41"/>
       <c r="G45" s="17">
         <f>G16+G23+G29+G35+G41</f>
-        <v>167.49797282340009</v>
+        <v>167.87150719122158</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B46" s="41"/>
       <c r="C46" s="17">
         <f>C14/C45</f>
-        <v>142.30037215210351</v>
+        <v>142.14162994438382</v>
       </c>
       <c r="E46" s="48" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F46" s="41"/>
       <c r="G46" s="17">
         <f>G14/G45</f>
-        <v>163.65386507798704</v>
+        <v>163.56149121480675</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="48" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B47" s="41"/>
       <c r="C47" s="36">
         <f>C45/C14</f>
-        <v>7.0273885083807766E-3</v>
+        <v>7.0352366185140337E-3</v>
       </c>
       <c r="E47" s="48" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F47" s="41"/>
       <c r="G47" s="36">
         <f>G45/G14</f>
-        <v>6.1104575777875068E-3</v>
+        <v>6.1139085525130799E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="40" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B48" s="41"/>
       <c r="C48" s="23">
         <f>C16/(C18*$C$8)</f>
-        <v>18.170264634640169</v>
+        <v>18.224966413129145</v>
       </c>
       <c r="E48" s="40" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F48" s="41"/>
       <c r="G48" s="23">
         <f>G16/(G18*$C$8)</f>
-        <v>18.336800754595274</v>
+        <v>18.386732493563766</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -7274,32 +7292,32 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="40" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B3" s="41"/>
       <c r="C3" s="26">
         <f>'Котлован (оконч.)'!$C$60</f>
-        <v>3970.4648798091712</v>
+        <v>3971.7374877451716</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="40" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B4" s="41"/>
       <c r="C4" s="14">
         <f>'Котлован (оконч.)'!$C$39</f>
-        <v>2.0911999999999997</v>
+        <v>2.0917999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B5" s="41"/>
       <c r="C5" s="37">
@@ -7309,48 +7327,48 @@
     </row>
     <row r="7" spans="1:10" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="32" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C8" s="10">
         <v>0.5</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E8" s="21">
         <v>2.9</v>
@@ -7374,16 +7392,16 @@
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="32" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C9" s="10">
         <v>0.65</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E9" s="21">
         <v>2.2999999999999998</v>
@@ -7407,16 +7425,16 @@
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C10" s="10">
         <v>0.65</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E10" s="21">
         <v>2.1</v>
@@ -7440,12 +7458,12 @@
     </row>
     <row r="11" spans="1:10" ht="93.6" x14ac:dyDescent="0.3">
       <c r="E11" s="38" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A12" s="48" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" s="15" t="str">
@@ -7453,21 +7471,21 @@
         <v>ЭО-4121А</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="40" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" s="12">
@@ -7475,7 +7493,7 @@
         <v>0.65</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F13" s="22">
         <v>0</v>
@@ -7490,7 +7508,7 @@
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="40" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B14" s="41"/>
       <c r="C14" s="23">
@@ -7498,7 +7516,7 @@
         <v>2.1</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F14" s="22">
         <v>500</v>
@@ -7513,7 +7531,7 @@
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="40" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B15" s="41"/>
       <c r="C15" s="12">
@@ -7521,7 +7539,7 @@
         <v>0.1</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F15" s="22">
         <v>1500</v>
@@ -7536,15 +7554,15 @@
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="40" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B16" s="41"/>
       <c r="C16" s="16">
         <f>C4-C15</f>
-        <v>1.9911999999999996</v>
+        <v>1.9917999999999996</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F16" s="22">
         <v>2000</v>
@@ -7559,7 +7577,7 @@
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="40" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B17" s="41"/>
       <c r="C17" s="3" t="str">
@@ -7567,7 +7585,7 @@
         <v>выполняется</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F17" s="22">
         <v>6000</v>
@@ -7582,12 +7600,12 @@
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="40" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B18" s="41"/>
       <c r="C18" s="12">
         <f>C14*C3/800</f>
-        <v>10.422470309499074</v>
+        <v>10.425810905331074</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>96</v>
@@ -7605,15 +7623,15 @@
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="40" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B19" s="41"/>
       <c r="C19" s="23">
         <f>C18/C5</f>
-        <v>5.211235154749537</v>
+        <v>5.2129054526655372</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F19" s="22">
         <v>13000</v>
@@ -7628,7 +7646,7 @@
     </row>
     <row r="20" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E20" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F20" s="22">
         <v>17000</v>
@@ -7643,12 +7661,12 @@
     </row>
     <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="40" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B22" s="41"/>
       <c r="C22" s="8">
@@ -7667,7 +7685,7 @@
     </row>
     <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="40" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B24" s="41"/>
       <c r="C24" s="39">
@@ -7677,7 +7695,7 @@
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="40" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="16">
@@ -7687,7 +7705,7 @@
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="40" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B26" s="41"/>
       <c r="C26" s="16">
@@ -7697,7 +7715,7 @@
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="40" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B27" s="41"/>
       <c r="C27" s="21">
@@ -7706,7 +7724,7 @@
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="40" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B28" s="41"/>
       <c r="C28" s="21">
@@ -7715,7 +7733,7 @@
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="40" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B29" s="41"/>
       <c r="C29" s="21">
@@ -7724,7 +7742,7 @@
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="40" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B30" s="41"/>
       <c r="C30" s="21">
@@ -7733,7 +7751,7 @@
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="40" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B31" s="41"/>
       <c r="C31" s="21">
@@ -7742,69 +7760,69 @@
     </row>
     <row r="33" spans="1:20" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="32" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B34" s="21">
         <v>4.5</v>
@@ -7880,7 +7898,7 @@
     </row>
     <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="32" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B35" s="21">
         <v>4.5</v>
@@ -7956,7 +7974,7 @@
     </row>
     <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="32" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B36" s="21">
         <v>3.8</v>
@@ -8032,7 +8050,7 @@
     </row>
     <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="32" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B37" s="21">
         <v>5.4</v>
@@ -8108,7 +8126,7 @@
     </row>
     <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="32" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B38" s="21">
         <v>5.5</v>
@@ -8184,7 +8202,7 @@
     </row>
     <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="32" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B39" s="21">
         <v>5.5</v>
@@ -8260,7 +8278,7 @@
     </row>
     <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="32" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B40" s="21">
         <v>10.5</v>
@@ -8336,7 +8354,7 @@
     </row>
     <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="32" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B41" s="21">
         <v>11</v>
@@ -8412,7 +8430,7 @@
     </row>
     <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="32" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B42" s="21">
         <v>12</v>
@@ -8488,7 +8506,7 @@
     </row>
     <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B43" s="21">
         <v>11</v>
@@ -8564,7 +8582,7 @@
     </row>
     <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="32" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B44" s="21">
         <v>6.6</v>
@@ -8640,7 +8658,7 @@
     </row>
     <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B45" s="21">
         <v>8.5</v>
@@ -8716,7 +8734,7 @@
     </row>
     <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B46" s="21">
         <v>6.5</v>
@@ -8792,7 +8810,7 @@
     </row>
     <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B47" s="21">
         <v>12</v>
@@ -8868,7 +8886,7 @@
     </row>
     <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B48" s="21">
         <v>10.5</v>
@@ -8944,7 +8962,7 @@
     </row>
     <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="32" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B49" s="21">
         <v>10.5</v>
@@ -9020,7 +9038,7 @@
     </row>
     <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="32" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B50" s="21">
         <v>20</v>
@@ -9096,7 +9114,7 @@
     </row>
     <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="32" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B51" s="21">
         <v>18</v>
@@ -9172,7 +9190,7 @@
     </row>
     <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="48" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B53" s="41"/>
       <c r="C53" s="15" t="str">
@@ -9182,7 +9200,7 @@
     </row>
     <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="40" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B54" s="41"/>
       <c r="C54" s="35">
@@ -9192,7 +9210,7 @@
     </row>
     <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="40" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B55" s="41"/>
       <c r="C55" s="35">
@@ -9202,7 +9220,7 @@
     </row>
     <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="40" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B56" s="41"/>
       <c r="C56" s="16">
@@ -12126,7 +12144,7 @@
         <v>32253.811756603707</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -12137,13 +12155,12 @@
         <f>'Котлован (черн.)'!$C$60</f>
         <v>3851.618956403689</v>
       </c>
-      <c r="D6" s="26">
-        <f>'Котлован (черн.)'!$C$70</f>
-        <v>132.29651566188372</v>
+      <c r="D6" s="10">
+        <v>0</v>
       </c>
       <c r="E6" s="12">
         <f>D6/'Исходные данные'!$B$4</f>
-        <v>127.20818813642664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -12157,11 +12174,11 @@
       </c>
       <c r="D7" s="17">
         <f>SUM(D5:D6)</f>
-        <v>33676.260742529739</v>
+        <v>33543.964226867858</v>
       </c>
       <c r="E7" s="17">
         <f>SUM(E5:E6)</f>
-        <v>32381.019944740136</v>
+        <v>32253.811756603707</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
@@ -12171,7 +12188,7 @@
       </c>
       <c r="C8" s="44">
         <f>C7-E7</f>
-        <v>-8319.9260275814158</v>
+        <v>-8192.7178394449875</v>
       </c>
       <c r="D8" s="41"/>
       <c r="E8" s="41"/>
@@ -12184,7 +12201,7 @@
       <c r="C10" s="41"/>
       <c r="D10" s="28">
         <f>ABS(C8)/MAX(C7,E7)</f>
-        <v>0.25693835591898573</v>
+        <v>0.25400774027173995</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -12205,8 +12222,8 @@
       <c r="B12" s="41"/>
       <c r="C12" s="41"/>
       <c r="D12" s="17">
-        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2-IF('Котлован (черн.)'!$C$37="насыпи",'Котлован (черн.)'!$C$48,0)</f>
-        <v>148027.81290639</v>
+        <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
+        <v>150000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -12216,8 +12233,8 @@
       <c r="B13" s="41"/>
       <c r="C13" s="41"/>
       <c r="D13" s="29">
-        <f>C8/D12</f>
-        <v>-5.6205154046576236E-2</v>
+        <f>C8*'Исходные данные'!$B$4/D12</f>
+        <v>-5.6802843686818587E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
@@ -12228,7 +12245,7 @@
       <c r="C14" s="41"/>
       <c r="D14" s="30">
         <f>ROUND(D13,4)</f>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -12269,7 +12286,7 @@
       </c>
       <c r="B3" s="14">
         <f>'Табл. 2 баланс (черн.)'!$D$14</f>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
@@ -12299,11 +12316,11 @@
       </c>
       <c r="C9" s="16">
         <f t="shared" ref="C9:C32" si="0">$B$3</f>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D9" s="16">
         <f t="shared" ref="D9:D32" si="1">B9+C9</f>
-        <v>-0.30620000000000003</v>
+        <v>-0.30680000000000002</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>51</v>
@@ -12334,35 +12351,35 @@
       </c>
       <c r="C10" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D10" s="16">
         <f t="shared" si="1"/>
-        <v>9.3799999999999994E-2</v>
+        <v>9.3199999999999991E-2</v>
       </c>
       <c r="F10" s="16">
         <f>D9</f>
-        <v>-0.30620000000000003</v>
+        <v>-0.30680000000000002</v>
       </c>
       <c r="G10" s="16">
         <f>D10</f>
-        <v>9.3799999999999994E-2</v>
+        <v>9.3199999999999991E-2</v>
       </c>
       <c r="H10" s="16">
         <f>D11</f>
-        <v>0.28380000000000005</v>
+        <v>0.28320000000000001</v>
       </c>
       <c r="I10" s="16">
         <f>D12</f>
-        <v>0.41379999999999995</v>
+        <v>0.41319999999999996</v>
       </c>
       <c r="J10" s="16">
         <f>D13</f>
-        <v>0.6038</v>
+        <v>0.60320000000000007</v>
       </c>
       <c r="K10" s="16">
         <f>D14</f>
-        <v>0.79379999999999995</v>
+        <v>0.79320000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -12375,11 +12392,11 @@
       </c>
       <c r="C11" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D11" s="16">
         <f t="shared" si="1"/>
-        <v>0.28380000000000005</v>
+        <v>0.28320000000000001</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>57</v>
@@ -12410,35 +12427,35 @@
       </c>
       <c r="C12" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D12" s="16">
         <f t="shared" si="1"/>
-        <v>0.41379999999999995</v>
+        <v>0.41319999999999996</v>
       </c>
       <c r="F12" s="16">
         <f>D15</f>
-        <v>-0.54620000000000002</v>
+        <v>-0.54679999999999995</v>
       </c>
       <c r="G12" s="16">
         <f>D16</f>
-        <v>-0.36619999999999997</v>
+        <v>-0.36680000000000001</v>
       </c>
       <c r="H12" s="16">
         <f>D17</f>
-        <v>0.22380000000000003</v>
+        <v>0.22320000000000001</v>
       </c>
       <c r="I12" s="16">
         <f>D18</f>
-        <v>0.46379999999999999</v>
+        <v>0.4632</v>
       </c>
       <c r="J12" s="16">
         <f>D19</f>
-        <v>0.78379999999999994</v>
+        <v>0.78320000000000001</v>
       </c>
       <c r="K12" s="16">
         <f>D20</f>
-        <v>0.41379999999999995</v>
+        <v>0.41319999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -12451,11 +12468,11 @@
       </c>
       <c r="C13" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D13" s="16">
         <f t="shared" si="1"/>
-        <v>0.6038</v>
+        <v>0.60320000000000007</v>
       </c>
       <c r="F13" s="11" t="s">
         <v>63</v>
@@ -12486,35 +12503,35 @@
       </c>
       <c r="C14" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D14" s="16">
         <f t="shared" si="1"/>
-        <v>0.79379999999999995</v>
+        <v>0.79320000000000002</v>
       </c>
       <c r="F14" s="16">
         <f>D21</f>
-        <v>-0.29620000000000002</v>
+        <v>-0.29680000000000001</v>
       </c>
       <c r="G14" s="16">
         <f>D22</f>
-        <v>-0.48619999999999997</v>
+        <v>-0.48680000000000001</v>
       </c>
       <c r="H14" s="16">
         <f>D23</f>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
       <c r="I14" s="16">
         <f>D24</f>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
       <c r="J14" s="16">
         <f>D25</f>
-        <v>0.30379999999999996</v>
+        <v>0.30319999999999997</v>
       </c>
       <c r="K14" s="16">
         <f>D26</f>
-        <v>0.70379999999999998</v>
+        <v>0.70320000000000005</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
@@ -12527,11 +12544,11 @@
       </c>
       <c r="C15" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D15" s="16">
         <f t="shared" si="1"/>
-        <v>-0.54620000000000002</v>
+        <v>-0.54679999999999995</v>
       </c>
       <c r="F15" s="11" t="s">
         <v>69</v>
@@ -12562,35 +12579,35 @@
       </c>
       <c r="C16" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D16" s="16">
         <f t="shared" si="1"/>
-        <v>-0.36619999999999997</v>
+        <v>-0.36680000000000001</v>
       </c>
       <c r="F16" s="16">
         <f>D27</f>
-        <v>-0.45620000000000005</v>
+        <v>-0.45680000000000004</v>
       </c>
       <c r="G16" s="16">
         <f>D28</f>
-        <v>-0.70620000000000005</v>
+        <v>-0.70679999999999998</v>
       </c>
       <c r="H16" s="16">
         <f>D29</f>
-        <v>-0.57620000000000005</v>
+        <v>-0.57679999999999998</v>
       </c>
       <c r="I16" s="16">
         <f>D30</f>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
       <c r="J16" s="16">
         <f>D31</f>
-        <v>-0.48619999999999997</v>
+        <v>-0.48680000000000001</v>
       </c>
       <c r="K16" s="16">
         <f>D32</f>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12603,11 +12620,11 @@
       </c>
       <c r="C17" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D17" s="16">
         <f t="shared" si="1"/>
-        <v>0.22380000000000003</v>
+        <v>0.22320000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12620,11 +12637,11 @@
       </c>
       <c r="C18" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D18" s="16">
         <f t="shared" si="1"/>
-        <v>0.46379999999999999</v>
+        <v>0.4632</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12637,11 +12654,11 @@
       </c>
       <c r="C19" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D19" s="16">
         <f t="shared" si="1"/>
-        <v>0.78379999999999994</v>
+        <v>0.78320000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12654,11 +12671,11 @@
       </c>
       <c r="C20" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D20" s="16">
         <f t="shared" si="1"/>
-        <v>0.41379999999999995</v>
+        <v>0.41319999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12671,11 +12688,11 @@
       </c>
       <c r="C21" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D21" s="16">
         <f t="shared" si="1"/>
-        <v>-0.29620000000000002</v>
+        <v>-0.29680000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12688,11 +12705,11 @@
       </c>
       <c r="C22" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D22" s="16">
         <f t="shared" si="1"/>
-        <v>-0.48619999999999997</v>
+        <v>-0.48680000000000001</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12705,11 +12722,11 @@
       </c>
       <c r="C23" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D23" s="16">
         <f t="shared" si="1"/>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12722,11 +12739,11 @@
       </c>
       <c r="C24" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D24" s="16">
         <f t="shared" si="1"/>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12739,11 +12756,11 @@
       </c>
       <c r="C25" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D25" s="16">
         <f t="shared" si="1"/>
-        <v>0.30379999999999996</v>
+        <v>0.30319999999999997</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12756,11 +12773,11 @@
       </c>
       <c r="C26" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D26" s="16">
         <f t="shared" si="1"/>
-        <v>0.70379999999999998</v>
+        <v>0.70320000000000005</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12773,11 +12790,11 @@
       </c>
       <c r="C27" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D27" s="16">
         <f t="shared" si="1"/>
-        <v>-0.45620000000000005</v>
+        <v>-0.45680000000000004</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12790,11 +12807,11 @@
       </c>
       <c r="C28" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D28" s="16">
         <f t="shared" si="1"/>
-        <v>-0.70620000000000005</v>
+        <v>-0.70679999999999998</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12807,11 +12824,11 @@
       </c>
       <c r="C29" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D29" s="16">
         <f t="shared" si="1"/>
-        <v>-0.57620000000000005</v>
+        <v>-0.57679999999999998</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12824,11 +12841,11 @@
       </c>
       <c r="C30" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D30" s="16">
         <f t="shared" si="1"/>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12841,11 +12858,11 @@
       </c>
       <c r="C31" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D31" s="16">
         <f t="shared" si="1"/>
-        <v>-0.48619999999999997</v>
+        <v>-0.48680000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
@@ -12858,11 +12875,11 @@
       </c>
       <c r="C32" s="16">
         <f t="shared" si="0"/>
-        <v>-5.62E-2</v>
+        <v>-5.6800000000000003E-2</v>
       </c>
       <c r="D32" s="16">
         <f t="shared" si="1"/>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -12936,22 +12953,22 @@
       </c>
       <c r="D5" s="14">
         <f>'Отметки (оконч.)'!$D$9</f>
-        <v>-0.30620000000000003</v>
+        <v>-0.30680000000000002</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>52</v>
       </c>
       <c r="F5" s="14">
         <f>'Отметки (оконч.)'!$D$10</f>
-        <v>9.3799999999999994E-2</v>
+        <v>9.3199999999999991E-2</v>
       </c>
       <c r="G5" s="12">
         <f>'Исходные данные'!$B$3*ABS(D5)/(ABS(D5)+ABS(F5))</f>
-        <v>76.550000000000011</v>
+        <v>76.7</v>
       </c>
       <c r="H5" s="12">
         <f>'Исходные данные'!$B$3-G5</f>
-        <v>23.449999999999989</v>
+        <v>23.299999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -12966,22 +12983,22 @@
       </c>
       <c r="D6" s="14">
         <f>'Отметки (оконч.)'!$D$10</f>
-        <v>9.3799999999999994E-2</v>
+        <v>9.3199999999999991E-2</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F6" s="14">
         <f>'Отметки (оконч.)'!$D$16</f>
-        <v>-0.36619999999999997</v>
+        <v>-0.36680000000000001</v>
       </c>
       <c r="G6" s="12">
         <f>'Исходные данные'!$B$3*ABS(D6)/(ABS(D6)+ABS(F6))</f>
-        <v>20.391304347826086</v>
+        <v>20.260869565217387</v>
       </c>
       <c r="H6" s="12">
         <f>'Исходные данные'!$B$3-G6</f>
-        <v>79.608695652173907</v>
+        <v>79.739130434782609</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -12996,22 +13013,22 @@
       </c>
       <c r="D7" s="14">
         <f>'Отметки (оконч.)'!$D$16</f>
-        <v>-0.36619999999999997</v>
+        <v>-0.36680000000000001</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F7" s="14">
         <f>'Отметки (оконч.)'!$D$17</f>
-        <v>0.22380000000000003</v>
+        <v>0.22320000000000001</v>
       </c>
       <c r="G7" s="12">
         <f>'Исходные данные'!$B$3*ABS(D7)/(ABS(D7)+ABS(F7))</f>
-        <v>62.067796610169488</v>
+        <v>62.169491525423723</v>
       </c>
       <c r="H7" s="12">
         <f>'Исходные данные'!$B$3-G7</f>
-        <v>37.932203389830512</v>
+        <v>37.830508474576277</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -13026,22 +13043,22 @@
       </c>
       <c r="D8" s="14">
         <f>'Отметки (оконч.)'!$D$17</f>
-        <v>0.22380000000000003</v>
+        <v>0.22320000000000001</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F8" s="14">
         <f>'Отметки (оконч.)'!$D$23</f>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
       <c r="G8" s="12">
         <f>'Исходные данные'!$B$3*ABS(D8)/(ABS(D8)+ABS(F8))</f>
-        <v>39.964285714285715</v>
+        <v>39.857142857142854</v>
       </c>
       <c r="H8" s="12">
         <f>'Исходные данные'!$B$3-G8</f>
-        <v>60.035714285714285</v>
+        <v>60.142857142857146</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -13056,22 +13073,22 @@
       </c>
       <c r="D9" s="14">
         <f>'Отметки (оконч.)'!$D$23</f>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F9" s="14">
         <f>'Отметки (оконч.)'!$D$24</f>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
       <c r="G9" s="12">
         <f>'Исходные данные'!$B$3*ABS(D9)/(ABS(D9)+ABS(F9))</f>
-        <v>80.047619047619051</v>
+        <v>80.190476190476204</v>
       </c>
       <c r="H9" s="12">
         <f>'Исходные данные'!$B$3-G9</f>
-        <v>19.952380952380949</v>
+        <v>19.809523809523796</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -13086,22 +13103,22 @@
       </c>
       <c r="D10" s="14">
         <f>'Отметки (оконч.)'!$D$24</f>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>72</v>
       </c>
       <c r="F10" s="14">
         <f>'Отметки (оконч.)'!$D$30</f>
-        <v>-0.33620000000000005</v>
+        <v>-0.33680000000000004</v>
       </c>
       <c r="G10" s="12">
         <f>'Исходные данные'!$B$3*ABS(D10)/(ABS(D10)+ABS(F10))</f>
-        <v>19.952380952380953</v>
+        <v>19.809523809523807</v>
       </c>
       <c r="H10" s="12">
         <f>'Исходные данные'!$B$3-G10</f>
-        <v>80.047619047619051</v>
+        <v>80.19047619047619</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
@@ -13116,22 +13133,22 @@
       </c>
       <c r="D11" s="14">
         <f>'Отметки (оконч.)'!$D$25</f>
-        <v>0.30379999999999996</v>
+        <v>0.30319999999999997</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>73</v>
       </c>
       <c r="F11" s="14">
         <f>'Отметки (оконч.)'!$D$31</f>
-        <v>-0.48619999999999997</v>
+        <v>-0.48680000000000001</v>
       </c>
       <c r="G11" s="12">
         <f>'Исходные данные'!$B$3*ABS(D11)/(ABS(D11)+ABS(F11))</f>
-        <v>38.455696202531641</v>
+        <v>38.379746835443029</v>
       </c>
       <c r="H11" s="12">
         <f>'Исходные данные'!$B$3-G11</f>
-        <v>61.544303797468359</v>
+        <v>61.620253164556971</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
@@ -13146,22 +13163,22 @@
       </c>
       <c r="D12" s="14">
         <f>'Отметки (оконч.)'!$D$31</f>
-        <v>-0.48619999999999997</v>
+        <v>-0.48680000000000001</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>74</v>
       </c>
       <c r="F12" s="14">
         <f>'Отметки (оконч.)'!$D$32</f>
-        <v>8.3800000000000013E-2</v>
+        <v>8.320000000000001E-2</v>
       </c>
       <c r="G12" s="12">
         <f>'Исходные данные'!$B$3*ABS(D12)/(ABS(D12)+ABS(F12))</f>
-        <v>85.298245614035096</v>
+        <v>85.403508771929822</v>
       </c>
       <c r="H12" s="12">
         <f>'Исходные данные'!$B$3-G12</f>
-        <v>14.701754385964904</v>
+        <v>14.596491228070178</v>
       </c>
     </row>
   </sheetData>
@@ -13249,34 +13266,34 @@
       </c>
       <c r="B6" s="12">
         <f>'Исходные данные'!$B$3^2-$F$6</f>
-        <v>9760.9119565217388</v>
+        <v>9763.9608695652169</v>
       </c>
       <c r="C6" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$15)+ABS('Отметки (оконч.)'!$D$16)+0)/5</f>
-        <v>0.24371999999999999</v>
+        <v>0.24407999999999999</v>
       </c>
       <c r="D6" s="12">
         <f>B6*C6</f>
-        <v>2378.929462043478</v>
+        <v>2383.1875690434781</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>97</v>
       </c>
       <c r="F6" s="12">
         <f>'ЛНР (оконч.)'!$G$6*'ЛНР (оконч.)'!$H$5/2</f>
-        <v>239.08804347826074</v>
+        <v>236.03913043478252</v>
       </c>
       <c r="G6" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$10)+0)/3</f>
-        <v>3.1266666666666665E-2</v>
+        <v>3.1066666666666663E-2</v>
       </c>
       <c r="H6" s="12">
         <f>F6*G6</f>
-        <v>7.475486159420285</v>
+        <v>7.3329489855072429</v>
       </c>
       <c r="I6" s="12">
         <f>H6/'Исходные данные'!$B$4</f>
-        <v>7.1879674609810431</v>
+        <v>7.0509124860646564</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13285,34 +13302,34 @@
       </c>
       <c r="B7" s="12">
         <f>'ЛНР (оконч.)'!$H$6*'ЛНР (оконч.)'!$G$7/2</f>
-        <v>2470.5681650700071</v>
+        <v>2478.6705969049372</v>
       </c>
       <c r="C7" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$16)+0)/3</f>
-        <v>0.12206666666666666</v>
+        <v>0.12226666666666668</v>
       </c>
       <c r="D7" s="12">
         <f>B7*C7</f>
-        <v>301.57402068287882</v>
+        <v>303.0587916482437</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>99</v>
       </c>
       <c r="F7" s="12">
         <f>'Исходные данные'!$B$3^2-$B$7</f>
-        <v>7529.4318349299929</v>
+        <v>7521.3294030950628</v>
       </c>
       <c r="G7" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$17)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$10)+0)/5</f>
-        <v>0.12028000000000001</v>
+        <v>0.11991999999999998</v>
       </c>
       <c r="H7" s="12">
         <f>F7*G7</f>
-        <v>905.64006110537969</v>
+        <v>901.95782201915983</v>
       </c>
       <c r="I7" s="12">
         <f>H7/'Исходные данные'!$B$4</f>
-        <v>870.80775106286501</v>
+        <v>867.26713655688445</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13337,15 +13354,15 @@
       </c>
       <c r="G8" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$17)+ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$11))/4</f>
-        <v>0.3463</v>
+        <v>0.34570000000000001</v>
       </c>
       <c r="H8" s="12">
         <f>F8*G8</f>
-        <v>3463</v>
+        <v>3457</v>
       </c>
       <c r="I8" s="12">
         <f>H8/'Исходные данные'!$B$4</f>
-        <v>3329.8076923076924</v>
+        <v>3324.0384615384614</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13370,15 +13387,15 @@
       </c>
       <c r="G9" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$12))/4</f>
-        <v>0.56630000000000003</v>
+        <v>0.56569999999999998</v>
       </c>
       <c r="H9" s="12">
         <f>F9*G9</f>
-        <v>5663</v>
+        <v>5657</v>
       </c>
       <c r="I9" s="12">
         <f>H9/'Исходные данные'!$B$4</f>
-        <v>5445.1923076923076</v>
+        <v>5439.4230769230771</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13403,15 +13420,15 @@
       </c>
       <c r="G10" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$13))/4</f>
-        <v>0.64880000000000004</v>
+        <v>0.6482</v>
       </c>
       <c r="H10" s="12">
         <f>F10*G10</f>
-        <v>6488</v>
+        <v>6482</v>
       </c>
       <c r="I10" s="12">
         <f>H10/'Исходные данные'!$B$4</f>
-        <v>6238.4615384615381</v>
+        <v>6232.6923076923076</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13424,11 +13441,11 @@
       </c>
       <c r="C11" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$16)+ABS('Отметки (оконч.)'!$D$15))/4</f>
-        <v>0.42370000000000002</v>
+        <v>0.42430000000000001</v>
       </c>
       <c r="D11" s="12">
         <f>B11*C11</f>
-        <v>4237</v>
+        <v>4243</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>100</v>
@@ -13452,34 +13469,34 @@
       </c>
       <c r="B12" s="12">
         <f>'Исходные данные'!$B$3^2-$F$12</f>
-        <v>9242.0332929782089</v>
+        <v>9246.0920096852296</v>
       </c>
       <c r="C12" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$16)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$23)+0)/5</f>
-        <v>0.23772000000000001</v>
+        <v>0.23808000000000001</v>
       </c>
       <c r="D12" s="12">
         <f>B12*C12</f>
-        <v>2197.0161544067801</v>
+        <v>2201.3095856658597</v>
       </c>
       <c r="E12" s="15" t="s">
         <v>106</v>
       </c>
       <c r="F12" s="12">
         <f>'ЛНР (оконч.)'!$G$8*'ЛНР (оконч.)'!$H$7/2</f>
-        <v>757.96670702179188</v>
+        <v>753.90799031477002</v>
       </c>
       <c r="G12" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$17)+0)/3</f>
-        <v>7.4600000000000014E-2</v>
+        <v>7.4400000000000008E-2</v>
       </c>
       <c r="H12" s="12">
         <f>F12*G12</f>
-        <v>56.544316343825685</v>
+        <v>56.090754479418898</v>
       </c>
       <c r="I12" s="12">
         <f>H12/'Исходные данные'!$B$4</f>
-        <v>54.369534945986231</v>
+        <v>53.933417768672015</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13488,34 +13505,34 @@
       </c>
       <c r="B13" s="12">
         <f>'ЛНР (оконч.)'!$H$8*'ЛНР (оконч.)'!$G$9/2</f>
-        <v>2402.857993197279</v>
+        <v>2411.4421768707489</v>
       </c>
       <c r="C13" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$23)+0)/3</f>
-        <v>0.11206666666666669</v>
+        <v>0.11226666666666668</v>
       </c>
       <c r="D13" s="12">
         <f>B13*C13</f>
-        <v>269.28028577097513</v>
+        <v>270.72457505668945</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>108</v>
       </c>
       <c r="F13" s="12">
         <f>'Исходные данные'!$B$3^2-$B$13</f>
-        <v>7597.142006802721</v>
+        <v>7588.5578231292511</v>
       </c>
       <c r="G13" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$24)+ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$17)+0)/5</f>
-        <v>0.15428</v>
+        <v>0.15392</v>
       </c>
       <c r="H13" s="12">
         <f>F13*G13</f>
-        <v>1172.0870688095238</v>
+        <v>1168.0308201360544</v>
       </c>
       <c r="I13" s="12">
         <f>H13/'Исходные данные'!$B$4</f>
-        <v>1127.0067969322345</v>
+        <v>1123.1065578231292</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13540,15 +13557,15 @@
       </c>
       <c r="G14" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$24)+ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$18))/4</f>
-        <v>0.40879999999999994</v>
+        <v>0.40820000000000001</v>
       </c>
       <c r="H14" s="12">
         <f>F14*G14</f>
-        <v>4087.9999999999995</v>
+        <v>4082</v>
       </c>
       <c r="I14" s="12">
         <f>H14/'Исходные данные'!$B$4</f>
-        <v>3930.76923076923</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13573,15 +13590,15 @@
       </c>
       <c r="G15" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$19))/4</f>
-        <v>0.55130000000000001</v>
+        <v>0.55069999999999997</v>
       </c>
       <c r="H15" s="12">
         <f>F15*G15</f>
-        <v>5513</v>
+        <v>5507</v>
       </c>
       <c r="I15" s="12">
         <f>H15/'Исходные данные'!$B$4</f>
-        <v>5300.9615384615381</v>
+        <v>5295.1923076923076</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13594,11 +13611,11 @@
       </c>
       <c r="C16" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$21))/4</f>
-        <v>0.48620000000000002</v>
+        <v>0.48679999999999995</v>
       </c>
       <c r="D16" s="12">
         <f>B16*C16</f>
-        <v>4862</v>
+        <v>4868</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>100</v>
@@ -13626,11 +13643,11 @@
       </c>
       <c r="C17" s="16">
         <f>(ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$23)+ABS('Отметки (оконч.)'!$D$22))/4</f>
-        <v>0.5262</v>
+        <v>0.52679999999999993</v>
       </c>
       <c r="D17" s="12">
         <f>B17*C17</f>
-        <v>5262</v>
+        <v>5267.9999999999991</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>100</v>
@@ -13654,34 +13671,34 @@
       </c>
       <c r="B18" s="12">
         <f>'Исходные данные'!$B$3^2-$F$18</f>
-        <v>9800.9512471655325</v>
+        <v>9803.7913832199556</v>
       </c>
       <c r="C18" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$23)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$30)+0)/5</f>
-        <v>0.24972000000000003</v>
+        <v>0.25007999999999997</v>
       </c>
       <c r="D18" s="12">
         <f>B18*C18</f>
-        <v>2447.493545442177</v>
+        <v>2451.7321491156463</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>114</v>
       </c>
       <c r="F18" s="12">
         <f>'ЛНР (оконч.)'!$G$10*'ЛНР (оконч.)'!$H$9/2</f>
-        <v>199.04875283446708</v>
+        <v>196.20861678004519</v>
       </c>
       <c r="G18" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$24)+0)/3</f>
-        <v>2.7933333333333338E-2</v>
+        <v>2.7733333333333336E-2</v>
       </c>
       <c r="H18" s="12">
         <f>F18*G18</f>
-        <v>5.5600951625094481</v>
+        <v>5.4415189720332533</v>
       </c>
       <c r="I18" s="12">
         <f>H18/'Исходные данные'!$B$4</f>
-        <v>5.3462453485667769</v>
+        <v>5.2322297808012053</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13690,34 +13707,34 @@
       </c>
       <c r="B19" s="12">
         <f>('ЛНР (оконч.)'!$H$10+'ЛНР (оконч.)'!$H$11)/2*'Исходные данные'!$B$3</f>
-        <v>7079.5961422543714</v>
+        <v>7090.5364677516591</v>
       </c>
       <c r="C19" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$31)+0)/4</f>
-        <v>0.2056</v>
+        <v>0.20590000000000003</v>
       </c>
       <c r="D19" s="12">
         <f>B19*C19</f>
-        <v>1455.5649668474989</v>
+        <v>1459.9414587100669</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>116</v>
       </c>
       <c r="F19" s="12">
         <f>('ЛНР (оконч.)'!$G$11+'ЛНР (оконч.)'!$G$10)/2*'Исходные данные'!$B$3</f>
-        <v>2920.4038577456295</v>
+        <v>2909.4635322483418</v>
       </c>
       <c r="G19" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$24)+0)/4</f>
-        <v>9.6899999999999986E-2</v>
+        <v>9.6599999999999991E-2</v>
       </c>
       <c r="H19" s="12">
         <f>F19*G19</f>
-        <v>282.98713381555143</v>
+        <v>281.05417721518978</v>
       </c>
       <c r="I19" s="12">
         <f>H19/'Исходные данные'!$B$4</f>
-        <v>272.10301328418404</v>
+        <v>270.2444011684517</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13726,34 +13743,34 @@
       </c>
       <c r="B20" s="12">
         <f>'ЛНР (оконч.)'!$H$11*'ЛНР (оконч.)'!$G$12/2</f>
-        <v>2624.8105707306245</v>
+        <v>2631.2929158338889</v>
       </c>
       <c r="C20" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$31)+0)/3</f>
-        <v>0.16206666666666666</v>
+        <v>0.16226666666666667</v>
       </c>
       <c r="D20" s="12">
         <f>B20*C20</f>
-        <v>425.3942998297432</v>
+        <v>426.97113047597907</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>118</v>
       </c>
       <c r="F20" s="12">
         <f>'Исходные данные'!$B$3^2-$B$20</f>
-        <v>7375.189429269376</v>
+        <v>7368.7070841661116</v>
       </c>
       <c r="G20" s="16">
         <f>(0+ABS('Отметки (оконч.)'!$D$32)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$25)+0)/5</f>
-        <v>0.21827999999999997</v>
+        <v>0.21792000000000003</v>
       </c>
       <c r="H20" s="12">
         <f>F20*G20</f>
-        <v>1609.8563486209191</v>
+        <v>1605.7886477814793</v>
       </c>
       <c r="I20" s="12">
         <f>H20/'Исходные данные'!$B$4</f>
-        <v>1547.9387967508837</v>
+        <v>1544.02754594373</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13762,28 +13779,28 @@
       </c>
       <c r="B21" s="17">
         <f>SUM(B6:B20)</f>
-        <v>73381.729367917767</v>
+        <v>73425.786419831638</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="17">
         <f>SUM(D6:D20)</f>
-        <v>23836.252735023529</v>
+        <v>23875.925259715961</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>119</v>
       </c>
       <c r="F21" s="17">
         <f>SUM(F6:F20)</f>
-        <v>76618.270632082233</v>
+        <v>76574.213580168347</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="17">
         <f>SUM(H6:H20)</f>
-        <v>29255.150510017127</v>
+        <v>29210.69668958884</v>
       </c>
       <c r="I21" s="17">
         <f>SUM(I6:I20)</f>
-        <v>28129.952413478011</v>
+        <v>28087.208355373888</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13817,21 +13834,21 @@
       </c>
       <c r="B25" s="16">
         <f>ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$31)+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$15)</f>
-        <v>3.7096</v>
+        <v>3.7144000000000004</v>
       </c>
       <c r="C25" s="3">
         <v>8</v>
       </c>
       <c r="D25" s="12">
         <f>'ЛНР (оконч.)'!$G$5+'ЛНР (оконч.)'!$G$12+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3</f>
-        <v>861.84824561403514</v>
+        <v>862.1035087719298</v>
       </c>
       <c r="E25" s="10">
         <v>0.25</v>
       </c>
       <c r="F25" s="12">
         <f>(B25/C25)^2*D25*E25/2</f>
-        <v>23.16407736281031</v>
+        <v>23.230940528839916</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13840,21 +13857,21 @@
       </c>
       <c r="B26" s="16">
         <f>ABS('Отметки (оконч.)'!$D$10)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$32)</f>
-        <v>3.3904000000000005</v>
+        <v>3.3855999999999997</v>
       </c>
       <c r="C26" s="3">
         <v>8</v>
       </c>
       <c r="D26" s="12">
         <f>'ЛНР (оконч.)'!$H$5+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'Исходные данные'!$B$3+'ЛНР (оконч.)'!$H$12</f>
-        <v>738.15175438596498</v>
+        <v>737.89649122807009</v>
       </c>
       <c r="E26" s="10">
         <v>0.25</v>
       </c>
       <c r="F26" s="12">
         <f>(B26/C26)^2*D26*E26/2</f>
-        <v>16.572101098127199</v>
+        <v>16.519495360140347</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13898,7 +13915,7 @@
       <c r="E31" s="41"/>
       <c r="F31" s="17">
         <f>D21+F25</f>
-        <v>23859.416812386338</v>
+        <v>23899.156200244801</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
@@ -13911,7 +13928,7 @@
       <c r="E32" s="41"/>
       <c r="F32" s="17">
         <f>H21+F26</f>
-        <v>29271.722611115256</v>
+        <v>29227.216184948978</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
@@ -13924,7 +13941,7 @@
       <c r="E33" s="41"/>
       <c r="F33" s="17">
         <f>F32/'Исходные данные'!$B$4</f>
-        <v>28145.887126072361</v>
+        <v>28103.092485527864</v>
       </c>
     </row>
   </sheetData>

--- a/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
+++ b/kursovaya-tsp/Объёмы_планировки_вариант2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Kursovoy\.claude\worktrees\earthwork-drawings-autocad-d57f76\kursovaya-tsp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62D731E-D3D9-4F0B-AFDE-BE9619795814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C46F983-06BB-45E0-9530-8A0A8684C8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3360" yWindow="1404" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Содержание" sheetId="1" r:id="rId1"/>
@@ -2784,7 +2784,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2820,6 +2820,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3536,13 +3537,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -3551,13 +3552,13 @@
       <c r="B6" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>2.4</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -3566,13 +3567,13 @@
       <c r="B7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>0.4</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -3581,13 +3582,13 @@
       <c r="B8" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>0.15</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="20"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -3596,13 +3597,13 @@
       <c r="B9" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>0.1</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="20"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -3611,13 +3612,13 @@
       <c r="B10" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>0.2</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3628,13 +3629,13 @@
       <c r="B11" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>0.4</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>161</v>
       </c>
     </row>
@@ -3643,13 +3644,13 @@
         <v>162</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>0.5</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3658,13 +3659,13 @@
         <v>164</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>0.2</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>165</v>
       </c>
     </row>
@@ -3673,13 +3674,13 @@
         <v>166</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>0.5</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3688,78 +3689,78 @@
         <v>167</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <v>60</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E15" s="20"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <v>30</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E16" s="20"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>169</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="21">
+      <c r="C18" s="22">
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="20"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>171</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <v>200</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="20"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>172</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <v>100</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E20" s="20"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
@@ -3768,14 +3769,14 @@
       <c r="B21" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
         <v>220</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -3784,37 +3785,37 @@
       <c r="B22" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>$C$20+'Исходные данные'!$B$3/2-$C$16/2</f>
         <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="20"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <f>$C$11/2</f>
         <v>0.2</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -3823,42 +3824,42 @@
       <c r="B25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <f>$C$24+$C$12</f>
         <v>0.7</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="20"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>181</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <f>$C$25+$C$13</f>
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="20"/>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>182</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <f>$C$26+$C$14</f>
         <v>1.4</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="20"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -3867,14 +3868,14 @@
       <c r="B28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <f>$C$27-$C$25</f>
         <v>0.7</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="21" t="s">
         <v>185</v>
       </c>
     </row>
@@ -3885,13 +3886,13 @@
       <c r="B29" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="22">
         <v>2.5</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3902,14 +3903,14 @@
       <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="24">
         <f>1+2*$C$29+1</f>
         <v>7</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="21" t="s">
         <v>191</v>
       </c>
     </row>
@@ -3918,23 +3919,23 @@
         <v>192</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <f>$C$25+$C$30</f>
         <v>7.7</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="20"/>
+      <c r="E31" s="21"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
     </row>
     <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -3948,7 +3949,7 @@
         <v>0.67</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="21" t="s">
         <v>196</v>
       </c>
     </row>
@@ -3957,28 +3958,28 @@
         <v>197</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="24">
+      <c r="C34" s="25">
         <f>$C$27+$C$6*$C$33</f>
         <v>3.008</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="20"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>198</v>
       </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="24">
+      <c r="C35" s="25">
         <f>$C$31+$C$6*$C$33</f>
         <v>9.3079999999999998</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="20"/>
+      <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -3987,14 +3988,14 @@
       <c r="B36" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="17">
         <f>AVERAGE(H75:H80)</f>
         <v>9.3763323050666647E-2</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="21" t="s">
         <v>201</v>
       </c>
     </row>
@@ -4003,12 +4004,12 @@
         <v>202</v>
       </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="24" t="str">
+      <c r="C37" s="25" t="str">
         <f>IF($C$36&gt;0,"насыпи","выемки")</f>
         <v>насыпи</v>
       </c>
       <c r="D37" s="3"/>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>203</v>
       </c>
     </row>
@@ -4019,14 +4020,14 @@
       <c r="B38" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="17">
         <f>('Отметки (оконч.)'!$D$17+'Отметки (оконч.)'!$D$18+'Отметки (оконч.)'!$D$23+'Отметки (оконч.)'!$D$24)/4</f>
         <v>0.10819999999999999</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="21" t="s">
         <v>206</v>
       </c>
     </row>
@@ -4037,25 +4038,25 @@
       <c r="B39" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="17">
         <f>IF($C$37="насыпи",$C$6-$C$10-$C$38,$C$6-$C$10)</f>
         <v>2.0917999999999997</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="21" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -4069,7 +4070,7 @@
         <v>0.67</v>
       </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="21" t="s">
         <v>212</v>
       </c>
     </row>
@@ -4080,14 +4081,14 @@
       <c r="B42" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="17">
         <f>$C$39*$C$41</f>
         <v>1.4015059999999999</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="21" t="s">
         <v>215</v>
       </c>
     </row>
@@ -4096,28 +4097,28 @@
         <v>216</v>
       </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="24">
+      <c r="C43" s="25">
         <f>$C$15+$C$27+$C$31</f>
         <v>69.099999999999994</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="20"/>
+      <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>217</v>
       </c>
       <c r="B44" s="3"/>
-      <c r="C44" s="24">
+      <c r="C44" s="25">
         <f>$C$16+2*$C$27</f>
         <v>32.799999999999997</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="20"/>
+      <c r="E44" s="21"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
@@ -4133,7 +4134,7 @@
       <c r="D45" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="21" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4142,28 +4143,28 @@
         <v>222</v>
       </c>
       <c r="B46" s="3"/>
-      <c r="C46" s="24">
+      <c r="C46" s="25">
         <f>$C$43+2*$C$42</f>
         <v>71.90301199999999</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E46" s="20"/>
+      <c r="E46" s="21"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>223</v>
       </c>
       <c r="B47" s="3"/>
-      <c r="C47" s="24">
+      <c r="C47" s="25">
         <f>$C$44+2*$C$42</f>
         <v>35.603012</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="20"/>
+      <c r="E47" s="21"/>
     </row>
     <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
@@ -4179,7 +4180,7 @@
       <c r="D48" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E48" s="20"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
@@ -4195,7 +4196,7 @@
       <c r="D49" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="20"/>
+      <c r="E49" s="21"/>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
@@ -4211,7 +4212,7 @@
       <c r="D50" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E50" s="20"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
@@ -4227,16 +4228,16 @@
       <c r="D51" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E51" s="20"/>
+      <c r="E51" s="21"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="B52" s="43"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
     </row>
     <row r="53" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
@@ -4245,13 +4246,13 @@
       <c r="B53" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C53" s="21">
+      <c r="C53" s="22">
         <v>6</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="21" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4266,7 +4267,7 @@
         <v>0.1</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="21" t="s">
         <v>238</v>
       </c>
     </row>
@@ -4282,7 +4283,7 @@
         <v>10</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="21" t="s">
         <v>241</v>
       </c>
     </row>
@@ -4291,14 +4292,14 @@
         <v>242</v>
       </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="24">
+      <c r="C56" s="25">
         <f>$C$39*$C$55</f>
         <v>20.917999999999996</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E56" s="20"/>
+      <c r="E56" s="21"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
@@ -4314,18 +4315,18 @@
       <c r="D57" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="21" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="46" t="s">
         <v>247</v>
       </c>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
@@ -4339,7 +4340,7 @@
       <c r="D59" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="21" t="s">
         <v>249</v>
       </c>
     </row>
@@ -4357,7 +4358,7 @@
       <c r="D60" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E60" s="20"/>
+      <c r="E60" s="21"/>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -4373,7 +4374,7 @@
       <c r="D61" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="21" t="s">
         <v>254</v>
       </c>
     </row>
@@ -4391,7 +4392,7 @@
       <c r="D62" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="21" t="s">
         <v>257</v>
       </c>
     </row>
@@ -4408,7 +4409,7 @@
       <c r="D63" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="21" t="s">
         <v>260</v>
       </c>
     </row>
@@ -4425,7 +4426,7 @@
       <c r="D64" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="21" t="s">
         <v>263</v>
       </c>
     </row>
@@ -4443,7 +4444,7 @@
       <c r="D65" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="21" t="s">
         <v>266</v>
       </c>
     </row>
@@ -4452,14 +4453,14 @@
         <v>267</v>
       </c>
       <c r="B66" s="3"/>
-      <c r="C66" s="24">
+      <c r="C66" s="25">
         <f>$C$39-$C$7-$C$8-$C$9</f>
         <v>1.4417999999999997</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="21" t="s">
         <v>268</v>
       </c>
     </row>
@@ -4477,7 +4478,7 @@
       <c r="D67" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E67" s="20"/>
+      <c r="E67" s="21"/>
     </row>
     <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
@@ -4493,7 +4494,7 @@
       <c r="D68" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="21" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4511,7 +4512,7 @@
       <c r="D69" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="21" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4529,7 +4530,7 @@
       <c r="D70" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E70" s="20"/>
+      <c r="E70" s="21"/>
     </row>
     <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
@@ -4545,7 +4546,7 @@
       <c r="D71" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E71" s="20" t="s">
+      <c r="E71" s="21" t="s">
         <v>280</v>
       </c>
     </row>
@@ -4584,31 +4585,31 @@
       <c r="A75" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B75" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="25">
         <f t="shared" ref="D75:D80" si="0">$C$21+B75</f>
         <v>216.99199999999999</v>
       </c>
-      <c r="E75" s="24">
+      <c r="E75" s="25">
         <f t="shared" ref="E75:E80" si="1">$C$22+C75</f>
         <v>131.99199999999999</v>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="17">
         <f>(D75-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G75" s="16">
+      <c r="G75" s="17">
         <f>(E75-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H75" s="16">
+      <c r="H75" s="17">
         <f>'Отметки (оконч.)'!$D$23*(1-F75)*(1-G75)+'Отметки (оконч.)'!$D$24*F75*(1-G75)+'Отметки (оконч.)'!$D$17*(1-F75)*G75+'Отметки (оконч.)'!$D$18*F75*G75</f>
         <v>-9.6063345152000115E-2</v>
       </c>
@@ -4617,31 +4618,31 @@
       <c r="A76" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B76" s="25">
         <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C76" s="24">
+      <c r="C76" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D76" s="24">
+      <c r="D76" s="25">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E76" s="24">
+      <c r="E76" s="25">
         <f t="shared" si="1"/>
         <v>131.99199999999999</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="17">
         <f>(D76-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G76" s="16">
+      <c r="G76" s="17">
         <f>(E76-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H76" s="16">
+      <c r="H76" s="17">
         <f>'Отметки (оконч.)'!$D$23*(1-F76)*(1-G76)+'Отметки (оконч.)'!$D$24*F76*(1-G76)+'Отметки (оконч.)'!$D$17*(1-F76)*G76+'Отметки (оконч.)'!$D$18*F76*G76</f>
         <v>-9.0259028480000059E-3</v>
       </c>
@@ -4650,31 +4651,31 @@
       <c r="A77" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B77" s="25">
         <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C77" s="24">
+      <c r="C77" s="25">
         <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D77" s="24">
+      <c r="D77" s="25">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E77" s="24">
+      <c r="E77" s="25">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="17">
         <f>(D77-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G77" s="16">
+      <c r="G77" s="17">
         <f>(E77-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H77" s="16">
+      <c r="H77" s="17">
         <f>'Отметки (оконч.)'!$D$23*(1-F77)*(1-G77)+'Отметки (оконч.)'!$D$24*F77*(1-G77)+'Отметки (оконч.)'!$D$17*(1-F77)*G77+'Отметки (оконч.)'!$D$18*F77*G77</f>
         <v>4.9316369151999967E-2</v>
       </c>
@@ -4683,31 +4684,31 @@
       <c r="A78" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B78" s="25">
         <f>$C$15+$C$35</f>
         <v>69.307999999999993</v>
       </c>
-      <c r="C78" s="24">
+      <c r="C78" s="25">
         <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D78" s="24">
+      <c r="D78" s="25">
         <f t="shared" si="0"/>
         <v>289.30799999999999</v>
       </c>
-      <c r="E78" s="24">
+      <c r="E78" s="25">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="17">
         <f>(D78-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.89307999999999987</v>
       </c>
-      <c r="G78" s="16">
+      <c r="G78" s="17">
         <f>(E78-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H78" s="16">
+      <c r="H78" s="17">
         <f>'Отметки (оконч.)'!$D$23*(1-F78)*(1-G78)+'Отметки (оконч.)'!$D$24*F78*(1-G78)+'Отметки (оконч.)'!$D$17*(1-F78)*G78+'Отметки (оконч.)'!$D$18*F78*G78</f>
         <v>0.21392972435199992</v>
       </c>
@@ -4716,31 +4717,31 @@
       <c r="A79" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B79" s="25">
         <f>$C$15+$C$35</f>
         <v>69.307999999999993</v>
       </c>
-      <c r="C79" s="24">
+      <c r="C79" s="25">
         <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D79" s="24">
+      <c r="D79" s="25">
         <f t="shared" si="0"/>
         <v>289.30799999999999</v>
       </c>
-      <c r="E79" s="24">
+      <c r="E79" s="25">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="17">
         <f>(D79-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.89307999999999987</v>
       </c>
-      <c r="G79" s="16">
+      <c r="G79" s="17">
         <f>(E79-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H79" s="16">
+      <c r="H79" s="17">
         <f>'Отметки (оконч.)'!$D$23*(1-F79)*(1-G79)+'Отметки (оконч.)'!$D$24*F79*(1-G79)+'Отметки (оконч.)'!$D$17*(1-F79)*G79+'Отметки (оконч.)'!$D$18*F79*G79</f>
         <v>0.30981254764800004</v>
       </c>
@@ -4749,37 +4750,37 @@
       <c r="A80" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B80" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C80" s="24">
+      <c r="C80" s="25">
         <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D80" s="24">
+      <c r="D80" s="25">
         <f t="shared" si="0"/>
         <v>216.99199999999999</v>
       </c>
-      <c r="E80" s="24">
+      <c r="E80" s="25">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="17">
         <f>(D80-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G80" s="16">
+      <c r="G80" s="17">
         <f>(E80-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H80" s="16">
+      <c r="H80" s="17">
         <f>'Отметки (оконч.)'!$D$23*(1-F80)*(1-G80)+'Отметки (оконч.)'!$D$24*F80*(1-G80)+'Отметки (оконч.)'!$D$17*(1-F80)*G80+'Отметки (оконч.)'!$D$18*F80*G80</f>
         <v>9.4610545152000028E-2</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="25" t="s">
+      <c r="A81" s="26" t="s">
         <v>289</v>
       </c>
     </row>
@@ -4844,11 +4845,11 @@
       <c r="B5" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Табл. 1 объёмы (оконч.)'!$F$31</f>
         <v>23899.156200244801</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>'Табл. 1 объёмы (оконч.)'!$F$32</f>
         <v>29227.216184948978</v>
       </c>
@@ -4864,7 +4865,7 @@
       <c r="B6" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>'Котлован (оконч.)'!$C$60</f>
         <v>3971.7374877451716</v>
       </c>
@@ -4878,85 +4879,85 @@
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>SUM(C5:C6)</f>
         <v>27870.893687989974</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>SUM(D5:D6)</f>
         <v>29227.216184948978</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>SUM(E5:E6)</f>
         <v>28103.092485527864</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="47">
         <f>C7-E7</f>
         <v>-232.19879753789064</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="28">
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="29">
         <f>ABS(C8)/MAX(C7,E7)</f>
         <v>8.2623931034445808E-3</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>301</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="15" t="str">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="16" t="str">
         <f>IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
         <v>баланс соблюдён</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="17">
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="18">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="29">
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="30">
         <f>C8*'Исходные данные'!$B$4/D12</f>
         <v>-1.6099116629293751E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>304</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="30">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="31">
         <f>ROUND(D13,4)</f>
         <v>-1.6000000000000001E-3</v>
       </c>
@@ -5006,19 +5007,19 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="45" t="s">
         <v>315</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="G4" s="44" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="G4" s="45" t="s">
         <v>316</v>
       </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -5030,10 +5031,10 @@
       <c r="C5" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="45" t="s">
         <v>320</v>
       </c>
-      <c r="E5" s="43"/>
+      <c r="E5" s="44"/>
       <c r="G5" s="2" t="s">
         <v>317</v>
       </c>
@@ -5054,7 +5055,7 @@
       <c r="B6" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>'Котлован (оконч.)'!$C$59</f>
         <v>3831.4695286661999</v>
       </c>
@@ -5071,7 +5072,7 @@
       <c r="H6" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="27">
         <f>'Котлован (оконч.)'!$C$69</f>
         <v>953.30324066620062</v>
       </c>
@@ -5087,7 +5088,7 @@
       <c r="B7" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <f>'Котлован (оконч.)'!$C$70</f>
         <v>140.26795907897184</v>
       </c>
@@ -5104,7 +5105,7 @@
       <c r="H7" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>'Котлован (оконч.)'!$C$70</f>
         <v>140.26795907897184</v>
       </c>
@@ -5115,84 +5116,84 @@
     </row>
     <row r="8" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>330</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="18">
         <f>C6+C7</f>
         <v>3971.7374877451716</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="18">
         <f>E6+E7</f>
         <v>4567.4981109069467</v>
       </c>
       <c r="G8" s="3"/>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="28" t="s">
         <v>332</v>
       </c>
       <c r="I8" s="3"/>
-      <c r="J8" s="17">
+      <c r="J8" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="43" t="s">
         <v>333</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="44"/>
       <c r="E10" s="12">
         <f>E6</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="44"/>
       <c r="E11" s="12">
         <f>E7</f>
         <v>4567.4981109069467</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>335</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="44"/>
       <c r="E12" s="12">
         <f>MIN(C8-J8,'Табл. 4 распределение'!B19-SUM('Табл. 4 распределение'!C5:L5))*'Исходные данные'!$B$7</f>
         <v>4567.4981109069467</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>336</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="44"/>
       <c r="E13" s="12">
         <f>E11-E12</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>337</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
       <c r="E14" s="12">
         <f>J6</f>
         <v>916.63773140980823</v>
@@ -5203,12 +5204,12 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="43" t="s">
         <v>338</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
       <c r="E15" s="12">
         <f>J7</f>
         <v>134.87303757593446</v>
@@ -5219,12 +5220,12 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="43" t="s">
         <v>339</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
       <c r="E16" s="12">
         <f>'Котлован (оконч.)'!$C$61/'Исходные данные'!$B$4</f>
         <v>162.19999999999999</v>
@@ -5235,12 +5236,12 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="43" t="s">
         <v>340</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
+      <c r="B17" s="44"/>
+      <c r="C17" s="44"/>
+      <c r="D17" s="44"/>
       <c r="E17" s="12">
         <f>E6+E7-C8*'Исходные данные'!$B$7</f>
         <v>0</v>
@@ -5334,7 +5335,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="2" t="s">
         <v>344</v>
       </c>
@@ -5382,24 +5383,24 @@
       <c r="B6" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
       <c r="O6" s="2" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>101</v>
       </c>
       <c r="B7" s="10">
@@ -5425,7 +5426,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>103</v>
       </c>
       <c r="B8" s="10">
@@ -5451,7 +5452,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="16" t="s">
         <v>105</v>
       </c>
       <c r="B9" s="10">
@@ -5481,7 +5482,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>106</v>
       </c>
       <c r="B10" s="10">
@@ -5511,7 +5512,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>107</v>
       </c>
       <c r="B11" s="10">
@@ -5541,7 +5542,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>110</v>
       </c>
       <c r="B12" s="10">
@@ -5567,7 +5568,7 @@
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>112</v>
       </c>
       <c r="B13" s="10">
@@ -5593,7 +5594,7 @@
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>113</v>
       </c>
       <c r="B14" s="10">
@@ -5623,7 +5624,7 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="16" t="s">
         <v>114</v>
       </c>
       <c r="B15" s="10">
@@ -5653,7 +5654,7 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>118</v>
       </c>
       <c r="B16" s="10">
@@ -5679,7 +5680,7 @@
       </c>
     </row>
     <row r="17" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>120</v>
       </c>
       <c r="B17" s="10">
@@ -5705,7 +5706,7 @@
       </c>
     </row>
     <row r="18" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>122</v>
       </c>
       <c r="B18" s="10">
@@ -5733,67 +5734,67 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="18">
         <f t="shared" ref="B19:N19" si="1">SUM(B7:B18)</f>
         <v>28087.208355373888</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <f t="shared" si="1"/>
         <v>2383.1875690434781</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <f t="shared" si="1"/>
         <v>303.0587916482437</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <f t="shared" si="1"/>
         <v>4243</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="18">
         <f t="shared" si="1"/>
         <v>2201.3095856658601</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="18">
         <f t="shared" si="1"/>
         <v>270.72457505668928</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="18">
         <f t="shared" si="1"/>
         <v>4868</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="18">
         <f t="shared" si="1"/>
         <v>5268</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="18">
         <f t="shared" si="1"/>
         <v>2451.7321491156458</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="18">
         <f t="shared" si="1"/>
         <v>1459.9414587100666</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="18">
         <f t="shared" si="1"/>
         <v>426.97113047597901</v>
       </c>
-      <c r="M19" s="17">
+      <c r="M19" s="18">
         <f t="shared" si="1"/>
         <v>3971.737487745173</v>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="18">
         <f t="shared" si="1"/>
         <v>239.54560791275179</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="42" t="s">
+      <c r="A20" s="43" t="s">
         <v>347</v>
       </c>
-      <c r="B20" s="47"/>
+      <c r="B20" s="48"/>
       <c r="C20" s="12">
         <f t="shared" ref="C20:N20" si="2">C19-C5</f>
         <v>0</v>
@@ -5870,7 +5871,7 @@
       </c>
     </row>
     <row r="2" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="2" t="s">
         <v>315</v>
       </c>
@@ -6010,7 +6011,7 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>130</v>
       </c>
       <c r="B4" s="10">
@@ -6081,7 +6082,7 @@
       </c>
     </row>
     <row r="5" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>350</v>
       </c>
       <c r="B5" s="10">
@@ -6152,7 +6153,7 @@
       </c>
     </row>
     <row r="6" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>351</v>
       </c>
       <c r="B6" s="10">
@@ -6223,237 +6224,237 @@
       </c>
     </row>
     <row r="7" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f t="shared" ref="B7:W7" si="0">B5*B4</f>
         <v>116726.2134514435</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="24">
         <f t="shared" si="0"/>
         <v>36586.216157851246</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
         <f t="shared" si="0"/>
         <v>212150</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="24">
         <f t="shared" si="0"/>
         <v>323485.32168002968</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f t="shared" si="0"/>
         <v>61381.425874757922</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="24">
         <f t="shared" si="0"/>
         <v>243400</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="24">
         <f t="shared" si="0"/>
         <v>790200</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="24">
         <f t="shared" si="0"/>
         <v>610803.64832148561</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="24">
         <f t="shared" si="0"/>
         <v>507793.16978099244</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="24">
         <f t="shared" si="0"/>
         <v>182943.39641938033</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="24">
         <f t="shared" si="0"/>
         <v>650.32916163136383</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="24">
         <f t="shared" si="0"/>
         <v>138457.67677588767</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="24">
         <f t="shared" si="0"/>
         <v>831009.61538461526</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="24">
         <f t="shared" si="0"/>
         <v>1903798.076923077</v>
       </c>
-      <c r="P7" s="23">
+      <c r="P7" s="24">
         <f t="shared" si="0"/>
         <v>909634.14541547233</v>
       </c>
-      <c r="Q7" s="23">
+      <c r="Q7" s="24">
         <f t="shared" si="0"/>
         <v>10106.5740144142</v>
       </c>
-      <c r="R7" s="23">
+      <c r="R7" s="24">
         <f t="shared" si="0"/>
         <v>289081.49320548528</v>
       </c>
-      <c r="S7" s="23">
+      <c r="S7" s="24">
         <f t="shared" si="0"/>
         <v>1373750</v>
       </c>
-      <c r="T7" s="23">
+      <c r="T7" s="24">
         <f t="shared" si="0"/>
         <v>2382836.5384615385</v>
       </c>
-      <c r="U7" s="23">
+      <c r="U7" s="24">
         <f t="shared" si="0"/>
         <v>1535.1196074338027</v>
       </c>
-      <c r="V7" s="23">
+      <c r="V7" s="24">
         <f t="shared" si="0"/>
         <v>96022.947095099007</v>
       </c>
-      <c r="W7" s="23">
+      <c r="W7" s="24">
         <f t="shared" si="0"/>
         <v>706684.30637456942</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="24">
         <f t="shared" ref="B8:W8" si="1">B6*B4</f>
         <v>593305.36336269171</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <f t="shared" si="1"/>
         <v>68666.97316853104</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <f t="shared" si="1"/>
         <v>636450</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <f t="shared" si="1"/>
         <v>323606.57549503969</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f t="shared" si="1"/>
         <v>32499.840653233998</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <f t="shared" si="1"/>
         <v>243400</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <f t="shared" si="1"/>
         <v>263400</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="24">
         <f t="shared" si="1"/>
         <v>120457.21849835652</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="24">
         <f t="shared" si="1"/>
         <v>52054.696062279487</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="24">
         <f t="shared" si="1"/>
         <v>8770.023051295635</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="24">
         <f t="shared" si="1"/>
         <v>2067.6545397540917</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="24">
         <f t="shared" si="1"/>
         <v>223510.53218293676</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="24">
         <f t="shared" si="1"/>
         <v>831009.61538461526</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="24">
         <f t="shared" si="1"/>
         <v>1359855.7692307692</v>
       </c>
-      <c r="P8" s="23">
+      <c r="P8" s="24">
         <f t="shared" si="1"/>
         <v>505352.30300859577</v>
       </c>
-      <c r="Q8" s="23">
+      <c r="Q8" s="24">
         <f t="shared" si="1"/>
         <v>10070.139574807758</v>
       </c>
-      <c r="R8" s="23">
+      <c r="R8" s="24">
         <f t="shared" si="1"/>
         <v>179155.79201295745</v>
       </c>
-      <c r="S8" s="23">
+      <c r="S8" s="24">
         <f t="shared" si="1"/>
         <v>588750</v>
       </c>
-      <c r="T8" s="23">
+      <c r="T8" s="24">
         <f t="shared" si="1"/>
         <v>794278.84615384613</v>
       </c>
-      <c r="U8" s="23">
+      <c r="U8" s="24">
         <f t="shared" si="1"/>
         <v>488.67365127356055</v>
       </c>
-      <c r="V8" s="23">
+      <c r="V8" s="24">
         <f t="shared" si="1"/>
         <v>22959.644153172754</v>
       </c>
-      <c r="W8" s="23">
+      <c r="W8" s="24">
         <f t="shared" si="1"/>
         <v>93444.310034892245</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>354</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="17">
+      <c r="B11" s="44"/>
+      <c r="C11" s="18">
         <f>SUM(B7:K7)/SUM(B4:K4)</f>
         <v>129.22931187474518</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>355</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="17">
+      <c r="B12" s="44"/>
+      <c r="C12" s="18">
         <f>SUM(B8:K8)/SUM(B4:K4)</f>
         <v>98.116017067784028</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>356</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="17">
+      <c r="B13" s="44"/>
+      <c r="C13" s="18">
         <f>SUM(L7:W7)/SUM(L4:W4)</f>
         <v>362.02018260640386</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>357</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="17">
+      <c r="B14" s="44"/>
+      <c r="C14" s="18">
         <f>SUM(L8:W8)/SUM(L4:W4)</f>
         <v>193.12103006568361</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="43" t="s">
         <v>358</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="17">
+      <c r="B15" s="44"/>
+      <c r="C15" s="18">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
         <v>251.43098852515158</v>
       </c>
@@ -6489,7 +6490,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="31"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="2" t="s">
         <v>324</v>
       </c>
@@ -6509,7 +6510,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="16" t="s">
         <v>130</v>
       </c>
       <c r="B4" s="10">
@@ -6520,7 +6521,7 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>350</v>
       </c>
       <c r="B5" s="10">
@@ -6531,7 +6532,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>351</v>
       </c>
       <c r="B6" s="10">
@@ -6542,77 +6543,77 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="24">
         <f>B5*B4</f>
         <v>992934.3719362932</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="24">
         <f>C5*C4</f>
         <v>1787281.8694853277</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="24">
         <f>B6*B4</f>
         <v>595760.62316177599</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="24">
         <f>C6*C4</f>
         <v>992934.3719362932</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>361</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="17">
+      <c r="B11" s="44"/>
+      <c r="C11" s="18">
         <f>SUM(B7:B7)/SUM(B4:B4)</f>
         <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>362</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="17">
+      <c r="B12" s="44"/>
+      <c r="C12" s="18">
         <f>SUM(B8:B8)/SUM(B4:B4)</f>
         <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>356</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="17">
+      <c r="B13" s="44"/>
+      <c r="C13" s="18">
         <f>SUM(C7:C7)/SUM(C4:C4)</f>
         <v>450</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>357</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="17">
+      <c r="B14" s="44"/>
+      <c r="C14" s="18">
         <f>SUM(C8:C8)/SUM(C4:C4)</f>
         <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="43" t="s">
         <v>358</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="17">
+      <c r="B15" s="44"/>
+      <c r="C15" s="18">
         <f>SQRT((C11-C13)^2+(C12-C14)^2)</f>
         <v>223.60679774997897</v>
       </c>
@@ -6655,40 +6656,40 @@
       <c r="A3" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="49" t="s">
         <v>365</v>
       </c>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="44"/>
     </row>
     <row r="4" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="49" t="s">
         <v>367</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
     </row>
     <row r="5" spans="1:7" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="B5" s="49">
+      <c r="B5" s="50">
         <v>1650</v>
       </c>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
@@ -6732,7 +6733,7 @@
       <c r="F8" s="6">
         <v>10</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="21" t="s">
         <v>379</v>
       </c>
     </row>
@@ -6755,7 +6756,7 @@
       <c r="F9" s="6">
         <v>100</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="21" t="s">
         <v>383</v>
       </c>
     </row>
@@ -6778,7 +6779,7 @@
       <c r="F10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="21" t="s">
         <v>387</v>
       </c>
     </row>
@@ -6801,7 +6802,7 @@
       <c r="F11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="21" t="s">
         <v>391</v>
       </c>
     </row>
@@ -6824,7 +6825,7 @@
       <c r="F12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="21" t="s">
         <v>395</v>
       </c>
     </row>
@@ -6847,7 +6848,7 @@
       <c r="F13" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="21" t="s">
         <v>400</v>
       </c>
     </row>
@@ -6895,105 +6896,105 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="43" t="s">
         <v>404</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="26">
+      <c r="B4" s="44"/>
+      <c r="C4" s="27">
         <f>'Табл. 5 скрепер'!$C$15</f>
         <v>251.43098852515158</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="43" t="s">
         <v>405</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="26">
+      <c r="B5" s="44"/>
+      <c r="C5" s="27">
         <f>SUM('Табл. 4 распределение'!C5:L5)</f>
         <v>23875.925259715965</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="43" t="s">
         <v>406</v>
       </c>
-      <c r="B6" s="43"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="12">
         <f>C5*'Исходные данные'!$B$7</f>
         <v>27457.314048673357</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="43" t="s">
         <v>407</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="26">
+      <c r="B7" s="44"/>
+      <c r="C7" s="27">
         <f>'Табл. 4 распределение'!B19*'Исходные данные'!$B$4</f>
         <v>29210.696689588844</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="43" t="s">
         <v>408</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="33">
+      <c r="B8" s="44"/>
+      <c r="C8" s="34">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="43" t="s">
         <v>409</v>
       </c>
-      <c r="B9" s="43"/>
-      <c r="C9" s="33">
+      <c r="B9" s="44"/>
+      <c r="C9" s="34">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="43" t="s">
         <v>410</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="33">
+      <c r="B10" s="44"/>
+      <c r="C10" s="34">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="45" t="s">
         <v>411</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="E12" s="44" t="s">
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="E12" s="45" t="s">
         <v>412</v>
       </c>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
+      <c r="F12" s="44"/>
+      <c r="G12" s="44"/>
     </row>
     <row r="13" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>413</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="52" t="s">
         <v>377</v>
       </c>
-      <c r="C13" s="43"/>
-      <c r="E13" s="18" t="s">
+      <c r="C13" s="44"/>
+      <c r="E13" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="52" t="s">
         <v>381</v>
       </c>
-      <c r="G13" s="43"/>
+      <c r="G13" s="44"/>
     </row>
     <row r="14" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="35" t="s">
         <v>415</v>
       </c>
       <c r="C14" s="12">
@@ -7003,7 +7004,7 @@
       <c r="E14" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F14" s="24"/>
+      <c r="F14" s="25"/>
       <c r="G14" s="12">
         <f>$C$6</f>
         <v>27457.314048673357</v>
@@ -7013,7 +7014,7 @@
       <c r="A15" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="B15" s="24"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$8+'2.3 Грунт и нормы ЕНиР'!$E$8*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$8)/10</f>
         <v>5.3100507590281829</v>
@@ -7021,7 +7022,7 @@
       <c r="E15" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="F15" s="24"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$9+'2.3 Грунт и нормы ЕНиР'!$E$9*($C$4-'2.3 Грунт и нормы ЕНиР'!$F$9)/10</f>
         <v>3.2143098852515157</v>
@@ -7031,7 +7032,7 @@
       <c r="A16" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="B16" s="24"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="12">
         <f>C15*C14/800</f>
         <v>182.24966413129144</v>
@@ -7039,7 +7040,7 @@
       <c r="E16" s="5" t="s">
         <v>417</v>
       </c>
-      <c r="F16" s="24"/>
+      <c r="F16" s="25"/>
       <c r="G16" s="12">
         <f>G15*G14/800</f>
         <v>110.3203949613826</v>
@@ -7049,7 +7050,7 @@
       <c r="A17" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="B17" s="24"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="12">
         <f>100*$C$8*8/C15</f>
         <v>301.3153871042889</v>
@@ -7057,7 +7058,7 @@
       <c r="E17" s="5" t="s">
         <v>418</v>
       </c>
-      <c r="F17" s="24"/>
+      <c r="F17" s="25"/>
       <c r="G17" s="12">
         <f>100*$C$8*8/G15</f>
         <v>497.77403458870361</v>
@@ -7067,59 +7068,59 @@
       <c r="A18" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="25">
         <f>C16/($C$8*$C$9)</f>
         <v>4.5562416032822863</v>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="36">
         <f>ROUNDUP(ROUND(B18,6),0)</f>
         <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F18" s="24">
+      <c r="F18" s="25">
         <f>G16/($C$8*$C$9)</f>
         <v>2.7580098740345651</v>
       </c>
-      <c r="G18" s="35">
+      <c r="G18" s="36">
         <f>ROUNDUP(ROUND(F18,6),0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="E19" s="50" t="s">
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="E19" s="51" t="s">
         <v>420</v>
       </c>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
     </row>
     <row r="20" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="B20" s="51" t="s">
+      <c r="B20" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="C20" s="43"/>
-      <c r="E20" s="18" t="s">
+      <c r="C20" s="44"/>
+      <c r="E20" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="52" t="s">
         <v>385</v>
       </c>
-      <c r="G20" s="43"/>
+      <c r="G20" s="44"/>
     </row>
     <row r="21" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="35" t="s">
         <v>421</v>
       </c>
       <c r="C21" s="12">
@@ -7129,7 +7130,7 @@
       <c r="E21" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="24"/>
+      <c r="F21" s="25"/>
       <c r="G21" s="12">
         <f>$C$5</f>
         <v>23875.925259715965</v>
@@ -7139,7 +7140,7 @@
       <c r="A22" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B22" s="24"/>
+      <c r="B22" s="25"/>
       <c r="C22" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$10</f>
         <v>0.06</v>
@@ -7147,7 +7148,7 @@
       <c r="E22" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="F22" s="24"/>
+      <c r="F22" s="25"/>
       <c r="G22" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$10</f>
         <v>0.06</v>
@@ -7157,7 +7158,7 @@
       <c r="A23" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B23" s="24"/>
+      <c r="B23" s="25"/>
       <c r="C23" s="12">
         <f>C22*C21/800</f>
         <v>1.7906943944786975</v>
@@ -7165,7 +7166,7 @@
       <c r="E23" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F23" s="24"/>
+      <c r="F23" s="25"/>
       <c r="G23" s="12">
         <f>G22*G21/800</f>
         <v>1.7906943944786975</v>
@@ -7175,7 +7176,7 @@
       <c r="A24" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B24" s="24"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="12">
         <f>100*$C$8*8/C22</f>
         <v>26666.666666666668</v>
@@ -7183,7 +7184,7 @@
       <c r="E24" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="F24" s="24"/>
+      <c r="F24" s="25"/>
       <c r="G24" s="12">
         <f>100*$C$8*8/G22</f>
         <v>26666.666666666668</v>
@@ -7193,47 +7194,47 @@
       <c r="A25" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="25">
         <f>C18*C17/C24</f>
         <v>5.6496635082054165E-2</v>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="36">
         <f>ROUNDUP(ROUND(B25,6),0)</f>
         <v>1</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="25">
         <f>G18*G17/G24</f>
         <v>5.5999578891229154E-2</v>
       </c>
-      <c r="G25" s="35">
+      <c r="G25" s="36">
         <f>ROUNDUP(ROUND(F25,6),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="B26" s="51" t="s">
+      <c r="B26" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="C26" s="43"/>
-      <c r="E26" s="18" t="s">
+      <c r="C26" s="44"/>
+      <c r="E26" s="19" t="s">
         <v>425</v>
       </c>
-      <c r="F26" s="51" t="s">
+      <c r="F26" s="52" t="s">
         <v>389</v>
       </c>
-      <c r="G26" s="43"/>
+      <c r="G26" s="44"/>
     </row>
     <row r="27" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B27" s="24"/>
+      <c r="B27" s="25"/>
       <c r="C27" s="12">
         <f>$C$7</f>
         <v>29210.696689588844</v>
@@ -7241,7 +7242,7 @@
       <c r="E27" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F27" s="24"/>
+      <c r="F27" s="25"/>
       <c r="G27" s="12">
         <f>$C$7</f>
         <v>29210.696689588844</v>
@@ -7251,7 +7252,7 @@
       <c r="A28" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="B28" s="24"/>
+      <c r="B28" s="25"/>
       <c r="C28" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$12</f>
         <v>0.25</v>
@@ -7259,7 +7260,7 @@
       <c r="E28" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="F28" s="24"/>
+      <c r="F28" s="25"/>
       <c r="G28" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$11</f>
         <v>0.27</v>
@@ -7269,7 +7270,7 @@
       <c r="A29" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B29" s="24"/>
+      <c r="B29" s="25"/>
       <c r="C29" s="12">
         <f>C28*C27/800</f>
         <v>9.1283427154965135</v>
@@ -7277,7 +7278,7 @@
       <c r="E29" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F29" s="24"/>
+      <c r="F29" s="25"/>
       <c r="G29" s="12">
         <f>G28*G27/800</f>
         <v>9.858610132736235</v>
@@ -7287,7 +7288,7 @@
       <c r="A30" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="B30" s="24"/>
+      <c r="B30" s="25"/>
       <c r="C30" s="12">
         <f>100*$C$8*8/C28</f>
         <v>6400</v>
@@ -7295,7 +7296,7 @@
       <c r="E30" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="F30" s="24"/>
+      <c r="F30" s="25"/>
       <c r="G30" s="12">
         <f>100*$C$8*8/G28</f>
         <v>5925.9259259259252</v>
@@ -7305,40 +7306,40 @@
       <c r="A31" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B31" s="25">
         <f>C18*C17/C30</f>
         <v>0.23540264617522572</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <f>ROUNDUP(ROUND(B31,6),0)</f>
         <v>1</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F31" s="24">
+      <c r="F31" s="25">
         <f>G18*G17/G30</f>
         <v>0.25199810501053121</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <f>ROUNDUP(ROUND(F31,6),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="F32" s="51" t="s">
+      <c r="F32" s="52" t="s">
         <v>393</v>
       </c>
-      <c r="G32" s="43"/>
+      <c r="G32" s="44"/>
     </row>
     <row r="33" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F33" s="24"/>
+      <c r="F33" s="25"/>
       <c r="G33" s="12">
         <f>$C$7</f>
         <v>29210.696689588844</v>
@@ -7348,7 +7349,7 @@
       <c r="E34" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="F34" s="24"/>
+      <c r="F34" s="25"/>
       <c r="G34" s="14">
         <f>'2.3 Грунт и нормы ЕНиР'!$D$12</f>
         <v>0.25</v>
@@ -7358,7 +7359,7 @@
       <c r="E35" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F35" s="24"/>
+      <c r="F35" s="25"/>
       <c r="G35" s="12">
         <f>G34*G33/800</f>
         <v>9.1283427154965135</v>
@@ -7368,7 +7369,7 @@
       <c r="E36" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="F36" s="24"/>
+      <c r="F36" s="25"/>
       <c r="G36" s="12">
         <f>100*$C$8*8/G34</f>
         <v>6400</v>
@@ -7378,29 +7379,29 @@
       <c r="E37" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="25">
         <f>G18*G17/G36</f>
         <v>0.23333157871345481</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="36">
         <f>ROUNDUP(ROUND(F37,6),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E38" s="18" t="s">
+      <c r="E38" s="19" t="s">
         <v>396</v>
       </c>
-      <c r="F38" s="51" t="s">
+      <c r="F38" s="52" t="s">
         <v>397</v>
       </c>
-      <c r="G38" s="43"/>
+      <c r="G38" s="44"/>
     </row>
     <row r="39" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="E39" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F39" s="24"/>
+      <c r="F39" s="25"/>
       <c r="G39" s="12">
         <f>$C$6</f>
         <v>27457.314048673357</v>
@@ -7410,8 +7411,8 @@
       <c r="E40" s="5" t="s">
         <v>422</v>
       </c>
-      <c r="F40" s="24"/>
-      <c r="G40" s="16">
+      <c r="F40" s="25"/>
+      <c r="G40" s="17">
         <f>G15/$C$10</f>
         <v>1.0714366284171719</v>
       </c>
@@ -7420,7 +7421,7 @@
       <c r="E41" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F41" s="24"/>
+      <c r="F41" s="25"/>
       <c r="G41" s="12">
         <f>G40*G39/800</f>
         <v>36.773464987127539</v>
@@ -7430,7 +7431,7 @@
       <c r="E42" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="F42" s="24"/>
+      <c r="F42" s="25"/>
       <c r="G42" s="12">
         <f>100*$C$8*8/G40</f>
         <v>1493.322103766111</v>
@@ -7440,98 +7441,98 @@
       <c r="E43" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F43" s="25">
         <f>G18*G17/G42</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="G43" s="35">
+      <c r="G43" s="36">
         <f>ROUNDUP(ROUND(F43,6),0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="50" t="s">
+      <c r="A45" s="51" t="s">
         <v>426</v>
       </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="17">
+      <c r="B45" s="44"/>
+      <c r="C45" s="18">
         <f>C16+C23+C29</f>
         <v>193.16870124126663</v>
       </c>
-      <c r="E45" s="50" t="s">
+      <c r="E45" s="51" t="s">
         <v>426</v>
       </c>
-      <c r="F45" s="43"/>
-      <c r="G45" s="17">
+      <c r="F45" s="44"/>
+      <c r="G45" s="18">
         <f>G16+G23+G29+G35+G41</f>
         <v>167.87150719122158</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="50" t="s">
+      <c r="A46" s="51" t="s">
         <v>427</v>
       </c>
-      <c r="B46" s="43"/>
-      <c r="C46" s="17">
+      <c r="B46" s="44"/>
+      <c r="C46" s="18">
         <f>C14/C45</f>
         <v>142.14162994438382</v>
       </c>
-      <c r="E46" s="50" t="s">
+      <c r="E46" s="51" t="s">
         <v>427</v>
       </c>
-      <c r="F46" s="43"/>
-      <c r="G46" s="17">
+      <c r="F46" s="44"/>
+      <c r="G46" s="18">
         <f>G14/G45</f>
         <v>163.56149121480675</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="50" t="s">
+      <c r="A47" s="51" t="s">
         <v>428</v>
       </c>
-      <c r="B47" s="43"/>
-      <c r="C47" s="36">
+      <c r="B47" s="44"/>
+      <c r="C47" s="37">
         <f>C45/C14</f>
         <v>7.0352366185140337E-3</v>
       </c>
-      <c r="E47" s="50" t="s">
+      <c r="E47" s="51" t="s">
         <v>428</v>
       </c>
-      <c r="F47" s="43"/>
-      <c r="G47" s="36">
+      <c r="F47" s="44"/>
+      <c r="G47" s="37">
         <f>G45/G14</f>
         <v>6.1139085525130799E-3</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="42" t="s">
+      <c r="A48" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="B48" s="43"/>
-      <c r="C48" s="23">
+      <c r="B48" s="44"/>
+      <c r="C48" s="24">
         <f>C16/(C18*$C$8)</f>
         <v>18.224966413129145</v>
       </c>
-      <c r="E48" s="42" t="s">
+      <c r="E48" s="43" t="s">
         <v>429</v>
       </c>
-      <c r="F48" s="43"/>
-      <c r="G48" s="23">
+      <c r="F48" s="44"/>
+      <c r="G48" s="24">
         <f>G16/(G18*$C$8)</f>
         <v>18.386732493563766</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="50" t="str">
+      <c r="A50" s="51" t="str">
         <f>IF(C47&lt;G47,"Принимается вариант 1 - ведущая машина бульдозер: меньше маш.-см на 1 м³","Принимается вариант 2 - ведущая машина скрепер: меньше маш.-см на 1 м³")</f>
         <v>Принимается вариант 2 - ведущая машина скрепер: меньше маш.-см на 1 м³</v>
       </c>
-      <c r="B50" s="43"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -7591,31 +7592,31 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="26">
+      <c r="B3" s="44"/>
+      <c r="C3" s="27">
         <f>'Котлован (оконч.)'!$C$60</f>
         <v>3971.7374877451716</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="B4" s="43"/>
+      <c r="B4" s="44"/>
       <c r="C4" s="14">
         <f>'Котлован (оконч.)'!$C$39</f>
         <v>2.0917999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="43" t="s">
         <v>433</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="37">
+      <c r="B5" s="44"/>
+      <c r="C5" s="38">
         <f>'Табл. 7 варианты'!$C$8</f>
         <v>2</v>
       </c>
@@ -7653,115 +7654,115 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="33" t="s">
         <v>443</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="33" t="s">
         <v>444</v>
       </c>
       <c r="C8" s="10">
         <v>0.5</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="33" t="s">
         <v>445</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="22">
         <v>2.9</v>
       </c>
       <c r="F8" s="12">
         <f>100*8/E8</f>
         <v>275.86206896551727</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <v>4</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="22">
         <v>9.1999999999999993</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="22">
         <v>1.7</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="23">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="33" t="s">
         <v>446</v>
       </c>
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="33" t="s">
         <v>444</v>
       </c>
       <c r="C9" s="10">
         <v>0.65</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="33" t="s">
         <v>447</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="22">
         <v>2.2999999999999998</v>
       </c>
       <c r="F9" s="12">
         <f>100*8/E9</f>
         <v>347.82608695652175</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <v>4</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="22">
         <v>9.1999999999999993</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="22">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="23">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>449</v>
       </c>
       <c r="C10" s="10">
         <v>0.65</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="33" t="s">
         <v>450</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="22">
         <v>2.1</v>
       </c>
       <c r="F10" s="12">
         <f>100*8/E10</f>
         <v>380.95238095238096</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="22">
         <v>5.8</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="22">
         <v>9</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="22">
         <v>5</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="E11" s="38" t="s">
+      <c r="E11" s="39" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="50" t="s">
+      <c r="A12" s="51" t="s">
         <v>452</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="15" t="str">
+      <c r="B12" s="44"/>
+      <c r="C12" s="16" t="str">
         <f>INDEX($A$8:$A$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))</f>
         <v>ЭО-4121А</v>
       </c>
@@ -7779,10 +7780,10 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>436</v>
       </c>
-      <c r="B13" s="43"/>
+      <c r="B13" s="44"/>
       <c r="C13" s="12">
         <f>INDEX($C$8:$C$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))</f>
         <v>0.65</v>
@@ -7790,10 +7791,10 @@
       <c r="E13" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="23">
         <v>0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <v>500</v>
       </c>
       <c r="H13" s="3" t="str">
@@ -7802,21 +7803,21 @@
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>372</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="23">
+      <c r="B14" s="44"/>
+      <c r="C14" s="24">
         <f>INDEX($E$8:$E$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))</f>
         <v>2.1</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="23">
         <v>500</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>1500</v>
       </c>
       <c r="H14" s="3" t="str">
@@ -7825,10 +7826,10 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="43" t="s">
         <v>459</v>
       </c>
-      <c r="B15" s="43"/>
+      <c r="B15" s="44"/>
       <c r="C15" s="12">
         <f>INDEX($J$8:$J$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))/100</f>
         <v>0.1</v>
@@ -7836,10 +7837,10 @@
       <c r="E15" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="F15" s="22">
+      <c r="F15" s="23">
         <v>1500</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <v>5000</v>
       </c>
       <c r="H15" s="3" t="str">
@@ -7848,21 +7849,21 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="43" t="s">
         <v>461</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="16">
+      <c r="B16" s="44"/>
+      <c r="C16" s="17">
         <f>C4-C15</f>
         <v>1.9917999999999996</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="23">
         <v>2000</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>8000</v>
       </c>
       <c r="H16" s="3" t="str">
@@ -7871,10 +7872,10 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="B17" s="43"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="3" t="str">
         <f>IF(INDEX($G$8:$G$10,MATCH(MAX($F$8:$F$10),$F$8:$F$10,0))&gt;=C16,"выполняется","НЕТ")</f>
         <v>выполняется</v>
@@ -7882,10 +7883,10 @@
       <c r="E17" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="23">
         <v>6000</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>11000</v>
       </c>
       <c r="H17" s="3" t="str">
@@ -7894,10 +7895,10 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="42" t="s">
+      <c r="A18" s="43" t="s">
         <v>465</v>
       </c>
-      <c r="B18" s="43"/>
+      <c r="B18" s="44"/>
       <c r="C18" s="12">
         <f>C14*C3/800</f>
         <v>10.425810905331074</v>
@@ -7905,10 +7906,10 @@
       <c r="E18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="23">
         <v>11000</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <v>15000</v>
       </c>
       <c r="H18" s="3" t="str">
@@ -7917,21 +7918,21 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="42" t="s">
+      <c r="A19" s="43" t="s">
         <v>466</v>
       </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="23">
+      <c r="B19" s="44"/>
+      <c r="C19" s="24">
         <f>C18/C5</f>
         <v>5.2129054526655372</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="23">
         <v>13000</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <v>18000</v>
       </c>
       <c r="H19" s="3" t="str">
@@ -7943,10 +7944,10 @@
       <c r="E20" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="23">
         <v>17000</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="23" t="s">
         <v>104</v>
       </c>
       <c r="H20" s="3" t="str">
@@ -7955,101 +7956,101 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="39" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="42" t="s">
+      <c r="A22" s="43" t="s">
         <v>470</v>
       </c>
-      <c r="B22" s="43"/>
+      <c r="B22" s="44"/>
       <c r="C22" s="8">
         <v>0.9</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="A23" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="26">
+      <c r="B23" s="44"/>
+      <c r="C23" s="27">
         <f>'Исходные данные'!$B$7</f>
         <v>1.1499999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="43" t="s">
         <v>471</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="39">
+      <c r="B24" s="44"/>
+      <c r="C24" s="40">
         <f>'2.3 Грунт и нормы ЕНиР'!$B$5/1000</f>
         <v>1.65</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="42" t="s">
+      <c r="A25" s="43" t="s">
         <v>472</v>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="16">
+      <c r="B25" s="44"/>
+      <c r="C25" s="17">
         <f>C13*C22/C23</f>
         <v>0.5086956521739131</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="42" t="s">
+      <c r="A26" s="43" t="s">
         <v>473</v>
       </c>
-      <c r="B26" s="43"/>
-      <c r="C26" s="16">
+      <c r="B26" s="44"/>
+      <c r="C26" s="17">
         <f>C25*C24</f>
         <v>0.83934782608695657</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="42" t="s">
+      <c r="A27" s="43" t="s">
         <v>474</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="21">
+      <c r="B27" s="44"/>
+      <c r="C27" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="43" t="s">
         <v>475</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="21">
+      <c r="B28" s="44"/>
+      <c r="C28" s="22">
         <v>0.3</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="43" t="s">
         <v>476</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="21">
+      <c r="B29" s="44"/>
+      <c r="C29" s="22">
         <v>0.6</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="43" t="s">
         <v>477</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="21">
+      <c r="B30" s="44"/>
+      <c r="C30" s="22">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="43" t="s">
         <v>478</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="21">
+      <c r="B31" s="44"/>
+      <c r="C31" s="22">
         <v>2</v>
       </c>
     </row>
@@ -8116,10 +8117,10 @@
       </c>
     </row>
     <row r="34" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="B34" s="21">
+      <c r="B34" s="22">
         <v>4.5</v>
       </c>
       <c r="C34" s="10">
@@ -8128,10 +8129,10 @@
       <c r="D34" s="10">
         <v>2.48</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="23">
         <v>45</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="23">
         <v>60</v>
       </c>
       <c r="G34" s="12">
@@ -8142,7 +8143,7 @@
         <f t="shared" ref="H34:H51" si="2">B34/$C$13</f>
         <v>6.9230769230769225</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="36">
         <f t="shared" ref="I34:I51" si="3">INT(ROUND(MIN(G34,H34),6))</f>
         <v>4</v>
       </c>
@@ -8150,7 +8151,7 @@
         <f t="shared" ref="J34:J51" si="4">IF(AND(I34&gt;=6,I34&lt;=11),"да","нет")</f>
         <v>нет</v>
       </c>
-      <c r="K34" s="24">
+      <c r="K34" s="25">
         <f t="shared" ref="K34:K51" si="5">I34*$C$25</f>
         <v>2.0347826086956524</v>
       </c>
@@ -8174,7 +8175,7 @@
         <f t="shared" ref="P34:P51" si="10">O34/L34</f>
         <v>11.622145344367565</v>
       </c>
-      <c r="Q34" s="35">
+      <c r="Q34" s="36">
         <f t="shared" ref="Q34:Q51" si="11">ROUNDUP(ROUND(P34,6),0)</f>
         <v>12</v>
       </c>
@@ -8182,20 +8183,20 @@
         <f t="shared" ref="R34:R51" si="12">$C$13*$C$22*I34</f>
         <v>2.3400000000000003</v>
       </c>
-      <c r="S34" s="16">
+      <c r="S34" s="17">
         <f t="shared" ref="S34:S51" si="13">O34/(R34*60)</f>
         <v>0.21223048020149468</v>
       </c>
-      <c r="T34" s="16" t="str">
+      <c r="T34" s="17" t="str">
         <f t="shared" ref="T34:T51" si="14">IF(J34="да",S34,"")</f>
         <v/>
       </c>
     </row>
     <row r="35" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="33" t="s">
         <v>500</v>
       </c>
-      <c r="B35" s="21">
+      <c r="B35" s="22">
         <v>4.5</v>
       </c>
       <c r="C35" s="10">
@@ -8204,10 +8205,10 @@
       <c r="D35" s="10">
         <v>2.48</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>47</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>60</v>
       </c>
       <c r="G35" s="12">
@@ -8218,7 +8219,7 @@
         <f t="shared" si="2"/>
         <v>6.9230769230769225</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
@@ -8226,7 +8227,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K35" s="24">
+      <c r="K35" s="25">
         <f t="shared" si="5"/>
         <v>2.0347826086956524</v>
       </c>
@@ -8250,7 +8251,7 @@
         <f t="shared" si="10"/>
         <v>11.400844886660488</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <f t="shared" si="11"/>
         <v>12</v>
       </c>
@@ -8258,20 +8259,20 @@
         <f t="shared" si="12"/>
         <v>2.3400000000000003</v>
       </c>
-      <c r="S35" s="16">
+      <c r="S35" s="17">
         <f t="shared" si="13"/>
         <v>0.20818934140858286</v>
       </c>
-      <c r="T35" s="16" t="str">
+      <c r="T35" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="36" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="33" t="s">
         <v>501</v>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <v>3.8</v>
       </c>
       <c r="C36" s="10">
@@ -8280,10 +8281,10 @@
       <c r="D36" s="10">
         <v>2.81</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <v>42</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="23">
         <v>60</v>
       </c>
       <c r="G36" s="12">
@@ -8294,7 +8295,7 @@
         <f t="shared" si="2"/>
         <v>5.8461538461538458</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
@@ -8302,7 +8303,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="25">
         <f t="shared" si="5"/>
         <v>2.5434782608695654</v>
       </c>
@@ -8326,7 +8327,7 @@
         <f t="shared" si="10"/>
         <v>9.7948911758435546</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="36">
         <f t="shared" si="11"/>
         <v>10</v>
       </c>
@@ -8334,20 +8335,20 @@
         <f t="shared" si="12"/>
         <v>2.9250000000000003</v>
       </c>
-      <c r="S36" s="16">
+      <c r="S36" s="17">
         <f t="shared" si="13"/>
         <v>0.17886323016757796</v>
       </c>
-      <c r="T36" s="16" t="str">
+      <c r="T36" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="37" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="33" t="s">
         <v>502</v>
       </c>
-      <c r="B37" s="21">
+      <c r="B37" s="22">
         <v>5.4</v>
       </c>
       <c r="C37" s="10">
@@ -8356,10 +8357,10 @@
       <c r="D37" s="10">
         <v>2.15</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="23">
         <v>48</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="23">
         <v>60</v>
       </c>
       <c r="G37" s="12">
@@ -8370,7 +8371,7 @@
         <f t="shared" si="2"/>
         <v>8.3076923076923084</v>
       </c>
-      <c r="I37" s="35">
+      <c r="I37" s="36">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
@@ -8378,7 +8379,7 @@
         <f t="shared" si="4"/>
         <v>да</v>
       </c>
-      <c r="K37" s="24">
+      <c r="K37" s="25">
         <f t="shared" si="5"/>
         <v>4.0695652173913048</v>
       </c>
@@ -8402,7 +8403,7 @@
         <f t="shared" si="10"/>
         <v>6.1485551485551486</v>
       </c>
-      <c r="Q37" s="35">
+      <c r="Q37" s="36">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
@@ -8410,20 +8411,20 @@
         <f t="shared" si="12"/>
         <v>4.6800000000000006</v>
       </c>
-      <c r="S37" s="16">
+      <c r="S37" s="17">
         <f t="shared" si="13"/>
         <v>0.11227796358231142</v>
       </c>
-      <c r="T37" s="16">
+      <c r="T37" s="17">
         <f t="shared" si="14"/>
         <v>0.11227796358231142</v>
       </c>
     </row>
     <row r="38" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="33" t="s">
         <v>503</v>
       </c>
-      <c r="B38" s="21">
+      <c r="B38" s="22">
         <v>5.5</v>
       </c>
       <c r="C38" s="10">
@@ -8432,10 +8433,10 @@
       <c r="D38" s="10">
         <v>2.15</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="23">
         <v>40</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="23">
         <v>60</v>
       </c>
       <c r="G38" s="12">
@@ -8446,7 +8447,7 @@
         <f t="shared" si="2"/>
         <v>8.4615384615384617</v>
       </c>
-      <c r="I38" s="35">
+      <c r="I38" s="36">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
@@ -8454,7 +8455,7 @@
         <f t="shared" si="4"/>
         <v>да</v>
       </c>
-      <c r="K38" s="24">
+      <c r="K38" s="25">
         <f t="shared" si="5"/>
         <v>4.0695652173913048</v>
       </c>
@@ -8478,7 +8479,7 @@
         <f t="shared" si="10"/>
         <v>6.6361077194410525</v>
       </c>
-      <c r="Q38" s="35">
+      <c r="Q38" s="36">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
@@ -8486,20 +8487,20 @@
         <f t="shared" si="12"/>
         <v>4.6800000000000006</v>
       </c>
-      <c r="S38" s="16">
+      <c r="S38" s="17">
         <f t="shared" si="13"/>
         <v>0.12118109748544532</v>
       </c>
-      <c r="T38" s="16">
+      <c r="T38" s="17">
         <f t="shared" si="14"/>
         <v>0.12118109748544532</v>
       </c>
     </row>
     <row r="39" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="33" t="s">
         <v>504</v>
       </c>
-      <c r="B39" s="21">
+      <c r="B39" s="22">
         <v>5.5</v>
       </c>
       <c r="C39" s="10">
@@ -8508,10 +8509,10 @@
       <c r="D39" s="10">
         <v>2.15</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="23">
         <v>42</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="23">
         <v>60</v>
       </c>
       <c r="G39" s="12">
@@ -8522,7 +8523,7 @@
         <f t="shared" si="2"/>
         <v>8.4615384615384617</v>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="36">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
@@ -8530,7 +8531,7 @@
         <f t="shared" si="4"/>
         <v>да</v>
       </c>
-      <c r="K39" s="24">
+      <c r="K39" s="25">
         <f t="shared" si="5"/>
         <v>4.0695652173913048</v>
       </c>
@@ -8554,7 +8555,7 @@
         <f t="shared" si="10"/>
         <v>6.4968069849022223</v>
       </c>
-      <c r="Q39" s="35">
+      <c r="Q39" s="36">
         <f t="shared" si="11"/>
         <v>7</v>
       </c>
@@ -8562,20 +8563,20 @@
         <f t="shared" si="12"/>
         <v>4.6800000000000006</v>
       </c>
-      <c r="S39" s="16">
+      <c r="S39" s="17">
         <f t="shared" si="13"/>
         <v>0.11863734494169277</v>
       </c>
-      <c r="T39" s="16">
+      <c r="T39" s="17">
         <f t="shared" si="14"/>
         <v>0.11863734494169277</v>
       </c>
     </row>
     <row r="40" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="32" t="s">
+      <c r="A40" s="33" t="s">
         <v>505</v>
       </c>
-      <c r="B40" s="21">
+      <c r="B40" s="22">
         <v>10.5</v>
       </c>
       <c r="C40" s="10">
@@ -8584,10 +8585,10 @@
       <c r="D40" s="10">
         <v>2.6</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="23">
         <v>50</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="23">
         <v>60</v>
       </c>
       <c r="G40" s="12">
@@ -8598,7 +8599,7 @@
         <f t="shared" si="2"/>
         <v>16.153846153846153</v>
       </c>
-      <c r="I40" s="35">
+      <c r="I40" s="36">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -8606,7 +8607,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K40" s="24">
+      <c r="K40" s="25">
         <f t="shared" si="5"/>
         <v>8.1391304347826097</v>
       </c>
@@ -8630,7 +8631,7 @@
         <f t="shared" si="10"/>
         <v>3.5255223171889836</v>
       </c>
-      <c r="Q40" s="35">
+      <c r="Q40" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -8638,20 +8639,20 @@
         <f t="shared" si="12"/>
         <v>9.3600000000000012</v>
       </c>
-      <c r="S40" s="16">
+      <c r="S40" s="17">
         <f t="shared" si="13"/>
         <v>6.4379103183451011E-2</v>
       </c>
-      <c r="T40" s="16" t="str">
+      <c r="T40" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="41" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="33" t="s">
         <v>506</v>
       </c>
-      <c r="B41" s="21">
+      <c r="B41" s="22">
         <v>11</v>
       </c>
       <c r="C41" s="10">
@@ -8660,10 +8661,10 @@
       <c r="D41" s="10">
         <v>2.5299999999999998</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="23">
         <v>48</v>
       </c>
-      <c r="F41" s="22">
+      <c r="F41" s="23">
         <v>60</v>
       </c>
       <c r="G41" s="12">
@@ -8674,7 +8675,7 @@
         <f t="shared" si="2"/>
         <v>16.923076923076923</v>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="36">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -8682,7 +8683,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K41" s="24">
+      <c r="K41" s="25">
         <f t="shared" si="5"/>
         <v>8.1391304347826097</v>
       </c>
@@ -8706,7 +8707,7 @@
         <f t="shared" si="10"/>
         <v>3.5742775742775739</v>
       </c>
-      <c r="Q41" s="35">
+      <c r="Q41" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -8714,20 +8715,20 @@
         <f t="shared" si="12"/>
         <v>9.3600000000000012</v>
       </c>
-      <c r="S41" s="16">
+      <c r="S41" s="17">
         <f t="shared" si="13"/>
         <v>6.5269416573764394E-2</v>
       </c>
-      <c r="T41" s="16" t="str">
+      <c r="T41" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="42" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="32" t="s">
+      <c r="A42" s="33" t="s">
         <v>507</v>
       </c>
-      <c r="B42" s="21">
+      <c r="B42" s="22">
         <v>12</v>
       </c>
       <c r="C42" s="10">
@@ -8736,10 +8737,10 @@
       <c r="D42" s="10">
         <v>3.2</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>55</v>
       </c>
-      <c r="F42" s="22">
+      <c r="F42" s="23">
         <v>60</v>
       </c>
       <c r="G42" s="12">
@@ -8750,7 +8751,7 @@
         <f t="shared" si="2"/>
         <v>18.46153846153846</v>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="36">
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
@@ -8758,7 +8759,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K42" s="24">
+      <c r="K42" s="25">
         <f t="shared" si="5"/>
         <v>8.6478260869565222</v>
       </c>
@@ -8782,7 +8783,7 @@
         <f t="shared" si="10"/>
         <v>3.2768444337071791</v>
       </c>
-      <c r="Q42" s="35">
+      <c r="Q42" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -8790,20 +8791,20 @@
         <f t="shared" si="12"/>
         <v>9.9450000000000021</v>
       </c>
-      <c r="S42" s="16">
+      <c r="S42" s="17">
         <f t="shared" si="13"/>
         <v>5.9838028789435428E-2</v>
       </c>
-      <c r="T42" s="16" t="str">
+      <c r="T42" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="32" t="s">
+      <c r="A43" s="33" t="s">
         <v>508</v>
       </c>
-      <c r="B43" s="21">
+      <c r="B43" s="22">
         <v>11</v>
       </c>
       <c r="C43" s="10">
@@ -8812,10 +8813,10 @@
       <c r="D43" s="10">
         <v>3.02</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="23">
         <v>55</v>
       </c>
-      <c r="F43" s="22">
+      <c r="F43" s="23">
         <v>60</v>
       </c>
       <c r="G43" s="12">
@@ -8826,7 +8827,7 @@
         <f t="shared" si="2"/>
         <v>16.923076923076923</v>
       </c>
-      <c r="I43" s="35">
+      <c r="I43" s="36">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -8834,7 +8835,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K43" s="24">
+      <c r="K43" s="25">
         <f t="shared" si="5"/>
         <v>8.1391304347826097</v>
       </c>
@@ -8858,7 +8859,7 @@
         <f t="shared" si="10"/>
         <v>3.4191472108138776</v>
       </c>
-      <c r="Q43" s="35">
+      <c r="Q43" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -8866,20 +8867,20 @@
         <f t="shared" si="12"/>
         <v>9.3600000000000012</v>
       </c>
-      <c r="S43" s="16">
+      <c r="S43" s="17">
         <f t="shared" si="13"/>
         <v>6.2436601240949074E-2</v>
       </c>
-      <c r="T43" s="16" t="str">
+      <c r="T43" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="44" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="32" t="s">
+      <c r="A44" s="33" t="s">
         <v>509</v>
       </c>
-      <c r="B44" s="21">
+      <c r="B44" s="22">
         <v>6.6</v>
       </c>
       <c r="C44" s="10">
@@ -8888,10 +8889,10 @@
       <c r="D44" s="10">
         <v>2.85</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="23">
         <v>55</v>
       </c>
-      <c r="F44" s="22">
+      <c r="F44" s="23">
         <v>60</v>
       </c>
       <c r="G44" s="12">
@@ -8902,7 +8903,7 @@
         <f t="shared" si="2"/>
         <v>10.153846153846153</v>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="36">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -8910,7 +8911,7 @@
         <f t="shared" si="4"/>
         <v>да</v>
       </c>
-      <c r="K44" s="24">
+      <c r="K44" s="25">
         <f t="shared" si="5"/>
         <v>5.0869565217391308</v>
       </c>
@@ -8934,7 +8935,7 @@
         <f t="shared" si="10"/>
         <v>4.8706355373022037</v>
       </c>
-      <c r="Q44" s="35">
+      <c r="Q44" s="36">
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
@@ -8942,20 +8943,20 @@
         <f t="shared" si="12"/>
         <v>5.8500000000000005</v>
       </c>
-      <c r="S44" s="16">
+      <c r="S44" s="17">
         <f t="shared" si="13"/>
         <v>8.8942040246388063E-2</v>
       </c>
-      <c r="T44" s="16">
+      <c r="T44" s="17">
         <f t="shared" si="14"/>
         <v>8.8942040246388063E-2</v>
       </c>
     </row>
     <row r="45" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="32" t="s">
+      <c r="A45" s="33" t="s">
         <v>510</v>
       </c>
-      <c r="B45" s="21">
+      <c r="B45" s="22">
         <v>8.5</v>
       </c>
       <c r="C45" s="10">
@@ -8964,10 +8965,10 @@
       <c r="D45" s="10">
         <v>2.96</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="23">
         <v>55</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="23">
         <v>60</v>
       </c>
       <c r="G45" s="12">
@@ -8978,7 +8979,7 @@
         <f t="shared" si="2"/>
         <v>13.076923076923077</v>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="36">
         <f t="shared" si="3"/>
         <v>13</v>
       </c>
@@ -8986,7 +8987,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K45" s="24">
+      <c r="K45" s="25">
         <f t="shared" si="5"/>
         <v>6.6130434782608702</v>
       </c>
@@ -9010,7 +9011,7 @@
         <f t="shared" si="10"/>
         <v>3.9774119517709265</v>
       </c>
-      <c r="Q45" s="35">
+      <c r="Q45" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -9018,20 +9019,20 @@
         <f t="shared" si="12"/>
         <v>7.6050000000000013</v>
       </c>
-      <c r="S45" s="16">
+      <c r="S45" s="17">
         <f t="shared" si="13"/>
         <v>7.2631000858425609E-2</v>
       </c>
-      <c r="T45" s="16" t="str">
+      <c r="T45" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="46" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="32" t="s">
+      <c r="A46" s="33" t="s">
         <v>511</v>
       </c>
-      <c r="B46" s="21">
+      <c r="B46" s="22">
         <v>6.5</v>
       </c>
       <c r="C46" s="10">
@@ -9040,10 +9041,10 @@
       <c r="D46" s="10">
         <v>2.87</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="23">
         <v>52</v>
       </c>
-      <c r="F46" s="22">
+      <c r="F46" s="23">
         <v>60</v>
       </c>
       <c r="G46" s="12">
@@ -9054,7 +9055,7 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="I46" s="35">
+      <c r="I46" s="36">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
@@ -9062,7 +9063,7 @@
         <f t="shared" si="4"/>
         <v>да</v>
       </c>
-      <c r="K46" s="24">
+      <c r="K46" s="25">
         <f t="shared" si="5"/>
         <v>4.0695652173913048</v>
       </c>
@@ -9086,7 +9087,7 @@
         <f t="shared" si="10"/>
         <v>5.9610349289836462</v>
       </c>
-      <c r="Q46" s="35">
+      <c r="Q46" s="36">
         <f t="shared" si="11"/>
         <v>6</v>
       </c>
@@ -9094,20 +9095,20 @@
         <f t="shared" si="12"/>
         <v>4.6800000000000006</v>
       </c>
-      <c r="S46" s="16">
+      <c r="S46" s="17">
         <f t="shared" si="13"/>
         <v>0.1088536813118753</v>
       </c>
-      <c r="T46" s="16">
+      <c r="T46" s="17">
         <f t="shared" si="14"/>
         <v>0.1088536813118753</v>
       </c>
     </row>
     <row r="47" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="32" t="s">
+      <c r="A47" s="33" t="s">
         <v>512</v>
       </c>
-      <c r="B47" s="21">
+      <c r="B47" s="22">
         <v>12</v>
       </c>
       <c r="C47" s="10">
@@ -9116,10 +9117,10 @@
       <c r="D47" s="10">
         <v>2.7</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="23">
         <v>45</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="23">
         <v>60</v>
       </c>
       <c r="G47" s="12">
@@ -9130,7 +9131,7 @@
         <f t="shared" si="2"/>
         <v>18.46153846153846</v>
       </c>
-      <c r="I47" s="35">
+      <c r="I47" s="36">
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
@@ -9138,7 +9139,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K47" s="24">
+      <c r="K47" s="25">
         <f t="shared" si="5"/>
         <v>9.1565217391304365</v>
       </c>
@@ -9162,7 +9163,7 @@
         <f t="shared" si="10"/>
         <v>3.360476743192792</v>
       </c>
-      <c r="Q47" s="35">
+      <c r="Q47" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -9170,20 +9171,20 @@
         <f t="shared" si="12"/>
         <v>10.530000000000001</v>
       </c>
-      <c r="S47" s="16">
+      <c r="S47" s="17">
         <f t="shared" si="13"/>
         <v>6.1365227484390127E-2</v>
       </c>
-      <c r="T47" s="16" t="str">
+      <c r="T47" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="48" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="32" t="s">
+      <c r="A48" s="33" t="s">
         <v>513</v>
       </c>
-      <c r="B48" s="21">
+      <c r="B48" s="22">
         <v>10.5</v>
       </c>
       <c r="C48" s="10">
@@ -9192,10 +9193,10 @@
       <c r="D48" s="10">
         <v>2.42</v>
       </c>
-      <c r="E48" s="22">
+      <c r="E48" s="23">
         <v>45</v>
       </c>
-      <c r="F48" s="22">
+      <c r="F48" s="23">
         <v>60</v>
       </c>
       <c r="G48" s="12">
@@ -9206,7 +9207,7 @@
         <f t="shared" si="2"/>
         <v>16.153846153846153</v>
       </c>
-      <c r="I48" s="35">
+      <c r="I48" s="36">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -9214,7 +9215,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K48" s="24">
+      <c r="K48" s="25">
         <f t="shared" si="5"/>
         <v>8.1391304347826097</v>
       </c>
@@ -9238,7 +9239,7 @@
         <f t="shared" si="10"/>
         <v>3.6555363360918913</v>
       </c>
-      <c r="Q48" s="35">
+      <c r="Q48" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -9246,20 +9247,20 @@
         <f t="shared" si="12"/>
         <v>9.3600000000000012</v>
       </c>
-      <c r="S48" s="16">
+      <c r="S48" s="17">
         <f t="shared" si="13"/>
         <v>6.6753272224286717E-2</v>
       </c>
-      <c r="T48" s="16" t="str">
+      <c r="T48" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="32" t="s">
+      <c r="A49" s="33" t="s">
         <v>514</v>
       </c>
-      <c r="B49" s="21">
+      <c r="B49" s="22">
         <v>10.5</v>
       </c>
       <c r="C49" s="10">
@@ -9268,10 +9269,10 @@
       <c r="D49" s="10">
         <v>2.46</v>
       </c>
-      <c r="E49" s="22">
+      <c r="E49" s="23">
         <v>45</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="23">
         <v>60</v>
       </c>
       <c r="G49" s="12">
@@ -9282,7 +9283,7 @@
         <f t="shared" si="2"/>
         <v>16.153846153846153</v>
       </c>
-      <c r="I49" s="35">
+      <c r="I49" s="36">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
@@ -9290,7 +9291,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K49" s="24">
+      <c r="K49" s="25">
         <f t="shared" si="5"/>
         <v>8.1391304347826097</v>
       </c>
@@ -9314,7 +9315,7 @@
         <f t="shared" si="10"/>
         <v>3.6555363360918913</v>
       </c>
-      <c r="Q49" s="35">
+      <c r="Q49" s="36">
         <f t="shared" si="11"/>
         <v>4</v>
       </c>
@@ -9322,20 +9323,20 @@
         <f t="shared" si="12"/>
         <v>9.3600000000000012</v>
       </c>
-      <c r="S49" s="16">
+      <c r="S49" s="17">
         <f t="shared" si="13"/>
         <v>6.6753272224286717E-2</v>
       </c>
-      <c r="T49" s="16" t="str">
+      <c r="T49" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="32" t="s">
+      <c r="A50" s="33" t="s">
         <v>515</v>
       </c>
-      <c r="B50" s="21">
+      <c r="B50" s="22">
         <v>20</v>
       </c>
       <c r="C50" s="10">
@@ -9344,10 +9345,10 @@
       <c r="D50" s="10">
         <v>2.96</v>
       </c>
-      <c r="E50" s="22">
+      <c r="E50" s="23">
         <v>40</v>
       </c>
-      <c r="F50" s="22">
+      <c r="F50" s="23">
         <v>60</v>
       </c>
       <c r="G50" s="12">
@@ -9358,7 +9359,7 @@
         <f t="shared" si="2"/>
         <v>30.769230769230766</v>
       </c>
-      <c r="I50" s="35">
+      <c r="I50" s="36">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -9366,7 +9367,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K50" s="24">
+      <c r="K50" s="25">
         <f t="shared" si="5"/>
         <v>13.22608695652174</v>
       </c>
@@ -9390,7 +9391,7 @@
         <f t="shared" si="10"/>
         <v>2.7341869905972471</v>
       </c>
-      <c r="Q50" s="35">
+      <c r="Q50" s="36">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -9398,20 +9399,20 @@
         <f t="shared" si="12"/>
         <v>15.210000000000003</v>
       </c>
-      <c r="S50" s="16">
+      <c r="S50" s="17">
         <f t="shared" si="13"/>
         <v>4.99286320022106E-2</v>
       </c>
-      <c r="T50" s="16" t="str">
+      <c r="T50" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="32" t="s">
+      <c r="A51" s="33" t="s">
         <v>516</v>
       </c>
-      <c r="B51" s="21">
+      <c r="B51" s="22">
         <v>18</v>
       </c>
       <c r="C51" s="10">
@@ -9420,10 +9421,10 @@
       <c r="D51" s="10">
         <v>2.96</v>
       </c>
-      <c r="E51" s="22">
+      <c r="E51" s="23">
         <v>40</v>
       </c>
-      <c r="F51" s="22">
+      <c r="F51" s="23">
         <v>60</v>
       </c>
       <c r="G51" s="12">
@@ -9434,7 +9435,7 @@
         <f t="shared" si="2"/>
         <v>27.69230769230769</v>
       </c>
-      <c r="I51" s="35">
+      <c r="I51" s="36">
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
@@ -9442,7 +9443,7 @@
         <f t="shared" si="4"/>
         <v>нет</v>
       </c>
-      <c r="K51" s="24">
+      <c r="K51" s="25">
         <f t="shared" si="5"/>
         <v>12.208695652173915</v>
       </c>
@@ -9466,7 +9467,7 @@
         <f t="shared" si="10"/>
         <v>2.8787025731470175</v>
       </c>
-      <c r="Q51" s="35">
+      <c r="Q51" s="36">
         <f t="shared" si="11"/>
         <v>3</v>
       </c>
@@ -9474,51 +9475,51 @@
         <f t="shared" si="12"/>
         <v>14.040000000000003</v>
       </c>
-      <c r="S51" s="16">
+      <c r="S51" s="17">
         <f t="shared" si="13"/>
         <v>5.2567612205293351E-2</v>
       </c>
-      <c r="T51" s="16" t="str">
+      <c r="T51" s="17" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="50" t="s">
+      <c r="A53" s="51" t="s">
         <v>517</v>
       </c>
-      <c r="B53" s="43"/>
-      <c r="C53" s="15" t="str">
+      <c r="B53" s="44"/>
+      <c r="C53" s="16" t="str">
         <f>INDEX($A$34:$A$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
         <v>КамАЗ-55111</v>
       </c>
     </row>
     <row r="54" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="42" t="s">
+      <c r="A54" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="B54" s="43"/>
-      <c r="C54" s="35">
+      <c r="B54" s="44"/>
+      <c r="C54" s="36">
         <f>INDEX($I$34:$I$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
         <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="42" t="s">
+      <c r="A55" s="43" t="s">
         <v>519</v>
       </c>
-      <c r="B55" s="43"/>
-      <c r="C55" s="35">
+      <c r="B55" s="44"/>
+      <c r="C55" s="36">
         <f>INDEX($Q$34:$Q$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:20" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A56" s="42" t="s">
+      <c r="A56" s="43" t="s">
         <v>520</v>
       </c>
-      <c r="B56" s="43"/>
-      <c r="C56" s="16">
+      <c r="B56" s="44"/>
+      <c r="C56" s="17">
         <f>INDEX($S$34:$S$51,MATCH(MIN($T$34:$T$51),$T$34:$T$51,0))</f>
         <v>8.8942040246388063E-2</v>
       </c>
@@ -9622,58 +9623,58 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="A5" s="16">
         <v>1</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="16">
         <v>2</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <v>3</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <v>4</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="16">
         <v>5</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="16">
         <v>6</v>
       </c>
-      <c r="G5" s="15">
+      <c r="G5" s="16">
         <v>7</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="16">
         <v>8</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="16">
         <v>9</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="16">
         <v>10</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="16">
         <v>11</v>
       </c>
-      <c r="L5" s="15">
+      <c r="L5" s="16">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="46" t="s">
         <v>534</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
-      <c r="K6" s="52"/>
-      <c r="L6" s="52"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
@@ -9685,7 +9686,7 @@
       <c r="C7" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>150</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -9694,7 +9695,7 @@
       <c r="F7" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="41">
         <v>1.3</v>
       </c>
       <c r="H7" s="12">
@@ -9705,7 +9706,7 @@
         <f t="shared" ref="I7:I14" si="1">H7/8</f>
         <v>24.375</v>
       </c>
-      <c r="J7" s="40">
+      <c r="J7" s="41">
         <v>1.3</v>
       </c>
       <c r="K7" s="12">
@@ -9727,7 +9728,7 @@
       <c r="C8" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>238.75925259715959</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -9736,7 +9737,7 @@
       <c r="F8" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="41">
         <v>0.06</v>
       </c>
       <c r="H8" s="12">
@@ -9747,7 +9748,7 @@
         <f t="shared" si="1"/>
         <v>1.7906943944786968</v>
       </c>
-      <c r="J8" s="40">
+      <c r="J8" s="41">
         <v>0.06</v>
       </c>
       <c r="K8" s="12">
@@ -9769,7 +9770,7 @@
       <c r="C9" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>274.57314048673362</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -9778,7 +9779,7 @@
       <c r="F9" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="41">
         <v>3.2143098852515162</v>
       </c>
       <c r="H9" s="12">
@@ -9789,7 +9790,7 @@
         <f t="shared" si="1"/>
         <v>110.32039496138265</v>
       </c>
-      <c r="J9" s="40">
+      <c r="J9" s="41">
         <v>3.2143098852515162</v>
       </c>
       <c r="K9" s="12">
@@ -9811,7 +9812,7 @@
       <c r="C10" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>274.57314048673362</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -9820,7 +9821,7 @@
       <c r="F10" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="41">
         <v>1.0714366284171719</v>
       </c>
       <c r="H10" s="12">
@@ -9831,7 +9832,7 @@
         <f t="shared" si="1"/>
         <v>36.773464987127547</v>
       </c>
-      <c r="J10" s="40">
+      <c r="J10" s="41">
         <v>1.0714366284171719</v>
       </c>
       <c r="K10" s="12">
@@ -9853,7 +9854,7 @@
       <c r="C11" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>275.47744909966451</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -9862,7 +9863,7 @@
       <c r="F11" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="H11" s="12">
@@ -9873,7 +9874,7 @@
         <f t="shared" si="1"/>
         <v>3.0626907955993357</v>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="K11" s="12">
@@ -9895,7 +9896,7 @@
       <c r="C12" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <v>292.10696689588838</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -9904,7 +9905,7 @@
       <c r="F12" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="41">
         <v>0.27</v>
       </c>
       <c r="H12" s="12">
@@ -9915,7 +9916,7 @@
         <f t="shared" si="1"/>
         <v>9.8586101327362332</v>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="41">
         <v>0.27</v>
       </c>
       <c r="K12" s="12">
@@ -9937,7 +9938,7 @@
       <c r="C13" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>292.10696689588838</v>
       </c>
       <c r="E13" s="5" t="s">
@@ -9946,7 +9947,7 @@
       <c r="F13" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="41">
         <v>0.25</v>
       </c>
       <c r="H13" s="12">
@@ -9957,7 +9958,7 @@
         <f t="shared" si="1"/>
         <v>9.1283427154965118</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="41">
         <v>0.25</v>
       </c>
       <c r="K13" s="12">
@@ -9979,7 +9980,7 @@
       <c r="C14" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <v>150</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -9988,7 +9989,7 @@
       <c r="F14" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="41">
         <v>0.23</v>
       </c>
       <c r="H14" s="12">
@@ -9999,7 +10000,7 @@
         <f t="shared" si="1"/>
         <v>4.3125</v>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="41">
         <v>0.23</v>
       </c>
       <c r="K14" s="12">
@@ -10012,20 +10013,20 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="46" t="s">
         <v>551</v>
       </c>
-      <c r="B15" s="52"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
     </row>
     <row r="16" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
@@ -10037,7 +10038,7 @@
       <c r="C16" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <v>39.717374877451732</v>
       </c>
       <c r="E16" s="5" t="s">
@@ -10046,7 +10047,7 @@
       <c r="F16" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="41">
         <v>2.1</v>
       </c>
       <c r="H16" s="12">
@@ -10057,7 +10058,7 @@
         <f t="shared" ref="I16:I22" si="5">H16/8</f>
         <v>10.42581090533108</v>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="41">
         <v>2.1</v>
       </c>
       <c r="K16" s="12">
@@ -10079,7 +10080,7 @@
       <c r="C17" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="20">
         <v>4567.4981109069486</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -10088,7 +10089,7 @@
       <c r="F17" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="H17" s="12">
@@ -10099,7 +10100,7 @@
         <f t="shared" si="5"/>
         <v>50.78032510069842</v>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="K17" s="12">
@@ -10121,7 +10122,7 @@
       <c r="C18" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="20">
         <v>1.6868799999999999</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -10130,7 +10131,7 @@
       <c r="F18" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="41">
         <v>0.46479901356350178</v>
       </c>
       <c r="H18" s="12">
@@ -10141,7 +10142,7 @@
         <f t="shared" si="5"/>
         <v>9.8007519999999987E-2</v>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="41">
         <v>0.46479901356350178</v>
       </c>
       <c r="K18" s="12">
@@ -10163,7 +10164,7 @@
       <c r="C19" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="20">
         <v>1.0189999999999999</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -10172,7 +10173,7 @@
       <c r="F19" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="41">
         <v>4.5999999999999996</v>
       </c>
       <c r="H19" s="12">
@@ -10203,7 +10204,7 @@
       <c r="C20" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <v>186.53</v>
       </c>
       <c r="E20" s="5" t="s">
@@ -10212,7 +10213,7 @@
       <c r="F20" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="H20" s="12">
@@ -10223,7 +10224,7 @@
         <f t="shared" si="5"/>
         <v>2.0737948458948461</v>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="K20" s="12">
@@ -10245,7 +10246,7 @@
       <c r="C21" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <v>1.6868799999999999</v>
       </c>
       <c r="E21" s="5" t="s">
@@ -10254,7 +10255,7 @@
       <c r="F21" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="41">
         <v>0.38</v>
       </c>
       <c r="H21" s="12">
@@ -10265,7 +10266,7 @@
         <f t="shared" si="5"/>
         <v>8.0126799999999998E-2</v>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="41">
         <v>0.38</v>
       </c>
       <c r="K21" s="12">
@@ -10287,7 +10288,7 @@
       <c r="C22" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <v>1.6868799999999999</v>
       </c>
       <c r="E22" s="5" t="s">
@@ -10296,7 +10297,7 @@
       <c r="F22" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="41">
         <v>1.3</v>
       </c>
       <c r="H22" s="12">
@@ -10307,7 +10308,7 @@
         <f t="shared" si="5"/>
         <v>0.27411799999999997</v>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="41">
         <v>1.3</v>
       </c>
       <c r="K22" s="12">
@@ -10320,20 +10321,20 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="46" t="s">
         <v>566</v>
       </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="52"/>
-      <c r="K23" s="52"/>
-      <c r="L23" s="52"/>
+      <c r="B23" s="53"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="53"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="53"/>
+      <c r="H23" s="53"/>
+      <c r="I23" s="53"/>
+      <c r="J23" s="53"/>
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
     </row>
     <row r="24" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
@@ -10345,7 +10346,7 @@
       <c r="C24" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <v>1209.237384333605</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -10354,7 +10355,7 @@
       <c r="F24" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="H24" s="12">
@@ -10365,7 +10366,7 @@
         <f t="shared" ref="I24:I30" si="7">H24/8</f>
         <v>13.444005013104567</v>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="41">
         <v>8.8942040246388077E-2</v>
       </c>
       <c r="K24" s="12">
@@ -10387,7 +10388,7 @@
       <c r="C25" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <v>9.5330324066620147</v>
       </c>
       <c r="E25" s="5" t="s">
@@ -10396,7 +10397,7 @@
       <c r="F25" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="41">
         <v>0.25</v>
       </c>
       <c r="H25" s="12">
@@ -10407,7 +10408,7 @@
         <f t="shared" si="7"/>
         <v>0.29790726270818796</v>
       </c>
-      <c r="J25" s="40">
+      <c r="J25" s="41">
         <v>0.25</v>
       </c>
       <c r="K25" s="12">
@@ -10429,7 +10430,7 @@
       <c r="C26" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <v>17.485535557536888</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -10438,7 +10439,7 @@
       <c r="F26" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="41">
         <v>3.5</v>
       </c>
       <c r="H26" s="12">
@@ -10469,7 +10470,7 @@
       <c r="C27" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="20">
         <v>17.485535557536888</v>
       </c>
       <c r="E27" s="5" t="s">
@@ -10478,7 +10479,7 @@
       <c r="F27" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="41">
         <v>1.9</v>
       </c>
       <c r="H27" s="12">
@@ -10489,7 +10490,7 @@
         <f t="shared" si="7"/>
         <v>4.1528146949150111</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="41">
         <v>1.9</v>
       </c>
       <c r="K27" s="12">
@@ -10511,7 +10512,7 @@
       <c r="C28" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="20">
         <v>0.98584717280410805</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -10520,7 +10521,7 @@
       <c r="F28" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G28" s="40">
+      <c r="G28" s="41">
         <v>1.3</v>
       </c>
       <c r="H28" s="12">
@@ -10531,7 +10532,7 @@
         <f t="shared" si="7"/>
         <v>0.16020016558066758</v>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="41">
         <v>1.3</v>
       </c>
       <c r="K28" s="12">
@@ -10553,7 +10554,7 @@
       <c r="C29" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="20">
         <v>1.4026795907897189</v>
       </c>
       <c r="E29" s="5" t="s">
@@ -10562,7 +10563,7 @@
       <c r="F29" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G29" s="40">
+      <c r="G29" s="41">
         <v>0.22</v>
       </c>
       <c r="H29" s="12">
@@ -10573,7 +10574,7 @@
         <f t="shared" si="7"/>
         <v>3.8573688746717273E-2</v>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="41">
         <v>0.22</v>
       </c>
       <c r="K29" s="12">
@@ -10595,7 +10596,7 @@
       <c r="C30" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="20">
         <v>0.4023366260989728</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -10604,7 +10605,7 @@
       <c r="F30" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="41">
         <v>1.3</v>
       </c>
       <c r="H30" s="12">
@@ -10615,7 +10616,7 @@
         <f t="shared" si="7"/>
         <v>6.5379701741083082E-2</v>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="41">
         <v>1.3</v>
       </c>
       <c r="K30" s="12">
@@ -10628,28 +10629,29 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="50" t="s">
+      <c r="A31" s="51" t="s">
         <v>579</v>
       </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="17">
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="18">
         <f>SUM(H6:H30)</f>
         <v>2317.9888679357118</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="18">
         <f>SUM(I6:I30)</f>
         <v>289.74860849196398</v>
       </c>
-      <c r="K31" s="17">
+      <c r="J31" s="15"/>
+      <c r="K31" s="18">
         <f>SUM(K6:K30)</f>
         <v>2252.1020934843327</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="18">
         <f>SUM(L6:L30)</f>
         <v>281.51276168554159</v>
       </c>
@@ -11126,7 +11128,7 @@
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="36" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
     <col min="12" max="12" width="9" customWidth="1"/>
@@ -11142,7 +11144,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="64.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>317</v>
       </c>
@@ -11180,7 +11182,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1</v>
       </c>
@@ -11190,14 +11192,14 @@
       <c r="C5" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="20">
         <v>150</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f>'Табл. 12 калькуляция'!I7</f>
         <v>24.375</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F5" s="27">
         <f>'Табл. 12 калькуляция'!L7</f>
         <v>24.375</v>
       </c>
@@ -11207,7 +11209,7 @@
       <c r="H5" s="6">
         <v>1</v>
       </c>
-      <c r="I5" s="35">
+      <c r="I5" s="36">
         <f t="shared" ref="I5:I13" si="0">ROUNDUP(E5/H5,0)</f>
         <v>25</v>
       </c>
@@ -11217,12 +11219,12 @@
       <c r="K5" s="6">
         <v>13</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="42">
         <f t="shared" ref="L5:L13" si="1">E5/(H5*I5)</f>
         <v>0.97499999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>2</v>
       </c>
@@ -11232,14 +11234,14 @@
       <c r="C6" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>238.75925259715959</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>'Табл. 12 калькуляция'!I8</f>
         <v>1.7906943944786968</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <f>'Табл. 12 калькуляция'!L8</f>
         <v>1.7906943944786968</v>
       </c>
@@ -11249,7 +11251,7 @@
       <c r="H6" s="6">
         <v>1</v>
       </c>
-      <c r="I6" s="35">
+      <c r="I6" s="36">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -11259,12 +11261,12 @@
       <c r="K6" s="6">
         <v>1</v>
       </c>
-      <c r="L6" s="41">
+      <c r="L6" s="42">
         <f t="shared" si="1"/>
         <v>0.89534719723934841</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>3</v>
       </c>
@@ -11274,14 +11276,14 @@
       <c r="C7" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <v>274.57314048673362</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f>'Табл. 12 калькуляция'!I9+'Табл. 12 калькуляция'!I10</f>
         <v>147.09385994851019</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="27">
         <f>'Табл. 12 калькуляция'!L9+'Табл. 12 калькуляция'!L10</f>
         <v>147.09385994851019</v>
       </c>
@@ -11291,7 +11293,7 @@
       <c r="H7" s="6">
         <v>4</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="36">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -11301,12 +11303,12 @@
       <c r="K7" s="6">
         <v>19</v>
       </c>
-      <c r="L7" s="41">
+      <c r="L7" s="42">
         <f t="shared" si="1"/>
         <v>0.99387743208452828</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>4</v>
       </c>
@@ -11316,14 +11318,14 @@
       <c r="C8" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <v>292.10696689588838</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>'Табл. 12 калькуляция'!I12</f>
         <v>9.8586101327362332</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>'Табл. 12 калькуляция'!L12</f>
         <v>9.8586101327362332</v>
       </c>
@@ -11333,7 +11335,7 @@
       <c r="H8" s="6">
         <v>1</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="36">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -11343,12 +11345,12 @@
       <c r="K8" s="6">
         <v>10</v>
       </c>
-      <c r="L8" s="41">
+      <c r="L8" s="42">
         <f t="shared" si="1"/>
         <v>0.9858610132736233</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>5</v>
       </c>
@@ -11358,14 +11360,14 @@
       <c r="C9" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <v>292.10696689588838</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f>'Табл. 12 калькуляция'!I13</f>
         <v>9.1283427154965118</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>'Табл. 12 калькуляция'!L13</f>
         <v>9.1283427154965118</v>
       </c>
@@ -11375,7 +11377,7 @@
       <c r="H9" s="6">
         <v>1</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="36">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -11385,12 +11387,12 @@
       <c r="K9" s="6">
         <v>10</v>
       </c>
-      <c r="L9" s="41">
+      <c r="L9" s="42">
         <f t="shared" si="1"/>
         <v>0.91283427154965113</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>6</v>
       </c>
@@ -11400,14 +11402,14 @@
       <c r="C10" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <v>39.717374877451732</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>'Табл. 12 калькуляция'!I16+'Табл. 12 калькуляция'!I17</f>
         <v>61.206136006029496</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>'Табл. 12 калькуляция'!L16+'Табл. 12 калькуляция'!L17</f>
         <v>61.206136006029496</v>
       </c>
@@ -11417,7 +11419,7 @@
       <c r="H10" s="6">
         <v>6</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="36">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -11427,12 +11429,12 @@
       <c r="K10" s="6">
         <v>6</v>
       </c>
-      <c r="L10" s="41">
+      <c r="L10" s="42">
         <f t="shared" si="1"/>
         <v>0.92736569706105298</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>7</v>
       </c>
@@ -11442,14 +11444,14 @@
       <c r="C11" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <v>1.6868799999999999</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>'Табл. 12 калькуляция'!I18+'Табл. 12 калькуляция'!I19+'Табл. 12 калькуляция'!I20+'Табл. 12 калькуляция'!I21+'Табл. 12 калькуляция'!I22+'Табл. 12 калькуляция'!I11</f>
         <v>6.1746629614941817</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>'Табл. 12 калькуляция'!L18+'Табл. 12 калькуляция'!L20+'Табл. 12 калькуляция'!L21+'Табл. 12 калькуляция'!L22+'Табл. 12 калькуляция'!L11</f>
         <v>5.5887379614941821</v>
       </c>
@@ -11459,7 +11461,7 @@
       <c r="H11" s="6">
         <v>7</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="36">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -11469,12 +11471,12 @@
       <c r="K11" s="6">
         <v>1</v>
       </c>
-      <c r="L11" s="41">
+      <c r="L11" s="42">
         <f t="shared" si="1"/>
         <v>0.88209470878488305</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>8</v>
       </c>
@@ -11484,14 +11486,14 @@
       <c r="C12" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <v>150</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>'Табл. 12 калькуляция'!I14</f>
         <v>4.3125</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>'Табл. 12 калькуляция'!L14</f>
         <v>4.3125</v>
       </c>
@@ -11501,7 +11503,7 @@
       <c r="H12" s="6">
         <v>1</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="36">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -11511,12 +11513,12 @@
       <c r="K12" s="6">
         <v>3</v>
       </c>
-      <c r="L12" s="41">
+      <c r="L12" s="42">
         <f t="shared" si="1"/>
         <v>0.86250000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -11526,14 +11528,14 @@
       <c r="C13" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <v>9.5330324066620147</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f>'Табл. 12 калькуляция'!I24+'Табл. 12 калькуляция'!I25+'Табл. 12 калькуляция'!I26+'Табл. 12 калькуляция'!I27+'Табл. 12 калькуляция'!I28+'Табл. 12 калькуляция'!I29+'Табл. 12 калькуляция'!I30</f>
         <v>25.808802333218622</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>'Табл. 12 калькуляция'!L24+'Табл. 12 калькуляция'!L25+'Табл. 12 калькуляция'!L27+'Табл. 12 калькуляция'!L28+'Табл. 12 калькуляция'!L29+'Табл. 12 калькуляция'!L30</f>
         <v>18.158880526796235</v>
       </c>
@@ -11543,7 +11545,7 @@
       <c r="H13" s="6">
         <v>10</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="36">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -11553,35 +11555,36 @@
       <c r="K13" s="6">
         <v>2</v>
       </c>
-      <c r="L13" s="41">
+      <c r="L13" s="42">
         <f t="shared" si="1"/>
         <v>0.86029341110728741</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="50" t="s">
+    <row r="14" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="51" t="s">
         <v>579</v>
       </c>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="17">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="18">
         <f>SUM(E5:E13)</f>
         <v>289.74860849196392</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="18">
         <f>SUM(F5:F13)</f>
         <v>281.51276168554153</v>
       </c>
-      <c r="G14" s="42" t="s">
+      <c r="G14" s="43" t="s">
         <v>603</v>
       </c>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="15">
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="16">
         <v>29</v>
       </c>
+      <c r="L14" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11922,19 +11925,19 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -11966,14 +11969,14 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="12">
         <f>'Исходные данные'!$B$3^2-$F$6</f>
         <v>9388.5869565217399</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>(0+ABS('Исходные данные'!$B$9)+ABS('Исходные данные'!$B$15)+ABS('Исходные данные'!$B$16)+0)/5</f>
         <v>0.21000000000000002</v>
       </c>
@@ -11981,14 +11984,14 @@
         <f>B6*C6</f>
         <v>1971.6032608695655</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>101</v>
       </c>
       <c r="F6" s="12">
         <f>'ЛНР (черн.)'!$G$6*'ЛНР (черн.)'!$H$5/2</f>
         <v>611.41304347826087</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="17">
         <f>(0+ABS('Исходные данные'!$B$10)+0)/3</f>
         <v>4.9999999999999996E-2</v>
       </c>
@@ -12002,14 +12005,14 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>102</v>
       </c>
       <c r="B7" s="12">
         <f>'ЛНР (черн.)'!$H$6*'ЛНР (черн.)'!$G$7/2</f>
         <v>1770.4495210022105</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>(0+ABS('Исходные данные'!$B$16)+0)/3</f>
         <v>0.10333333333333333</v>
       </c>
@@ -12017,14 +12020,14 @@
         <f>B7*C7</f>
         <v>182.94645050356175</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F7" s="12">
         <f>'Исходные данные'!$B$3^2-$B$7</f>
         <v>8229.5504789977895</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>(0+ABS('Исходные данные'!$B$17)+ABS('Исходные данные'!$B$11)+ABS('Исходные данные'!$B$10)+0)/5</f>
         <v>0.15400000000000003</v>
       </c>
@@ -12050,14 +12053,14 @@
       <c r="D8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>105</v>
       </c>
       <c r="F8" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="17">
         <f>(ABS('Исходные данные'!$B$17)+ABS('Исходные данные'!$B$18)+ABS('Исходные данные'!$B$12)+ABS('Исходные данные'!$B$11))/4</f>
         <v>0.40250000000000002</v>
       </c>
@@ -12083,14 +12086,14 @@
       <c r="D9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>106</v>
       </c>
       <c r="F9" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="17">
         <f>(ABS('Исходные данные'!$B$18)+ABS('Исходные данные'!$B$19)+ABS('Исходные данные'!$B$13)+ABS('Исходные данные'!$B$12))/4</f>
         <v>0.62250000000000005</v>
       </c>
@@ -12116,14 +12119,14 @@
       <c r="D10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F10" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>(ABS('Исходные данные'!$B$19)+ABS('Исходные данные'!$B$20)+ABS('Исходные данные'!$B$14)+ABS('Исходные данные'!$B$13))/4</f>
         <v>0.70500000000000007</v>
       </c>
@@ -12137,14 +12140,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>108</v>
       </c>
       <c r="B11" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <f>(ABS('Исходные данные'!$B$21)+ABS('Исходные данные'!$B$22)+ABS('Исходные данные'!$B$16)+ABS('Исходные данные'!$B$15))/4</f>
         <v>0.36749999999999999</v>
       </c>
@@ -12169,14 +12172,14 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>109</v>
       </c>
       <c r="B12" s="12">
         <f>'Исходные данные'!$B$3^2-$F$12</f>
         <v>8813.5593220338978</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f>(0+ABS('Исходные данные'!$B$16)+ABS('Исходные данные'!$B$22)+ABS('Исходные данные'!$B$23)+0)/5</f>
         <v>0.20400000000000001</v>
       </c>
@@ -12184,14 +12187,14 @@
         <f>B12*C12</f>
         <v>1797.9661016949153</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>110</v>
       </c>
       <c r="F12" s="12">
         <f>'ЛНР (черн.)'!$G$8*'ЛНР (черн.)'!$H$7/2</f>
         <v>1186.4406779661019</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>(0+ABS('Исходные данные'!$B$17)+0)/3</f>
         <v>9.3333333333333338E-2</v>
       </c>
@@ -12205,14 +12208,14 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B13" s="12">
         <f>'ЛНР (черн.)'!$H$8*'ЛНР (черн.)'!$G$9/2</f>
         <v>1666.6666666666667</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>(0+ABS('Исходные данные'!$B$23)+0)/3</f>
         <v>9.3333333333333338E-2</v>
       </c>
@@ -12220,14 +12223,14 @@
         <f>B13*C13</f>
         <v>155.55555555555557</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>112</v>
       </c>
       <c r="F13" s="12">
         <f>'Исходные данные'!$B$3^2-$B$13</f>
         <v>8333.3333333333339</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="17">
         <f>(0+ABS('Исходные данные'!$B$24)+ABS('Исходные данные'!$B$18)+ABS('Исходные данные'!$B$17)+0)/5</f>
         <v>0.188</v>
       </c>
@@ -12253,14 +12256,14 @@
       <c r="D14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>113</v>
       </c>
       <c r="F14" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>(ABS('Исходные данные'!$B$24)+ABS('Исходные данные'!$B$25)+ABS('Исходные данные'!$B$19)+ABS('Исходные данные'!$B$18))/4</f>
         <v>0.46499999999999997</v>
       </c>
@@ -12286,14 +12289,14 @@
       <c r="D15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>114</v>
       </c>
       <c r="F15" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="17">
         <f>(ABS('Исходные данные'!$B$25)+ABS('Исходные данные'!$B$26)+ABS('Исходные данные'!$B$20)+ABS('Исходные данные'!$B$19))/4</f>
         <v>0.60750000000000004</v>
       </c>
@@ -12307,14 +12310,14 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>115</v>
       </c>
       <c r="B16" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f>(ABS('Исходные данные'!$B$27)+ABS('Исходные данные'!$B$28)+ABS('Исходные данные'!$B$22)+ABS('Исходные данные'!$B$21))/4</f>
         <v>0.43</v>
       </c>
@@ -12339,14 +12342,14 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>116</v>
       </c>
       <c r="B17" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <f>(ABS('Исходные данные'!$B$28)+ABS('Исходные данные'!$B$29)+ABS('Исходные данные'!$B$23)+ABS('Исходные данные'!$B$22))/4</f>
         <v>0.47</v>
       </c>
@@ -12371,14 +12374,14 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>117</v>
       </c>
       <c r="B18" s="12">
         <f>'Исходные данные'!$B$3^2-$F$18</f>
         <v>9444.4444444444453</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="17">
         <f>(0+ABS('Исходные данные'!$B$23)+ABS('Исходные данные'!$B$29)+ABS('Исходные данные'!$B$30)+0)/5</f>
         <v>0.21600000000000003</v>
       </c>
@@ -12386,14 +12389,14 @@
         <f>B18*C18</f>
         <v>2040.0000000000005</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="12">
         <f>'ЛНР (черн.)'!$G$10*'ЛНР (черн.)'!$H$9/2</f>
         <v>555.55555555555554</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="17">
         <f>(0+ABS('Исходные данные'!$B$24)+0)/3</f>
         <v>4.6666666666666669E-2</v>
       </c>
@@ -12407,14 +12410,14 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>119</v>
       </c>
       <c r="B19" s="12">
         <f>('ЛНР (черн.)'!$H$10+'ЛНР (черн.)'!$H$11)/2*'Исходные данные'!$B$3</f>
         <v>6054.8523206751051</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <f>(0+ABS('Исходные данные'!$B$30)+ABS('Исходные данные'!$B$31)+0)/4</f>
         <v>0.17749999999999999</v>
       </c>
@@ -12422,14 +12425,14 @@
         <f>B19*C19</f>
         <v>1074.7362869198312</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>120</v>
       </c>
       <c r="F19" s="12">
         <f>('ЛНР (черн.)'!$G$11+'ЛНР (черн.)'!$G$10)/2*'Исходные данные'!$B$3</f>
         <v>3945.1476793248944</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="17">
         <f>(0+ABS('Исходные данные'!$B$25)+ABS('Исходные данные'!$B$24)+0)/4</f>
         <v>0.125</v>
       </c>
@@ -12443,14 +12446,14 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>121</v>
       </c>
       <c r="B20" s="12">
         <f>'ЛНР (черн.)'!$H$11*'ЛНР (черн.)'!$G$12/2</f>
         <v>2053.0757272929159</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <f>(0+ABS('Исходные данные'!$B$31)+0)/3</f>
         <v>0.14333333333333334</v>
       </c>
@@ -12458,14 +12461,14 @@
         <f>B20*C20</f>
         <v>294.27418757865127</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>122</v>
       </c>
       <c r="F20" s="12">
         <f>'Исходные данные'!$B$3^2-$B$20</f>
         <v>7946.9242727070841</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="17">
         <f>(0+ABS('Исходные данные'!$B$32)+ABS('Исходные данные'!$B$26)+ABS('Исходные данные'!$B$25)+0)/5</f>
         <v>0.252</v>
       </c>
@@ -12479,31 +12482,31 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="18">
         <f>SUM(B6:B20)</f>
         <v>69191.634958636991</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <f>SUM(D6:D20)</f>
         <v>20192.08184312208</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <f>SUM(F6:F20)</f>
         <v>80808.365041363009</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="17">
+      <c r="H21" s="18">
         <f>SUM(H6:H20)</f>
         <v>33522.016858446805</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <f>SUM(I6:I20)</f>
         <v>32232.708517737305</v>
       </c>
@@ -12537,7 +12540,7 @@
       <c r="A25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <f>ABS('Исходные данные'!$B$9)+ABS('Исходные данные'!$B$31)+ABS('Исходные данные'!$B$30)+ABS('Исходные данные'!$B$29)+ABS('Исходные данные'!$B$28)+ABS('Исходные данные'!$B$27)+ABS('Исходные данные'!$B$21)+ABS('Исходные данные'!$B$15)</f>
         <v>3.26</v>
       </c>
@@ -12560,7 +12563,7 @@
       <c r="A26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <f>ABS('Исходные данные'!$B$10)+ABS('Исходные данные'!$B$11)+ABS('Исходные данные'!$B$12)+ABS('Исходные данные'!$B$13)+ABS('Исходные данные'!$B$14)+ABS('Исходные данные'!$B$20)+ABS('Исходные данные'!$B$26)+ABS('Исходные данные'!$B$32)</f>
         <v>3.8400000000000003</v>
       </c>
@@ -12585,66 +12588,66 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="17">
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="18">
         <f>B21+F21</f>
         <v>150000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="17">
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="18">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="17">
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="18">
         <f>D21+F25</f>
         <v>20209.474960755029</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="17">
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="18">
         <f>H21+F26</f>
         <v>33543.964226867858</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="17">
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="18">
         <f>F32/'Исходные данные'!$B$4</f>
         <v>32253.811756603707</v>
       </c>
@@ -12710,13 +12713,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="45" t="s">
+      <c r="A5" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
     </row>
     <row r="6" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
@@ -12725,13 +12728,13 @@
       <c r="B6" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>2.4</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
@@ -12740,13 +12743,13 @@
       <c r="B7" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="20">
         <v>0.4</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E7" s="20"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
@@ -12755,13 +12758,13 @@
       <c r="B8" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="20">
         <v>0.15</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="20"/>
+      <c r="E8" s="21"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
@@ -12770,13 +12773,13 @@
       <c r="B9" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <v>0.1</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="20"/>
+      <c r="E9" s="21"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
@@ -12785,13 +12788,13 @@
       <c r="B10" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <v>0.2</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="21" t="s">
         <v>158</v>
       </c>
     </row>
@@ -12802,13 +12805,13 @@
       <c r="B11" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <v>0.4</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="21" t="s">
         <v>161</v>
       </c>
     </row>
@@ -12817,13 +12820,13 @@
         <v>162</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>0.5</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>163</v>
       </c>
     </row>
@@ -12832,13 +12835,13 @@
         <v>164</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <v>0.2</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>165</v>
       </c>
     </row>
@@ -12847,13 +12850,13 @@
         <v>166</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <v>0.5</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="21" t="s">
         <v>163</v>
       </c>
     </row>
@@ -12862,78 +12865,78 @@
         <v>167</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <v>60</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E15" s="20"/>
+      <c r="E15" s="21"/>
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>168</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="21">
+      <c r="C16" s="22">
         <v>30</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E16" s="20"/>
+      <c r="E16" s="21"/>
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>169</v>
       </c>
       <c r="B17" s="3"/>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E17" s="20"/>
+      <c r="E17" s="21"/>
     </row>
     <row r="18" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>170</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="21">
+      <c r="C18" s="22">
         <v>12</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="20"/>
+      <c r="E18" s="21"/>
     </row>
     <row r="19" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>171</v>
       </c>
       <c r="B19" s="3"/>
-      <c r="C19" s="22">
+      <c r="C19" s="23">
         <v>200</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="20"/>
+      <c r="E19" s="21"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>172</v>
       </c>
       <c r="B20" s="3"/>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <v>100</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E20" s="20"/>
+      <c r="E20" s="21"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
@@ -12942,14 +12945,14 @@
       <c r="B21" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="24">
         <f>$C$19+'Исходные данные'!$B$3/2-$C$15/2</f>
         <v>220</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E21" s="20"/>
+      <c r="E21" s="21"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
@@ -12958,37 +12961,37 @@
       <c r="B22" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>$C$20+'Исходные данные'!$B$3/2-$C$16/2</f>
         <v>135</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="20"/>
+      <c r="E22" s="21"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>178</v>
       </c>
       <c r="B24" s="3"/>
-      <c r="C24" s="24">
+      <c r="C24" s="25">
         <f>$C$11/2</f>
         <v>0.2</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="20"/>
+      <c r="E24" s="21"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
@@ -12997,42 +13000,42 @@
       <c r="B25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <f>$C$24+$C$12</f>
         <v>0.7</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E25" s="20"/>
+      <c r="E25" s="21"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>181</v>
       </c>
       <c r="B26" s="3"/>
-      <c r="C26" s="24">
+      <c r="C26" s="25">
         <f>$C$25+$C$13</f>
         <v>0.89999999999999991</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E26" s="20"/>
+      <c r="E26" s="21"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>182</v>
       </c>
       <c r="B27" s="3"/>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <f>$C$26+$C$14</f>
         <v>1.4</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="20"/>
+      <c r="E27" s="21"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
@@ -13041,14 +13044,14 @@
       <c r="B28" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="25">
         <f>$C$27-$C$25</f>
         <v>0.7</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="21" t="s">
         <v>185</v>
       </c>
     </row>
@@ -13059,13 +13062,13 @@
       <c r="B29" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="21">
+      <c r="C29" s="22">
         <v>2.5</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="21" t="s">
         <v>188</v>
       </c>
     </row>
@@ -13076,14 +13079,14 @@
       <c r="B30" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="24">
         <f>1+2*$C$29+1</f>
         <v>7</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="21" t="s">
         <v>191</v>
       </c>
     </row>
@@ -13092,23 +13095,23 @@
         <v>192</v>
       </c>
       <c r="B31" s="3"/>
-      <c r="C31" s="24">
+      <c r="C31" s="25">
         <f>$C$25+$C$30</f>
         <v>7.7</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E31" s="20"/>
+      <c r="E31" s="21"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="45" t="s">
+      <c r="A32" s="46" t="s">
         <v>193</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
     </row>
     <row r="33" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
@@ -13122,7 +13125,7 @@
         <v>0.67</v>
       </c>
       <c r="D33" s="3"/>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="21" t="s">
         <v>196</v>
       </c>
     </row>
@@ -13131,28 +13134,28 @@
         <v>197</v>
       </c>
       <c r="B34" s="3"/>
-      <c r="C34" s="24">
+      <c r="C34" s="25">
         <f>$C$27+$C$6*$C$33</f>
         <v>3.008</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E34" s="20"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
         <v>198</v>
       </c>
       <c r="B35" s="3"/>
-      <c r="C35" s="24">
+      <c r="C35" s="25">
         <f>$C$31+$C$6*$C$33</f>
         <v>9.3079999999999998</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E35" s="20"/>
+      <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
@@ -13161,14 +13164,14 @@
       <c r="B36" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C36" s="16">
+      <c r="C36" s="17">
         <f>AVERAGE(H75:H80)</f>
         <v>0.15056332305066666</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="21" t="s">
         <v>201</v>
       </c>
     </row>
@@ -13177,12 +13180,12 @@
         <v>202</v>
       </c>
       <c r="B37" s="3"/>
-      <c r="C37" s="24" t="str">
+      <c r="C37" s="25" t="str">
         <f>IF($C$36&gt;0,"насыпи","выемки")</f>
         <v>насыпи</v>
       </c>
       <c r="D37" s="3"/>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="21" t="s">
         <v>203</v>
       </c>
     </row>
@@ -13193,14 +13196,14 @@
       <c r="B38" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="17">
         <f>('Исходные данные'!$B$17+'Исходные данные'!$B$18+'Исходные данные'!$B$23+'Исходные данные'!$B$24)/4</f>
         <v>0.16500000000000001</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="21" t="s">
         <v>206</v>
       </c>
     </row>
@@ -13211,25 +13214,25 @@
       <c r="B39" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="17">
         <f>IF($C$37="насыпи",$C$6-$C$10-$C$38,$C$6-$C$10)</f>
         <v>2.0349999999999997</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="21" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="45" t="s">
+      <c r="A40" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
+      <c r="B40" s="44"/>
+      <c r="C40" s="44"/>
+      <c r="D40" s="44"/>
+      <c r="E40" s="44"/>
     </row>
     <row r="41" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
@@ -13243,7 +13246,7 @@
         <v>0.67</v>
       </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="21" t="s">
         <v>212</v>
       </c>
     </row>
@@ -13254,14 +13257,14 @@
       <c r="B42" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="17">
         <f>$C$39*$C$41</f>
         <v>1.3634499999999998</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="21" t="s">
         <v>215</v>
       </c>
     </row>
@@ -13270,28 +13273,28 @@
         <v>216</v>
       </c>
       <c r="B43" s="3"/>
-      <c r="C43" s="24">
+      <c r="C43" s="25">
         <f>$C$15+$C$27+$C$31</f>
         <v>69.099999999999994</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E43" s="20"/>
+      <c r="E43" s="21"/>
     </row>
     <row r="44" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
         <v>217</v>
       </c>
       <c r="B44" s="3"/>
-      <c r="C44" s="24">
+      <c r="C44" s="25">
         <f>$C$16+2*$C$27</f>
         <v>32.799999999999997</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E44" s="20"/>
+      <c r="E44" s="21"/>
     </row>
     <row r="45" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="s">
@@ -13307,7 +13310,7 @@
       <c r="D45" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="21" t="s">
         <v>221</v>
       </c>
     </row>
@@ -13316,28 +13319,28 @@
         <v>222</v>
       </c>
       <c r="B46" s="3"/>
-      <c r="C46" s="24">
+      <c r="C46" s="25">
         <f>$C$43+2*$C$42</f>
         <v>71.826899999999995</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E46" s="20"/>
+      <c r="E46" s="21"/>
     </row>
     <row r="47" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
         <v>223</v>
       </c>
       <c r="B47" s="3"/>
-      <c r="C47" s="24">
+      <c r="C47" s="25">
         <f>$C$44+2*$C$42</f>
         <v>35.526899999999998</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E47" s="20"/>
+      <c r="E47" s="21"/>
     </row>
     <row r="48" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
@@ -13353,7 +13356,7 @@
       <c r="D48" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E48" s="20"/>
+      <c r="E48" s="21"/>
     </row>
     <row r="49" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
@@ -13369,7 +13372,7 @@
       <c r="D49" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="20"/>
+      <c r="E49" s="21"/>
     </row>
     <row r="50" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
@@ -13385,7 +13388,7 @@
       <c r="D50" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E50" s="20"/>
+      <c r="E50" s="21"/>
     </row>
     <row r="51" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
@@ -13401,16 +13404,16 @@
       <c r="D51" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E51" s="20"/>
+      <c r="E51" s="21"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="45" t="s">
+      <c r="A52" s="46" t="s">
         <v>232</v>
       </c>
-      <c r="B52" s="43"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
     </row>
     <row r="53" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
@@ -13419,13 +13422,13 @@
       <c r="B53" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C53" s="21">
+      <c r="C53" s="22">
         <v>6</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="21" t="s">
         <v>235</v>
       </c>
     </row>
@@ -13440,7 +13443,7 @@
         <v>0.1</v>
       </c>
       <c r="D54" s="3"/>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="21" t="s">
         <v>238</v>
       </c>
     </row>
@@ -13456,7 +13459,7 @@
         <v>10</v>
       </c>
       <c r="D55" s="3"/>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="21" t="s">
         <v>241</v>
       </c>
     </row>
@@ -13465,14 +13468,14 @@
         <v>242</v>
       </c>
       <c r="B56" s="3"/>
-      <c r="C56" s="24">
+      <c r="C56" s="25">
         <f>$C$39*$C$55</f>
         <v>20.349999999999998</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E56" s="20"/>
+      <c r="E56" s="21"/>
     </row>
     <row r="57" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
@@ -13488,18 +13491,18 @@
       <c r="D57" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="21" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="45" t="s">
+      <c r="A58" s="46" t="s">
         <v>247</v>
       </c>
-      <c r="B58" s="43"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="43"/>
-      <c r="E58" s="43"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
     </row>
     <row r="59" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
@@ -13513,7 +13516,7 @@
       <c r="D59" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="21" t="s">
         <v>249</v>
       </c>
     </row>
@@ -13531,7 +13534,7 @@
       <c r="D60" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E60" s="20"/>
+      <c r="E60" s="21"/>
     </row>
     <row r="61" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
@@ -13547,7 +13550,7 @@
       <c r="D61" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="21" t="s">
         <v>254</v>
       </c>
     </row>
@@ -13565,7 +13568,7 @@
       <c r="D62" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="21" t="s">
         <v>257</v>
       </c>
     </row>
@@ -13582,7 +13585,7 @@
       <c r="D63" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="21" t="s">
         <v>260</v>
       </c>
     </row>
@@ -13599,7 +13602,7 @@
       <c r="D64" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="21" t="s">
         <v>263</v>
       </c>
     </row>
@@ -13617,7 +13620,7 @@
       <c r="D65" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="21" t="s">
         <v>266</v>
       </c>
     </row>
@@ -13626,14 +13629,14 @@
         <v>267</v>
       </c>
       <c r="B66" s="3"/>
-      <c r="C66" s="24">
+      <c r="C66" s="25">
         <f>$C$39-$C$7-$C$8-$C$9</f>
         <v>1.3849999999999998</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="21" t="s">
         <v>268</v>
       </c>
     </row>
@@ -13651,7 +13654,7 @@
       <c r="D67" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E67" s="20"/>
+      <c r="E67" s="21"/>
     </row>
     <row r="68" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
@@ -13667,7 +13670,7 @@
       <c r="D68" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="21" t="s">
         <v>273</v>
       </c>
     </row>
@@ -13685,7 +13688,7 @@
       <c r="D69" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="21" t="s">
         <v>276</v>
       </c>
     </row>
@@ -13703,7 +13706,7 @@
       <c r="D70" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E70" s="20"/>
+      <c r="E70" s="21"/>
     </row>
     <row r="71" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
@@ -13719,7 +13722,7 @@
       <c r="D71" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E71" s="20" t="s">
+      <c r="E71" s="21" t="s">
         <v>280</v>
       </c>
     </row>
@@ -13758,31 +13761,31 @@
       <c r="A75" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B75" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D75" s="24">
+      <c r="D75" s="25">
         <f t="shared" ref="D75:D80" si="0">$C$21+B75</f>
         <v>216.99199999999999</v>
       </c>
-      <c r="E75" s="24">
+      <c r="E75" s="25">
         <f t="shared" ref="E75:E80" si="1">$C$22+C75</f>
         <v>131.99199999999999</v>
       </c>
-      <c r="F75" s="16">
+      <c r="F75" s="17">
         <f>(D75-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G75" s="16">
+      <c r="G75" s="17">
         <f>(E75-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H75" s="16">
+      <c r="H75" s="17">
         <f>'Исходные данные'!$B$23*(1-F75)*(1-G75)+'Исходные данные'!$B$24*F75*(1-G75)+'Исходные данные'!$B$17*(1-F75)*G75+'Исходные данные'!$B$18*F75*G75</f>
         <v>-3.926334515200007E-2</v>
       </c>
@@ -13791,31 +13794,31 @@
       <c r="A76" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B76" s="25">
         <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C76" s="24">
+      <c r="C76" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="D76" s="24">
+      <c r="D76" s="25">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E76" s="24">
+      <c r="E76" s="25">
         <f t="shared" si="1"/>
         <v>131.99199999999999</v>
       </c>
-      <c r="F76" s="16">
+      <c r="F76" s="17">
         <f>(D76-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G76" s="16">
+      <c r="G76" s="17">
         <f>(E76-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.31991999999999993</v>
       </c>
-      <c r="H76" s="16">
+      <c r="H76" s="17">
         <f>'Исходные данные'!$B$23*(1-F76)*(1-G76)+'Исходные данные'!$B$24*F76*(1-G76)+'Исходные данные'!$B$17*(1-F76)*G76+'Исходные данные'!$B$18*F76*G76</f>
         <v>4.7774097152000004E-2</v>
       </c>
@@ -13824,31 +13827,31 @@
       <c r="A77" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B77" s="25">
         <f>$C$15-$C$17+$C$34</f>
         <v>21.007999999999999</v>
       </c>
-      <c r="C77" s="24">
+      <c r="C77" s="25">
         <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D77" s="24">
+      <c r="D77" s="25">
         <f t="shared" si="0"/>
         <v>241.00800000000001</v>
       </c>
-      <c r="E77" s="24">
+      <c r="E77" s="25">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F77" s="16">
+      <c r="F77" s="17">
         <f>(D77-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.41008000000000011</v>
       </c>
-      <c r="G77" s="16">
+      <c r="G77" s="17">
         <f>(E77-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H77" s="16">
+      <c r="H77" s="17">
         <f>'Исходные данные'!$B$23*(1-F77)*(1-G77)+'Исходные данные'!$B$24*F77*(1-G77)+'Исходные данные'!$B$17*(1-F77)*G77+'Исходные данные'!$B$18*F77*G77</f>
         <v>0.10611636915200001</v>
       </c>
@@ -13857,31 +13860,31 @@
       <c r="A78" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B78" s="25">
         <f>$C$15+$C$35</f>
         <v>69.307999999999993</v>
       </c>
-      <c r="C78" s="24">
+      <c r="C78" s="25">
         <f>$C$18-$C$34</f>
         <v>8.9920000000000009</v>
       </c>
-      <c r="D78" s="24">
+      <c r="D78" s="25">
         <f t="shared" si="0"/>
         <v>289.30799999999999</v>
       </c>
-      <c r="E78" s="24">
+      <c r="E78" s="25">
         <f t="shared" si="1"/>
         <v>143.99199999999999</v>
       </c>
-      <c r="F78" s="16">
+      <c r="F78" s="17">
         <f>(D78-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.89307999999999987</v>
       </c>
-      <c r="G78" s="16">
+      <c r="G78" s="17">
         <f>(E78-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.43991999999999992</v>
       </c>
-      <c r="H78" s="16">
+      <c r="H78" s="17">
         <f>'Исходные данные'!$B$23*(1-F78)*(1-G78)+'Исходные данные'!$B$24*F78*(1-G78)+'Исходные данные'!$B$17*(1-F78)*G78+'Исходные данные'!$B$18*F78*G78</f>
         <v>0.27072972435199993</v>
       </c>
@@ -13890,31 +13893,31 @@
       <c r="A79" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B79" s="25">
         <f>$C$15+$C$35</f>
         <v>69.307999999999993</v>
       </c>
-      <c r="C79" s="24">
+      <c r="C79" s="25">
         <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D79" s="24">
+      <c r="D79" s="25">
         <f t="shared" si="0"/>
         <v>289.30799999999999</v>
       </c>
-      <c r="E79" s="24">
+      <c r="E79" s="25">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F79" s="16">
+      <c r="F79" s="17">
         <f>(D79-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.89307999999999987</v>
       </c>
-      <c r="G79" s="16">
+      <c r="G79" s="17">
         <f>(E79-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H79" s="16">
+      <c r="H79" s="17">
         <f>'Исходные данные'!$B$23*(1-F79)*(1-G79)+'Исходные данные'!$B$24*F79*(1-G79)+'Исходные данные'!$B$17*(1-F79)*G79+'Исходные данные'!$B$18*F79*G79</f>
         <v>0.36661254764800005</v>
       </c>
@@ -13923,37 +13926,37 @@
       <c r="A80" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B80" s="25">
         <f>-$C$34</f>
         <v>-3.008</v>
       </c>
-      <c r="C80" s="24">
+      <c r="C80" s="25">
         <f>$C$16+$C$34</f>
         <v>33.008000000000003</v>
       </c>
-      <c r="D80" s="24">
+      <c r="D80" s="25">
         <f t="shared" si="0"/>
         <v>216.99199999999999</v>
       </c>
-      <c r="E80" s="24">
+      <c r="E80" s="25">
         <f t="shared" si="1"/>
         <v>168.00800000000001</v>
       </c>
-      <c r="F80" s="16">
+      <c r="F80" s="17">
         <f>(D80-$C$19)/'Исходные данные'!$B$3</f>
         <v>0.1699199999999999</v>
       </c>
-      <c r="G80" s="16">
+      <c r="G80" s="17">
         <f>(E80-$C$20)/'Исходные данные'!$B$3</f>
         <v>0.68008000000000013</v>
       </c>
-      <c r="H80" s="16">
+      <c r="H80" s="17">
         <f>'Исходные данные'!$B$23*(1-F80)*(1-G80)+'Исходные данные'!$B$24*F80*(1-G80)+'Исходные данные'!$B$17*(1-F80)*G80+'Исходные данные'!$B$18*F80*G80</f>
         <v>0.15141054515200006</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A81" s="25" t="s">
+      <c r="A81" s="26" t="s">
         <v>289</v>
       </c>
     </row>
@@ -14018,11 +14021,11 @@
       <c r="B5" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="27">
         <f>'Табл. 1 объёмы (черн.)'!$F$31</f>
         <v>20209.474960755029</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="27">
         <f>'Табл. 1 объёмы (черн.)'!$F$32</f>
         <v>33543.964226867858</v>
       </c>
@@ -14038,7 +14041,7 @@
       <c r="B6" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <f>'Котлован (черн.)'!$C$60</f>
         <v>3851.618956403689</v>
       </c>
@@ -14052,85 +14055,85 @@
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>SUM(C5:C6)</f>
         <v>24061.09391715872</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>SUM(D5:D6)</f>
         <v>33543.964226867858</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="18">
         <f>SUM(E5:E6)</f>
         <v>32253.811756603707</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="28" t="s">
         <v>299</v>
       </c>
-      <c r="C8" s="46">
+      <c r="C8" s="47">
         <f>C7-E7</f>
         <v>-8192.7178394449875</v>
       </c>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="44"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="43" t="s">
         <v>300</v>
       </c>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="28">
+      <c r="B10" s="44"/>
+      <c r="C10" s="44"/>
+      <c r="D10" s="29">
         <f>ABS(C8)/MAX(C7,E7)</f>
         <v>0.25400774027173995</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="43" t="s">
         <v>301</v>
       </c>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="15" t="str">
+      <c r="B11" s="44"/>
+      <c r="C11" s="44"/>
+      <c r="D11" s="16" t="str">
         <f>IF(D10&lt;=0.05,"баланс соблюдён",IF(C8&lt;0,"не хватает грунта — нужен перерасчёт Нср (Δh)","излишек грунта — нужен перерасчёт Нср (Δh)"))</f>
         <v>не хватает грунта — нужен перерасчёт Нср (Δh)</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="17">
+      <c r="B12" s="44"/>
+      <c r="C12" s="44"/>
+      <c r="D12" s="18">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="29">
+      <c r="B13" s="44"/>
+      <c r="C13" s="44"/>
+      <c r="D13" s="30">
         <f>C8*'Исходные данные'!$B$4/D12</f>
         <v>-5.6802843686818587E-2</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="43" t="s">
         <v>304</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="30">
+      <c r="B14" s="44"/>
+      <c r="C14" s="44"/>
+      <c r="D14" s="31">
         <f>ROUND(D13,4)</f>
         <v>-5.6800000000000003E-2</v>
       </c>
@@ -14197,15 +14200,15 @@
       <c r="A9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="27">
         <f>'Исходные данные'!$B$9</f>
         <v>-0.25</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="17">
         <f t="shared" ref="C9:C32" si="0">$B$3</f>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="17">
         <f t="shared" ref="D9:D32" si="1">B9+C9</f>
         <v>-0.30680000000000002</v>
       </c>
@@ -14232,39 +14235,39 @@
       <c r="A10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>'Исходные данные'!$B$10</f>
         <v>0.15</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="17">
         <f t="shared" si="1"/>
         <v>9.3199999999999991E-2</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="17">
         <f>D9</f>
         <v>-0.30680000000000002</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>D10</f>
         <v>9.3199999999999991E-2</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="17">
         <f>D11</f>
         <v>0.28320000000000001</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="17">
         <f>D12</f>
         <v>0.41319999999999996</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="17">
         <f>D13</f>
         <v>0.60320000000000007</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="17">
         <f>D14</f>
         <v>0.79320000000000002</v>
       </c>
@@ -14273,15 +14276,15 @@
       <c r="A11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="27">
         <f>'Исходные данные'!$B$11</f>
         <v>0.34</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="17">
         <f t="shared" si="1"/>
         <v>0.28320000000000001</v>
       </c>
@@ -14308,39 +14311,39 @@
       <c r="A12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="27">
         <f>'Исходные данные'!$B$12</f>
         <v>0.47</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="17">
         <f t="shared" si="1"/>
         <v>0.41319999999999996</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="17">
         <f>D15</f>
         <v>-0.54679999999999995</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>D16</f>
         <v>-0.36680000000000001</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="17">
         <f>D17</f>
         <v>0.22320000000000001</v>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="17">
         <f>D18</f>
         <v>0.4632</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="17">
         <f>D19</f>
         <v>0.78320000000000001</v>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="17">
         <f>D20</f>
         <v>0.41319999999999996</v>
       </c>
@@ -14349,15 +14352,15 @@
       <c r="A13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="27">
         <f>'Исходные данные'!$B$13</f>
         <v>0.66</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D13" s="17">
         <f t="shared" si="1"/>
         <v>0.60320000000000007</v>
       </c>
@@ -14384,39 +14387,39 @@
       <c r="A14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="27">
         <f>'Исходные данные'!$B$14</f>
         <v>0.85</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="17">
         <f t="shared" si="1"/>
         <v>0.79320000000000002</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="17">
         <f>D21</f>
         <v>-0.29680000000000001</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>D22</f>
         <v>-0.48680000000000001</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="17">
         <f>D23</f>
         <v>-0.33680000000000004</v>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="17">
         <f>D24</f>
         <v>8.320000000000001E-2</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="17">
         <f>D25</f>
         <v>0.30319999999999997</v>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="17">
         <f>D26</f>
         <v>0.70320000000000005</v>
       </c>
@@ -14425,15 +14428,15 @@
       <c r="A15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="27">
         <f>'Исходные данные'!$B$15</f>
         <v>-0.49</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D15" s="17">
         <f t="shared" si="1"/>
         <v>-0.54679999999999995</v>
       </c>
@@ -14460,39 +14463,39 @@
       <c r="A16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="27">
         <f>'Исходные данные'!$B$16</f>
         <v>-0.31</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="17">
         <f t="shared" si="1"/>
         <v>-0.36680000000000001</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="17">
         <f>D27</f>
         <v>-0.45680000000000004</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="17">
         <f>D28</f>
         <v>-0.70679999999999998</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="17">
         <f>D29</f>
         <v>-0.57679999999999998</v>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="17">
         <f>D30</f>
         <v>-0.33680000000000004</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="17">
         <f>D31</f>
         <v>-0.48680000000000001</v>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="17">
         <f>D32</f>
         <v>8.320000000000001E-2</v>
       </c>
@@ -14501,15 +14504,15 @@
       <c r="A17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="27">
         <f>'Исходные данные'!$B$17</f>
         <v>0.28000000000000003</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D17" s="17">
         <f t="shared" si="1"/>
         <v>0.22320000000000001</v>
       </c>
@@ -14518,15 +14521,15 @@
       <c r="A18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="27">
         <f>'Исходные данные'!$B$18</f>
         <v>0.52</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="17">
         <f t="shared" si="1"/>
         <v>0.4632</v>
       </c>
@@ -14535,15 +14538,15 @@
       <c r="A19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="27">
         <f>'Исходные данные'!$B$19</f>
         <v>0.84</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D19" s="16">
+      <c r="D19" s="17">
         <f t="shared" si="1"/>
         <v>0.78320000000000001</v>
       </c>
@@ -14552,15 +14555,15 @@
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="27">
         <f>'Исходные данные'!$B$20</f>
         <v>0.47</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="17">
         <f t="shared" si="1"/>
         <v>0.41319999999999996</v>
       </c>
@@ -14569,15 +14572,15 @@
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="27">
         <f>'Исходные данные'!$B$21</f>
         <v>-0.24</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C21" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D21" s="17">
         <f t="shared" si="1"/>
         <v>-0.29680000000000001</v>
       </c>
@@ -14586,15 +14589,15 @@
       <c r="A22" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="27">
         <f>'Исходные данные'!$B$22</f>
         <v>-0.43</v>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <f t="shared" si="1"/>
         <v>-0.48680000000000001</v>
       </c>
@@ -14603,15 +14606,15 @@
       <c r="A23" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="27">
         <f>'Исходные данные'!$B$23</f>
         <v>-0.28000000000000003</v>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <f t="shared" si="1"/>
         <v>-0.33680000000000004</v>
       </c>
@@ -14620,15 +14623,15 @@
       <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="27">
         <f>'Исходные данные'!$B$24</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <f t="shared" si="1"/>
         <v>8.320000000000001E-2</v>
       </c>
@@ -14637,15 +14640,15 @@
       <c r="A25" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="27">
         <f>'Исходные данные'!$B$25</f>
         <v>0.36</v>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="17">
         <f t="shared" si="1"/>
         <v>0.30319999999999997</v>
       </c>
@@ -14654,15 +14657,15 @@
       <c r="A26" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="27">
         <f>'Исходные данные'!$B$26</f>
         <v>0.76</v>
       </c>
-      <c r="C26" s="16">
+      <c r="C26" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <f t="shared" si="1"/>
         <v>0.70320000000000005</v>
       </c>
@@ -14671,15 +14674,15 @@
       <c r="A27" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="27">
         <f>'Исходные данные'!$B$27</f>
         <v>-0.4</v>
       </c>
-      <c r="C27" s="16">
+      <c r="C27" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D27" s="16">
+      <c r="D27" s="17">
         <f t="shared" si="1"/>
         <v>-0.45680000000000004</v>
       </c>
@@ -14688,15 +14691,15 @@
       <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="27">
         <f>'Исходные данные'!$B$28</f>
         <v>-0.65</v>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="17">
         <f t="shared" si="1"/>
         <v>-0.70679999999999998</v>
       </c>
@@ -14705,15 +14708,15 @@
       <c r="A29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="27">
         <f>'Исходные данные'!$B$29</f>
         <v>-0.52</v>
       </c>
-      <c r="C29" s="16">
+      <c r="C29" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D29" s="17">
         <f t="shared" si="1"/>
         <v>-0.57679999999999998</v>
       </c>
@@ -14722,15 +14725,15 @@
       <c r="A30" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <f>'Исходные данные'!$B$30</f>
         <v>-0.28000000000000003</v>
       </c>
-      <c r="C30" s="16">
+      <c r="C30" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <f t="shared" si="1"/>
         <v>-0.33680000000000004</v>
       </c>
@@ -14739,15 +14742,15 @@
       <c r="A31" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="27">
         <f>'Исходные данные'!$B$31</f>
         <v>-0.43</v>
       </c>
-      <c r="C31" s="16">
+      <c r="C31" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <f t="shared" si="1"/>
         <v>-0.48680000000000001</v>
       </c>
@@ -14756,15 +14759,15 @@
       <c r="A32" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <f>'Исходные данные'!$B$32</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="17">
         <f t="shared" si="0"/>
         <v>-5.6800000000000003E-2</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <f t="shared" si="1"/>
         <v>8.320000000000001E-2</v>
       </c>
@@ -15104,19 +15107,19 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
     </row>
     <row r="5" spans="1:9" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -15148,14 +15151,14 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="16" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="12">
         <f>'Исходные данные'!$B$3^2-$F$6</f>
         <v>9763.9608695652169</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$15)+ABS('Отметки (оконч.)'!$D$16)+0)/5</f>
         <v>0.24407999999999999</v>
       </c>
@@ -15163,14 +15166,14 @@
         <f>B6*C6</f>
         <v>2383.1875690434781</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="16" t="s">
         <v>101</v>
       </c>
       <c r="F6" s="12">
         <f>'ЛНР (оконч.)'!$G$6*'ЛНР (оконч.)'!$H$5/2</f>
         <v>236.03913043478252</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$10)+0)/3</f>
         <v>3.1066666666666663E-2</v>
       </c>
@@ -15184,14 +15187,14 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>102</v>
       </c>
       <c r="B7" s="12">
         <f>'ЛНР (оконч.)'!$H$6*'ЛНР (оконч.)'!$G$7/2</f>
         <v>2478.6705969049372</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$16)+0)/3</f>
         <v>0.12226666666666668</v>
       </c>
@@ -15199,14 +15202,14 @@
         <f>B7*C7</f>
         <v>303.0587916482437</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F7" s="12">
         <f>'Исходные данные'!$B$3^2-$B$7</f>
         <v>7521.3294030950628</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$17)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$10)+0)/5</f>
         <v>0.11991999999999998</v>
       </c>
@@ -15232,14 +15235,14 @@
       <c r="D8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="16" t="s">
         <v>105</v>
       </c>
       <c r="F8" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$17)+ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$11))/4</f>
         <v>0.34570000000000001</v>
       </c>
@@ -15265,14 +15268,14 @@
       <c r="D9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="16" t="s">
         <v>106</v>
       </c>
       <c r="F9" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$12))/4</f>
         <v>0.56569999999999998</v>
       </c>
@@ -15298,14 +15301,14 @@
       <c r="D10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F10" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$13))/4</f>
         <v>0.6482</v>
       </c>
@@ -15319,14 +15322,14 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="16" t="s">
         <v>108</v>
       </c>
       <c r="B11" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$16)+ABS('Отметки (оконч.)'!$D$15))/4</f>
         <v>0.42430000000000001</v>
       </c>
@@ -15351,14 +15354,14 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>109</v>
       </c>
       <c r="B12" s="12">
         <f>'Исходные данные'!$B$3^2-$F$12</f>
         <v>9246.0920096852296</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$16)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$23)+0)/5</f>
         <v>0.23808000000000001</v>
       </c>
@@ -15366,14 +15369,14 @@
         <f>B12*C12</f>
         <v>2201.3095856658597</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="16" t="s">
         <v>110</v>
       </c>
       <c r="F12" s="12">
         <f>'ЛНР (оконч.)'!$G$8*'ЛНР (оконч.)'!$H$7/2</f>
         <v>753.90799031477002</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$17)+0)/3</f>
         <v>7.4400000000000008E-2</v>
       </c>
@@ -15387,14 +15390,14 @@
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>111</v>
       </c>
       <c r="B13" s="12">
         <f>'ЛНР (оконч.)'!$H$8*'ЛНР (оконч.)'!$G$9/2</f>
         <v>2411.4421768707489</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$23)+0)/3</f>
         <v>0.11226666666666668</v>
       </c>
@@ -15402,14 +15405,14 @@
         <f>B13*C13</f>
         <v>270.72457505668945</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="16" t="s">
         <v>112</v>
       </c>
       <c r="F13" s="12">
         <f>'Исходные данные'!$B$3^2-$B$13</f>
         <v>7588.5578231292511</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$24)+ABS('Отметки (оконч.)'!$D$18)+ABS('Отметки (оконч.)'!$D$17)+0)/5</f>
         <v>0.15392</v>
       </c>
@@ -15435,14 +15438,14 @@
       <c r="D14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="16" t="s">
         <v>113</v>
       </c>
       <c r="F14" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$24)+ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$19)+ABS('Отметки (оконч.)'!$D$18))/4</f>
         <v>0.40820000000000001</v>
       </c>
@@ -15468,14 +15471,14 @@
       <c r="D15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="16" t="s">
         <v>114</v>
       </c>
       <c r="F15" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$19))/4</f>
         <v>0.55069999999999997</v>
       </c>
@@ -15489,14 +15492,14 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>115</v>
       </c>
       <c r="B16" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$22)+ABS('Отметки (оконч.)'!$D$21))/4</f>
         <v>0.48679999999999995</v>
       </c>
@@ -15521,14 +15524,14 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="16" t="s">
         <v>116</v>
       </c>
       <c r="B17" s="12">
         <f>'Исходные данные'!$B$3^2</f>
         <v>10000</v>
       </c>
-      <c r="C17" s="16">
+      <c r="C17" s="17">
         <f>(ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$23)+ABS('Отметки (оконч.)'!$D$22))/4</f>
         <v>0.52679999999999993</v>
       </c>
@@ -15553,14 +15556,14 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="16" t="s">
         <v>117</v>
       </c>
       <c r="B18" s="12">
         <f>'Исходные данные'!$B$3^2-$F$18</f>
         <v>9803.7913832199556</v>
       </c>
-      <c r="C18" s="16">
+      <c r="C18" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$23)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$30)+0)/5</f>
         <v>0.25007999999999997</v>
       </c>
@@ -15568,14 +15571,14 @@
         <f>B18*C18</f>
         <v>2451.7321491156463</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="16" t="s">
         <v>118</v>
       </c>
       <c r="F18" s="12">
         <f>'ЛНР (оконч.)'!$G$10*'ЛНР (оконч.)'!$H$9/2</f>
         <v>196.20861678004519</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$24)+0)/3</f>
         <v>2.7733333333333336E-2</v>
       </c>
@@ -15589,14 +15592,14 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="16" t="s">
         <v>119</v>
       </c>
       <c r="B19" s="12">
         <f>('ЛНР (оконч.)'!$H$10+'ЛНР (оконч.)'!$H$11)/2*'Исходные данные'!$B$3</f>
         <v>7090.5364677516591</v>
       </c>
-      <c r="C19" s="16">
+      <c r="C19" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$31)+0)/4</f>
         <v>0.20590000000000003</v>
       </c>
@@ -15604,14 +15607,14 @@
         <f>B19*C19</f>
         <v>1459.9414587100669</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="16" t="s">
         <v>120</v>
       </c>
       <c r="F19" s="12">
         <f>('ЛНР (оконч.)'!$G$11+'ЛНР (оконч.)'!$G$10)/2*'Исходные данные'!$B$3</f>
         <v>2909.4635322483418</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$25)+ABS('Отметки (оконч.)'!$D$24)+0)/4</f>
         <v>9.6599999999999991E-2</v>
       </c>
@@ -15625,14 +15628,14 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="16" t="s">
         <v>121</v>
       </c>
       <c r="B20" s="12">
         <f>'ЛНР (оконч.)'!$H$11*'ЛНР (оконч.)'!$G$12/2</f>
         <v>2631.2929158338889</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$31)+0)/3</f>
         <v>0.16226666666666667</v>
       </c>
@@ -15640,14 +15643,14 @@
         <f>B20*C20</f>
         <v>426.97113047597907</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="16" t="s">
         <v>122</v>
       </c>
       <c r="F20" s="12">
         <f>'Исходные данные'!$B$3^2-$B$20</f>
         <v>7368.7070841661116</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="17">
         <f>(0+ABS('Отметки (оконч.)'!$D$32)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$25)+0)/5</f>
         <v>0.21792000000000003</v>
       </c>
@@ -15661,31 +15664,31 @@
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="18">
         <f>SUM(B6:B20)</f>
         <v>73425.786419831638</v>
       </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <f>SUM(D6:D20)</f>
         <v>23875.925259715961</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <f>SUM(F6:F20)</f>
         <v>76574.213580168347</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="17">
+      <c r="H21" s="18">
         <f>SUM(H6:H20)</f>
         <v>29210.69668958884</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <f>SUM(I6:I20)</f>
         <v>28087.208355373888</v>
       </c>
@@ -15719,7 +15722,7 @@
       <c r="A25" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="17">
         <f>ABS('Отметки (оконч.)'!$D$9)+ABS('Отметки (оконч.)'!$D$31)+ABS('Отметки (оконч.)'!$D$30)+ABS('Отметки (оконч.)'!$D$29)+ABS('Отметки (оконч.)'!$D$28)+ABS('Отметки (оконч.)'!$D$27)+ABS('Отметки (оконч.)'!$D$21)+ABS('Отметки (оконч.)'!$D$15)</f>
         <v>3.7144000000000004</v>
       </c>
@@ -15742,7 +15745,7 @@
       <c r="A26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <f>ABS('Отметки (оконч.)'!$D$10)+ABS('Отметки (оконч.)'!$D$11)+ABS('Отметки (оконч.)'!$D$12)+ABS('Отметки (оконч.)'!$D$13)+ABS('Отметки (оконч.)'!$D$14)+ABS('Отметки (оконч.)'!$D$20)+ABS('Отметки (оконч.)'!$D$26)+ABS('Отметки (оконч.)'!$D$32)</f>
         <v>3.3855999999999997</v>
       </c>
@@ -15767,66 +15770,66 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="42" t="s">
+      <c r="A29" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="17">
+      <c r="B29" s="44"/>
+      <c r="C29" s="44"/>
+      <c r="D29" s="44"/>
+      <c r="E29" s="44"/>
+      <c r="F29" s="18">
         <f>B21+F21</f>
         <v>150000</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="42" t="s">
+      <c r="A30" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="17">
+      <c r="B30" s="44"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="18">
         <f>'Исходные данные'!$B$6*'Исходные данные'!$B$3^2</f>
         <v>150000</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="42" t="s">
+      <c r="A31" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="17">
+      <c r="B31" s="44"/>
+      <c r="C31" s="44"/>
+      <c r="D31" s="44"/>
+      <c r="E31" s="44"/>
+      <c r="F31" s="18">
         <f>D21+F25</f>
         <v>23899.156200244801</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="42" t="s">
+      <c r="A32" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="17">
+      <c r="B32" s="44"/>
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="18">
         <f>H21+F26</f>
         <v>29227.216184948978</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="42" t="s">
+      <c r="A33" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="43"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="17">
+      <c r="B33" s="44"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="44"/>
+      <c r="E33" s="44"/>
+      <c r="F33" s="18">
         <f>F32/'Исходные данные'!$B$4</f>
         <v>28103.092485527864</v>
       </c>
